--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -7979,34 +7979,34 @@
         <v>20.45</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>23.96</v>
+        <v>24.01</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>17.16381418092909</v>
+        <v>17.40831295843521</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>24.54</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>21.31</v>
+        <v>21.32</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>21.711</v>
+        <v>21.731</v>
       </c>
       <c r="M115" s="4" t="n">
-        <v>-1.84699000506654</v>
+        <v>-1.891307348948501</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>21.902</v>
+        <v>21.922</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>21.901</v>
+        <v>21.921</v>
       </c>
       <c r="P115" s="4" t="n">
-        <v>0.004566001552452903</v>
+        <v>0.004561835682692639</v>
       </c>
       <c r="Q115" s="5" t="n">
-        <v>1.851556006618993</v>
+        <v>1.895869184631194</v>
       </c>
       <c r="R115" t="inlineStr">
         <is>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5破10明日门槛完整名单｜信号日 2026-10-26｜75 只｜报告 多空阶段_2026-10-26.xlsx</t>
+          <t>5破10明日门槛完整名单｜信号日 2026-10-26｜74 只｜报告 多空阶段_2026-10-26.xlsx</t>
         </is>
       </c>
     </row>
@@ -5425,76 +5425,8 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>002115</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>三维通信</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>9.587628865979392</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>9.746</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>9.763</v>
-      </c>
-      <c r="M77" s="4" t="n">
-        <v>-0.1741268052852574</v>
-      </c>
-      <c r="N77" s="3" t="n">
-        <v>9.918000000000001</v>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>9.788</v>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v>1.328156926849222</v>
-      </c>
-      <c r="Q77" s="5" t="n">
-        <v>1.50228373213448</v>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:R77"/>
+  <autoFilter ref="A2:R76"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5破10明日门槛完整名单｜信号日 2026-10-26｜74 只｜报告 多空阶段_2026-10-26.xlsx</t>
+          <t>5破10明日门槛完整名单｜信号日 2026-10-26｜75 只｜报告 多空阶段_2026-10-26.xlsx</t>
         </is>
       </c>
     </row>
@@ -5425,8 +5425,76 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>002115</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>三维通信</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>9.587628865979392</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>9.746</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>9.763</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>-0.1741268052852574</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>9.918000000000001</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>9.788</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>1.328156926849222</v>
+      </c>
+      <c r="Q77" s="5" t="n">
+        <v>1.50228373213448</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R76"/>
+  <autoFilter ref="A2:R77"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5破10明日门槛完整名单｜信号日 2026-10-26｜75 只｜报告 多空阶段_2026-10-26.xlsx</t>
+          <t>5破10明日门槛完整名单｜信号日 2026-10-27｜88 只｜报告 多空阶段_2026-10-27.xlsx</t>
         </is>
       </c>
     </row>
@@ -570,12 +570,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CPO</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -585,46 +585,46 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>688312</t>
+          <t>688308</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>燕麦科技</t>
+          <t>欧科亿</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>33.82</v>
+        <v>59.41</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>40.44</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>19.57421643997634</v>
+        <v>16.07473489311564</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>40.58</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>36.23399999999999</v>
+        <v>64.092</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>36.473</v>
+        <v>64.788</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.6552792476626657</v>
+        <v>-1.074273013521021</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>36.95</v>
+        <v>65.364</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>36.636</v>
+        <v>65.086</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.857080467299931</v>
+        <v>0.4271271855698755</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>1.512359714962597</v>
+        <v>1.501400199090897</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -635,64 +635,61 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>300613</t>
+          <t>300776</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>富瀚微</t>
+          <t>帝尔激光</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>65.61</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>73</v>
+        <v>92.8</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11.26352690138699</v>
+        <v>16.99445284921837</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>78.73</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>68.196</v>
+        <v>84.974</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>68.44800000000001</v>
+        <v>85.59400000000001</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.3681626928471404</v>
+        <v>-0.7243498376054425</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>69.184</v>
+        <v>86.774</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>68.26300000000001</v>
+        <v>86.10400000000001</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>1.349193560200979</v>
+        <v>0.7781287745052268</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>1.717356253048119</v>
+        <v>1.502478612110669</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -703,12 +700,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -718,46 +715,46 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>688141</t>
+          <t>688388</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>杰华特</t>
+          <t>嘉元科技</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>71</v>
+        <v>21.41</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>82.16</v>
+        <v>25.46</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15.71830985915492</v>
+        <v>18.91639420831388</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>85.2</v>
+        <v>25.69</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>75.15000000000001</v>
+        <v>22.902</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>75.92099999999999</v>
+        <v>23.614</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-1.015529300193607</v>
+        <v>-3.015160498009672</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>76.574</v>
+        <v>23.562</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>76.06799999999998</v>
+        <v>23.56</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>0.665194299837002</v>
+        <v>0.008488964346353711</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>1.680723600030609</v>
+        <v>3.023649462356026</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -768,12 +765,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -783,46 +780,46 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>688508</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>芯朋微</t>
+          <t>凯格精机</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>59.51</v>
+        <v>65.19</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>69.22</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.3165854478239</v>
+        <v>18.00889707010278</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>71.41</v>
+        <v>78.22</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>62.724</v>
+        <v>70.116</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>63.951</v>
+        <v>71.02500000000001</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.91865647136088</v>
+        <v>-1.279831045406554</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>64.02799999999999</v>
+        <v>71.69000000000001</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>63.80399999999999</v>
+        <v>71.53200000000001</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3510751677010759</v>
+        <v>0.2208801655203319</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>2.269731639061956</v>
+        <v>1.500711210926886</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -833,12 +830,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -848,46 +845,46 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>300632</t>
+          <t>688628</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>光莆股份</t>
+          <t>优利德</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>14.24</v>
+        <v>65.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>16.61</v>
+        <v>77.08</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.64325842696628</v>
+        <v>18.03981623277182</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>17.08</v>
+        <v>78.36</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>15.036</v>
+        <v>71.622</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>15.081</v>
+        <v>71.79900000000001</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.298388701014507</v>
+        <v>-0.2465215392972175</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15.336</v>
+        <v>73.21600000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>15.153</v>
+        <v>72.22999999999999</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.207681647198577</v>
+        <v>1.365083760210473</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>1.506070348213084</v>
+        <v>1.61160529950769</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -898,7 +895,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -913,46 +910,46 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>688347</t>
+          <t>300632</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>华虹宏力</t>
+          <t>光莆股份</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>158.2</v>
+        <v>13.92</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>185.01</v>
+        <v>16</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16.94690265486727</v>
+        <v>14.94252873563218</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>189.84</v>
+        <v>16.7</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>168.466</v>
+        <v>14.676</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>170.547</v>
+        <v>14.823</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.220191501462953</v>
+        <v>-0.991702084598256</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>171.522</v>
+        <v>14.984</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>170.878</v>
+        <v>14.908</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3768770701904289</v>
+        <v>0.5097933995170445</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>1.597068571653382</v>
+        <v>1.501495484115301</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -963,7 +960,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -978,46 +975,46 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>688693</t>
+          <t>300672</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>锴威特</t>
+          <t>国科微</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55.87</v>
+        <v>128.51</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>65.34</v>
+        <v>150.65</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16.95006264542689</v>
+        <v>17.22823126604936</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>67.04000000000001</v>
+        <v>154.21</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>59.1</v>
+        <v>137.146</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>59.14700000000001</v>
+        <v>138.103</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.07946303278273392</v>
+        <v>-0.6929610508098927</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>60.348</v>
+        <v>140.342</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59.502</v>
+        <v>139.218</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.421800947867302</v>
+        <v>0.8073668634802855</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>1.501263980650036</v>
+        <v>1.500327914290178</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1028,7 +1025,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1043,46 +1040,46 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>920125</t>
+          <t>688515</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>鸿仕达</t>
+          <t>裕太微-U</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>116.4</v>
+        <v>100.5</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>137.29</v>
+        <v>118.36</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>17.94673539518898</v>
+        <v>17.77114427860695</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>139.68</v>
+        <v>120.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>120.636</v>
+        <v>107.958</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>123.444</v>
+        <v>108.01</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.274715660542437</v>
+        <v>-0.04814369039902733</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>123.594</v>
+        <v>110.678</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>123.593</v>
+        <v>109.094</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0008091073119054215</v>
+        <v>1.451958861165581</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>2.275524767854342</v>
+        <v>1.500102551564608</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1093,7 +1090,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1108,46 +1105,46 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>688807</t>
+          <t>300671</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>优迅股份</t>
+          <t>富满微</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>222.14</v>
+        <v>38.85</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>263.07</v>
+        <v>45.77</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18.42531736742594</v>
+        <v>17.81209781209783</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>266.56</v>
+        <v>46.62</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>235.59</v>
+        <v>41.904</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>237.211</v>
+        <v>42.463</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.6833578543996688</v>
+        <v>-1.316440194993285</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>240.054</v>
+        <v>42.79</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>238.109</v>
+        <v>42.684</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8168527859089947</v>
+        <v>0.2483366132508547</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>1.500210640308663</v>
+        <v>1.564776808244139</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1158,7 +1155,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1173,46 +1170,46 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>300671</t>
+          <t>300042</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>富满微</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>40.52</v>
+        <v>27.55</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>48.06</v>
+        <v>32.7</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18.60809476801579</v>
+        <v>18.69328493647913</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>48.62</v>
+        <v>33.06</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>43.32000000000001</v>
+        <v>29.592</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>43.383</v>
+        <v>29.773</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1452181730170476</v>
+        <v>-0.607933362442481</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>44.204</v>
+        <v>30.336</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>43.613</v>
+        <v>30.067</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.355100543415966</v>
+        <v>0.894668573519164</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>1.500318716433013</v>
+        <v>1.502601935961645</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1223,12 +1220,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>半导体芯片</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1238,46 +1235,46 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>301717</t>
+          <t>688416</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>超纯应材</t>
+          <t>恒烁股份</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>274.35</v>
+        <v>51.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>313.9</v>
+        <v>61.03</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14.41589210862035</v>
+        <v>18.73540856031128</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>329.22</v>
+        <v>61.68</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>284.934</v>
+        <v>55.61</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>287.693</v>
+        <v>56.00699999999999</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.959008387412974</v>
+        <v>-0.7088399664327505</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>291.014</v>
+        <v>56.98</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>289.134</v>
+        <v>56.532</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6502175461896575</v>
+        <v>0.7924715205547272</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>1.609225933602632</v>
+        <v>1.501311486987478</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1288,12 +1285,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>半导体芯片</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1303,46 +1300,46 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>688141</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>杰华特</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>66.43000000000001</v>
+        <v>67.45</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>77.97</v>
+        <v>80.7</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>17.37166942646393</v>
+        <v>19.64418087472202</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>79.70999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>69.78600000000002</v>
+        <v>73.34</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>70.00399999999999</v>
+        <v>74.45099999999999</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3114107765270213</v>
+        <v>-1.492256652026147</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>71.438</v>
+        <v>75.048</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>70.598</v>
+        <v>74.98099999999999</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.189835406102158</v>
+        <v>0.08935597017911689</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>1.501246182629179</v>
+        <v>1.581612622205264</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1353,7 +1350,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,46 +1365,46 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>688419</t>
+          <t>301717</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>耐科装备</t>
+          <t>超纯应材</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>37.8</v>
+        <v>263.63</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>44.92</v>
+        <v>299.5</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18.83597883597885</v>
+        <v>13.60619049425331</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>45.36</v>
+        <v>316.35</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>40.602</v>
+        <v>278.08</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>40.776</v>
+        <v>282.667</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.4267216009417485</v>
+        <v>-1.622757520333107</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>41.41799999999999</v>
+        <v>283.302</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>40.97799999999999</v>
+        <v>282.917</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.073746888574356</v>
+        <v>0.1360823138941702</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1.500468489516105</v>
+        <v>1.758839834227277</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1418,12 +1415,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1433,46 +1430,46 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>688733</t>
+          <t>688797</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>壹石通</t>
+          <t>臻宝科技</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>22.66</v>
+        <v>185</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>26.17</v>
+        <v>220.88</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>15.48984995586937</v>
+        <v>19.39459459459458</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>27.19</v>
+        <v>222</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>23.584</v>
+        <v>199.554</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>23.648</v>
+        <v>200.066</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.2706359945872983</v>
+        <v>-0.2559155478691899</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>24.158</v>
+        <v>204.524</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>23.781</v>
+        <v>202.01</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.585299188427758</v>
+        <v>1.244492846888767</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>1.855935183015056</v>
+        <v>1.500408394757957</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1483,12 +1480,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1498,46 +1495,46 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>688268</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>华特气体</t>
+          <t>珂玛科技</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>101.29</v>
+        <v>62.45</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>118.52</v>
+        <v>74.62</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17.01056372790994</v>
+        <v>19.48759007205765</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>121.54</v>
+        <v>74.94</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>106.222</v>
+        <v>67.664</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>107.072</v>
+        <v>68.711</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.7938583383144016</v>
+        <v>-1.523773486050262</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>108.492</v>
+        <v>69.11800000000001</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>107.731</v>
+        <v>69.11600000000001</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7063890616442858</v>
+        <v>0.002893685977189975</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1.500247399958687</v>
+        <v>1.526667172027452</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1548,12 +1545,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1563,46 +1560,46 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>300821</t>
+          <t>688605</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>先锋精科</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>16.94</v>
+        <v>55.81</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>19.84</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>17.11924439197166</v>
+        <v>19.67389356746103</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>20.32</v>
+        <v>66.97</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>17.254</v>
+        <v>60.182</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>17.425</v>
+        <v>61.573</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9813486370157998</v>
+        <v>-2.25910707615351</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>17.7</v>
+        <v>61.818</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.608</v>
+        <v>61.816</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5224897773739245</v>
+        <v>0.003235408308555066</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1.503838414389724</v>
+        <v>2.262342484462065</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1613,7 +1610,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1628,46 +1625,46 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>688233</t>
+          <t>003026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>神工股份</t>
+          <t>中晶科技</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>65.91</v>
+        <v>27.83</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>77.37</v>
+        <v>29.67</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>17.38734638142923</v>
+        <v>6.611570247933907</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>79.09</v>
+        <v>30.61</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>69.282</v>
+        <v>27.57</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>69.48099999999999</v>
+        <v>27.731</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2864092341791302</v>
+        <v>-0.5805776928347273</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>70.86200000000001</v>
+        <v>28.148</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>69.867</v>
+        <v>27.891</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.424134426839574</v>
+        <v>0.9214441934674467</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>1.710543661018704</v>
+        <v>1.502021886302174</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1678,7 +1675,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1693,46 +1690,46 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>688106</t>
+          <t>688268</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>金宏气体</t>
+          <t>华特气体</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.96</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.55</v>
+        <v>112.39</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>17.98597194388778</v>
+        <v>13.41069626639759</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>23.95</v>
+        <v>118.92</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>21.006</v>
+        <v>103.382</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>21.265</v>
+        <v>105.176</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.217963790265708</v>
+        <v>-1.705712329809095</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>21.472</v>
+        <v>105.626</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>21.357</v>
+        <v>105.624</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.538465140235056</v>
+        <v>0.001893509050976405</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>1.756428930500764</v>
+        <v>1.707605838860071</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1743,7 +1740,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1758,46 +1755,46 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>688584</t>
+          <t>300540</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>上海合晶</t>
+          <t>蜀道装备</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>19.59</v>
+        <v>20.65</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>23.14</v>
+        <v>23.96</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>18.12149055640633</v>
+        <v>16.02905569007265</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>23.5</v>
+        <v>24.78</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>20.696</v>
+        <v>21.898</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>20.844</v>
+        <v>22.063</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7100364613317978</v>
+        <v>-0.7478584054752102</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>21.16</v>
+        <v>22.424</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>20.994</v>
+        <v>22.256</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.79070210536345</v>
+        <v>0.7548526240114928</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>1.500738566695248</v>
+        <v>1.502711029486703</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1808,7 +1805,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1823,46 +1820,46 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>688727</t>
+          <t>688138</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>恒坤新材</t>
+          <t>清溢光电</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>34.65</v>
+        <v>26</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>41.28</v>
+        <v>30.19</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>19.13419913419914</v>
+        <v>16.11538461538462</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>41.58</v>
+        <v>31.2</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>36.852</v>
+        <v>27.528</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>37.17399999999999</v>
+        <v>27.97</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8661968042179891</v>
+        <v>-1.580264569181256</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>37.656</v>
+        <v>28.154</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>37.418</v>
+        <v>28.153</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6360575124271683</v>
+        <v>0.003552019323005418</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>1.502254316645157</v>
+        <v>1.583816588504261</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -1873,7 +1870,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1888,46 +1885,46 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>688234</t>
+          <t>300821</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>天岳先进</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>83.41</v>
+        <v>15.55</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>99.38</v>
+        <v>18.11</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19.14638532550055</v>
+        <v>16.46302250803857</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>100.09</v>
+        <v>18.66</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>88.33799999999999</v>
+        <v>16.496</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>89.22299999999998</v>
+        <v>17.006</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.9918967082478636</v>
+        <v>-2.998941550041145</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>90.50999999999999</v>
+        <v>16.986</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>90.05199999999999</v>
+        <v>16.985</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5085950339803746</v>
+        <v>0.005887547836302964</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>1.500491742228238</v>
+        <v>3.004829097877448</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -1938,64 +1935,61 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MLCC</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>300806</t>
+          <t>688733</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>斯迪克</t>
+          <t>壹石通</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>37.47</v>
+        <v>21.41</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>42.94</v>
+        <v>25.07</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>14.59834534294102</v>
+        <v>17.09481550677254</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>44.96</v>
+        <v>25.69</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>38.972</v>
+        <v>22.986</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>39.031</v>
+        <v>23.195</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1511618969536999</v>
+        <v>-0.9010562621254548</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>39.72799999999999</v>
+        <v>23.484</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>39.106</v>
+        <v>23.344</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.590548764895394</v>
+        <v>0.5997258396161831</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>1.741710661849094</v>
+        <v>1.500782101741638</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2006,12 +2000,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MLCC</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2021,46 +2015,46 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>300285</t>
+          <t>688106</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>国瓷材料</t>
+          <t>金宏气体</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>43.19</v>
+        <v>19.28</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>51.45</v>
+        <v>22.64</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>19.12479740680715</v>
+        <v>17.42738589211619</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>51.82</v>
+        <v>23.13</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>46.66799999999999</v>
+        <v>20.436</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46.795</v>
+        <v>20.839</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.271396516721889</v>
+        <v>-1.933873986275725</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>47.572</v>
+        <v>20.96</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>46.948</v>
+        <v>20.919</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.329130101388776</v>
+        <v>0.1959940723744058</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>1.600526618110665</v>
+        <v>2.129868058650131</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2071,12 +2065,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2086,46 +2080,46 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>688629</t>
+          <t>688233</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>华丰科技</t>
+          <t>神工股份</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>75.09</v>
+        <v>61.55</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>89.45</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19.12371820482088</v>
+        <v>19.43135662063364</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>73.86</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>79.44</v>
+        <v>66.926</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>79.988</v>
+        <v>67.899</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6851027654148134</v>
+        <v>-1.433010795446177</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>81.334</v>
+        <v>68.548</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>80.355</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.218343600273775</v>
+        <v>0.289685442574994</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>1.903446365688588</v>
+        <v>1.722696238021171</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2136,64 +2130,61 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>存储</t>
+          <t>MLCC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>688825</t>
+          <t>300806</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>长鑫科技</t>
+          <t>斯迪克</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>42.66</v>
+        <v>36.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>47</v>
+        <v>42.2</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10.17346460384436</v>
+        <v>15.30054644808743</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>51.19</v>
+        <v>43.92</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>42.636</v>
+        <v>38.312</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>42.963</v>
+        <v>38.398</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7611200335172041</v>
+        <v>-0.2239699984374344</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>43.842</v>
+        <v>39.27800000000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>43.063</v>
+        <v>38.63399999999999</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.808977544527779</v>
+        <v>1.666925506030981</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>2.570097578044983</v>
+        <v>1.890895504468415</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2204,64 +2195,61 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>601519</t>
+          <t>920493</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>大智慧</t>
+          <t>并行科技</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.34408602150538</v>
+        <v>14.74025222723592</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>10.23</v>
+        <v>103.71</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>9.158000000000001</v>
+        <v>91.07600000000001</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>9.257</v>
+        <v>91.12800000000001</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.069460948471412</v>
+        <v>-0.0570625932754032</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>9.348000000000001</v>
+        <v>93.11000000000001</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9.307</v>
+        <v>91.785</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4405286343612369</v>
+        <v>1.443591000708189</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>1.509989582832649</v>
+        <v>1.500653593983592</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2272,64 +2260,61 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>600621</t>
+          <t>301169</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>华鑫股份</t>
+          <t>零点有数</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>14.9</v>
+        <v>42.89</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>15.91</v>
+        <v>51.1</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.778523489932886</v>
+        <v>19.14199114012591</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>16.39</v>
+        <v>51.46</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>14.66</v>
+        <v>45.654</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>14.77</v>
+        <v>46.396</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.7447528774542911</v>
+        <v>-1.599275799637889</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.996</v>
+        <v>47.072</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>14.883</v>
+        <v>47.072</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.7592555264395617</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>1.504008403893853</v>
+        <v>1.599275799637911</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2340,7 +2325,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2350,51 +2335,54 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>601211</t>
+          <t>600621</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>国泰海通</t>
+          <t>华鑫股份</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>16.61</v>
+        <v>14.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17.68</v>
+        <v>15.91</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.441902468392535</v>
+        <v>6.778523489932886</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>18.27</v>
+        <v>16.39</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>16.436</v>
+        <v>14.66</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>16.495</v>
+        <v>14.77</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.3576841467111125</v>
+        <v>-0.7447528774542911</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>16.788</v>
+        <v>14.996</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>16.598</v>
+        <v>14.883</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.144716230871179</v>
+        <v>0.7592555264395617</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1.502400377582291</v>
+        <v>1.504008403893853</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2405,7 +2393,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2420,46 +2408,46 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>600958</t>
+          <t>601519</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>东方证券</t>
+          <t>大智慧</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.57</v>
+        <v>8.76</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>9.25</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.934655775962662</v>
+        <v>7.191780821917826</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.42</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>8.584</v>
+        <v>9.022</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>8.635999999999999</v>
+        <v>9.144000000000002</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.602130616025931</v>
+        <v>-1.334208223972022</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.76</v>
+        <v>9.218</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>8.682</v>
+        <v>9.118</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.8984105044920421</v>
+        <v>1.096731739416534</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>1.500541120517973</v>
+        <v>2.430939963388556</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2470,7 +2458,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2485,46 +2473,46 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>002736</t>
+          <t>600958</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>国信证券</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>9.73</v>
+        <v>8.48</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>10.53</v>
+        <v>9.15</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.221993833504616</v>
+        <v>7.900943396226423</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>10.7</v>
+        <v>9.32</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>9.786000000000001</v>
+        <v>8.586</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>9.854000000000001</v>
+        <v>8.595000000000002</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6900750964075497</v>
+        <v>-0.1047120418848468</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>9.981999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9.901</v>
+        <v>8.629</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.818099181900811</v>
+        <v>1.402248232703673</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>1.508174278308361</v>
+        <v>1.50696027458852</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2535,7 +2523,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2550,46 +2538,46 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>601236</t>
+          <t>601377</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>红塔证券</t>
+          <t>兴业证券</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>6.94</v>
+        <v>5.52</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.57</v>
+        <v>6</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.077809798270886</v>
+        <v>8.695652173913061</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>7.63</v>
+        <v>6.07</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>7.014000000000001</v>
+        <v>5.613999999999999</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>7.015000000000001</v>
+        <v>5.625999999999999</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.01425516749821165</v>
+        <v>-0.2132954141486065</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>7.164</v>
+        <v>5.726</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>7.059</v>
+        <v>5.653</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.487462813429663</v>
+        <v>1.291349725809288</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1.501717980927875</v>
+        <v>1.504645139957894</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2600,7 +2588,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2615,46 +2603,46 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>600030</t>
+          <t>002736</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>中信证券</t>
+          <t>国信证券</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>25.69</v>
+        <v>9.66</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>28.07</v>
+        <v>10.52</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.264305177111719</v>
+        <v>8.902691511387161</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>28.25</v>
+        <v>10.62</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>25.9</v>
+        <v>9.806000000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>25.947</v>
+        <v>9.812999999999999</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1811384745828204</v>
+        <v>-0.07133394476712684</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>26.512</v>
+        <v>10.008</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>26.166</v>
+        <v>9.866999999999999</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.322326683482378</v>
+        <v>1.429005776831871</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>1.503465158065198</v>
+        <v>1.500339721598998</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2665,7 +2653,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2680,46 +2668,46 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>600918</t>
+          <t>601136</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>中泰证券</t>
+          <t>首创证券</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>5.45</v>
+        <v>13.49</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.97</v>
+        <v>14.78</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.541284403669724</v>
+        <v>9.562638991845795</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.99</v>
+        <v>14.83</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>5.484</v>
+        <v>13.94</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>5.485000000000001</v>
+        <v>14.029</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01823154056519449</v>
+        <v>-0.6344001710741898</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>5.612</v>
+        <v>14.184</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>5.529999999999999</v>
+        <v>14.062</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.482820976491883</v>
+        <v>0.8675864030721181</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>1.501052517057078</v>
+        <v>1.501986574146308</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2730,7 +2718,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2745,46 +2733,46 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>000776</t>
+          <t>688318</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>广发证券</t>
+          <t>财富趋势</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>18.94</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>20.76</v>
+        <v>77.61</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>9.60929250263991</v>
+        <v>10.88726960994428</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>20.83</v>
+        <v>83.98</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>19.154</v>
+        <v>73.66400000000002</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>19.226</v>
+        <v>73.70700000000001</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>-0.3744928742327902</v>
+        <v>-0.05833909940710091</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.57</v>
+        <v>75.06800000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>19.352</v>
+        <v>74.001</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>1.126498553121125</v>
+        <v>1.441872407129652</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>1.500991427353915</v>
+        <v>1.500211506536753</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -2795,7 +2783,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2810,46 +2798,46 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>300085</t>
+          <t>300803</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>银之杰</t>
+          <t>指南针</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>26.43</v>
+        <v>48.38</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>29.61</v>
+        <v>55.17</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>12.03178206583429</v>
+        <v>14.03472509301364</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>31.71</v>
+        <v>58.05</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>27.31799999999999</v>
+        <v>51.812</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>27.469</v>
+        <v>52.057</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>-0.5497105828388582</v>
+        <v>-0.4706379545498129</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>27.81</v>
+        <v>52.79600000000001</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>27.548</v>
+        <v>52.258</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>0.9510672281109356</v>
+        <v>1.029507443836364</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>1.500777810949794</v>
+        <v>1.500145398386177</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -2860,7 +2848,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2875,46 +2863,46 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>300377</t>
+          <t>300085</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>赢时胜</t>
+          <t>银之杰</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>12.69</v>
+        <v>24.89</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>14.69</v>
+        <v>28.83</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>15.76044129235619</v>
+        <v>15.82965046203293</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>15.22</v>
+        <v>29.86</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>13.31</v>
+        <v>26.71</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>13.561</v>
+        <v>26.998</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-1.850895951625986</v>
+        <v>-1.066745684865533</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>13.59</v>
+        <v>27.322</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>13.589</v>
+        <v>27.123</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.007358893222431107</v>
+        <v>0.7336946502968011</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>1.858254844848417</v>
+        <v>1.800440335162334</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2925,7 +2913,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2939,50 +2927,50 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>002517</t>
+          <t>301052</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>果麦文化</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>15.57</v>
+        <v>32.45</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>16.49</v>
+        <v>34.69</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>5.908798972382767</v>
+        <v>6.902927580893659</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.12</v>
+        <v>38.94</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>15.342</v>
+        <v>32.11799999999999</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>15.368</v>
+        <v>33.262</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-0.1691827173347038</v>
+        <v>-3.439360230894128</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>15.638</v>
+        <v>33.19600000000001</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>15.432</v>
+        <v>33.194</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>1.334888543286694</v>
+        <v>0.006025185274460831</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>1.504071260621398</v>
+        <v>3.445385416168589</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -2993,7 +2981,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3020,37 +3008,37 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>16.41</v>
+        <v>16.16</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7.25490196078431</v>
+        <v>7.733333333333325</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>16.83</v>
+        <v>16.5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>14.734</v>
+        <v>14.786</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>15.09</v>
+        <v>14.95</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-2.359178263750827</v>
+        <v>-1.096989966555195</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>15.118</v>
+        <v>15.306</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>15.116</v>
+        <v>14.885</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.01323101349564038</v>
+        <v>2.828350688612713</v>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>2.372409277246468</v>
+        <v>3.925340655167908</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -3061,7 +3049,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3071,54 +3059,51 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>002425</t>
+          <t>300251</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>凯撒文化</t>
+          <t>光线传媒</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.31</v>
+        <v>11.59</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>3.6</v>
+        <v>12.01</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>8.761329305135956</v>
+        <v>3.623813632441752</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>3.64</v>
+        <v>13.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3.29</v>
+        <v>11.622</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>3.327999999999999</v>
+        <v>11.649</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-1.141826923076905</v>
+        <v>-0.2317795518928856</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>3.346</v>
+        <v>11.816</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>3.334000000000001</v>
+        <v>11.668</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>0.359928014397104</v>
+        <v>1.26842646554679</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>1.501754937474009</v>
+        <v>1.500206017439676</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -3129,7 +3114,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3139,54 +3124,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>000676</t>
+          <t>300133</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>智度股份</t>
+          <t>华策影视</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>6.47</v>
+        <v>8.92</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>7.05</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>8.964451313755806</v>
+        <v>5.94170403587444</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>7.11</v>
+        <v>10.7</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>6.496</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>6.544</v>
+        <v>9.052000000000001</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-0.7334963325183352</v>
+        <v>-1.789659743703054</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>6.609999999999999</v>
+        <v>9.059999999999999</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>6.559</v>
+        <v>9.058000000000002</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.7775575545052593</v>
+        <v>0.02207992934419867</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>1.511053887023595</v>
+        <v>1.811739673047252</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3197,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3207,54 +3189,51 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>300418</t>
+          <t>002400</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>省广集团</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>39.95</v>
+        <v>6.45</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>43.67</v>
+        <v>6.85</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>9.311639549436791</v>
+        <v>6.201550387596888</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>47.94</v>
+        <v>7.09</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>40.326</v>
+        <v>6.525999999999999</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>40.457</v>
+        <v>6.565</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-0.3238005783918751</v>
+        <v>-0.5940594059406057</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>41.092</v>
+        <v>6.641999999999999</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>40.614</v>
+        <v>6.581999999999999</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>1.176934062146051</v>
+        <v>0.9115770282588809</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>1.500734640537926</v>
+        <v>1.505636434199487</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -3265,7 +3244,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3275,54 +3254,51 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>301171</t>
+          <t>002555</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>易点天下</t>
+          <t>三七互娱</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>30.62</v>
+        <v>16.1</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>33.96</v>
+        <v>17.29</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10.9079033311561</v>
+        <v>7.391304347826066</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>36.74</v>
+        <v>17.71</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>31.378</v>
+        <v>16.418</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>31.395</v>
+        <v>16.676</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-0.05414874980090856</v>
+        <v>-1.547133605181095</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>31.902</v>
+        <v>16.684</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>31.405</v>
+        <v>16.678</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>1.582550549275585</v>
+        <v>0.03597553663508002</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>1.636699299076494</v>
+        <v>1.583109141816175</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -3333,7 +3309,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3348,46 +3324,46 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>002558</t>
+          <t>300418</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>20.88</v>
+        <v>39.19</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>22.42</v>
+        <v>42.11</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>7.375478927203072</v>
+        <v>7.45088032661394</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>22.96</v>
+        <v>47.02</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>20.83</v>
+        <v>39.884</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>21.137</v>
+        <v>40.01</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>-1.452429389222687</v>
+        <v>-0.3149212696825776</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>21.182</v>
+        <v>40.746</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>21.162</v>
+        <v>40.009</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>0.09450902561192187</v>
+        <v>1.842085530755577</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>1.546938414834609</v>
+        <v>2.157006800438155</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -3398,7 +3374,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3413,46 +3389,46 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>300182</t>
+          <t>600986</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>捷成股份</t>
+          <t>浙文互联</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>5.53</v>
+        <v>6.79</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>6.12</v>
+        <v>7.34</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10.66907775768535</v>
+        <v>8.100147275405</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>6.63</v>
+        <v>7.46</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>5.620000000000001</v>
+        <v>6.907999999999999</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>5.633</v>
+        <v>6.93</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-0.2307828865613204</v>
+        <v>-0.3174603174603163</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>5.728</v>
+        <v>7.058</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>5.656000000000001</v>
+        <v>6.953999999999999</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>1.272984441301261</v>
+        <v>1.495542134023609</v>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>1.503767327862582</v>
+        <v>1.813002451483925</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -3463,7 +3439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3478,46 +3454,46 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>300063</t>
+          <t>600556</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>天龙集团</t>
+          <t>天下秀</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>8.210000000000001</v>
+        <v>4.68</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>9.16</v>
+        <v>5.06</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11.57125456760049</v>
+        <v>8.119658119658112</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>9.85</v>
+        <v>5.14</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>8.384</v>
+        <v>4.81</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>8.469999999999999</v>
+        <v>4.857</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-1.015348288075546</v>
+        <v>-0.9676755198682274</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>8.528</v>
+        <v>4.895999999999999</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>8.485999999999999</v>
+        <v>4.867</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>0.4949328305444478</v>
+        <v>0.5958495993424906</v>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>1.510281118619994</v>
+        <v>1.563525119210718</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -3528,7 +3504,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3543,46 +3519,46 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>300364</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>吉比特</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>23.39</v>
+        <v>328.69</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>26.35</v>
+        <v>358.12</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12.65498076100897</v>
+        <v>8.953725394748858</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>28.06</v>
+        <v>361.55</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>24.358</v>
+        <v>332.52</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>24.578</v>
+        <v>334.83</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-0.8951094474733634</v>
+        <v>-0.6899023385001368</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>24.704</v>
+        <v>339.542</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>24.555</v>
+        <v>336.813</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>0.6068010588474948</v>
+        <v>0.8102418849628812</v>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>1.501910506320858</v>
+        <v>1.500144223463018</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -3593,7 +3569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3608,46 +3584,46 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>301262</t>
+          <t>300182</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>海看股份</t>
+          <t>捷成股份</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>20.67</v>
+        <v>5.33</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>23.35</v>
+        <v>5.9</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>12.96565070149975</v>
+        <v>10.69418386491559</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>24.8</v>
+        <v>6.39</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>21.122</v>
+        <v>5.526000000000001</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>21.511</v>
+        <v>5.555000000000001</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-1.808377109385872</v>
+        <v>-0.5220522052205245</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>21.512</v>
+        <v>5.648</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>21.51</v>
+        <v>5.58</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>0.009298000929791606</v>
+        <v>1.218637992831528</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>1.817675110315664</v>
+        <v>1.740690198052053</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -3658,7 +3634,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3673,46 +3649,46 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>300785</t>
+          <t>300364</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>值得买</t>
+          <t>中文在线</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>34.27</v>
+        <v>23.45</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>38.78</v>
+        <v>26.59</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13.16019842427778</v>
+        <v>13.39019189765458</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>41.12</v>
+        <v>28.14</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>35.188</v>
+        <v>24.172</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>35.45699999999999</v>
+        <v>24.289</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>-0.7586654257269121</v>
+        <v>-0.4816995347688091</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>35.804</v>
+        <v>24.904</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>35.54000000000001</v>
+        <v>24.422</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>0.742824985931323</v>
+        <v>1.973630333306042</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>1.501490411658235</v>
+        <v>2.455329868074851</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -3723,7 +3699,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3738,46 +3714,46 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>300063</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>线上线下</t>
+          <t>天龙集团</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>71.55</v>
+        <v>7.93</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>82.33</v>
+        <v>9.01</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>15.06638714185884</v>
+        <v>13.61916771752838</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>85.86</v>
+        <v>9.51</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>74.24799999999999</v>
+        <v>8.251999999999999</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>74.785</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>-0.7180584341779817</v>
+        <v>-1.149976042165812</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>75.70399999999999</v>
+        <v>8.484</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>75.116</v>
+        <v>8.375</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>0.7827892859044505</v>
+        <v>1.301492537313442</v>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>1.500847720082432</v>
+        <v>2.451468579479255</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -3788,7 +3764,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3803,46 +3779,46 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>301231</t>
+          <t>301262</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>荣信文化</t>
+          <t>海看股份</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>28.52</v>
+        <v>20.35</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>34.01</v>
+        <v>23.36</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>19.24964936886395</v>
+        <v>14.79115479115478</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>34.22</v>
+        <v>24.42</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>30.25</v>
+        <v>20.914</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>30.754</v>
+        <v>21.211</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>-1.638811211549707</v>
+        <v>-1.400216868605919</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>30.88</v>
+        <v>21.638</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>30.878</v>
+        <v>21.336</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.006477103439306298</v>
+        <v>1.415448068991365</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>1.645288314989013</v>
+        <v>2.815664937597284</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -3853,12 +3829,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3868,46 +3844,46 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>688697</t>
+          <t>300959</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>纽威数控</t>
+          <t>线上线下</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>12.25</v>
+        <v>68.5</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>13.77</v>
+        <v>79.03</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>12.40816326530611</v>
+        <v>15.37226277372263</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>14.7</v>
+        <v>82.2</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>12.554</v>
+        <v>72.27799999999999</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>12.748</v>
+        <v>73.40299999999999</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>-1.521807342328219</v>
+        <v>-1.532634905930275</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>12.874</v>
+        <v>74.042</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>12.748</v>
+        <v>73.756</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>0.9883903357389423</v>
+        <v>0.3877650631813001</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>2.510197678067161</v>
+        <v>1.920399969111575</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -3918,12 +3894,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3933,46 +3909,46 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>301182</t>
+          <t>300785</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>凯旺科技</t>
+          <t>值得买</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45.29</v>
+        <v>32.47</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52.25</v>
+        <v>37.95</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>15.36763082358137</v>
+        <v>16.87711733908224</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>54.34</v>
+        <v>38.96</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>47.432</v>
+        <v>34.376</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>47.541</v>
+        <v>34.82600000000001</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>-0.2292757830083536</v>
+        <v>-1.292138057772951</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>48.318</v>
+        <v>35.33</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>47.711</v>
+        <v>35.05500000000001</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>1.2722432981912</v>
+        <v>0.7844815290257934</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>1.501519081199554</v>
+        <v>2.076619586798745</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -3983,12 +3959,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3998,46 +3974,46 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>688090</t>
+          <t>301171</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>瑞松科技</t>
+          <t>易点天下</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>55.8</v>
+        <v>28.9</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>65.2</v>
+        <v>33.87</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>16.84587813620073</v>
+        <v>17.19723183391002</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>66.95999999999999</v>
+        <v>34.68</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>57.492</v>
+        <v>30.872</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>58.30399999999999</v>
+        <v>30.89</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>-1.392700329308449</v>
+        <v>-0.0582712852055467</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>58.974</v>
+        <v>31.734</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>58.389</v>
+        <v>31.077</v>
       </c>
       <c r="P55" s="4" t="n">
-        <v>1.001901043004683</v>
+        <v>2.11410367796121</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>2.394601372313132</v>
+        <v>2.172374963166757</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -4048,64 +4024,61 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>300204</t>
+          <t>301182</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>舒泰神</t>
+          <t>凯旺科技</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>17.77</v>
+        <v>43.21</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>19.81</v>
+        <v>50.56</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>11.48002250984805</v>
+        <v>17.00995140013886</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>21.32</v>
+        <v>51.85</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>18.234</v>
+        <v>46.172</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>18.5</v>
+        <v>46.638</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>-1.437837837837852</v>
+        <v>-0.9991852137741675</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>18.552</v>
+        <v>47.264</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>18.502</v>
+        <v>46.95</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.2702410550210921</v>
+        <v>0.6687965921192696</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>1.708078892858944</v>
+        <v>1.667981805893437</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -4116,64 +4089,61 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>920367</t>
+          <t>688697</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>新赣江</t>
+          <t>纽威数控</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>21.7</v>
+        <v>11.76</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>24.21</v>
+        <v>13.78</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>11.56682027649771</v>
+        <v>17.17687074829932</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>26.04</v>
+        <v>14.11</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>21.954</v>
+        <v>12.474</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>22.394</v>
+        <v>12.548</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>-1.964812003215133</v>
+        <v>-0.5897354160025459</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>22.436</v>
+        <v>12.832</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>22.435</v>
+        <v>12.656</v>
       </c>
       <c r="P57" s="4" t="n">
-        <v>0.004457321149975435</v>
+        <v>1.390644753476589</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>1.969269324365108</v>
+        <v>1.980380169479135</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -4184,7 +4154,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4198,50 +4168,50 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>300246</t>
+          <t>300006</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>宝莱特</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>12.68</v>
+        <v>8.27</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>14.32</v>
+        <v>9.58</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12.93375394321767</v>
+        <v>15.8403869407497</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>15.21</v>
+        <v>9.92</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>13.132</v>
+        <v>8.528</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>13.15</v>
+        <v>8.674000000000001</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>-0.1368821292775713</v>
+        <v>-1.683191145953433</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>13.378</v>
+        <v>8.82</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>13.198</v>
+        <v>8.818999999999999</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>1.36384300651613</v>
+        <v>0.01133915409912145</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>1.500725135793701</v>
+        <v>1.694530300052555</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -4252,7 +4222,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4262,54 +4232,51 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>300255</t>
+          <t>002950</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>常山药业</t>
+          <t>奥美医疗</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>19.33</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>22.19</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14.79565442317643</v>
+        <v>7.785888077858871</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>23.19</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>20.042</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>20.065</v>
+        <v>8.372</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>-0.1146274607525477</v>
+        <v>-0.3344481605351279</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>20.476</v>
+        <v>8.504</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>20.196</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>1.386413151119048</v>
+        <v>1.165833928146554</v>
       </c>
       <c r="Q59" s="5" t="n">
-        <v>1.501040611871596</v>
+        <v>1.500282088681681</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -4320,7 +4287,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4335,46 +4302,46 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>300702</t>
+          <t>301408</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>天宇股份</t>
+          <t>华人健康</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>20.33</v>
+        <v>13.78</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>22.1</v>
+        <v>14.88</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8.706345302508623</v>
+        <v>7.982583454281578</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>24.39</v>
+        <v>16.53</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>20.484</v>
+        <v>13.936</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>20.757</v>
+        <v>13.95</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>-1.315218962277787</v>
+        <v>-0.100358422939073</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>20.878</v>
+        <v>14.236</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>20.79</v>
+        <v>14.039</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.4232804232804366</v>
+        <v>1.403233848564733</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>1.738499385558223</v>
+        <v>1.503592271503806</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -4385,7 +4352,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4400,46 +4367,46 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>300702</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>天宇股份</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>20.01</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>10.57</v>
+        <v>21.77</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9.647302904564302</v>
+        <v>8.795602198900543</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>11.56</v>
+        <v>24.01</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>9.778000000000002</v>
+        <v>20.394</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>9.91</v>
+        <v>20.548</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>-1.331987891019148</v>
+        <v>-0.749464668094213</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>20.792</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>9.933000000000002</v>
+        <v>20.632</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>0.1711466827745589</v>
+        <v>0.7754943776657752</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>1.503134573793707</v>
+        <v>1.524959045759988</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -4450,7 +4417,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4465,46 +4432,46 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>920047</t>
+          <t>603259</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>诺思兰德</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>13.21</v>
+        <v>141.48</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>14.93</v>
+        <v>154.19</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>13.02043906131718</v>
+        <v>8.983601922533225</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>15.85</v>
+        <v>155.62</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>13.638</v>
+        <v>145.54</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>13.712</v>
+        <v>146.801</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>-0.5396732788798153</v>
+        <v>-0.8589859742099804</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>13.932</v>
+        <v>148.116</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>13.799</v>
+        <v>146.77</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.9638379592723956</v>
+        <v>0.9170811473734553</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>1.503511238152211</v>
+        <v>1.776067121583436</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -4515,7 +4482,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4530,46 +4497,46 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>300347</t>
+          <t>600479</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>泰格医药</t>
+          <t>XD千金药</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>50.11</v>
+        <v>10.46</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>57.09</v>
+        <v>11.42</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13.92935541808022</v>
+        <v>9.17782026768641</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>60.13</v>
+        <v>11.5</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>51.37</v>
+        <v>10.754</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>51.443</v>
+        <v>10.879</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-0.1419046323114959</v>
+        <v>-1.149002665686183</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>52.55</v>
+        <v>10.928</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>51.84500000000001</v>
+        <v>10.889</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>1.359822547979528</v>
+        <v>0.3581596106162044</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>1.501727180291024</v>
+        <v>1.507162276302387</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -4580,7 +4547,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4595,46 +4562,46 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>300109</t>
+          <t>688710</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>新开源</t>
+          <t>益诺思</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>11.25</v>
+        <v>83.36</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>12.87</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>14.39999999999999</v>
+        <v>9.812859884836866</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>13.5</v>
+        <v>100.03</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>11.656</v>
+        <v>83.75</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>11.723</v>
+        <v>84.50099999999999</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>-0.5715260598822991</v>
+        <v>-0.8887468787351471</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>11.888</v>
+        <v>85.82000000000001</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>11.778</v>
+        <v>84.71000000000001</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.9339446425539188</v>
+        <v>1.310352968952899</v>
       </c>
       <c r="Q64" s="5" t="n">
-        <v>1.505470702436218</v>
+        <v>2.199099847688046</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -4645,7 +4612,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4660,46 +4627,46 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>301257</t>
+          <t>300363</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>普蕊斯</t>
+          <t>博腾股份</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>32.94</v>
+        <v>20.93</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>37.77</v>
+        <v>23.15</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>14.66302367941714</v>
+        <v>10.60678451982799</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>39.52</v>
+        <v>25.11</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>34.008</v>
+        <v>21.43</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>34.349</v>
+        <v>21.526</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>-0.9927508806660823</v>
+        <v>-0.4459723125522785</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>34.736</v>
+        <v>21.876</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>34.45800000000001</v>
+        <v>21.647</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>0.8067792675140684</v>
+        <v>1.057883309465502</v>
       </c>
       <c r="Q65" s="5" t="n">
-        <v>1.799530148180151</v>
+        <v>1.50385562201778</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -4710,7 +4677,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4725,46 +4692,46 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>301333</t>
+          <t>300255</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>诺思格</t>
+          <t>常山药业</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>52.87</v>
+        <v>18.73</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>61.15</v>
+        <v>20.9</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>15.66105541895215</v>
+        <v>11.58569140416443</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>63.44</v>
+        <v>22.47</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>54.5</v>
+        <v>19.526</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>55.198</v>
+        <v>19.721</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>-1.26453857023805</v>
+        <v>-0.9887936717204893</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>55.908</v>
+        <v>19.884</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>55.468</v>
+        <v>19.782</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0.793250162255732</v>
+        <v>0.515620260843197</v>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>2.057788732493782</v>
+        <v>1.504413932563686</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -4775,7 +4742,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4790,46 +4757,46 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>300534</t>
+          <t>300705</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>九典制药</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>10.09</v>
+        <v>10.33</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>11.7</v>
+        <v>11.54</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>15.95639246778988</v>
+        <v>11.71345595353339</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>12.1</v>
+        <v>12.39</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>10.56</v>
+        <v>10.682</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>10.717</v>
+        <v>10.718</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>-1.464962209573595</v>
+        <v>-0.3358835603657573</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>10.764</v>
+        <v>10.926</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>10.755</v>
+        <v>10.8</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>0.08368200836819106</v>
+        <v>1.166666666666649</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>1.548644217941786</v>
+        <v>1.502550227032406</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -4840,7 +4807,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4855,46 +4822,46 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>300683</t>
+          <t>688607</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>海特生物</t>
+          <t>康众科技</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>22.93</v>
+        <v>31</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>26.64</v>
+        <v>34.67</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>16.17967727867422</v>
+        <v>11.83870967741936</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>27.51</v>
+        <v>37.2</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>24.024</v>
+        <v>32.822</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>24.083</v>
+        <v>33.042</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>-0.2449860897728695</v>
+        <v>-0.6658192603353319</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>24.566</v>
+        <v>33.384</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>24.261</v>
+        <v>33.10700000000001</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>1.257161699847509</v>
+        <v>0.8366810644274469</v>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>1.502147789620378</v>
+        <v>1.502500324762779</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -4905,7 +4872,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4920,46 +4887,46 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>688710</t>
+          <t>300434</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>益诺思</t>
+          <t>金石亚药</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>81.5</v>
+        <v>11.31</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>95.72</v>
+        <v>12.66</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>17.44785276073619</v>
+        <v>11.93633952254642</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>97.8</v>
+        <v>13.57</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>84.828</v>
+        <v>12.044</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>85.736</v>
+        <v>12.294</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>-1.059065036857332</v>
+        <v>-2.033512282414185</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>87.05799999999999</v>
+        <v>12.242</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>86.155</v>
+        <v>12.24</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>1.048110962799598</v>
+        <v>0.01633986928104569</v>
       </c>
       <c r="Q69" s="5" t="n">
-        <v>2.107175999656929</v>
+        <v>2.049852151695231</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -4970,7 +4937,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4985,46 +4952,46 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>诚达药业</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>24.86</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>29.22</v>
+        <v>10.34</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>17.53821399839099</v>
+        <v>12.14750542299348</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>29.83</v>
+        <v>11.06</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>26.29</v>
+        <v>9.634</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>26.477</v>
+        <v>9.775000000000002</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>-0.7062733693394163</v>
+        <v>-1.442455242966767</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>26.828</v>
+        <v>9.818000000000001</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>26.604</v>
+        <v>9.792000000000002</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.8419786498270687</v>
+        <v>0.2655228758169814</v>
       </c>
       <c r="Q70" s="5" t="n">
-        <v>1.548252019166485</v>
+        <v>1.707978118783748</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -5035,7 +5002,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5050,46 +5017,46 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>301333</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>华兰股份</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>49.96</v>
+        <v>51.85</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>58.78</v>
+        <v>58.46</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>17.65412329863891</v>
+        <v>12.74831243972998</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>59.95</v>
+        <v>62.22</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>52.13200000000001</v>
+        <v>53.51000000000001</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>52.383</v>
+        <v>54.26900000000001</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>-0.4791630872611252</v>
+        <v>-1.398588512778931</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>53.348</v>
+        <v>54.876</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>52.80799999999999</v>
+        <v>54.463</v>
       </c>
       <c r="P71" s="4" t="n">
-        <v>1.02257233752463</v>
+        <v>0.7583129831261637</v>
       </c>
       <c r="Q71" s="5" t="n">
-        <v>1.501735424785755</v>
+        <v>2.156901495905095</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -5100,7 +5067,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5115,46 +5082,46 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>301111</t>
+          <t>300246</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>粤万年青</t>
+          <t>宝莱特</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>18.48</v>
+        <v>12.22</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>21.82</v>
+        <v>13.85</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>18.07359307359306</v>
+        <v>13.33878887070377</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>22.17</v>
+        <v>14.66</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>19.374</v>
+        <v>12.864</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>19.46</v>
+        <v>12.941</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>-0.4419321685508626</v>
+        <v>-0.5950081137470087</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>19.802</v>
+        <v>13.106</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>19.594</v>
+        <v>12.988</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>1.061549453914457</v>
+        <v>0.9085309516476681</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>1.503481622465319</v>
+        <v>1.503539065394677</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -5165,7 +5132,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5180,46 +5147,46 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>300109</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>奥浦迈</t>
+          <t>新开源</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>57.5</v>
+        <v>10.77</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>68</v>
+        <v>12.33</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>18.2608695652174</v>
+        <v>14.48467966573816</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>69</v>
+        <v>12.92</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>59.85599999999999</v>
+        <v>11.36</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>60.91800000000001</v>
+        <v>11.514</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>-1.743327095439795</v>
+        <v>-1.337502171269755</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>61.63199999999999</v>
+        <v>11.602</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>61.30999999999999</v>
+        <v>11.577</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>0.5251998042733685</v>
+        <v>0.2159454090005841</v>
       </c>
       <c r="Q73" s="5" t="n">
-        <v>2.268526899713164</v>
+        <v>1.55344758027034</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -5230,64 +5197,61 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>603011</t>
+          <t>300347</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>合锻智能</t>
+          <t>泰格医药</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>19.69</v>
+        <v>47.82</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>21.12</v>
+        <v>54.89</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>7.262569832402233</v>
+        <v>14.78460895023004</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>21.65</v>
+        <v>57.38</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>19.464</v>
+        <v>50.25599999999999</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>19.515</v>
+        <v>50.69799999999999</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>-0.2613374327440354</v>
+        <v>-0.8718292634817937</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>19.832</v>
+        <v>51.302</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>19.537</v>
+        <v>50.98099999999999</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>1.509955469109903</v>
+        <v>0.6296463388321349</v>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>1.771292901853938</v>
+        <v>1.501475602313929</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -5298,12 +5262,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5313,46 +5277,46 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>301082</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>久盛电气</t>
+          <t>一品红</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>9.140000000000001</v>
+        <v>28.77</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>10.36</v>
+        <v>33.08</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13.34792122538291</v>
+        <v>14.98088286409454</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>10.96</v>
+        <v>34.52</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>9.41</v>
+        <v>30.38</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>9.443999999999999</v>
+        <v>30.584</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>-0.3600169419737287</v>
+        <v>-0.6670154329060929</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>9.638</v>
+        <v>31.088</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>9.495000000000001</v>
+        <v>30.831</v>
       </c>
       <c r="P75" s="4" t="n">
-        <v>1.506055818852015</v>
+        <v>0.8335765949855745</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>1.866072760825743</v>
+        <v>1.500592027891667</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -5363,12 +5327,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5378,46 +5342,46 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>300427</t>
+          <t>300683</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>红相股份</t>
+          <t>海特生物</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>5.37</v>
+        <v>21.76</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>6.26</v>
+        <v>25.03</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>16.57355679702048</v>
+        <v>15.02757352941175</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>6.44</v>
+        <v>26.11</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>5.642</v>
+        <v>23.268</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>5.661</v>
+        <v>23.612</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>-0.3356297473944392</v>
+        <v>-1.456886328985241</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>5.772</v>
+        <v>23.674</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>5.705</v>
+        <v>23.663</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>1.174408413672223</v>
+        <v>0.0464860753074392</v>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>1.510038161066662</v>
+        <v>1.50337240429268</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -5428,64 +5392,61 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>商业航天</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>002115</t>
+          <t>300725</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>三维通信</t>
+          <t>药石科技</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>41.36</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>10.63</v>
+        <v>47.86</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>9.587628865979392</v>
+        <v>15.71566731141198</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>10.67</v>
+        <v>49.63</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>9.746</v>
+        <v>44.188</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>9.763</v>
+        <v>44.511</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>-0.1741268052852574</v>
+        <v>-0.7256633191795259</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>9.918000000000001</v>
+        <v>45.09999999999999</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>9.788</v>
+        <v>44.753</v>
       </c>
       <c r="P77" s="4" t="n">
-        <v>1.328156926849222</v>
+        <v>0.7753670145018043</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>1.50228373213448</v>
+        <v>1.50103033368133</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -5493,8 +5454,853 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>301257</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>普蕊斯</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>16.44444444444444</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>33.264</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>33.722</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>-1.358163809975699</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>34.134</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>33.854</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0.8270809948602853</v>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>2.185244804835984</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>301093</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>华兰股份</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>47.68</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>16.69463087248322</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>51.384</v>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>-1.720379884789036</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>51.824</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>51.822</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0.003859364748559635</v>
+      </c>
+      <c r="Q79" s="5" t="n">
+        <v>1.724239249537596</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>301201</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>诚达药业</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>16.70137442732194</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>25.546</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>25.963</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>-1.606131802950361</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>26.066</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>26.065</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>0.003836562440051594</v>
+      </c>
+      <c r="Q80" s="5" t="n">
+        <v>1.609968365390413</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>920047</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>诺思兰德</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>16.87797147385104</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>13.434</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v>-0.8560885608856372</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>13.722</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>13.634</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>0.6454452105031372</v>
+      </c>
+      <c r="Q81" s="5" t="n">
+        <v>1.501533771388774</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>300204</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>舒泰神</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>17.09047900650502</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>18.211</v>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>-1.323375981549613</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>18.264</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>1.127901883486615</v>
+      </c>
+      <c r="Q82" s="5" t="n">
+        <v>2.451277865036228</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>300534</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>陇神戎发</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>17.8719008264463</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>10.302</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>10.524</v>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>-2.109464082098089</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>10.564</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>10.562</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>0.01893580761218594</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <v>2.128399889710275</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>300436</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>广生堂</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>18.34978843441466</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>85.08</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>76.474</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>77.93899999999999</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <v>-1.879675130550806</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>78.164</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>78.16199999999999</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>0.002558788157935865</v>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>1.882233918708742</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>301234</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>五洲医疗</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>149.04</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>18.56801909307875</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>150.84</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>130.836</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>131.754</v>
+      </c>
+      <c r="M85" s="4" t="n">
+        <v>-0.6967530397559152</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>134.844</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>132.851</v>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>1.50017688989923</v>
+      </c>
+      <c r="Q85" s="5" t="n">
+        <v>2.196929929655145</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>920367</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>新赣江</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>19.2982456140351</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>21.502</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>21.968</v>
+      </c>
+      <c r="M86" s="4" t="n">
+        <v>-2.12126729788783</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>22.098</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>21.968</v>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>0.5917698470502719</v>
+      </c>
+      <c r="Q86" s="5" t="n">
+        <v>2.713037144938102</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>688293</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>XD奥浦迈</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>64.65000000000001</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>19.54511834319528</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>58.05799999999999</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>59.423</v>
+      </c>
+      <c r="M87" s="4" t="n">
+        <v>-2.297090352220532</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>59.706</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>59.70399999999999</v>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>0.003349859305923353</v>
+      </c>
+      <c r="Q87" s="5" t="n">
+        <v>2.300440211526456</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>300069</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>金利华电</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>13.91263057929724</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>21.766</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>22.147</v>
+      </c>
+      <c r="M88" s="4" t="n">
+        <v>-1.720323294351378</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>22.318</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>22.316</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>0.008962179602090004</v>
+      </c>
+      <c r="Q88" s="5" t="n">
+        <v>1.729285473953468</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>301082</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>久盛电气</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>16.51480637813214</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>9.296000000000001</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>9.324000000000002</v>
+      </c>
+      <c r="M89" s="4" t="n">
+        <v>-0.3003003003003046</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>9.526</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>9.413</v>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v>1.200467438648678</v>
+      </c>
+      <c r="Q89" s="5" t="n">
+        <v>1.500767738948983</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>300427</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>红相股份</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>17.85028790786946</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>5.538</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>5.588</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>-0.8947745168217613</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>5.678</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>5.643000000000001</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>0.6202374623427209</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>1.515011979164482</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R77"/>
+  <autoFilter ref="A2:R90"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5破10明日门槛完整名单｜信号日 2026-10-27｜88 只｜报告 多空阶段_2026-10-27.xlsx</t>
+          <t>5破10明日门槛完整名单｜信号日 2026-10-27｜90 只｜报告 多空阶段_2026-10-27.xlsx</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2343,46 +2343,46 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>600621</t>
+          <t>301052</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>华鑫股份</t>
+          <t>果麦文化</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.9</v>
+        <v>32.45</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>15.91</v>
+        <v>34.69</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.778523489932886</v>
+        <v>6.902927580893659</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.39</v>
+        <v>38.94</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>14.66</v>
+        <v>32.11799999999999</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>14.77</v>
+        <v>33.262</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.7447528774542911</v>
+        <v>-3.439360230894128</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>14.996</v>
+        <v>33.19600000000001</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14.883</v>
+        <v>33.194</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.7592555264395617</v>
+        <v>0.006025185274460831</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>1.504008403893853</v>
+        <v>3.445385416168589</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2398,56 +2398,59 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>601519</t>
+          <t>603258</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>大智慧</t>
+          <t>电魂网络</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.76</v>
+        <v>15</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>9.390000000000001</v>
+        <v>16.16</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.191780821917826</v>
+        <v>7.733333333333325</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.630000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>9.022</v>
+        <v>14.786</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>9.144000000000002</v>
+        <v>14.95</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.334208223972022</v>
+        <v>-1.096989966555195</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>9.218</v>
+        <v>15.306</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>9.118</v>
+        <v>14.885</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.096731739416534</v>
+        <v>2.828350688612713</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>2.430939963388556</v>
+        <v>3.925340655167908</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2463,7 +2466,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2473,46 +2476,46 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>600958</t>
+          <t>300251</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>东方证券</t>
+          <t>光线传媒</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.48</v>
+        <v>11.59</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9.15</v>
+        <v>12.01</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.900943396226423</v>
+        <v>3.623813632441752</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.32</v>
+        <v>13.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8.586</v>
+        <v>11.622</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>8.595000000000002</v>
+        <v>11.649</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1047120418848468</v>
+        <v>-0.2317795518928856</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.75</v>
+        <v>11.816</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>8.629</v>
+        <v>11.668</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.402248232703673</v>
+        <v>1.26842646554679</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>1.50696027458852</v>
+        <v>1.500206017439676</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2528,7 +2531,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2538,46 +2541,46 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>601377</t>
+          <t>300133</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>兴业证券</t>
+          <t>华策影视</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>5.52</v>
+        <v>8.92</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.695652173913061</v>
+        <v>5.94170403587444</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>6.07</v>
+        <v>10.7</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>5.613999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>5.625999999999999</v>
+        <v>9.052000000000001</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2132954141486065</v>
+        <v>-1.789659743703054</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>5.726</v>
+        <v>9.059999999999999</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>5.653</v>
+        <v>9.058000000000002</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.291349725809288</v>
+        <v>0.02207992934419867</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1.504645139957894</v>
+        <v>1.811739673047252</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2593,7 +2596,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2603,46 +2606,46 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>002736</t>
+          <t>002400</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>国信证券</t>
+          <t>省广集团</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>9.66</v>
+        <v>6.45</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>10.52</v>
+        <v>6.85</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8.902691511387161</v>
+        <v>6.201550387596888</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>10.62</v>
+        <v>7.09</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>9.806000000000001</v>
+        <v>6.525999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>9.812999999999999</v>
+        <v>6.565</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07133394476712684</v>
+        <v>-0.5940594059406057</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>10.008</v>
+        <v>6.641999999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>9.866999999999999</v>
+        <v>6.581999999999999</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.429005776831871</v>
+        <v>0.9115770282588809</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>1.500339721598998</v>
+        <v>1.505636434199487</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2658,7 +2661,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2668,46 +2671,46 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>601136</t>
+          <t>002555</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>首创证券</t>
+          <t>三七互娱</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>13.49</v>
+        <v>16.1</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>14.78</v>
+        <v>17.29</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.562638991845795</v>
+        <v>7.391304347826066</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>14.83</v>
+        <v>17.71</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>13.94</v>
+        <v>16.418</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>14.029</v>
+        <v>16.676</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.6344001710741898</v>
+        <v>-1.547133605181095</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>14.184</v>
+        <v>16.684</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>14.062</v>
+        <v>16.678</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.8675864030721181</v>
+        <v>0.03597553663508002</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>1.501986574146308</v>
+        <v>1.583109141816175</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2723,7 +2726,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2733,46 +2736,46 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>688318</t>
+          <t>300418</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>财富趋势</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>69.98999999999999</v>
+        <v>39.19</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>77.61</v>
+        <v>42.11</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>10.88726960994428</v>
+        <v>7.45088032661394</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>83.98</v>
+        <v>47.02</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>73.66400000000002</v>
+        <v>39.884</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>73.70700000000001</v>
+        <v>40.01</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>-0.05833909940710091</v>
+        <v>-0.3149212696825776</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>75.06800000000001</v>
+        <v>40.746</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>74.001</v>
+        <v>40.009</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>1.441872407129652</v>
+        <v>1.842085530755577</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>1.500211506536753</v>
+        <v>2.157006800438155</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -2788,7 +2791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2798,46 +2801,46 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>300803</t>
+          <t>600986</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>指南针</t>
+          <t>浙文互联</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>48.38</v>
+        <v>6.79</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>55.17</v>
+        <v>7.34</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>14.03472509301364</v>
+        <v>8.100147275405</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>58.05</v>
+        <v>7.46</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>51.812</v>
+        <v>6.907999999999999</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>52.057</v>
+        <v>6.93</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>-0.4706379545498129</v>
+        <v>-0.3174603174603163</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>52.79600000000001</v>
+        <v>7.058</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>52.258</v>
+        <v>6.953999999999999</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>1.029507443836364</v>
+        <v>1.495542134023609</v>
       </c>
       <c r="Q37" s="5" t="n">
-        <v>1.500145398386177</v>
+        <v>1.813002451483925</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -2853,7 +2856,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2863,46 +2866,46 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>300085</t>
+          <t>600556</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>银之杰</t>
+          <t>天下秀</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>24.89</v>
+        <v>4.68</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>28.83</v>
+        <v>5.06</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>15.82965046203293</v>
+        <v>8.119658119658112</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>29.86</v>
+        <v>5.14</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>26.71</v>
+        <v>4.81</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>26.998</v>
+        <v>4.857</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>-1.066745684865533</v>
+        <v>-0.9676755198682274</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>27.322</v>
+        <v>4.895999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>27.123</v>
+        <v>4.867</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.7336946502968011</v>
+        <v>0.5958495993424906</v>
       </c>
       <c r="Q38" s="5" t="n">
-        <v>1.800440335162334</v>
+        <v>1.563525119210718</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2923,54 +2926,51 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>301052</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>果麦文化</t>
+          <t>吉比特</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>32.45</v>
+        <v>328.69</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>34.69</v>
+        <v>358.12</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>6.902927580893659</v>
+        <v>8.953725394748858</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>38.94</v>
+        <v>361.55</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>32.11799999999999</v>
+        <v>332.52</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>33.262</v>
+        <v>334.83</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>-3.439360230894128</v>
+        <v>-0.6899023385001368</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>33.19600000000001</v>
+        <v>339.542</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>33.194</v>
+        <v>336.813</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>0.006025185274460831</v>
+        <v>0.8102418849628812</v>
       </c>
       <c r="Q39" s="5" t="n">
-        <v>3.445385416168589</v>
+        <v>1.500144223463018</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -2991,54 +2991,51 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>603258</t>
+          <t>300182</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>电魂网络</t>
+          <t>捷成股份</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>15</v>
+        <v>5.33</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>16.16</v>
+        <v>5.9</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>7.733333333333325</v>
+        <v>10.69418386491559</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>16.5</v>
+        <v>6.39</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>14.786</v>
+        <v>5.526000000000001</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>14.95</v>
+        <v>5.555000000000001</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>-1.096989966555195</v>
+        <v>-0.5220522052205245</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>15.306</v>
+        <v>5.648</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>14.885</v>
+        <v>5.58</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>2.828350688612713</v>
+        <v>1.218637992831528</v>
       </c>
       <c r="Q40" s="5" t="n">
-        <v>3.925340655167908</v>
+        <v>1.740690198052053</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -3064,46 +3061,46 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>300251</t>
+          <t>300364</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>光线传媒</t>
+          <t>中文在线</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>11.59</v>
+        <v>23.45</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.01</v>
+        <v>26.59</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>3.623813632441752</v>
+        <v>13.39019189765458</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>13.9</v>
+        <v>28.14</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.622</v>
+        <v>24.172</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>11.649</v>
+        <v>24.289</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>-0.2317795518928856</v>
+        <v>-0.4816995347688091</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.816</v>
+        <v>24.904</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>11.668</v>
+        <v>24.422</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>1.26842646554679</v>
+        <v>1.973630333306042</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>1.500206017439676</v>
+        <v>2.455329868074851</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -3129,46 +3126,46 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>300133</t>
+          <t>300063</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>华策影视</t>
+          <t>天龙集团</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>8.92</v>
+        <v>7.93</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>5.94170403587444</v>
+        <v>13.61916771752838</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.7</v>
+        <v>9.51</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.251999999999999</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>9.052000000000001</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>-1.789659743703054</v>
+        <v>-1.149976042165812</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.059999999999999</v>
+        <v>8.484</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>9.058000000000002</v>
+        <v>8.375</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.02207992934419867</v>
+        <v>1.301492537313442</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>1.811739673047252</v>
+        <v>2.451468579479255</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3194,46 +3191,46 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>002400</t>
+          <t>301262</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>省广集团</t>
+          <t>海看股份</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6.45</v>
+        <v>20.35</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>6.85</v>
+        <v>23.42</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>6.201550387596888</v>
+        <v>15.08599508599509</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>7.09</v>
+        <v>24.42</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>6.525999999999999</v>
+        <v>20.926</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>6.565</v>
+        <v>21.222</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-0.5940594059406057</v>
+        <v>-1.394779002921476</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>6.641999999999999</v>
+        <v>21.662</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>6.581999999999999</v>
+        <v>21.348</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>0.9115770282588809</v>
+        <v>1.470863781150444</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>1.505636434199487</v>
+        <v>2.86564278407192</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -3259,46 +3256,46 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>002555</t>
+          <t>300959</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>三七互娱</t>
+          <t>线上线下</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>16.1</v>
+        <v>68.5</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>17.29</v>
+        <v>79.03</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>7.391304347826066</v>
+        <v>15.37226277372263</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>17.71</v>
+        <v>82.2</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>16.418</v>
+        <v>72.27799999999999</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>16.676</v>
+        <v>73.40299999999999</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>-1.547133605181095</v>
+        <v>-1.532634905930275</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>16.684</v>
+        <v>74.042</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>16.678</v>
+        <v>73.756</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.03597553663508002</v>
+        <v>0.3877650631813001</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>1.583109141816175</v>
+        <v>1.920399969111575</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -3324,46 +3321,46 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>300418</t>
+          <t>300785</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>值得买</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>39.19</v>
+        <v>32.47</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>42.11</v>
+        <v>37.95</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>7.45088032661394</v>
+        <v>16.87711733908224</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>47.02</v>
+        <v>38.96</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>39.884</v>
+        <v>34.376</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>40.01</v>
+        <v>34.82600000000001</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>-0.3149212696825776</v>
+        <v>-1.292138057772951</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>40.746</v>
+        <v>35.33</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>40.009</v>
+        <v>35.05500000000001</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>1.842085530755577</v>
+        <v>0.7844815290257934</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>2.157006800438155</v>
+        <v>2.076619586798745</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -3389,46 +3386,46 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>600986</t>
+          <t>301171</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>浙文互联</t>
+          <t>易点天下</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>6.79</v>
+        <v>28.9</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>7.34</v>
+        <v>33.87</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>8.100147275405</v>
+        <v>17.19723183391002</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>7.46</v>
+        <v>34.68</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>6.907999999999999</v>
+        <v>30.872</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>6.93</v>
+        <v>30.89</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>-0.3174603174603163</v>
+        <v>-0.0582712852055467</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>7.058</v>
+        <v>31.734</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>6.953999999999999</v>
+        <v>31.077</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>1.495542134023609</v>
+        <v>2.11410367796121</v>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>1.813002451483925</v>
+        <v>2.172374963166757</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -3444,7 +3441,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3454,46 +3451,46 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>301182</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>天下秀</t>
+          <t>凯旺科技</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>4.68</v>
+        <v>43.21</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>5.06</v>
+        <v>50.56</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8.119658119658112</v>
+        <v>17.00995140013886</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>5.14</v>
+        <v>51.85</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>4.81</v>
+        <v>46.172</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>4.857</v>
+        <v>46.638</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>-0.9676755198682274</v>
+        <v>-0.9991852137741675</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>4.895999999999999</v>
+        <v>47.264</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>4.867</v>
+        <v>46.95</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>0.5958495993424906</v>
+        <v>0.6687965921192696</v>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>1.563525119210718</v>
+        <v>1.667981805893437</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -3509,7 +3506,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3519,46 +3516,46 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>603444</t>
+          <t>688697</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>吉比特</t>
+          <t>纽威数控</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>328.69</v>
+        <v>11.76</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>358.12</v>
+        <v>13.78</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8.953725394748858</v>
+        <v>17.17687074829932</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>361.55</v>
+        <v>14.11</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>332.52</v>
+        <v>12.474</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>334.83</v>
+        <v>12.548</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>-0.6899023385001368</v>
+        <v>-0.5897354160025459</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>339.542</v>
+        <v>12.832</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>336.813</v>
+        <v>12.656</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>0.8102418849628812</v>
+        <v>1.390644753476589</v>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>1.500144223463018</v>
+        <v>1.980380169479135</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -3574,56 +3571,59 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>300182</t>
+          <t>600380</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>捷成股份</t>
+          <t>健康元</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>5.33</v>
+        <v>9.85</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>5.9</v>
+        <v>10.03</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>10.69418386491559</v>
+        <v>1.827411167512683</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>6.39</v>
+        <v>10.83</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>5.526000000000001</v>
+        <v>9.582000000000001</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>5.555000000000001</v>
+        <v>9.684000000000001</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-0.5220522052205245</v>
+        <v>-1.053283767038415</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>5.648</v>
+        <v>9.763999999999999</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>5.58</v>
+        <v>9.685</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>1.218637992831528</v>
+        <v>0.8156943727413379</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>1.740690198052053</v>
+        <v>1.868978139779753</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -3639,56 +3639,59 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>300364</t>
+          <t>300006</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>23.45</v>
+        <v>8.27</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>26.59</v>
+        <v>9.58</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13.39019189765458</v>
+        <v>15.8403869407497</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>28.14</v>
+        <v>9.92</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>24.172</v>
+        <v>8.528</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>24.289</v>
+        <v>8.674000000000001</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>-0.4816995347688091</v>
+        <v>-1.683191145953433</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>24.904</v>
+        <v>8.82</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>24.422</v>
+        <v>8.818999999999999</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>1.973630333306042</v>
+        <v>0.01133915409912145</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>2.455329868074851</v>
+        <v>1.694530300052555</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -3704,7 +3707,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3714,46 +3717,46 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>300063</t>
+          <t>002950</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>天龙集团</t>
+          <t>奥美医疗</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>7.93</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>9.01</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>13.61916771752838</v>
+        <v>7.785888077858871</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>9.51</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>8.251999999999999</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>8.348000000000001</v>
+        <v>8.372</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>-1.149976042165812</v>
+        <v>-0.3344481605351279</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>8.484</v>
+        <v>8.504</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>8.375</v>
+        <v>8.406000000000001</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>1.301492537313442</v>
+        <v>1.165833928146554</v>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>2.451468579479255</v>
+        <v>1.500282088681681</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -3769,7 +3772,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3779,46 +3782,46 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>301262</t>
+          <t>301408</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>海看股份</t>
+          <t>华人健康</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>20.35</v>
+        <v>13.78</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>23.36</v>
+        <v>14.88</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>14.79115479115478</v>
+        <v>7.982583454281578</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>24.42</v>
+        <v>16.53</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>20.914</v>
+        <v>13.936</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>21.211</v>
+        <v>13.95</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>-1.400216868605919</v>
+        <v>-0.100358422939073</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>21.638</v>
+        <v>14.236</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>21.336</v>
+        <v>14.039</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>1.415448068991365</v>
+        <v>1.403233848564733</v>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>2.815664937597284</v>
+        <v>1.503592271503806</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -3834,7 +3837,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3844,46 +3847,46 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>300702</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>线上线下</t>
+          <t>天宇股份</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>68.5</v>
+        <v>20.01</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>79.03</v>
+        <v>21.77</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15.37226277372263</v>
+        <v>8.795602198900543</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>82.2</v>
+        <v>24.01</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>72.27799999999999</v>
+        <v>20.394</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>73.40299999999999</v>
+        <v>20.548</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>-1.532634905930275</v>
+        <v>-0.749464668094213</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>74.042</v>
+        <v>20.792</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>73.756</v>
+        <v>20.632</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>0.3877650631813001</v>
+        <v>0.7754943776657752</v>
       </c>
       <c r="Q53" s="5" t="n">
-        <v>1.920399969111575</v>
+        <v>1.524959045759988</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -3899,7 +3902,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3909,46 +3912,46 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>300785</t>
+          <t>603259</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>值得买</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>32.47</v>
+        <v>141.48</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>37.95</v>
+        <v>154.19</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>16.87711733908224</v>
+        <v>8.983601922533225</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>38.96</v>
+        <v>155.62</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>34.376</v>
+        <v>145.54</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>34.82600000000001</v>
+        <v>146.801</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>-1.292138057772951</v>
+        <v>-0.8589859742099804</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>35.33</v>
+        <v>148.116</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>35.05500000000001</v>
+        <v>146.77</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.7844815290257934</v>
+        <v>0.9170811473734553</v>
       </c>
       <c r="Q54" s="5" t="n">
-        <v>2.076619586798745</v>
+        <v>1.776067121583436</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -3964,7 +3967,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3974,46 +3977,46 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>301171</t>
+          <t>688710</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>易点天下</t>
+          <t>益诺思</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>28.9</v>
+        <v>83.36</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>33.87</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17.19723183391002</v>
+        <v>9.812859884836866</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>34.68</v>
+        <v>100.03</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>30.872</v>
+        <v>83.75</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>30.89</v>
+        <v>84.50099999999999</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>-0.0582712852055467</v>
+        <v>-0.8887468787351471</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>31.734</v>
+        <v>85.82000000000001</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>31.077</v>
+        <v>84.71000000000001</v>
       </c>
       <c r="P55" s="4" t="n">
-        <v>2.11410367796121</v>
+        <v>1.310352968952899</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>2.172374963166757</v>
+        <v>2.199099847688046</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -4029,7 +4032,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4039,46 +4042,46 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>301182</t>
+          <t>300363</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>凯旺科技</t>
+          <t>博腾股份</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>43.21</v>
+        <v>20.93</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>50.56</v>
+        <v>23.15</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>17.00995140013886</v>
+        <v>10.60678451982799</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>51.85</v>
+        <v>25.11</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>46.172</v>
+        <v>21.43</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>46.638</v>
+        <v>21.526</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>-0.9991852137741675</v>
+        <v>-0.4459723125522785</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>47.264</v>
+        <v>21.876</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>46.95</v>
+        <v>21.647</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.6687965921192696</v>
+        <v>1.057883309465502</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>1.667981805893437</v>
+        <v>1.50385562201778</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -4094,7 +4097,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4104,46 +4107,46 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>688697</t>
+          <t>300255</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>纽威数控</t>
+          <t>常山药业</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>11.76</v>
+        <v>18.73</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>13.78</v>
+        <v>20.9</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>17.17687074829932</v>
+        <v>11.58569140416443</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>14.11</v>
+        <v>22.47</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>12.474</v>
+        <v>19.526</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>12.548</v>
+        <v>19.721</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>-0.5897354160025459</v>
+        <v>-0.9887936717204893</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12.832</v>
+        <v>19.884</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>12.656</v>
+        <v>19.782</v>
       </c>
       <c r="P57" s="4" t="n">
-        <v>1.390644753476589</v>
+        <v>0.515620260843197</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>1.980380169479135</v>
+        <v>1.504413932563686</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -4164,54 +4167,51 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>300006</t>
+          <t>300705</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>九典制药</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>8.27</v>
+        <v>10.33</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>9.58</v>
+        <v>11.54</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15.8403869407497</v>
+        <v>11.71345595353339</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>9.92</v>
+        <v>12.39</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>8.528</v>
+        <v>10.682</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>8.674000000000001</v>
+        <v>10.718</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>-1.683191145953433</v>
+        <v>-0.3358835603657573</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>8.82</v>
+        <v>10.926</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>8.818999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.01133915409912145</v>
+        <v>1.166666666666649</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>1.694530300052555</v>
+        <v>1.502550227032406</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -4237,46 +4237,46 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>002950</t>
+          <t>688607</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>奥美医疗</t>
+          <t>康众科技</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>8.220000000000001</v>
+        <v>31</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>34.67</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>7.785888077858871</v>
+        <v>11.83870967741936</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>9.039999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>8.343999999999999</v>
+        <v>32.822</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>8.372</v>
+        <v>33.042</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>-0.3344481605351279</v>
+        <v>-0.6658192603353319</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>8.504</v>
+        <v>33.384</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>8.406000000000001</v>
+        <v>33.10700000000001</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>1.165833928146554</v>
+        <v>0.8366810644274469</v>
       </c>
       <c r="Q59" s="5" t="n">
-        <v>1.500282088681681</v>
+        <v>1.502500324762779</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -4302,46 +4302,46 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>301408</t>
+          <t>300434</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>华人健康</t>
+          <t>金石亚药</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>13.78</v>
+        <v>11.31</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>14.88</v>
+        <v>12.66</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>7.982583454281578</v>
+        <v>11.93633952254642</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>16.53</v>
+        <v>13.57</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>13.936</v>
+        <v>12.044</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>13.95</v>
+        <v>12.294</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>-0.100358422939073</v>
+        <v>-2.033512282414185</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>14.236</v>
+        <v>12.242</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>14.039</v>
+        <v>12.24</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>1.403233848564733</v>
+        <v>0.01633986928104569</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>1.503592271503806</v>
+        <v>2.049852151695231</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -4367,46 +4367,46 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>300702</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>天宇股份</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>20.01</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>21.77</v>
+        <v>10.34</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8.795602198900543</v>
+        <v>12.14750542299348</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>24.01</v>
+        <v>11.06</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>20.394</v>
+        <v>9.634</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>20.548</v>
+        <v>9.775000000000002</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>-0.749464668094213</v>
+        <v>-1.442455242966767</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>20.792</v>
+        <v>9.818000000000001</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>20.632</v>
+        <v>9.792000000000002</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>0.7754943776657752</v>
+        <v>0.2655228758169814</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>1.524959045759988</v>
+        <v>1.707978118783748</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -4432,46 +4432,46 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>603259</t>
+          <t>301333</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>141.48</v>
+        <v>51.85</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>154.19</v>
+        <v>58.46</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>8.983601922533225</v>
+        <v>12.74831243972998</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>155.62</v>
+        <v>62.22</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>145.54</v>
+        <v>53.51000000000001</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>146.801</v>
+        <v>54.26900000000001</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>-0.8589859742099804</v>
+        <v>-1.398588512778931</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>148.116</v>
+        <v>54.876</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>146.77</v>
+        <v>54.463</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.9170811473734553</v>
+        <v>0.7583129831261637</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>1.776067121583436</v>
+        <v>2.156901495905095</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -4497,46 +4497,46 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>600479</t>
+          <t>300246</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>XD千金药</t>
+          <t>宝莱特</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>10.46</v>
+        <v>12.22</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>11.42</v>
+        <v>13.85</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9.17782026768641</v>
+        <v>13.33878887070377</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>11.5</v>
+        <v>14.66</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>10.754</v>
+        <v>12.864</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>10.879</v>
+        <v>12.941</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>-1.149002665686183</v>
+        <v>-0.5950081137470087</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>10.928</v>
+        <v>13.106</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>10.889</v>
+        <v>12.988</v>
       </c>
       <c r="P63" s="4" t="n">
-        <v>0.3581596106162044</v>
+        <v>0.9085309516476681</v>
       </c>
       <c r="Q63" s="5" t="n">
-        <v>1.507162276302387</v>
+        <v>1.503539065394677</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -4562,46 +4562,46 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>688710</t>
+          <t>300109</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>益诺思</t>
+          <t>新开源</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>83.36</v>
+        <v>10.77</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>91.54000000000001</v>
+        <v>12.33</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>9.812859884836866</v>
+        <v>14.48467966573816</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>100.03</v>
+        <v>12.92</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>83.75</v>
+        <v>11.36</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>84.50099999999999</v>
+        <v>11.514</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>-0.8887468787351471</v>
+        <v>-1.337502171269755</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>85.82000000000001</v>
+        <v>11.602</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>84.71000000000001</v>
+        <v>11.577</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>1.310352968952899</v>
+        <v>0.2159454090005841</v>
       </c>
       <c r="Q64" s="5" t="n">
-        <v>2.199099847688046</v>
+        <v>1.55344758027034</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -4627,46 +4627,46 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>300363</t>
+          <t>300347</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>博腾股份</t>
+          <t>泰格医药</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>20.93</v>
+        <v>47.82</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>23.15</v>
+        <v>54.89</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>10.60678451982799</v>
+        <v>14.78460895023004</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>25.11</v>
+        <v>57.38</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>21.43</v>
+        <v>50.25599999999999</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>21.526</v>
+        <v>50.69799999999999</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>-0.4459723125522785</v>
+        <v>-0.8718292634817937</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>21.876</v>
+        <v>51.302</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>21.647</v>
+        <v>50.98099999999999</v>
       </c>
       <c r="P65" s="4" t="n">
-        <v>1.057883309465502</v>
+        <v>0.6296463388321349</v>
       </c>
       <c r="Q65" s="5" t="n">
-        <v>1.50385562201778</v>
+        <v>1.501475602313929</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -4692,46 +4692,46 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>300255</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>常山药业</t>
+          <t>一品红</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>18.73</v>
+        <v>28.77</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>20.9</v>
+        <v>33.08</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11.58569140416443</v>
+        <v>14.98088286409454</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>22.47</v>
+        <v>34.52</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>19.526</v>
+        <v>30.38</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19.721</v>
+        <v>30.584</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>-0.9887936717204893</v>
+        <v>-0.6670154329060929</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>19.884</v>
+        <v>31.088</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>19.782</v>
+        <v>30.831</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0.515620260843197</v>
+        <v>0.8335765949855745</v>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>1.504413932563686</v>
+        <v>1.500592027891667</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -4757,46 +4757,46 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>300705</t>
+          <t>300683</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>九典制药</t>
+          <t>海特生物</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>10.33</v>
+        <v>21.76</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>11.54</v>
+        <v>25.03</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11.71345595353339</v>
+        <v>15.02757352941175</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>12.39</v>
+        <v>26.11</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>10.682</v>
+        <v>23.268</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>10.718</v>
+        <v>23.612</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>-0.3358835603657573</v>
+        <v>-1.456886328985241</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>10.926</v>
+        <v>23.674</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>10.8</v>
+        <v>23.663</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>1.166666666666649</v>
+        <v>0.0464860753074392</v>
       </c>
       <c r="Q67" s="5" t="n">
-        <v>1.502550227032406</v>
+        <v>1.50337240429268</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -4822,46 +4822,46 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>688607</t>
+          <t>300725</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>康众科技</t>
+          <t>药石科技</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>31</v>
+        <v>41.36</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>34.67</v>
+        <v>47.86</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11.83870967741936</v>
+        <v>15.71566731141198</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>37.2</v>
+        <v>49.63</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>32.822</v>
+        <v>44.188</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>33.042</v>
+        <v>44.511</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>-0.6658192603353319</v>
+        <v>-0.7256633191795259</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>33.384</v>
+        <v>45.09999999999999</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>33.10700000000001</v>
+        <v>44.753</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0.8366810644274469</v>
+        <v>0.7753670145018043</v>
       </c>
       <c r="Q68" s="5" t="n">
-        <v>1.502500324762779</v>
+        <v>1.50103033368133</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -4887,46 +4887,46 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>300434</t>
+          <t>301257</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>金石亚药</t>
+          <t>普蕊斯</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>11.31</v>
+        <v>31.5</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>12.66</v>
+        <v>36.68</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>11.93633952254642</v>
+        <v>16.44444444444444</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>13.57</v>
+        <v>37.8</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>12.044</v>
+        <v>33.264</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>12.294</v>
+        <v>33.722</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>-2.033512282414185</v>
+        <v>-1.358163809975699</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>12.242</v>
+        <v>34.134</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>12.24</v>
+        <v>33.854</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>0.01633986928104569</v>
+        <v>0.8270809948602853</v>
       </c>
       <c r="Q69" s="5" t="n">
-        <v>2.049852151695231</v>
+        <v>2.185244804835984</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -4952,46 +4952,46 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>华兰股份</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>9.220000000000001</v>
+        <v>47.68</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>10.34</v>
+        <v>55.64</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>12.14750542299348</v>
+        <v>16.69463087248322</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>11.06</v>
+        <v>57.21</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>9.634</v>
+        <v>50.5</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>9.775000000000002</v>
+        <v>51.384</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>-1.442455242966767</v>
+        <v>-1.720379884789036</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>9.818000000000001</v>
+        <v>51.824</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>9.792000000000002</v>
+        <v>51.822</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.2655228758169814</v>
+        <v>0.003859364748559635</v>
       </c>
       <c r="Q70" s="5" t="n">
-        <v>1.707978118783748</v>
+        <v>1.724239249537596</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -5017,46 +5017,46 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>301333</t>
+          <t>301201</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>诺思格</t>
+          <t>诚达药业</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>51.85</v>
+        <v>24.01</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>58.46</v>
+        <v>28.02</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12.74831243972998</v>
+        <v>16.70137442732194</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>62.22</v>
+        <v>28.81</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>53.51000000000001</v>
+        <v>25.546</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>54.26900000000001</v>
+        <v>25.963</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>-1.398588512778931</v>
+        <v>-1.606131802950361</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>54.876</v>
+        <v>26.066</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>54.463</v>
+        <v>26.065</v>
       </c>
       <c r="P71" s="4" t="n">
-        <v>0.7583129831261637</v>
+        <v>0.003836562440051594</v>
       </c>
       <c r="Q71" s="5" t="n">
-        <v>2.156901495905095</v>
+        <v>1.609968365390413</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -5082,46 +5082,46 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>300246</t>
+          <t>920047</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>宝莱特</t>
+          <t>诺思兰德</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>12.22</v>
+        <v>12.62</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>13.85</v>
+        <v>14.75</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13.33878887070377</v>
+        <v>16.87797147385104</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>14.66</v>
+        <v>15.14</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>12.864</v>
+        <v>13.434</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>12.941</v>
+        <v>13.55</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>-0.5950081137470087</v>
+        <v>-0.8560885608856372</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>13.106</v>
+        <v>13.722</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>12.988</v>
+        <v>13.634</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.9085309516476681</v>
+        <v>0.6454452105031372</v>
       </c>
       <c r="Q72" s="5" t="n">
-        <v>1.503539065394677</v>
+        <v>1.501533771388774</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -5147,46 +5147,46 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>300109</t>
+          <t>300204</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>新开源</t>
+          <t>舒泰神</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>10.77</v>
+        <v>16.91</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>12.33</v>
+        <v>19.8</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14.48467966573816</v>
+        <v>17.09047900650502</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>12.92</v>
+        <v>20.29</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>11.36</v>
+        <v>17.97</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>11.514</v>
+        <v>18.211</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>-1.337502171269755</v>
+        <v>-1.323375981549613</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>11.602</v>
+        <v>18.47</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>11.577</v>
+        <v>18.264</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>0.2159454090005841</v>
+        <v>1.127901883486615</v>
       </c>
       <c r="Q73" s="5" t="n">
-        <v>1.55344758027034</v>
+        <v>2.451277865036228</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -5212,46 +5212,46 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>300347</t>
+          <t>300534</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>泰格医药</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>47.82</v>
+        <v>9.68</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>54.89</v>
+        <v>11.41</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14.78460895023004</v>
+        <v>17.8719008264463</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>57.38</v>
+        <v>11.61</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>50.25599999999999</v>
+        <v>10.302</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>50.69799999999999</v>
+        <v>10.524</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>-0.8718292634817937</v>
+        <v>-2.109464082098089</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>51.302</v>
+        <v>10.564</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>50.98099999999999</v>
+        <v>10.562</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.6296463388321349</v>
+        <v>0.01893580761218594</v>
       </c>
       <c r="Q74" s="5" t="n">
-        <v>1.501475602313929</v>
+        <v>2.128399889710275</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -5277,46 +5277,46 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>300723</t>
+          <t>300436</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>一品红</t>
+          <t>广生堂</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>28.77</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>33.08</v>
+        <v>83.91</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14.98088286409454</v>
+        <v>18.34978843441466</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>34.52</v>
+        <v>85.08</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>30.38</v>
+        <v>76.474</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>30.584</v>
+        <v>77.93899999999999</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>-0.6670154329060929</v>
+        <v>-1.879675130550806</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31.088</v>
+        <v>78.164</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>30.831</v>
+        <v>78.16199999999999</v>
       </c>
       <c r="P75" s="4" t="n">
-        <v>0.8335765949855745</v>
+        <v>0.002558788157935865</v>
       </c>
       <c r="Q75" s="5" t="n">
-        <v>1.500592027891667</v>
+        <v>1.882233918708742</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -5342,46 +5342,46 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>300683</t>
+          <t>301234</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>海特生物</t>
+          <t>五洲医疗</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>21.76</v>
+        <v>125.7</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>25.03</v>
+        <v>149.04</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15.02757352941175</v>
+        <v>18.56801909307875</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>26.11</v>
+        <v>150.84</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>23.268</v>
+        <v>130.836</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>23.612</v>
+        <v>131.754</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>-1.456886328985241</v>
+        <v>-0.6967530397559152</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>23.674</v>
+        <v>134.844</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>23.663</v>
+        <v>132.851</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.0464860753074392</v>
+        <v>1.50017688989923</v>
       </c>
       <c r="Q76" s="5" t="n">
-        <v>1.50337240429268</v>
+        <v>2.196929929655145</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -5407,46 +5407,46 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>300725</t>
+          <t>920367</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>药石科技</t>
+          <t>新赣江</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>41.36</v>
+        <v>19.95</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>47.86</v>
+        <v>23.8</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>15.71566731141198</v>
+        <v>19.2982456140351</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>49.63</v>
+        <v>23.94</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>44.188</v>
+        <v>21.502</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>44.511</v>
+        <v>21.968</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>-0.7256633191795259</v>
+        <v>-2.12126729788783</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>45.09999999999999</v>
+        <v>22.098</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>44.753</v>
+        <v>21.968</v>
       </c>
       <c r="P77" s="4" t="n">
-        <v>0.7753670145018043</v>
+        <v>0.5917698470502719</v>
       </c>
       <c r="Q77" s="5" t="n">
-        <v>1.50103033368133</v>
+        <v>2.713037144938102</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -5462,56 +5462,59 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>301257</t>
+          <t>601211</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>普蕊斯</t>
+          <t>国泰海通</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>31.5</v>
+        <v>16.27</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>36.68</v>
+        <v>17.35</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16.44444444444444</v>
+        <v>6.637984019668108</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>37.8</v>
+        <v>17.89</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>33.264</v>
+        <v>16.44</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>33.722</v>
+        <v>16.454</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-1.358163809975699</v>
+        <v>-0.08508569344841677</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>34.134</v>
+        <v>16.728</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>33.854</v>
+        <v>16.494</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.8270809948602853</v>
+        <v>1.418697708257555</v>
       </c>
       <c r="Q78" s="5" t="n">
-        <v>2.185244804835984</v>
+        <v>1.503783401705971</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -5527,56 +5530,59 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>3</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>600621</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>华兰股份</t>
+          <t>华鑫股份</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>47.68</v>
+        <v>14.9</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>55.64</v>
+        <v>15.91</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>16.69463087248322</v>
+        <v>6.778523489932886</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>57.21</v>
+        <v>16.39</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>50.5</v>
+        <v>14.66</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>51.384</v>
+        <v>14.77</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>-1.720379884789036</v>
+        <v>-0.7447528774542911</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>51.824</v>
+        <v>14.996</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>51.822</v>
+        <v>14.883</v>
       </c>
       <c r="P79" s="4" t="n">
-        <v>0.003859364748559635</v>
+        <v>0.7592555264395617</v>
       </c>
       <c r="Q79" s="5" t="n">
-        <v>1.724239249537596</v>
+        <v>1.504008403893853</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -5592,7 +5598,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5602,46 +5608,46 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>601519</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>诚达药业</t>
+          <t>大智慧</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>24.01</v>
+        <v>8.76</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>28.02</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>16.70137442732194</v>
+        <v>7.191780821917826</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>28.81</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>25.546</v>
+        <v>9.022</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>25.963</v>
+        <v>9.144000000000002</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>-1.606131802950361</v>
+        <v>-1.334208223972022</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>26.066</v>
+        <v>9.218</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>26.065</v>
+        <v>9.118</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.003836562440051594</v>
+        <v>1.096731739416534</v>
       </c>
       <c r="Q80" s="5" t="n">
-        <v>1.609968365390413</v>
+        <v>2.430939963388556</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -5657,7 +5663,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5667,46 +5673,46 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>920047</t>
+          <t>600958</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>诺思兰德</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>12.62</v>
+        <v>8.48</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>14.75</v>
+        <v>9.15</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>16.87797147385104</v>
+        <v>7.900943396226423</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>15.14</v>
+        <v>9.32</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>13.434</v>
+        <v>8.586</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>13.55</v>
+        <v>8.595000000000002</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>-0.8560885608856372</v>
+        <v>-0.1047120418848468</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>13.722</v>
+        <v>8.75</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>13.634</v>
+        <v>8.629</v>
       </c>
       <c r="P81" s="4" t="n">
-        <v>0.6454452105031372</v>
+        <v>1.402248232703673</v>
       </c>
       <c r="Q81" s="5" t="n">
-        <v>1.501533771388774</v>
+        <v>1.50696027458852</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -5722,7 +5728,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5732,46 +5738,46 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>300204</t>
+          <t>601377</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>舒泰神</t>
+          <t>兴业证券</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>16.91</v>
+        <v>5.52</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>19.8</v>
+        <v>6</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>17.09047900650502</v>
+        <v>8.695652173913061</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>20.29</v>
+        <v>6.07</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>17.97</v>
+        <v>5.613999999999999</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>18.211</v>
+        <v>5.625999999999999</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>-1.323375981549613</v>
+        <v>-0.2132954141486065</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>18.47</v>
+        <v>5.726</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>18.264</v>
+        <v>5.653</v>
       </c>
       <c r="P82" s="4" t="n">
-        <v>1.127901883486615</v>
+        <v>1.291349725809288</v>
       </c>
       <c r="Q82" s="5" t="n">
-        <v>2.451277865036228</v>
+        <v>1.504645139957894</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -5787,7 +5793,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5797,46 +5803,46 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>300534</t>
+          <t>002736</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>国信证券</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>9.68</v>
+        <v>9.66</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>11.41</v>
+        <v>10.52</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17.8719008264463</v>
+        <v>8.902691511387161</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>11.61</v>
+        <v>10.62</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>10.302</v>
+        <v>9.806000000000001</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>10.524</v>
+        <v>9.812999999999999</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>-2.109464082098089</v>
+        <v>-0.07133394476712684</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>10.564</v>
+        <v>10.008</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>10.562</v>
+        <v>9.866999999999999</v>
       </c>
       <c r="P83" s="4" t="n">
-        <v>0.01893580761218594</v>
+        <v>1.429005776831871</v>
       </c>
       <c r="Q83" s="5" t="n">
-        <v>2.128399889710275</v>
+        <v>1.500339721598998</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -5852,7 +5858,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5862,46 +5868,46 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>300436</t>
+          <t>601136</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>广生堂</t>
+          <t>首创证券</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>13.49</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>83.91</v>
+        <v>14.78</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>18.34978843441466</v>
+        <v>9.562638991845795</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>85.08</v>
+        <v>14.83</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>76.474</v>
+        <v>13.94</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>77.93899999999999</v>
+        <v>14.029</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>-1.879675130550806</v>
+        <v>-0.6344001710741898</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>78.164</v>
+        <v>14.184</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>78.16199999999999</v>
+        <v>14.062</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>0.002558788157935865</v>
+        <v>0.8675864030721181</v>
       </c>
       <c r="Q84" s="5" t="n">
-        <v>1.882233918708742</v>
+        <v>1.501986574146308</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -5917,7 +5923,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5927,46 +5933,46 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>301234</t>
+          <t>688318</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>五洲医疗</t>
+          <t>财富趋势</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>125.7</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>149.04</v>
+        <v>77.61</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>18.56801909307875</v>
+        <v>10.88726960994428</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>150.84</v>
+        <v>83.98</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>130.836</v>
+        <v>73.66400000000002</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>131.754</v>
+        <v>73.70700000000001</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>-0.6967530397559152</v>
+        <v>-0.05833909940710091</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>134.844</v>
+        <v>75.06800000000001</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>132.851</v>
+        <v>74.001</v>
       </c>
       <c r="P85" s="4" t="n">
-        <v>1.50017688989923</v>
+        <v>1.441872407129652</v>
       </c>
       <c r="Q85" s="5" t="n">
-        <v>2.196929929655145</v>
+        <v>1.500211506536753</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -5982,7 +5988,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5992,46 +5998,46 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>920367</t>
+          <t>300803</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>新赣江</t>
+          <t>指南针</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>19.95</v>
+        <v>48.38</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>23.8</v>
+        <v>55.17</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>19.2982456140351</v>
+        <v>14.03472509301364</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>23.94</v>
+        <v>58.05</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>21.502</v>
+        <v>51.812</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>21.968</v>
+        <v>52.057</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>-2.12126729788783</v>
+        <v>-0.4706379545498129</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>22.098</v>
+        <v>52.79600000000001</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>21.968</v>
+        <v>52.258</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>0.5917698470502719</v>
+        <v>1.029507443836364</v>
       </c>
       <c r="Q86" s="5" t="n">
-        <v>2.713037144938102</v>
+        <v>1.500145398386177</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -6047,7 +6053,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6057,46 +6063,46 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>300085</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>XD奥浦迈</t>
+          <t>银之杰</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>54.08</v>
+        <v>24.89</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>64.65000000000001</v>
+        <v>28.83</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>19.54511834319528</v>
+        <v>15.82965046203293</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>64.89</v>
+        <v>29.86</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>58.05799999999999</v>
+        <v>26.71</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>59.423</v>
+        <v>26.998</v>
       </c>
       <c r="M87" s="4" t="n">
-        <v>-2.297090352220532</v>
+        <v>-1.066745684865533</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>59.706</v>
+        <v>27.322</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>59.70399999999999</v>
+        <v>27.123</v>
       </c>
       <c r="P87" s="4" t="n">
-        <v>0.003349859305923353</v>
+        <v>0.7336946502968011</v>
       </c>
       <c r="Q87" s="5" t="n">
-        <v>2.300440211526456</v>
+        <v>1.800440335162334</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -6112,7 +6118,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>电网设备</t>
+          <t>黄金白银</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6122,46 +6128,46 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>300069</t>
+          <t>300945</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>金利华电</t>
+          <t>曼卡龙</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>21.06</v>
+        <v>10.02</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>23.99</v>
+        <v>11.52</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>13.91263057929724</v>
+        <v>14.97005988023952</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>25.27</v>
+        <v>12.02</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>21.766</v>
+        <v>10.506</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>22.147</v>
+        <v>10.536</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>-1.720323294351378</v>
+        <v>-0.2847380410022526</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>22.318</v>
+        <v>10.762</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>22.316</v>
+        <v>10.632</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>0.008962179602090004</v>
+        <v>1.222723852520691</v>
       </c>
       <c r="Q88" s="5" t="n">
-        <v>1.729285473953468</v>
+        <v>1.507461893522943</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -6187,46 +6193,46 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>301082</t>
+          <t>300069</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>久盛电气</t>
+          <t>金利华电</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>21.06</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>10.23</v>
+        <v>23.99</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>16.51480637813214</v>
+        <v>13.91263057929724</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>10.53</v>
+        <v>25.27</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>9.296000000000001</v>
+        <v>21.766</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>9.324000000000002</v>
+        <v>22.147</v>
       </c>
       <c r="M89" s="4" t="n">
-        <v>-0.3003003003003046</v>
+        <v>-1.720323294351378</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>9.526</v>
+        <v>22.318</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>9.413</v>
+        <v>22.316</v>
       </c>
       <c r="P89" s="4" t="n">
-        <v>1.200467438648678</v>
+        <v>0.008962179602090004</v>
       </c>
       <c r="Q89" s="5" t="n">
-        <v>1.500767738948983</v>
+        <v>1.729285473953468</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -6252,55 +6258,185 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>301082</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>久盛电气</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>16.51480637813214</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>9.296000000000001</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>9.324000000000002</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>-0.3003003003003046</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>9.526</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>9.413</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>1.200467438648678</v>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>1.500767738948983</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>300427</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>红相股份</t>
         </is>
       </c>
-      <c r="G90" s="3" t="n">
+      <c r="G91" s="3" t="n">
         <v>5.21</v>
       </c>
-      <c r="H90" s="3" t="n">
+      <c r="H91" s="3" t="n">
         <v>6.14</v>
       </c>
-      <c r="I90" s="4" t="n">
+      <c r="I91" s="4" t="n">
         <v>17.85028790786946</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="J91" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="K91" s="3" t="n">
         <v>5.538</v>
       </c>
-      <c r="L90" s="3" t="n">
+      <c r="L91" s="3" t="n">
         <v>5.588</v>
       </c>
-      <c r="M90" s="4" t="n">
+      <c r="M91" s="4" t="n">
         <v>-0.8947745168217613</v>
       </c>
-      <c r="N90" s="3" t="n">
+      <c r="N91" s="3" t="n">
         <v>5.678</v>
       </c>
-      <c r="O90" s="3" t="n">
+      <c r="O91" s="3" t="n">
         <v>5.643000000000001</v>
       </c>
-      <c r="P90" s="4" t="n">
+      <c r="P91" s="4" t="n">
         <v>0.6202374623427209</v>
       </c>
-      <c r="Q90" s="5" t="n">
+      <c r="Q91" s="5" t="n">
         <v>1.515011979164482</v>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>涨停内可达</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>商业航天</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>688323</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>瑞华泰</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>19.01639344262296</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>19.986</v>
+      </c>
+      <c r="M92" s="4" t="n">
+        <v>-0.7305113579505473</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>20.312</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>20.156</v>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v>0.7739630879142867</v>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <v>1.504474445864834</v>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R90"/>
+  <autoFilter ref="A2:R92"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$R$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$S$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,8 +77,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,27 +445,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10.2" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13.8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10.2" customWidth="1" min="7" max="7"/>
-    <col width="13.8" customWidth="1" min="8" max="8"/>
-    <col width="15.6" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10.2" customWidth="1" min="8" max="8"/>
+    <col width="13.8" customWidth="1" min="9" max="9"/>
+    <col width="15.6" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13.8" customWidth="1" min="12" max="12"/>
-    <col width="19.2" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="13.8" customWidth="1" min="15" max="15"/>
-    <col width="19.2" customWidth="1" min="16" max="16"/>
-    <col width="13.8" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13.8" customWidth="1" min="13" max="13"/>
+    <col width="19.2" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13.8" customWidth="1" min="16" max="16"/>
+    <col width="19.2" customWidth="1" min="17" max="17"/>
+    <col width="13.8" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -488,80 +489,85 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>分组多占比%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>进度</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>当前收盘</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>明日最低收盘</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>明日最低涨幅%</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>明日涨停价</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>明日MA5</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>明日MA10</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>明日5-10间距%</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>后天MA5</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>后天MA10</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>后天5-10间距%</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>间距增幅pp</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -578,55 +584,58 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>688308</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>欧科亿</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>59.41</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="3" t="n">
         <v>16.07473489311564</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>71.29000000000001</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>64.092</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="4" t="n">
         <v>64.788</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="3" t="n">
         <v>-1.074273013521021</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="O3" s="4" t="n">
         <v>65.364</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="P3" s="4" t="n">
         <v>65.086</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="Q3" s="3" t="n">
         <v>0.4271271855698755</v>
       </c>
-      <c r="Q3" s="5" t="n">
+      <c r="R3" s="5" t="n">
         <v>1.501400199090897</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -643,55 +652,58 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>300776</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>帝尔激光</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>79.31999999999999</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <v>92.8</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="3" t="n">
         <v>16.99445284921837</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <v>95.18000000000001</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>84.974</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="M4" s="4" t="n">
         <v>85.59400000000001</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="3" t="n">
         <v>-0.7243498376054425</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="O4" s="4" t="n">
         <v>86.774</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="P4" s="4" t="n">
         <v>86.10400000000001</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="Q4" s="3" t="n">
         <v>0.7781287745052268</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="R4" s="5" t="n">
         <v>1.502478612110669</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -708,55 +720,58 @@
           <t>PCB</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>688388</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>嘉元科技</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>21.41</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>25.46</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="J5" s="3" t="n">
         <v>18.91639420831388</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <v>25.69</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="L5" s="4" t="n">
         <v>22.902</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="M5" s="4" t="n">
         <v>23.614</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="3" t="n">
         <v>-3.015160498009672</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="O5" s="4" t="n">
         <v>23.562</v>
       </c>
-      <c r="O5" s="3" t="n">
+      <c r="P5" s="4" t="n">
         <v>23.56</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="Q5" s="3" t="n">
         <v>0.008488964346353711</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="R5" s="5" t="n">
         <v>3.023649462356026</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -773,55 +788,58 @@
           <t>CPO</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>301338</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>凯格精机</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>65.19</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="J6" s="3" t="n">
         <v>18.00889707010278</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="4" t="n">
         <v>78.22</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>70.116</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="M6" s="4" t="n">
         <v>71.02500000000001</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="3" t="n">
         <v>-1.279831045406554</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="O6" s="4" t="n">
         <v>71.69000000000001</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="P6" s="4" t="n">
         <v>71.53200000000001</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="Q6" s="3" t="n">
         <v>0.2208801655203319</v>
       </c>
-      <c r="Q6" s="5" t="n">
+      <c r="R6" s="5" t="n">
         <v>1.500711210926886</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -838,55 +856,58 @@
           <t>CPO</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>688628</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>优利德</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>65.3</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <v>77.08</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="3" t="n">
         <v>18.03981623277182</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <v>78.36</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>71.622</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="M7" s="4" t="n">
         <v>71.79900000000001</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="3" t="n">
         <v>-0.2465215392972175</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="O7" s="4" t="n">
         <v>73.21600000000001</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="P7" s="4" t="n">
         <v>72.22999999999999</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="Q7" s="3" t="n">
         <v>1.365083760210473</v>
       </c>
-      <c r="Q7" s="5" t="n">
+      <c r="R7" s="5" t="n">
         <v>1.61160529950769</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -903,55 +924,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>300632</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>光莆股份</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>13.92</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="J8" s="3" t="n">
         <v>14.94252873563218</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <v>16.7</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="L8" s="4" t="n">
         <v>14.676</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="M8" s="4" t="n">
         <v>14.823</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="3" t="n">
         <v>-0.991702084598256</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="O8" s="4" t="n">
         <v>14.984</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="P8" s="4" t="n">
         <v>14.908</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="Q8" s="3" t="n">
         <v>0.5097933995170445</v>
       </c>
-      <c r="Q8" s="5" t="n">
+      <c r="R8" s="5" t="n">
         <v>1.501495484115301</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -968,55 +992,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>300672</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>国科微</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>128.51</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="I9" s="4" t="n">
         <v>150.65</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="J9" s="3" t="n">
         <v>17.22823126604936</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="K9" s="4" t="n">
         <v>154.21</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="L9" s="4" t="n">
         <v>137.146</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="M9" s="4" t="n">
         <v>138.103</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="3" t="n">
         <v>-0.6929610508098927</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="O9" s="4" t="n">
         <v>140.342</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="P9" s="4" t="n">
         <v>139.218</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.8073668634802855</v>
       </c>
-      <c r="Q9" s="5" t="n">
+      <c r="R9" s="5" t="n">
         <v>1.500327914290178</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1033,55 +1060,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>688515</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>裕太微-U</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>100.5</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <v>118.36</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="J10" s="3" t="n">
         <v>17.77114427860695</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="4" t="n">
         <v>120.6</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>107.958</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="M10" s="4" t="n">
         <v>108.01</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="N10" s="3" t="n">
         <v>-0.04814369039902733</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="O10" s="4" t="n">
         <v>110.678</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="P10" s="4" t="n">
         <v>109.094</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="Q10" s="3" t="n">
         <v>1.451958861165581</v>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="R10" s="5" t="n">
         <v>1.500102551564608</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1098,55 +1128,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>300671</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>富满微</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>38.85</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>45.77</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="J11" s="3" t="n">
         <v>17.81209781209783</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="4" t="n">
         <v>46.62</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>41.904</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="M11" s="4" t="n">
         <v>42.463</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="3" t="n">
         <v>-1.316440194993285</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="O11" s="4" t="n">
         <v>42.79</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="P11" s="4" t="n">
         <v>42.684</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="Q11" s="3" t="n">
         <v>0.2483366132508547</v>
       </c>
-      <c r="Q11" s="5" t="n">
+      <c r="R11" s="5" t="n">
         <v>1.564776808244139</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1163,55 +1196,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>300042</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>朗科科技</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>27.55</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="J12" s="3" t="n">
         <v>18.69328493647913</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="4" t="n">
         <v>33.06</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>29.592</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="M12" s="4" t="n">
         <v>29.773</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="3" t="n">
         <v>-0.607933362442481</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="O12" s="4" t="n">
         <v>30.336</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="P12" s="4" t="n">
         <v>30.067</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="Q12" s="3" t="n">
         <v>0.894668573519164</v>
       </c>
-      <c r="Q12" s="5" t="n">
+      <c r="R12" s="5" t="n">
         <v>1.502601935961645</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1228,55 +1264,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>688416</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>恒烁股份</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>51.4</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="I13" s="4" t="n">
         <v>61.03</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="3" t="n">
         <v>18.73540856031128</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="K13" s="4" t="n">
         <v>61.68</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="L13" s="4" t="n">
         <v>55.61</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="M13" s="4" t="n">
         <v>56.00699999999999</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="N13" s="3" t="n">
         <v>-0.7088399664327505</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="O13" s="4" t="n">
         <v>56.98</v>
       </c>
-      <c r="O13" s="3" t="n">
+      <c r="P13" s="4" t="n">
         <v>56.532</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="Q13" s="3" t="n">
         <v>0.7924715205547272</v>
       </c>
-      <c r="Q13" s="5" t="n">
+      <c r="R13" s="5" t="n">
         <v>1.501311486987478</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1293,55 +1332,58 @@
           <t>半导体芯片</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>688141</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>杰华特</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>67.45</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="I14" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="J14" s="3" t="n">
         <v>19.64418087472202</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="4" t="n">
         <v>80.94</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="L14" s="4" t="n">
         <v>73.34</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="M14" s="4" t="n">
         <v>74.45099999999999</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="N14" s="3" t="n">
         <v>-1.492256652026147</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="O14" s="4" t="n">
         <v>75.048</v>
       </c>
-      <c r="O14" s="3" t="n">
+      <c r="P14" s="4" t="n">
         <v>74.98099999999999</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="Q14" s="3" t="n">
         <v>0.08935597017911689</v>
       </c>
-      <c r="Q14" s="5" t="n">
+      <c r="R14" s="5" t="n">
         <v>1.581612622205264</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1358,55 +1400,58 @@
           <t>半导体设备</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>301717</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>超纯应材</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <v>263.63</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="I15" s="4" t="n">
         <v>299.5</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="J15" s="3" t="n">
         <v>13.60619049425331</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="K15" s="4" t="n">
         <v>316.35</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="L15" s="4" t="n">
         <v>278.08</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="M15" s="4" t="n">
         <v>282.667</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="N15" s="3" t="n">
         <v>-1.622757520333107</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="O15" s="4" t="n">
         <v>283.302</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="P15" s="4" t="n">
         <v>282.917</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="Q15" s="3" t="n">
         <v>0.1360823138941702</v>
       </c>
-      <c r="Q15" s="5" t="n">
+      <c r="R15" s="5" t="n">
         <v>1.758839834227277</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1423,55 +1468,58 @@
           <t>半导体设备</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>688797</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>臻宝科技</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="I16" s="4" t="n">
         <v>220.88</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="J16" s="3" t="n">
         <v>19.39459459459458</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="L16" s="4" t="n">
         <v>199.554</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="M16" s="4" t="n">
         <v>200.066</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="N16" s="3" t="n">
         <v>-0.2559155478691899</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="O16" s="4" t="n">
         <v>204.524</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="P16" s="4" t="n">
         <v>202.01</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="Q16" s="3" t="n">
         <v>1.244492846888767</v>
       </c>
-      <c r="Q16" s="5" t="n">
+      <c r="R16" s="5" t="n">
         <v>1.500408394757957</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1488,55 +1536,58 @@
           <t>半导体设备</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>301611</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>珂玛科技</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <v>62.45</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="I17" s="4" t="n">
         <v>74.62</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="J17" s="3" t="n">
         <v>19.48759007205765</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="K17" s="4" t="n">
         <v>74.94</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="L17" s="4" t="n">
         <v>67.664</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="M17" s="4" t="n">
         <v>68.711</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="N17" s="3" t="n">
         <v>-1.523773486050262</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="O17" s="4" t="n">
         <v>69.11800000000001</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="P17" s="4" t="n">
         <v>69.11600000000001</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="Q17" s="3" t="n">
         <v>0.002893685977189975</v>
       </c>
-      <c r="Q17" s="5" t="n">
+      <c r="R17" s="5" t="n">
         <v>1.526667172027452</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1553,55 +1604,58 @@
           <t>半导体设备</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>688605</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>先锋精科</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="H18" s="4" t="n">
         <v>55.81</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="I18" s="4" t="n">
         <v>66.79000000000001</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="J18" s="3" t="n">
         <v>19.67389356746103</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="K18" s="4" t="n">
         <v>66.97</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="L18" s="4" t="n">
         <v>60.182</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="M18" s="4" t="n">
         <v>61.573</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="N18" s="3" t="n">
         <v>-2.25910707615351</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="O18" s="4" t="n">
         <v>61.818</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="P18" s="4" t="n">
         <v>61.816</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="Q18" s="3" t="n">
         <v>0.003235408308555066</v>
       </c>
-      <c r="Q18" s="5" t="n">
+      <c r="R18" s="5" t="n">
         <v>2.262342484462065</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1618,55 +1672,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>003026</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>中晶科技</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="4" t="n">
         <v>27.83</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="4" t="n">
         <v>29.67</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="J19" s="3" t="n">
         <v>6.611570247933907</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="4" t="n">
         <v>30.61</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="L19" s="4" t="n">
         <v>27.57</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="M19" s="4" t="n">
         <v>27.731</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="N19" s="3" t="n">
         <v>-0.5805776928347273</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="O19" s="4" t="n">
         <v>28.148</v>
       </c>
-      <c r="O19" s="3" t="n">
+      <c r="P19" s="4" t="n">
         <v>27.891</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="Q19" s="3" t="n">
         <v>0.9214441934674467</v>
       </c>
-      <c r="Q19" s="5" t="n">
+      <c r="R19" s="5" t="n">
         <v>1.502021886302174</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1683,55 +1740,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>688268</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>华特气体</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="H20" s="4" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="I20" s="4" t="n">
         <v>112.39</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="J20" s="3" t="n">
         <v>13.41069626639759</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="K20" s="4" t="n">
         <v>118.92</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="L20" s="4" t="n">
         <v>103.382</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="M20" s="4" t="n">
         <v>105.176</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="N20" s="3" t="n">
         <v>-1.705712329809095</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="O20" s="4" t="n">
         <v>105.626</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="P20" s="4" t="n">
         <v>105.624</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="Q20" s="3" t="n">
         <v>0.001893509050976405</v>
       </c>
-      <c r="Q20" s="5" t="n">
+      <c r="R20" s="5" t="n">
         <v>1.707605838860071</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1748,55 +1808,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>300540</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>蜀道装备</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="H21" s="4" t="n">
         <v>20.65</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="I21" s="4" t="n">
         <v>23.96</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="J21" s="3" t="n">
         <v>16.02905569007265</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="K21" s="4" t="n">
         <v>24.78</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="L21" s="4" t="n">
         <v>21.898</v>
       </c>
-      <c r="L21" s="3" t="n">
+      <c r="M21" s="4" t="n">
         <v>22.063</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="N21" s="3" t="n">
         <v>-0.7478584054752102</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="O21" s="4" t="n">
         <v>22.424</v>
       </c>
-      <c r="O21" s="3" t="n">
+      <c r="P21" s="4" t="n">
         <v>22.256</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="Q21" s="3" t="n">
         <v>0.7548526240114928</v>
       </c>
-      <c r="Q21" s="5" t="n">
+      <c r="R21" s="5" t="n">
         <v>1.502711029486703</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1813,55 +1876,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>688138</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>清溢光电</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="H22" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="I22" s="4" t="n">
         <v>30.19</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="J22" s="3" t="n">
         <v>16.11538461538462</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="K22" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="L22" s="4" t="n">
         <v>27.528</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="M22" s="4" t="n">
         <v>27.97</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="N22" s="3" t="n">
         <v>-1.580264569181256</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="O22" s="4" t="n">
         <v>28.154</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="P22" s="4" t="n">
         <v>28.153</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="Q22" s="3" t="n">
         <v>0.003552019323005418</v>
       </c>
-      <c r="Q22" s="5" t="n">
+      <c r="R22" s="5" t="n">
         <v>1.583816588504261</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1878,55 +1944,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>300821</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>东岳硅材</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="H23" s="4" t="n">
         <v>15.55</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="I23" s="4" t="n">
         <v>18.11</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="J23" s="3" t="n">
         <v>16.46302250803857</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="K23" s="4" t="n">
         <v>18.66</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="L23" s="4" t="n">
         <v>16.496</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="M23" s="4" t="n">
         <v>17.006</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="N23" s="3" t="n">
         <v>-2.998941550041145</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="O23" s="4" t="n">
         <v>16.986</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="P23" s="4" t="n">
         <v>16.985</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="Q23" s="3" t="n">
         <v>0.005887547836302964</v>
       </c>
-      <c r="Q23" s="5" t="n">
+      <c r="R23" s="5" t="n">
         <v>3.004829097877448</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1943,55 +2012,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>688733</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>壹石通</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="H24" s="4" t="n">
         <v>21.41</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="I24" s="4" t="n">
         <v>25.07</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="J24" s="3" t="n">
         <v>17.09481550677254</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="K24" s="4" t="n">
         <v>25.69</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="L24" s="4" t="n">
         <v>22.986</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="M24" s="4" t="n">
         <v>23.195</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="N24" s="3" t="n">
         <v>-0.9010562621254548</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="O24" s="4" t="n">
         <v>23.484</v>
       </c>
-      <c r="O24" s="3" t="n">
+      <c r="P24" s="4" t="n">
         <v>23.344</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="Q24" s="3" t="n">
         <v>0.5997258396161831</v>
       </c>
-      <c r="Q24" s="5" t="n">
+      <c r="R24" s="5" t="n">
         <v>1.500782101741638</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2008,55 +2080,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>688106</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>金宏气体</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="H25" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="I25" s="4" t="n">
         <v>22.64</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="J25" s="3" t="n">
         <v>17.42738589211619</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="K25" s="4" t="n">
         <v>23.13</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="L25" s="4" t="n">
         <v>20.436</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="M25" s="4" t="n">
         <v>20.839</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="N25" s="3" t="n">
         <v>-1.933873986275725</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="O25" s="4" t="n">
         <v>20.96</v>
       </c>
-      <c r="O25" s="3" t="n">
+      <c r="P25" s="4" t="n">
         <v>20.919</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="Q25" s="3" t="n">
         <v>0.1959940723744058</v>
       </c>
-      <c r="Q25" s="5" t="n">
+      <c r="R25" s="5" t="n">
         <v>2.129868058650131</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2073,55 +2148,58 @@
           <t>半导体上游</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>688233</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>神工股份</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="H26" s="4" t="n">
         <v>61.55</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="I26" s="4" t="n">
         <v>73.51000000000001</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="J26" s="3" t="n">
         <v>19.43135662063364</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="K26" s="4" t="n">
         <v>73.86</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="L26" s="4" t="n">
         <v>66.926</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="M26" s="4" t="n">
         <v>67.899</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="N26" s="3" t="n">
         <v>-1.433010795446177</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="O26" s="4" t="n">
         <v>68.548</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="P26" s="4" t="n">
         <v>68.34999999999999</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="Q26" s="3" t="n">
         <v>0.289685442574994</v>
       </c>
-      <c r="Q26" s="5" t="n">
+      <c r="R26" s="5" t="n">
         <v>1.722696238021171</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2138,55 +2216,58 @@
           <t>MLCC</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>300806</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>斯迪克</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="H27" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="I27" s="4" t="n">
         <v>42.2</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="J27" s="3" t="n">
         <v>15.30054644808743</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="K27" s="4" t="n">
         <v>43.92</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="L27" s="4" t="n">
         <v>38.312</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="M27" s="4" t="n">
         <v>38.398</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="N27" s="3" t="n">
         <v>-0.2239699984374344</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="O27" s="4" t="n">
         <v>39.27800000000001</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="P27" s="4" t="n">
         <v>38.63399999999999</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="Q27" s="3" t="n">
         <v>1.666925506030981</v>
       </c>
-      <c r="Q27" s="5" t="n">
+      <c r="R27" s="5" t="n">
         <v>1.890895504468415</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2203,55 +2284,58 @@
           <t>算力</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="C28" s="3" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>920493</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>并行科技</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="H28" s="4" t="n">
         <v>86.43000000000001</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="I28" s="4" t="n">
         <v>99.17</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="J28" s="3" t="n">
         <v>14.74025222723592</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="K28" s="4" t="n">
         <v>103.71</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="L28" s="4" t="n">
         <v>91.07600000000001</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="M28" s="4" t="n">
         <v>91.12800000000001</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="N28" s="3" t="n">
         <v>-0.0570625932754032</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="O28" s="4" t="n">
         <v>93.11000000000001</v>
       </c>
-      <c r="O28" s="3" t="n">
+      <c r="P28" s="4" t="n">
         <v>91.785</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="Q28" s="3" t="n">
         <v>1.443591000708189</v>
       </c>
-      <c r="Q28" s="5" t="n">
+      <c r="R28" s="5" t="n">
         <v>1.500653593983592</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2268,55 +2352,58 @@
           <t>算力</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="3" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>301169</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>零点有数</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="H29" s="4" t="n">
         <v>42.89</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="I29" s="4" t="n">
         <v>51.1</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="J29" s="3" t="n">
         <v>19.14199114012591</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="K29" s="4" t="n">
         <v>51.46</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="L29" s="4" t="n">
         <v>45.654</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="M29" s="4" t="n">
         <v>46.396</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N29" s="3" t="n">
         <v>-1.599275799637889</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="O29" s="4" t="n">
         <v>47.072</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="P29" s="4" t="n">
         <v>47.072</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="Q29" s="3" t="n">
         <v>2.220446049250313e-14</v>
       </c>
-      <c r="Q29" s="5" t="n">
+      <c r="R29" s="5" t="n">
         <v>1.599275799637911</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2333,58 +2420,61 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>301052</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>果麦文化</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="H30" s="4" t="n">
         <v>32.45</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="I30" s="4" t="n">
         <v>34.69</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="J30" s="3" t="n">
         <v>6.902927580893659</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="K30" s="4" t="n">
         <v>38.94</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="L30" s="4" t="n">
         <v>32.11799999999999</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="M30" s="4" t="n">
         <v>33.262</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="N30" s="3" t="n">
         <v>-3.439360230894128</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="O30" s="4" t="n">
         <v>33.19600000000001</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="P30" s="4" t="n">
         <v>33.194</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="Q30" s="3" t="n">
         <v>0.006025185274460831</v>
       </c>
-      <c r="Q30" s="5" t="n">
+      <c r="R30" s="5" t="n">
         <v>3.445385416168589</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2401,58 +2491,61 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>603258</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>电魂网络</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="H31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="I31" s="4" t="n">
         <v>16.16</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="J31" s="3" t="n">
         <v>7.733333333333325</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="K31" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="L31" s="4" t="n">
         <v>14.786</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="M31" s="4" t="n">
         <v>14.95</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="N31" s="3" t="n">
         <v>-1.096989966555195</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="O31" s="4" t="n">
         <v>15.306</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="P31" s="4" t="n">
         <v>14.885</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="Q31" s="3" t="n">
         <v>2.828350688612713</v>
       </c>
-      <c r="Q31" s="5" t="n">
+      <c r="R31" s="5" t="n">
         <v>3.925340655167908</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2469,55 +2562,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>300251</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>光线传媒</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="H32" s="4" t="n">
         <v>11.59</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="I32" s="4" t="n">
         <v>12.01</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="J32" s="3" t="n">
         <v>3.623813632441752</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="K32" s="4" t="n">
         <v>13.9</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="L32" s="4" t="n">
         <v>11.622</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="M32" s="4" t="n">
         <v>11.649</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="N32" s="3" t="n">
         <v>-0.2317795518928856</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="O32" s="4" t="n">
         <v>11.816</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="P32" s="4" t="n">
         <v>11.668</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="Q32" s="3" t="n">
         <v>1.26842646554679</v>
       </c>
-      <c r="Q32" s="5" t="n">
+      <c r="R32" s="5" t="n">
         <v>1.500206017439676</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2534,55 +2630,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>300133</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>华策影视</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="H33" s="4" t="n">
         <v>8.92</v>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="I33" s="4" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="J33" s="3" t="n">
         <v>5.94170403587444</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="K33" s="4" t="n">
         <v>10.7</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="L33" s="4" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="M33" s="4" t="n">
         <v>9.052000000000001</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="N33" s="3" t="n">
         <v>-1.789659743703054</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="O33" s="4" t="n">
         <v>9.059999999999999</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="P33" s="4" t="n">
         <v>9.058000000000002</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="Q33" s="3" t="n">
         <v>0.02207992934419867</v>
       </c>
-      <c r="Q33" s="5" t="n">
+      <c r="R33" s="5" t="n">
         <v>1.811739673047252</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2599,55 +2698,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>002400</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>省广集团</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="4" t="n">
         <v>6.45</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="I34" s="4" t="n">
         <v>6.85</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="J34" s="3" t="n">
         <v>6.201550387596888</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="K34" s="4" t="n">
         <v>7.09</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="L34" s="4" t="n">
         <v>6.525999999999999</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="M34" s="4" t="n">
         <v>6.565</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="N34" s="3" t="n">
         <v>-0.5940594059406057</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="O34" s="4" t="n">
         <v>6.641999999999999</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="P34" s="4" t="n">
         <v>6.581999999999999</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="Q34" s="3" t="n">
         <v>0.9115770282588809</v>
       </c>
-      <c r="Q34" s="5" t="n">
+      <c r="R34" s="5" t="n">
         <v>1.505636434199487</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2664,55 +2766,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="C35" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>002555</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>三七互娱</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="H35" s="4" t="n">
         <v>16.1</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="I35" s="4" t="n">
         <v>17.29</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="J35" s="3" t="n">
         <v>7.391304347826066</v>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="K35" s="4" t="n">
         <v>17.71</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="L35" s="4" t="n">
         <v>16.418</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="M35" s="4" t="n">
         <v>16.676</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="N35" s="3" t="n">
         <v>-1.547133605181095</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="O35" s="4" t="n">
         <v>16.684</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="P35" s="4" t="n">
         <v>16.678</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="Q35" s="3" t="n">
         <v>0.03597553663508002</v>
       </c>
-      <c r="Q35" s="5" t="n">
+      <c r="R35" s="5" t="n">
         <v>1.583109141816175</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2729,55 +2834,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="C36" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>300418</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>昆仑万维</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="H36" s="4" t="n">
         <v>39.19</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="I36" s="4" t="n">
         <v>42.11</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="J36" s="3" t="n">
         <v>7.45088032661394</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="K36" s="4" t="n">
         <v>47.02</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="L36" s="4" t="n">
         <v>39.884</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="M36" s="4" t="n">
         <v>40.01</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="N36" s="3" t="n">
         <v>-0.3149212696825776</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="O36" s="4" t="n">
         <v>40.746</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="P36" s="4" t="n">
         <v>40.009</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="Q36" s="3" t="n">
         <v>1.842085530755577</v>
       </c>
-      <c r="Q36" s="5" t="n">
+      <c r="R36" s="5" t="n">
         <v>2.157006800438155</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2794,55 +2902,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="C37" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>600986</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>浙文互联</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="H37" s="4" t="n">
         <v>6.79</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="I37" s="4" t="n">
         <v>7.34</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="J37" s="3" t="n">
         <v>8.100147275405</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="K37" s="4" t="n">
         <v>7.46</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="L37" s="4" t="n">
         <v>6.907999999999999</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="M37" s="4" t="n">
         <v>6.93</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="N37" s="3" t="n">
         <v>-0.3174603174603163</v>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="O37" s="4" t="n">
         <v>7.058</v>
       </c>
-      <c r="O37" s="3" t="n">
+      <c r="P37" s="4" t="n">
         <v>6.953999999999999</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="Q37" s="3" t="n">
         <v>1.495542134023609</v>
       </c>
-      <c r="Q37" s="5" t="n">
+      <c r="R37" s="5" t="n">
         <v>1.813002451483925</v>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2859,55 +2970,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="C38" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>600556</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>天下秀</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="H38" s="4" t="n">
         <v>4.68</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="I38" s="4" t="n">
         <v>5.06</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="J38" s="3" t="n">
         <v>8.119658119658112</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="K38" s="4" t="n">
         <v>5.14</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="L38" s="4" t="n">
         <v>4.81</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="M38" s="4" t="n">
         <v>4.857</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="N38" s="3" t="n">
         <v>-0.9676755198682274</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="O38" s="4" t="n">
         <v>4.895999999999999</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="P38" s="4" t="n">
         <v>4.867</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="Q38" s="3" t="n">
         <v>0.5958495993424906</v>
       </c>
-      <c r="Q38" s="5" t="n">
+      <c r="R38" s="5" t="n">
         <v>1.563525119210718</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2924,55 +3038,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="C39" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>603444</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>吉比特</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="H39" s="4" t="n">
         <v>328.69</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="I39" s="4" t="n">
         <v>358.12</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="J39" s="3" t="n">
         <v>8.953725394748858</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="K39" s="4" t="n">
         <v>361.55</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="L39" s="4" t="n">
         <v>332.52</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="M39" s="4" t="n">
         <v>334.83</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="N39" s="3" t="n">
         <v>-0.6899023385001368</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="O39" s="4" t="n">
         <v>339.542</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="P39" s="4" t="n">
         <v>336.813</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="Q39" s="3" t="n">
         <v>0.8102418849628812</v>
       </c>
-      <c r="Q39" s="5" t="n">
+      <c r="R39" s="5" t="n">
         <v>1.500144223463018</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2989,55 +3106,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="C40" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>300182</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>捷成股份</t>
         </is>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="H40" s="4" t="n">
         <v>5.33</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="I40" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="J40" s="3" t="n">
         <v>10.69418386491559</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="K40" s="4" t="n">
         <v>6.39</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="L40" s="4" t="n">
         <v>5.526000000000001</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="M40" s="4" t="n">
         <v>5.555000000000001</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="N40" s="3" t="n">
         <v>-0.5220522052205245</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="O40" s="4" t="n">
         <v>5.648</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="P40" s="4" t="n">
         <v>5.58</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="Q40" s="3" t="n">
         <v>1.218637992831528</v>
       </c>
-      <c r="Q40" s="5" t="n">
+      <c r="R40" s="5" t="n">
         <v>1.740690198052053</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3054,55 +3174,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="C41" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>300364</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>中文在线</t>
         </is>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="H41" s="4" t="n">
         <v>23.45</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="I41" s="4" t="n">
         <v>26.59</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="J41" s="3" t="n">
         <v>13.39019189765458</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="K41" s="4" t="n">
         <v>28.14</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="L41" s="4" t="n">
         <v>24.172</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="M41" s="4" t="n">
         <v>24.289</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="N41" s="3" t="n">
         <v>-0.4816995347688091</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="O41" s="4" t="n">
         <v>24.904</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="P41" s="4" t="n">
         <v>24.422</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="Q41" s="3" t="n">
         <v>1.973630333306042</v>
       </c>
-      <c r="Q41" s="5" t="n">
+      <c r="R41" s="5" t="n">
         <v>2.455329868074851</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3119,55 +3242,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="C42" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>300063</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>天龙集团</t>
         </is>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="H42" s="4" t="n">
         <v>7.93</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="I42" s="4" t="n">
         <v>9.01</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="J42" s="3" t="n">
         <v>13.61916771752838</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="K42" s="4" t="n">
         <v>9.51</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="L42" s="4" t="n">
         <v>8.251999999999999</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="M42" s="4" t="n">
         <v>8.348000000000001</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="N42" s="3" t="n">
         <v>-1.149976042165812</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="O42" s="4" t="n">
         <v>8.484</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="P42" s="4" t="n">
         <v>8.375</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="Q42" s="3" t="n">
         <v>1.301492537313442</v>
       </c>
-      <c r="Q42" s="5" t="n">
+      <c r="R42" s="5" t="n">
         <v>2.451468579479255</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3184,55 +3310,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="C43" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>301262</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>海看股份</t>
         </is>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="H43" s="4" t="n">
         <v>20.35</v>
       </c>
-      <c r="H43" s="3" t="n">
-        <v>23.42</v>
-      </c>
       <c r="I43" s="4" t="n">
-        <v>15.08599508599509</v>
+        <v>23.36</v>
       </c>
       <c r="J43" s="3" t="n">
+        <v>14.79115479115478</v>
+      </c>
+      <c r="K43" s="4" t="n">
         <v>24.42</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>20.926</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>21.222</v>
+      <c r="L43" s="4" t="n">
+        <v>20.914</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>-1.394779002921476</v>
+        <v>21.21099999999993</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>21.662</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>21.348</v>
+        <v>-1.400216868605564</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>21.638</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>1.470863781150444</v>
-      </c>
-      <c r="Q43" s="5" t="n">
-        <v>2.86564278407192</v>
-      </c>
-      <c r="R43" t="inlineStr">
+        <v>21.336</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>1.415448068991365</v>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>2.815664937596929</v>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3249,55 +3378,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="C44" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>300959</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>线上线下</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="H44" s="4" t="n">
         <v>68.5</v>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="I44" s="4" t="n">
         <v>79.03</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="J44" s="3" t="n">
         <v>15.37226277372263</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="K44" s="4" t="n">
         <v>82.2</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="L44" s="4" t="n">
         <v>72.27799999999999</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="M44" s="4" t="n">
         <v>73.40299999999999</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="N44" s="3" t="n">
         <v>-1.532634905930275</v>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="O44" s="4" t="n">
         <v>74.042</v>
       </c>
-      <c r="O44" s="3" t="n">
+      <c r="P44" s="4" t="n">
         <v>73.756</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="Q44" s="3" t="n">
         <v>0.3877650631813001</v>
       </c>
-      <c r="Q44" s="5" t="n">
+      <c r="R44" s="5" t="n">
         <v>1.920399969111575</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3314,55 +3446,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="C45" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>300785</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>值得买</t>
         </is>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="H45" s="4" t="n">
         <v>32.47</v>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="I45" s="4" t="n">
         <v>37.95</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="J45" s="3" t="n">
         <v>16.87711733908224</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="K45" s="4" t="n">
         <v>38.96</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="L45" s="4" t="n">
         <v>34.376</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="M45" s="4" t="n">
         <v>34.82600000000001</v>
       </c>
-      <c r="M45" s="4" t="n">
+      <c r="N45" s="3" t="n">
         <v>-1.292138057772951</v>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="O45" s="4" t="n">
         <v>35.33</v>
       </c>
-      <c r="O45" s="3" t="n">
+      <c r="P45" s="4" t="n">
         <v>35.05500000000001</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="Q45" s="3" t="n">
         <v>0.7844815290257934</v>
       </c>
-      <c r="Q45" s="5" t="n">
+      <c r="R45" s="5" t="n">
         <v>2.076619586798745</v>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3379,55 +3514,58 @@
           <t>AI应用</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="C46" s="3" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>301171</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>易点天下</t>
         </is>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="H46" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="I46" s="4" t="n">
         <v>33.87</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="J46" s="3" t="n">
         <v>17.19723183391002</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="K46" s="4" t="n">
         <v>34.68</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="L46" s="4" t="n">
         <v>30.872</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="M46" s="4" t="n">
         <v>30.89</v>
       </c>
-      <c r="M46" s="4" t="n">
+      <c r="N46" s="3" t="n">
         <v>-0.0582712852055467</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="O46" s="4" t="n">
         <v>31.734</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="P46" s="4" t="n">
         <v>31.077</v>
       </c>
-      <c r="P46" s="4" t="n">
+      <c r="Q46" s="3" t="n">
         <v>2.11410367796121</v>
       </c>
-      <c r="Q46" s="5" t="n">
+      <c r="R46" s="5" t="n">
         <v>2.172374963166757</v>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3444,55 +3582,58 @@
           <t>机器人</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="C47" s="3" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>301182</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>凯旺科技</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n">
+      <c r="H47" s="4" t="n">
         <v>43.21</v>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="I47" s="4" t="n">
         <v>50.56</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="J47" s="3" t="n">
         <v>17.00995140013886</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="K47" s="4" t="n">
         <v>51.85</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="L47" s="4" t="n">
         <v>46.172</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="M47" s="4" t="n">
         <v>46.638</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="N47" s="3" t="n">
         <v>-0.9991852137741675</v>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="O47" s="4" t="n">
         <v>47.264</v>
       </c>
-      <c r="O47" s="3" t="n">
+      <c r="P47" s="4" t="n">
         <v>46.95</v>
       </c>
-      <c r="P47" s="4" t="n">
+      <c r="Q47" s="3" t="n">
         <v>0.6687965921192696</v>
       </c>
-      <c r="Q47" s="5" t="n">
+      <c r="R47" s="5" t="n">
         <v>1.667981805893437</v>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3509,55 +3650,58 @@
           <t>机器人</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="C48" s="3" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>688697</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>纽威数控</t>
         </is>
       </c>
-      <c r="G48" s="3" t="n">
+      <c r="H48" s="4" t="n">
         <v>11.76</v>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="I48" s="4" t="n">
         <v>13.78</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="J48" s="3" t="n">
         <v>17.17687074829932</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="K48" s="4" t="n">
         <v>14.11</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="L48" s="4" t="n">
         <v>12.474</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="M48" s="4" t="n">
         <v>12.548</v>
       </c>
-      <c r="M48" s="4" t="n">
+      <c r="N48" s="3" t="n">
         <v>-0.5897354160025459</v>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="O48" s="4" t="n">
         <v>12.832</v>
       </c>
-      <c r="O48" s="3" t="n">
+      <c r="P48" s="4" t="n">
         <v>12.656</v>
       </c>
-      <c r="P48" s="4" t="n">
+      <c r="Q48" s="3" t="n">
         <v>1.390644753476589</v>
       </c>
-      <c r="Q48" s="5" t="n">
+      <c r="R48" s="5" t="n">
         <v>1.980380169479135</v>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3574,58 +3718,61 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>600380</t>
-        </is>
+      <c r="E49" t="n">
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>健康元</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>10.03</v>
+          <t>300006</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>莱美药业</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>8.27</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>1.827411167512683</v>
+        <v>9.58</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>9.582000000000001</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>9.684000000000001</v>
+        <v>15.8403869407497</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>8.528</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>-1.053283767038415</v>
+        <v>8.674000000000001</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>9.763999999999999</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>9.685</v>
+        <v>-1.683191145953433</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>8.82</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>0.8156943727413379</v>
-      </c>
-      <c r="Q49" s="5" t="n">
-        <v>1.868978139779753</v>
-      </c>
-      <c r="R49" t="inlineStr">
+        <v>8.818999999999999</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>0.01133915409912145</v>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>1.694530300052555</v>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3642,58 +3789,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>300006</t>
+      <c r="C50" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>莱美药业</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>9.58</v>
+          <t>002950</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>奥美医疗</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>8.220000000000001</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>15.8403869407497</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>8.528</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>8.674000000000001</v>
+        <v>7.785888077858871</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>8.343999999999999</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>-1.683191145953433</v>
+        <v>8.372</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="O50" s="3" t="n">
-        <v>8.818999999999999</v>
+        <v>-0.3344481605351279</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>8.504</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>0.01133915409912145</v>
-      </c>
-      <c r="Q50" s="5" t="n">
-        <v>1.694530300052555</v>
-      </c>
-      <c r="R50" t="inlineStr">
+        <v>8.406000000000001</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>1.165833928146554</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>1.500282088681681</v>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3710,55 +3857,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>002950</t>
+      <c r="C51" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>奥美医疗</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>8.859999999999999</v>
+          <t>301408</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>华人健康</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>13.78</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>7.785888077858871</v>
+        <v>14.88</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>8.343999999999999</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>8.372</v>
+        <v>7.982583454281578</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>13.936</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>-0.3344481605351279</v>
+        <v>13.95</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>8.504</v>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>8.406000000000001</v>
+        <v>-0.100358422939073</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>14.236</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>1.165833928146554</v>
-      </c>
-      <c r="Q51" s="5" t="n">
-        <v>1.500282088681681</v>
-      </c>
-      <c r="R51" t="inlineStr">
+        <v>14.039</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>1.403233848564733</v>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>1.503592271503806</v>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3775,55 +3925,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>301408</t>
+      <c r="C52" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>华人健康</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>14.88</v>
+          <t>300702</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>天宇股份</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>20.01</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>7.982583454281578</v>
+        <v>21.77</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>16.53</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>13.936</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>13.95</v>
+        <v>8.795602198900543</v>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>20.394</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>-0.100358422939073</v>
+        <v>20.548</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>14.236</v>
-      </c>
-      <c r="O52" s="3" t="n">
-        <v>14.039</v>
+        <v>-0.749464668094213</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>20.792</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>1.403233848564733</v>
-      </c>
-      <c r="Q52" s="5" t="n">
-        <v>1.503592271503806</v>
-      </c>
-      <c r="R52" t="inlineStr">
+        <v>20.632</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>0.7754943776657752</v>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>1.524959045759988</v>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3840,55 +3993,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>300702</t>
+      <c r="C53" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>天宇股份</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>21.77</v>
+          <t>603259</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>141.48</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8.795602198900543</v>
+        <v>154.19</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>20.394</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>20.548</v>
+        <v>8.983601922533225</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>155.62</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>145.54</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>-0.749464668094213</v>
+        <v>146.801</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>20.792</v>
-      </c>
-      <c r="O53" s="3" t="n">
-        <v>20.632</v>
+        <v>-0.8589859742099804</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>148.116</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>0.7754943776657752</v>
-      </c>
-      <c r="Q53" s="5" t="n">
-        <v>1.524959045759988</v>
-      </c>
-      <c r="R53" t="inlineStr">
+        <v>146.77</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>0.9170811473734553</v>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>1.776067121583436</v>
+      </c>
+      <c r="S53" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3905,55 +4061,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>603259</t>
+      <c r="C54" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>药明康德</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>141.48</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>154.19</v>
+          <t>600479</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>千金药业</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>10.46</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8.983601922533225</v>
+        <v>11.43</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>155.62</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>145.54</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>146.801</v>
+        <v>9.273422562141477</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>10.75629889298905</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>-0.8589859742099804</v>
+        <v>10.87729335793374</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>148.116</v>
-      </c>
-      <c r="O54" s="3" t="n">
-        <v>146.77</v>
+        <v>-1.112358203122654</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>10.93193357933587</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.9170811473734553</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>1.776067121583436</v>
-      </c>
-      <c r="R54" t="inlineStr">
+        <v>10.88938929889313</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>0.3906948247967001</v>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>1.503053027919354</v>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3970,55 +4129,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="C55" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>688710</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>益诺思</t>
         </is>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="H55" s="4" t="n">
         <v>83.36</v>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="I55" s="4" t="n">
         <v>91.54000000000001</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="J55" s="3" t="n">
         <v>9.812859884836866</v>
       </c>
-      <c r="J55" s="3" t="n">
+      <c r="K55" s="4" t="n">
         <v>100.03</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="L55" s="4" t="n">
         <v>83.75</v>
       </c>
-      <c r="L55" s="3" t="n">
+      <c r="M55" s="4" t="n">
         <v>84.50099999999999</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="N55" s="3" t="n">
         <v>-0.8887468787351471</v>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="O55" s="4" t="n">
         <v>85.82000000000001</v>
       </c>
-      <c r="O55" s="3" t="n">
+      <c r="P55" s="4" t="n">
         <v>84.71000000000001</v>
       </c>
-      <c r="P55" s="4" t="n">
+      <c r="Q55" s="3" t="n">
         <v>1.310352968952899</v>
       </c>
-      <c r="Q55" s="5" t="n">
+      <c r="R55" s="5" t="n">
         <v>2.199099847688046</v>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4035,55 +4197,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="C56" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>300363</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>博腾股份</t>
         </is>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="H56" s="4" t="n">
         <v>20.93</v>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="I56" s="4" t="n">
         <v>23.15</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="J56" s="3" t="n">
         <v>10.60678451982799</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="K56" s="4" t="n">
         <v>25.11</v>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="L56" s="4" t="n">
         <v>21.43</v>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="M56" s="4" t="n">
         <v>21.526</v>
       </c>
-      <c r="M56" s="4" t="n">
+      <c r="N56" s="3" t="n">
         <v>-0.4459723125522785</v>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="O56" s="4" t="n">
         <v>21.876</v>
       </c>
-      <c r="O56" s="3" t="n">
+      <c r="P56" s="4" t="n">
         <v>21.647</v>
       </c>
-      <c r="P56" s="4" t="n">
+      <c r="Q56" s="3" t="n">
         <v>1.057883309465502</v>
       </c>
-      <c r="Q56" s="5" t="n">
+      <c r="R56" s="5" t="n">
         <v>1.50385562201778</v>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4100,55 +4265,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>300255</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>常山药业</t>
         </is>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="H57" s="4" t="n">
         <v>18.73</v>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="I57" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="J57" s="3" t="n">
         <v>11.58569140416443</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="K57" s="4" t="n">
         <v>22.47</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="L57" s="4" t="n">
         <v>19.526</v>
       </c>
-      <c r="L57" s="3" t="n">
+      <c r="M57" s="4" t="n">
         <v>19.721</v>
       </c>
-      <c r="M57" s="4" t="n">
+      <c r="N57" s="3" t="n">
         <v>-0.9887936717204893</v>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="O57" s="4" t="n">
         <v>19.884</v>
       </c>
-      <c r="O57" s="3" t="n">
+      <c r="P57" s="4" t="n">
         <v>19.782</v>
       </c>
-      <c r="P57" s="4" t="n">
+      <c r="Q57" s="3" t="n">
         <v>0.515620260843197</v>
       </c>
-      <c r="Q57" s="5" t="n">
+      <c r="R57" s="5" t="n">
         <v>1.504413932563686</v>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4165,55 +4333,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="C58" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>300705</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>九典制药</t>
         </is>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="H58" s="4" t="n">
         <v>10.33</v>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="I58" s="4" t="n">
         <v>11.54</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="J58" s="3" t="n">
         <v>11.71345595353339</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="K58" s="4" t="n">
         <v>12.39</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="L58" s="4" t="n">
         <v>10.682</v>
       </c>
-      <c r="L58" s="3" t="n">
+      <c r="M58" s="4" t="n">
         <v>10.718</v>
       </c>
-      <c r="M58" s="4" t="n">
+      <c r="N58" s="3" t="n">
         <v>-0.3358835603657573</v>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="O58" s="4" t="n">
         <v>10.926</v>
       </c>
-      <c r="O58" s="3" t="n">
+      <c r="P58" s="4" t="n">
         <v>10.8</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="Q58" s="3" t="n">
         <v>1.166666666666649</v>
       </c>
-      <c r="Q58" s="5" t="n">
+      <c r="R58" s="5" t="n">
         <v>1.502550227032406</v>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4230,55 +4401,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="C59" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>688607</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>康众科技</t>
         </is>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="H59" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="I59" s="4" t="n">
         <v>34.67</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="J59" s="3" t="n">
         <v>11.83870967741936</v>
       </c>
-      <c r="J59" s="3" t="n">
+      <c r="K59" s="4" t="n">
         <v>37.2</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="L59" s="4" t="n">
         <v>32.822</v>
       </c>
-      <c r="L59" s="3" t="n">
+      <c r="M59" s="4" t="n">
         <v>33.042</v>
       </c>
-      <c r="M59" s="4" t="n">
+      <c r="N59" s="3" t="n">
         <v>-0.6658192603353319</v>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="O59" s="4" t="n">
         <v>33.384</v>
       </c>
-      <c r="O59" s="3" t="n">
+      <c r="P59" s="4" t="n">
         <v>33.10700000000001</v>
       </c>
-      <c r="P59" s="4" t="n">
+      <c r="Q59" s="3" t="n">
         <v>0.8366810644274469</v>
       </c>
-      <c r="Q59" s="5" t="n">
+      <c r="R59" s="5" t="n">
         <v>1.502500324762779</v>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4295,55 +4469,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="C60" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>300434</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>金石亚药</t>
         </is>
       </c>
-      <c r="G60" s="3" t="n">
+      <c r="H60" s="4" t="n">
         <v>11.31</v>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="I60" s="4" t="n">
         <v>12.66</v>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="J60" s="3" t="n">
         <v>11.93633952254642</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="K60" s="4" t="n">
         <v>13.57</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="L60" s="4" t="n">
         <v>12.044</v>
       </c>
-      <c r="L60" s="3" t="n">
+      <c r="M60" s="4" t="n">
         <v>12.294</v>
       </c>
-      <c r="M60" s="4" t="n">
+      <c r="N60" s="3" t="n">
         <v>-2.033512282414185</v>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="O60" s="4" t="n">
         <v>12.242</v>
       </c>
-      <c r="O60" s="3" t="n">
+      <c r="P60" s="4" t="n">
         <v>12.24</v>
       </c>
-      <c r="P60" s="4" t="n">
+      <c r="Q60" s="3" t="n">
         <v>0.01633986928104569</v>
       </c>
-      <c r="Q60" s="5" t="n">
+      <c r="R60" s="5" t="n">
         <v>2.049852151695231</v>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4360,55 +4537,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="C61" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>301277</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>新天地</t>
         </is>
       </c>
-      <c r="G61" s="3" t="n">
+      <c r="H61" s="4" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="I61" s="4" t="n">
         <v>10.34</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="J61" s="3" t="n">
         <v>12.14750542299348</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="K61" s="4" t="n">
         <v>11.06</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="L61" s="4" t="n">
         <v>9.634</v>
       </c>
-      <c r="L61" s="3" t="n">
+      <c r="M61" s="4" t="n">
         <v>9.775000000000002</v>
       </c>
-      <c r="M61" s="4" t="n">
+      <c r="N61" s="3" t="n">
         <v>-1.442455242966767</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="O61" s="4" t="n">
         <v>9.818000000000001</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="P61" s="4" t="n">
         <v>9.792000000000002</v>
       </c>
-      <c r="P61" s="4" t="n">
+      <c r="Q61" s="3" t="n">
         <v>0.2655228758169814</v>
       </c>
-      <c r="Q61" s="5" t="n">
+      <c r="R61" s="5" t="n">
         <v>1.707978118783748</v>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4425,55 +4605,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="C62" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>301333</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>诺思格</t>
         </is>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="H62" s="4" t="n">
         <v>51.85</v>
       </c>
-      <c r="H62" s="3" t="n">
+      <c r="I62" s="4" t="n">
         <v>58.46</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="J62" s="3" t="n">
         <v>12.74831243972998</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="K62" s="4" t="n">
         <v>62.22</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="L62" s="4" t="n">
         <v>53.51000000000001</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="M62" s="4" t="n">
         <v>54.26900000000001</v>
       </c>
-      <c r="M62" s="4" t="n">
+      <c r="N62" s="3" t="n">
         <v>-1.398588512778931</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="O62" s="4" t="n">
         <v>54.876</v>
       </c>
-      <c r="O62" s="3" t="n">
+      <c r="P62" s="4" t="n">
         <v>54.463</v>
       </c>
-      <c r="P62" s="4" t="n">
+      <c r="Q62" s="3" t="n">
         <v>0.7583129831261637</v>
       </c>
-      <c r="Q62" s="5" t="n">
+      <c r="R62" s="5" t="n">
         <v>2.156901495905095</v>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4490,55 +4673,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="C63" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>300246</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>宝莱特</t>
         </is>
       </c>
-      <c r="G63" s="3" t="n">
+      <c r="H63" s="4" t="n">
         <v>12.22</v>
       </c>
-      <c r="H63" s="3" t="n">
+      <c r="I63" s="4" t="n">
         <v>13.85</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="J63" s="3" t="n">
         <v>13.33878887070377</v>
       </c>
-      <c r="J63" s="3" t="n">
+      <c r="K63" s="4" t="n">
         <v>14.66</v>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="L63" s="4" t="n">
         <v>12.864</v>
       </c>
-      <c r="L63" s="3" t="n">
+      <c r="M63" s="4" t="n">
         <v>12.941</v>
       </c>
-      <c r="M63" s="4" t="n">
+      <c r="N63" s="3" t="n">
         <v>-0.5950081137470087</v>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="O63" s="4" t="n">
         <v>13.106</v>
       </c>
-      <c r="O63" s="3" t="n">
+      <c r="P63" s="4" t="n">
         <v>12.988</v>
       </c>
-      <c r="P63" s="4" t="n">
+      <c r="Q63" s="3" t="n">
         <v>0.9085309516476681</v>
       </c>
-      <c r="Q63" s="5" t="n">
+      <c r="R63" s="5" t="n">
         <v>1.503539065394677</v>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4555,55 +4741,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="C64" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>300109</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>新开源</t>
         </is>
       </c>
-      <c r="G64" s="3" t="n">
+      <c r="H64" s="4" t="n">
         <v>10.77</v>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="I64" s="4" t="n">
         <v>12.33</v>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="J64" s="3" t="n">
         <v>14.48467966573816</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="K64" s="4" t="n">
         <v>12.92</v>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="L64" s="4" t="n">
         <v>11.36</v>
       </c>
-      <c r="L64" s="3" t="n">
+      <c r="M64" s="4" t="n">
         <v>11.514</v>
       </c>
-      <c r="M64" s="4" t="n">
+      <c r="N64" s="3" t="n">
         <v>-1.337502171269755</v>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="O64" s="4" t="n">
         <v>11.602</v>
       </c>
-      <c r="O64" s="3" t="n">
+      <c r="P64" s="4" t="n">
         <v>11.577</v>
       </c>
-      <c r="P64" s="4" t="n">
+      <c r="Q64" s="3" t="n">
         <v>0.2159454090005841</v>
       </c>
-      <c r="Q64" s="5" t="n">
+      <c r="R64" s="5" t="n">
         <v>1.55344758027034</v>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4620,55 +4809,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="C65" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>300347</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>泰格医药</t>
         </is>
       </c>
-      <c r="G65" s="3" t="n">
+      <c r="H65" s="4" t="n">
         <v>47.82</v>
       </c>
-      <c r="H65" s="3" t="n">
+      <c r="I65" s="4" t="n">
         <v>54.89</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="J65" s="3" t="n">
         <v>14.78460895023004</v>
       </c>
-      <c r="J65" s="3" t="n">
+      <c r="K65" s="4" t="n">
         <v>57.38</v>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="L65" s="4" t="n">
         <v>50.25599999999999</v>
       </c>
-      <c r="L65" s="3" t="n">
+      <c r="M65" s="4" t="n">
         <v>50.69799999999999</v>
       </c>
-      <c r="M65" s="4" t="n">
+      <c r="N65" s="3" t="n">
         <v>-0.8718292634817937</v>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="O65" s="4" t="n">
         <v>51.302</v>
       </c>
-      <c r="O65" s="3" t="n">
+      <c r="P65" s="4" t="n">
         <v>50.98099999999999</v>
       </c>
-      <c r="P65" s="4" t="n">
+      <c r="Q65" s="3" t="n">
         <v>0.6296463388321349</v>
       </c>
-      <c r="Q65" s="5" t="n">
+      <c r="R65" s="5" t="n">
         <v>1.501475602313929</v>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4685,55 +4877,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="C66" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>300723</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>一品红</t>
         </is>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="H66" s="4" t="n">
         <v>28.77</v>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="I66" s="4" t="n">
         <v>33.08</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="J66" s="3" t="n">
         <v>14.98088286409454</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="K66" s="4" t="n">
         <v>34.52</v>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="L66" s="4" t="n">
         <v>30.38</v>
       </c>
-      <c r="L66" s="3" t="n">
+      <c r="M66" s="4" t="n">
         <v>30.584</v>
       </c>
-      <c r="M66" s="4" t="n">
+      <c r="N66" s="3" t="n">
         <v>-0.6670154329060929</v>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="O66" s="4" t="n">
         <v>31.088</v>
       </c>
-      <c r="O66" s="3" t="n">
+      <c r="P66" s="4" t="n">
         <v>30.831</v>
       </c>
-      <c r="P66" s="4" t="n">
+      <c r="Q66" s="3" t="n">
         <v>0.8335765949855745</v>
       </c>
-      <c r="Q66" s="5" t="n">
+      <c r="R66" s="5" t="n">
         <v>1.500592027891667</v>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4750,55 +4945,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="C67" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>300683</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>海特生物</t>
         </is>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="H67" s="4" t="n">
         <v>21.76</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="I67" s="4" t="n">
         <v>25.03</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="J67" s="3" t="n">
         <v>15.02757352941175</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="K67" s="4" t="n">
         <v>26.11</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="L67" s="4" t="n">
         <v>23.268</v>
       </c>
-      <c r="L67" s="3" t="n">
+      <c r="M67" s="4" t="n">
         <v>23.612</v>
       </c>
-      <c r="M67" s="4" t="n">
+      <c r="N67" s="3" t="n">
         <v>-1.456886328985241</v>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="O67" s="4" t="n">
         <v>23.674</v>
       </c>
-      <c r="O67" s="3" t="n">
+      <c r="P67" s="4" t="n">
         <v>23.663</v>
       </c>
-      <c r="P67" s="4" t="n">
+      <c r="Q67" s="3" t="n">
         <v>0.0464860753074392</v>
       </c>
-      <c r="Q67" s="5" t="n">
+      <c r="R67" s="5" t="n">
         <v>1.50337240429268</v>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4815,55 +5013,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="C68" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>300725</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>药石科技</t>
         </is>
       </c>
-      <c r="G68" s="3" t="n">
+      <c r="H68" s="4" t="n">
         <v>41.36</v>
       </c>
-      <c r="H68" s="3" t="n">
+      <c r="I68" s="4" t="n">
         <v>47.86</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="J68" s="3" t="n">
         <v>15.71566731141198</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="K68" s="4" t="n">
         <v>49.63</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="L68" s="4" t="n">
         <v>44.188</v>
       </c>
-      <c r="L68" s="3" t="n">
+      <c r="M68" s="4" t="n">
         <v>44.511</v>
       </c>
-      <c r="M68" s="4" t="n">
+      <c r="N68" s="3" t="n">
         <v>-0.7256633191795259</v>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="O68" s="4" t="n">
         <v>45.09999999999999</v>
       </c>
-      <c r="O68" s="3" t="n">
+      <c r="P68" s="4" t="n">
         <v>44.753</v>
       </c>
-      <c r="P68" s="4" t="n">
+      <c r="Q68" s="3" t="n">
         <v>0.7753670145018043</v>
       </c>
-      <c r="Q68" s="5" t="n">
+      <c r="R68" s="5" t="n">
         <v>1.50103033368133</v>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4880,55 +5081,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+      <c r="C69" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>301257</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>普蕊斯</t>
         </is>
       </c>
-      <c r="G69" s="3" t="n">
+      <c r="H69" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="I69" s="4" t="n">
         <v>36.68</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="J69" s="3" t="n">
         <v>16.44444444444444</v>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="K69" s="4" t="n">
         <v>37.8</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="L69" s="4" t="n">
         <v>33.264</v>
       </c>
-      <c r="L69" s="3" t="n">
+      <c r="M69" s="4" t="n">
         <v>33.722</v>
       </c>
-      <c r="M69" s="4" t="n">
+      <c r="N69" s="3" t="n">
         <v>-1.358163809975699</v>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="O69" s="4" t="n">
         <v>34.134</v>
       </c>
-      <c r="O69" s="3" t="n">
+      <c r="P69" s="4" t="n">
         <v>33.854</v>
       </c>
-      <c r="P69" s="4" t="n">
+      <c r="Q69" s="3" t="n">
         <v>0.8270809948602853</v>
       </c>
-      <c r="Q69" s="5" t="n">
+      <c r="R69" s="5" t="n">
         <v>2.185244804835984</v>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4945,55 +5149,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="C70" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>301093</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>华兰股份</t>
         </is>
       </c>
-      <c r="G70" s="3" t="n">
+      <c r="H70" s="4" t="n">
         <v>47.68</v>
       </c>
-      <c r="H70" s="3" t="n">
+      <c r="I70" s="4" t="n">
         <v>55.64</v>
       </c>
-      <c r="I70" s="4" t="n">
+      <c r="J70" s="3" t="n">
         <v>16.69463087248322</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="K70" s="4" t="n">
         <v>57.21</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="L70" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="L70" s="3" t="n">
+      <c r="M70" s="4" t="n">
         <v>51.384</v>
       </c>
-      <c r="M70" s="4" t="n">
+      <c r="N70" s="3" t="n">
         <v>-1.720379884789036</v>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="O70" s="4" t="n">
         <v>51.824</v>
       </c>
-      <c r="O70" s="3" t="n">
+      <c r="P70" s="4" t="n">
         <v>51.822</v>
       </c>
-      <c r="P70" s="4" t="n">
+      <c r="Q70" s="3" t="n">
         <v>0.003859364748559635</v>
       </c>
-      <c r="Q70" s="5" t="n">
+      <c r="R70" s="5" t="n">
         <v>1.724239249537596</v>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5010,55 +5217,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="C71" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>301201</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>诚达药业</t>
         </is>
       </c>
-      <c r="G71" s="3" t="n">
+      <c r="H71" s="4" t="n">
         <v>24.01</v>
       </c>
-      <c r="H71" s="3" t="n">
+      <c r="I71" s="4" t="n">
         <v>28.02</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="J71" s="3" t="n">
         <v>16.70137442732194</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="K71" s="4" t="n">
         <v>28.81</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="L71" s="4" t="n">
         <v>25.546</v>
       </c>
-      <c r="L71" s="3" t="n">
+      <c r="M71" s="4" t="n">
         <v>25.963</v>
       </c>
-      <c r="M71" s="4" t="n">
+      <c r="N71" s="3" t="n">
         <v>-1.606131802950361</v>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="O71" s="4" t="n">
         <v>26.066</v>
       </c>
-      <c r="O71" s="3" t="n">
+      <c r="P71" s="4" t="n">
         <v>26.065</v>
       </c>
-      <c r="P71" s="4" t="n">
+      <c r="Q71" s="3" t="n">
         <v>0.003836562440051594</v>
       </c>
-      <c r="Q71" s="5" t="n">
+      <c r="R71" s="5" t="n">
         <v>1.609968365390413</v>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5075,55 +5285,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
+      <c r="C72" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>920047</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>诺思兰德</t>
         </is>
       </c>
-      <c r="G72" s="3" t="n">
+      <c r="H72" s="4" t="n">
         <v>12.62</v>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="I72" s="4" t="n">
         <v>14.75</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="J72" s="3" t="n">
         <v>16.87797147385104</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="K72" s="4" t="n">
         <v>15.14</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="L72" s="4" t="n">
         <v>13.434</v>
       </c>
-      <c r="L72" s="3" t="n">
+      <c r="M72" s="4" t="n">
         <v>13.55</v>
       </c>
-      <c r="M72" s="4" t="n">
+      <c r="N72" s="3" t="n">
         <v>-0.8560885608856372</v>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="O72" s="4" t="n">
         <v>13.722</v>
       </c>
-      <c r="O72" s="3" t="n">
+      <c r="P72" s="4" t="n">
         <v>13.634</v>
       </c>
-      <c r="P72" s="4" t="n">
+      <c r="Q72" s="3" t="n">
         <v>0.6454452105031372</v>
       </c>
-      <c r="Q72" s="5" t="n">
+      <c r="R72" s="5" t="n">
         <v>1.501533771388774</v>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5140,55 +5353,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>300204</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>舒泰神</t>
         </is>
       </c>
-      <c r="G73" s="3" t="n">
+      <c r="H73" s="4" t="n">
         <v>16.91</v>
       </c>
-      <c r="H73" s="3" t="n">
+      <c r="I73" s="4" t="n">
         <v>19.8</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="J73" s="3" t="n">
         <v>17.09047900650502</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="K73" s="4" t="n">
         <v>20.29</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="L73" s="4" t="n">
         <v>17.97</v>
       </c>
-      <c r="L73" s="3" t="n">
+      <c r="M73" s="4" t="n">
         <v>18.211</v>
       </c>
-      <c r="M73" s="4" t="n">
+      <c r="N73" s="3" t="n">
         <v>-1.323375981549613</v>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="O73" s="4" t="n">
         <v>18.47</v>
       </c>
-      <c r="O73" s="3" t="n">
+      <c r="P73" s="4" t="n">
         <v>18.264</v>
       </c>
-      <c r="P73" s="4" t="n">
+      <c r="Q73" s="3" t="n">
         <v>1.127901883486615</v>
       </c>
-      <c r="Q73" s="5" t="n">
+      <c r="R73" s="5" t="n">
         <v>2.451277865036228</v>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5205,55 +5421,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="C74" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>300534</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>陇神戎发</t>
         </is>
       </c>
-      <c r="G74" s="3" t="n">
+      <c r="H74" s="4" t="n">
         <v>9.68</v>
       </c>
-      <c r="H74" s="3" t="n">
+      <c r="I74" s="4" t="n">
         <v>11.41</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="J74" s="3" t="n">
         <v>17.8719008264463</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="K74" s="4" t="n">
         <v>11.61</v>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="L74" s="4" t="n">
         <v>10.302</v>
       </c>
-      <c r="L74" s="3" t="n">
+      <c r="M74" s="4" t="n">
         <v>10.524</v>
       </c>
-      <c r="M74" s="4" t="n">
+      <c r="N74" s="3" t="n">
         <v>-2.109464082098089</v>
       </c>
-      <c r="N74" s="3" t="n">
+      <c r="O74" s="4" t="n">
         <v>10.564</v>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="P74" s="4" t="n">
         <v>10.562</v>
       </c>
-      <c r="P74" s="4" t="n">
+      <c r="Q74" s="3" t="n">
         <v>0.01893580761218594</v>
       </c>
-      <c r="Q74" s="5" t="n">
+      <c r="R74" s="5" t="n">
         <v>2.128399889710275</v>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5270,55 +5489,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="C75" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>300436</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>广生堂</t>
         </is>
       </c>
-      <c r="G75" s="3" t="n">
+      <c r="H75" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="H75" s="3" t="n">
+      <c r="I75" s="4" t="n">
         <v>83.91</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="J75" s="3" t="n">
         <v>18.34978843441466</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="K75" s="4" t="n">
         <v>85.08</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="L75" s="4" t="n">
         <v>76.474</v>
       </c>
-      <c r="L75" s="3" t="n">
+      <c r="M75" s="4" t="n">
         <v>77.93899999999999</v>
       </c>
-      <c r="M75" s="4" t="n">
+      <c r="N75" s="3" t="n">
         <v>-1.879675130550806</v>
       </c>
-      <c r="N75" s="3" t="n">
+      <c r="O75" s="4" t="n">
         <v>78.164</v>
       </c>
-      <c r="O75" s="3" t="n">
+      <c r="P75" s="4" t="n">
         <v>78.16199999999999</v>
       </c>
-      <c r="P75" s="4" t="n">
+      <c r="Q75" s="3" t="n">
         <v>0.002558788157935865</v>
       </c>
-      <c r="Q75" s="5" t="n">
+      <c r="R75" s="5" t="n">
         <v>1.882233918708742</v>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5335,55 +5557,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="C76" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>301234</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>五洲医疗</t>
         </is>
       </c>
-      <c r="G76" s="3" t="n">
+      <c r="H76" s="4" t="n">
         <v>125.7</v>
       </c>
-      <c r="H76" s="3" t="n">
+      <c r="I76" s="4" t="n">
         <v>149.04</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="J76" s="3" t="n">
         <v>18.56801909307875</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="K76" s="4" t="n">
         <v>150.84</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="L76" s="4" t="n">
         <v>130.836</v>
       </c>
-      <c r="L76" s="3" t="n">
+      <c r="M76" s="4" t="n">
         <v>131.754</v>
       </c>
-      <c r="M76" s="4" t="n">
+      <c r="N76" s="3" t="n">
         <v>-0.6967530397559152</v>
       </c>
-      <c r="N76" s="3" t="n">
+      <c r="O76" s="4" t="n">
         <v>134.844</v>
       </c>
-      <c r="O76" s="3" t="n">
+      <c r="P76" s="4" t="n">
         <v>132.851</v>
       </c>
-      <c r="P76" s="4" t="n">
+      <c r="Q76" s="3" t="n">
         <v>1.50017688989923</v>
       </c>
-      <c r="Q76" s="5" t="n">
+      <c r="R76" s="5" t="n">
         <v>2.196929929655145</v>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5400,55 +5625,58 @@
           <t>药</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
+      <c r="C77" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>920367</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>新赣江</t>
         </is>
       </c>
-      <c r="G77" s="3" t="n">
+      <c r="H77" s="4" t="n">
         <v>19.95</v>
       </c>
-      <c r="H77" s="3" t="n">
+      <c r="I77" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="I77" s="4" t="n">
+      <c r="J77" s="3" t="n">
         <v>19.2982456140351</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="K77" s="4" t="n">
         <v>23.94</v>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="L77" s="4" t="n">
         <v>21.502</v>
       </c>
-      <c r="L77" s="3" t="n">
+      <c r="M77" s="4" t="n">
         <v>21.968</v>
       </c>
-      <c r="M77" s="4" t="n">
+      <c r="N77" s="3" t="n">
         <v>-2.12126729788783</v>
       </c>
-      <c r="N77" s="3" t="n">
+      <c r="O77" s="4" t="n">
         <v>22.098</v>
       </c>
-      <c r="O77" s="3" t="n">
+      <c r="P77" s="4" t="n">
         <v>21.968</v>
       </c>
-      <c r="P77" s="4" t="n">
+      <c r="Q77" s="3" t="n">
         <v>0.5917698470502719</v>
       </c>
-      <c r="Q77" s="5" t="n">
+      <c r="R77" s="5" t="n">
         <v>2.713037144938102</v>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5462,61 +5690,61 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>互金证券</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>601211</t>
+          <t>药</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>空</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>国泰海通</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>17.35</v>
+          <t>688293</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>奥浦迈</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>54.08</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>6.637984019668108</v>
+        <v>64.63</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>17.89</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>16.454</v>
+        <v>19.50813609467454</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>58.05423652173778</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>-0.08508569344841677</v>
+        <v>59.41505217391117</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>16.728</v>
-      </c>
-      <c r="O78" s="3" t="n">
-        <v>16.494</v>
+        <v>-2.29035505714984</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>59.69761739130344</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>1.418697708257555</v>
-      </c>
-      <c r="Q78" s="5" t="n">
-        <v>1.503783401705971</v>
-      </c>
-      <c r="R78" t="inlineStr">
+        <v>59.69563130434619</v>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>0.00332702228595938</v>
+      </c>
+      <c r="R78" s="5" t="n">
+        <v>2.293682079435799</v>
+      </c>
+      <c r="S78" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5533,58 +5761,61 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>3</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>600621</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>华鑫股份</t>
         </is>
       </c>
-      <c r="G79" s="3" t="n">
+      <c r="H79" s="4" t="n">
         <v>14.9</v>
       </c>
-      <c r="H79" s="3" t="n">
+      <c r="I79" s="4" t="n">
         <v>15.91</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="J79" s="3" t="n">
         <v>6.778523489932886</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="K79" s="4" t="n">
         <v>16.39</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="L79" s="4" t="n">
         <v>14.66</v>
       </c>
-      <c r="L79" s="3" t="n">
+      <c r="M79" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="M79" s="4" t="n">
+      <c r="N79" s="3" t="n">
         <v>-0.7447528774542911</v>
       </c>
-      <c r="N79" s="3" t="n">
+      <c r="O79" s="4" t="n">
         <v>14.996</v>
       </c>
-      <c r="O79" s="3" t="n">
+      <c r="P79" s="4" t="n">
         <v>14.883</v>
       </c>
-      <c r="P79" s="4" t="n">
+      <c r="Q79" s="3" t="n">
         <v>0.7592555264395617</v>
       </c>
-      <c r="Q79" s="5" t="n">
+      <c r="R79" s="5" t="n">
         <v>1.504008403893853</v>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5601,55 +5832,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="C80" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>601519</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>大智慧</t>
         </is>
       </c>
-      <c r="G80" s="3" t="n">
+      <c r="H80" s="4" t="n">
         <v>8.76</v>
       </c>
-      <c r="H80" s="3" t="n">
+      <c r="I80" s="4" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="I80" s="4" t="n">
+      <c r="J80" s="3" t="n">
         <v>7.191780821917826</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="K80" s="4" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="L80" s="4" t="n">
         <v>9.022</v>
       </c>
-      <c r="L80" s="3" t="n">
+      <c r="M80" s="4" t="n">
         <v>9.144000000000002</v>
       </c>
-      <c r="M80" s="4" t="n">
+      <c r="N80" s="3" t="n">
         <v>-1.334208223972022</v>
       </c>
-      <c r="N80" s="3" t="n">
+      <c r="O80" s="4" t="n">
         <v>9.218</v>
       </c>
-      <c r="O80" s="3" t="n">
+      <c r="P80" s="4" t="n">
         <v>9.118</v>
       </c>
-      <c r="P80" s="4" t="n">
+      <c r="Q80" s="3" t="n">
         <v>1.096731739416534</v>
       </c>
-      <c r="Q80" s="5" t="n">
+      <c r="R80" s="5" t="n">
         <v>2.430939963388556</v>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5666,55 +5900,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="C81" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>600958</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>东方证券</t>
         </is>
       </c>
-      <c r="G81" s="3" t="n">
+      <c r="H81" s="4" t="n">
         <v>8.48</v>
       </c>
-      <c r="H81" s="3" t="n">
+      <c r="I81" s="4" t="n">
         <v>9.15</v>
       </c>
-      <c r="I81" s="4" t="n">
+      <c r="J81" s="3" t="n">
         <v>7.900943396226423</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="K81" s="4" t="n">
         <v>9.32</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="L81" s="4" t="n">
         <v>8.586</v>
       </c>
-      <c r="L81" s="3" t="n">
+      <c r="M81" s="4" t="n">
         <v>8.595000000000002</v>
       </c>
-      <c r="M81" s="4" t="n">
+      <c r="N81" s="3" t="n">
         <v>-0.1047120418848468</v>
       </c>
-      <c r="N81" s="3" t="n">
+      <c r="O81" s="4" t="n">
         <v>8.75</v>
       </c>
-      <c r="O81" s="3" t="n">
+      <c r="P81" s="4" t="n">
         <v>8.629</v>
       </c>
-      <c r="P81" s="4" t="n">
+      <c r="Q81" s="3" t="n">
         <v>1.402248232703673</v>
       </c>
-      <c r="Q81" s="5" t="n">
+      <c r="R81" s="5" t="n">
         <v>1.50696027458852</v>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5731,55 +5968,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="C82" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>601377</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>兴业证券</t>
         </is>
       </c>
-      <c r="G82" s="3" t="n">
+      <c r="H82" s="4" t="n">
         <v>5.52</v>
       </c>
-      <c r="H82" s="3" t="n">
+      <c r="I82" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I82" s="4" t="n">
+      <c r="J82" s="3" t="n">
         <v>8.695652173913061</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="K82" s="4" t="n">
         <v>6.07</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="L82" s="4" t="n">
         <v>5.613999999999999</v>
       </c>
-      <c r="L82" s="3" t="n">
+      <c r="M82" s="4" t="n">
         <v>5.625999999999999</v>
       </c>
-      <c r="M82" s="4" t="n">
+      <c r="N82" s="3" t="n">
         <v>-0.2132954141486065</v>
       </c>
-      <c r="N82" s="3" t="n">
+      <c r="O82" s="4" t="n">
         <v>5.726</v>
       </c>
-      <c r="O82" s="3" t="n">
+      <c r="P82" s="4" t="n">
         <v>5.653</v>
       </c>
-      <c r="P82" s="4" t="n">
+      <c r="Q82" s="3" t="n">
         <v>1.291349725809288</v>
       </c>
-      <c r="Q82" s="5" t="n">
+      <c r="R82" s="5" t="n">
         <v>1.504645139957894</v>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5796,55 +6036,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
+      <c r="C83" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>002736</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>国信证券</t>
         </is>
       </c>
-      <c r="G83" s="3" t="n">
+      <c r="H83" s="4" t="n">
         <v>9.66</v>
       </c>
-      <c r="H83" s="3" t="n">
+      <c r="I83" s="4" t="n">
         <v>10.52</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="J83" s="3" t="n">
         <v>8.902691511387161</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="K83" s="4" t="n">
         <v>10.62</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="L83" s="4" t="n">
         <v>9.806000000000001</v>
       </c>
-      <c r="L83" s="3" t="n">
+      <c r="M83" s="4" t="n">
         <v>9.812999999999999</v>
       </c>
-      <c r="M83" s="4" t="n">
+      <c r="N83" s="3" t="n">
         <v>-0.07133394476712684</v>
       </c>
-      <c r="N83" s="3" t="n">
+      <c r="O83" s="4" t="n">
         <v>10.008</v>
       </c>
-      <c r="O83" s="3" t="n">
+      <c r="P83" s="4" t="n">
         <v>9.866999999999999</v>
       </c>
-      <c r="P83" s="4" t="n">
+      <c r="Q83" s="3" t="n">
         <v>1.429005776831871</v>
       </c>
-      <c r="Q83" s="5" t="n">
+      <c r="R83" s="5" t="n">
         <v>1.500339721598998</v>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5861,55 +6104,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
+      <c r="C84" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>601136</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>首创证券</t>
         </is>
       </c>
-      <c r="G84" s="3" t="n">
+      <c r="H84" s="4" t="n">
         <v>13.49</v>
       </c>
-      <c r="H84" s="3" t="n">
+      <c r="I84" s="4" t="n">
         <v>14.78</v>
       </c>
-      <c r="I84" s="4" t="n">
+      <c r="J84" s="3" t="n">
         <v>9.562638991845795</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="K84" s="4" t="n">
         <v>14.83</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="L84" s="4" t="n">
         <v>13.94</v>
       </c>
-      <c r="L84" s="3" t="n">
+      <c r="M84" s="4" t="n">
         <v>14.029</v>
       </c>
-      <c r="M84" s="4" t="n">
+      <c r="N84" s="3" t="n">
         <v>-0.6344001710741898</v>
       </c>
-      <c r="N84" s="3" t="n">
+      <c r="O84" s="4" t="n">
         <v>14.184</v>
       </c>
-      <c r="O84" s="3" t="n">
+      <c r="P84" s="4" t="n">
         <v>14.062</v>
       </c>
-      <c r="P84" s="4" t="n">
+      <c r="Q84" s="3" t="n">
         <v>0.8675864030721181</v>
       </c>
-      <c r="Q84" s="5" t="n">
+      <c r="R84" s="5" t="n">
         <v>1.501986574146308</v>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5926,55 +6172,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="C85" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>688318</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>财富趋势</t>
         </is>
       </c>
-      <c r="G85" s="3" t="n">
+      <c r="H85" s="4" t="n">
         <v>69.98999999999999</v>
       </c>
-      <c r="H85" s="3" t="n">
+      <c r="I85" s="4" t="n">
         <v>77.61</v>
       </c>
-      <c r="I85" s="4" t="n">
+      <c r="J85" s="3" t="n">
         <v>10.88726960994428</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="K85" s="4" t="n">
         <v>83.98</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="L85" s="4" t="n">
         <v>73.66400000000002</v>
       </c>
-      <c r="L85" s="3" t="n">
+      <c r="M85" s="4" t="n">
         <v>73.70700000000001</v>
       </c>
-      <c r="M85" s="4" t="n">
+      <c r="N85" s="3" t="n">
         <v>-0.05833909940710091</v>
       </c>
-      <c r="N85" s="3" t="n">
+      <c r="O85" s="4" t="n">
         <v>75.06800000000001</v>
       </c>
-      <c r="O85" s="3" t="n">
+      <c r="P85" s="4" t="n">
         <v>74.001</v>
       </c>
-      <c r="P85" s="4" t="n">
+      <c r="Q85" s="3" t="n">
         <v>1.441872407129652</v>
       </c>
-      <c r="Q85" s="5" t="n">
+      <c r="R85" s="5" t="n">
         <v>1.500211506536753</v>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5991,55 +6240,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
+      <c r="C86" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>300803</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>指南针</t>
         </is>
       </c>
-      <c r="G86" s="3" t="n">
+      <c r="H86" s="4" t="n">
         <v>48.38</v>
       </c>
-      <c r="H86" s="3" t="n">
+      <c r="I86" s="4" t="n">
         <v>55.17</v>
       </c>
-      <c r="I86" s="4" t="n">
+      <c r="J86" s="3" t="n">
         <v>14.03472509301364</v>
       </c>
-      <c r="J86" s="3" t="n">
+      <c r="K86" s="4" t="n">
         <v>58.05</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="L86" s="4" t="n">
         <v>51.812</v>
       </c>
-      <c r="L86" s="3" t="n">
+      <c r="M86" s="4" t="n">
         <v>52.057</v>
       </c>
-      <c r="M86" s="4" t="n">
+      <c r="N86" s="3" t="n">
         <v>-0.4706379545498129</v>
       </c>
-      <c r="N86" s="3" t="n">
+      <c r="O86" s="4" t="n">
         <v>52.79600000000001</v>
       </c>
-      <c r="O86" s="3" t="n">
+      <c r="P86" s="4" t="n">
         <v>52.258</v>
       </c>
-      <c r="P86" s="4" t="n">
+      <c r="Q86" s="3" t="n">
         <v>1.029507443836364</v>
       </c>
-      <c r="Q86" s="5" t="n">
+      <c r="R86" s="5" t="n">
         <v>1.500145398386177</v>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6056,55 +6308,58 @@
           <t>互金证券</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="C87" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>300085</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>银之杰</t>
         </is>
       </c>
-      <c r="G87" s="3" t="n">
+      <c r="H87" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="H87" s="3" t="n">
+      <c r="I87" s="4" t="n">
         <v>28.83</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="J87" s="3" t="n">
         <v>15.82965046203293</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="K87" s="4" t="n">
         <v>29.86</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="L87" s="4" t="n">
         <v>26.71</v>
       </c>
-      <c r="L87" s="3" t="n">
+      <c r="M87" s="4" t="n">
         <v>26.998</v>
       </c>
-      <c r="M87" s="4" t="n">
+      <c r="N87" s="3" t="n">
         <v>-1.066745684865533</v>
       </c>
-      <c r="N87" s="3" t="n">
+      <c r="O87" s="4" t="n">
         <v>27.322</v>
       </c>
-      <c r="O87" s="3" t="n">
+      <c r="P87" s="4" t="n">
         <v>27.123</v>
       </c>
-      <c r="P87" s="4" t="n">
+      <c r="Q87" s="3" t="n">
         <v>0.7336946502968011</v>
       </c>
-      <c r="Q87" s="5" t="n">
+      <c r="R87" s="5" t="n">
         <v>1.800440335162334</v>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6121,55 +6376,58 @@
           <t>黄金白银</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
+      <c r="C88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>300945</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>曼卡龙</t>
         </is>
       </c>
-      <c r="G88" s="3" t="n">
+      <c r="H88" s="4" t="n">
         <v>10.02</v>
       </c>
-      <c r="H88" s="3" t="n">
+      <c r="I88" s="4" t="n">
         <v>11.52</v>
       </c>
-      <c r="I88" s="4" t="n">
+      <c r="J88" s="3" t="n">
         <v>14.97005988023952</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="K88" s="4" t="n">
         <v>12.02</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="L88" s="4" t="n">
         <v>10.506</v>
       </c>
-      <c r="L88" s="3" t="n">
+      <c r="M88" s="4" t="n">
         <v>10.536</v>
       </c>
-      <c r="M88" s="4" t="n">
+      <c r="N88" s="3" t="n">
         <v>-0.2847380410022526</v>
       </c>
-      <c r="N88" s="3" t="n">
+      <c r="O88" s="4" t="n">
         <v>10.762</v>
       </c>
-      <c r="O88" s="3" t="n">
+      <c r="P88" s="4" t="n">
         <v>10.632</v>
       </c>
-      <c r="P88" s="4" t="n">
+      <c r="Q88" s="3" t="n">
         <v>1.222723852520691</v>
       </c>
-      <c r="Q88" s="5" t="n">
+      <c r="R88" s="5" t="n">
         <v>1.507461893522943</v>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6186,55 +6444,58 @@
           <t>电网设备</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="C89" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>300069</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>金利华电</t>
         </is>
       </c>
-      <c r="G89" s="3" t="n">
+      <c r="H89" s="4" t="n">
         <v>21.06</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="I89" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="I89" s="4" t="n">
+      <c r="J89" s="3" t="n">
         <v>13.91263057929724</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="K89" s="4" t="n">
         <v>25.27</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="L89" s="4" t="n">
         <v>21.766</v>
       </c>
-      <c r="L89" s="3" t="n">
+      <c r="M89" s="4" t="n">
         <v>22.147</v>
       </c>
-      <c r="M89" s="4" t="n">
+      <c r="N89" s="3" t="n">
         <v>-1.720323294351378</v>
       </c>
-      <c r="N89" s="3" t="n">
+      <c r="O89" s="4" t="n">
         <v>22.318</v>
       </c>
-      <c r="O89" s="3" t="n">
+      <c r="P89" s="4" t="n">
         <v>22.316</v>
       </c>
-      <c r="P89" s="4" t="n">
+      <c r="Q89" s="3" t="n">
         <v>0.008962179602090004</v>
       </c>
-      <c r="Q89" s="5" t="n">
+      <c r="R89" s="5" t="n">
         <v>1.729285473953468</v>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6251,55 +6512,58 @@
           <t>电网设备</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
+      <c r="C90" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>301082</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>久盛电气</t>
         </is>
       </c>
-      <c r="G90" s="3" t="n">
+      <c r="H90" s="4" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="H90" s="3" t="n">
+      <c r="I90" s="4" t="n">
         <v>10.23</v>
       </c>
-      <c r="I90" s="4" t="n">
+      <c r="J90" s="3" t="n">
         <v>16.51480637813214</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="K90" s="4" t="n">
         <v>10.53</v>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="L90" s="4" t="n">
         <v>9.296000000000001</v>
       </c>
-      <c r="L90" s="3" t="n">
+      <c r="M90" s="4" t="n">
         <v>9.324000000000002</v>
       </c>
-      <c r="M90" s="4" t="n">
+      <c r="N90" s="3" t="n">
         <v>-0.3003003003003046</v>
       </c>
-      <c r="N90" s="3" t="n">
+      <c r="O90" s="4" t="n">
         <v>9.526</v>
       </c>
-      <c r="O90" s="3" t="n">
+      <c r="P90" s="4" t="n">
         <v>9.413</v>
       </c>
-      <c r="P90" s="4" t="n">
+      <c r="Q90" s="3" t="n">
         <v>1.200467438648678</v>
       </c>
-      <c r="Q90" s="5" t="n">
+      <c r="R90" s="5" t="n">
         <v>1.500767738948983</v>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6316,55 +6580,58 @@
           <t>电网设备</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="C91" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>300427</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>红相股份</t>
         </is>
       </c>
-      <c r="G91" s="3" t="n">
+      <c r="H91" s="4" t="n">
         <v>5.21</v>
       </c>
-      <c r="H91" s="3" t="n">
+      <c r="I91" s="4" t="n">
         <v>6.14</v>
       </c>
-      <c r="I91" s="4" t="n">
+      <c r="J91" s="3" t="n">
         <v>17.85028790786946</v>
       </c>
-      <c r="J91" s="3" t="n">
+      <c r="K91" s="4" t="n">
         <v>6.25</v>
       </c>
-      <c r="K91" s="3" t="n">
+      <c r="L91" s="4" t="n">
         <v>5.538</v>
       </c>
-      <c r="L91" s="3" t="n">
+      <c r="M91" s="4" t="n">
         <v>5.588</v>
       </c>
-      <c r="M91" s="4" t="n">
+      <c r="N91" s="3" t="n">
         <v>-0.8947745168217613</v>
       </c>
-      <c r="N91" s="3" t="n">
+      <c r="O91" s="4" t="n">
         <v>5.678</v>
       </c>
-      <c r="O91" s="3" t="n">
+      <c r="P91" s="4" t="n">
         <v>5.643000000000001</v>
       </c>
-      <c r="P91" s="4" t="n">
+      <c r="Q91" s="3" t="n">
         <v>0.6202374623427209</v>
       </c>
-      <c r="Q91" s="5" t="n">
+      <c r="R91" s="5" t="n">
         <v>1.515011979164482</v>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6381,64 +6648,67 @@
           <t>商业航天</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
+      <c r="C92" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>688323</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>瑞华泰</t>
         </is>
       </c>
-      <c r="G92" s="3" t="n">
+      <c r="H92" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="H92" s="3" t="n">
+      <c r="I92" s="4" t="n">
         <v>21.78</v>
       </c>
-      <c r="I92" s="4" t="n">
+      <c r="J92" s="3" t="n">
         <v>19.01639344262296</v>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="K92" s="4" t="n">
         <v>21.96</v>
       </c>
-      <c r="K92" s="3" t="n">
+      <c r="L92" s="4" t="n">
         <v>19.84</v>
       </c>
-      <c r="L92" s="3" t="n">
+      <c r="M92" s="4" t="n">
         <v>19.986</v>
       </c>
-      <c r="M92" s="4" t="n">
+      <c r="N92" s="3" t="n">
         <v>-0.7305113579505473</v>
       </c>
-      <c r="N92" s="3" t="n">
+      <c r="O92" s="4" t="n">
         <v>20.312</v>
       </c>
-      <c r="O92" s="3" t="n">
+      <c r="P92" s="4" t="n">
         <v>20.156</v>
       </c>
-      <c r="P92" s="4" t="n">
+      <c r="Q92" s="3" t="n">
         <v>0.7739630879142867</v>
       </c>
-      <c r="Q92" s="5" t="n">
+      <c r="R92" s="5" t="n">
         <v>1.504474445864834</v>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R92"/>
+  <autoFilter ref="A2:S92"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$S$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$U$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,28 +445,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S92"/>
+  <dimension ref="A1:U92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10.2" customWidth="1" min="2" max="2"/>
     <col width="13.8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10.2" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10.2" customWidth="1" min="8" max="8"/>
-    <col width="13.8" customWidth="1" min="9" max="9"/>
-    <col width="15.6" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13.8" customWidth="1" min="13" max="13"/>
-    <col width="19.2" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="13.8" customWidth="1" min="16" max="16"/>
-    <col width="19.2" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10.2" customWidth="1" min="10" max="10"/>
+    <col width="13.8" customWidth="1" min="11" max="11"/>
+    <col width="15.6" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13.8" customWidth="1" min="15" max="15"/>
+    <col width="19.2" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13.8" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="19.2" customWidth="1" min="19" max="19"/>
+    <col width="13.8" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -494,80 +496,90 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>综合评分</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>建议单票仓位%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>进度</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>当前收盘</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>明日最低收盘</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>明日最低涨幅%</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>明日涨停价</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>明日MA5</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>明日MA10</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>明日5-10间距%</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>后天MA5</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>后天MA10</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>后天5-10间距%</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>间距增幅pp</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -587,55 +599,56 @@
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>688308</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>欧科亿</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>59.41</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>68.95999999999999</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>16.07473489311564</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>71.29000000000001</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>64.092</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>64.788</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="P3" s="3" t="n">
         <v>-1.074273013521021</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="Q3" s="4" t="n">
         <v>65.364</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>65.086</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>0.4271271855698755</v>
       </c>
-      <c r="R3" s="5" t="n">
+      <c r="T3" s="5" t="n">
         <v>1.501400199090897</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -655,55 +668,56 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>300776</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>帝尔激光</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>79.31999999999999</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>92.8</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>16.99445284921837</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>95.18000000000001</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>84.974</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>85.59400000000001</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="P4" s="3" t="n">
         <v>-0.7243498376054425</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>86.774</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>86.10400000000001</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>0.7781287745052268</v>
       </c>
-      <c r="R4" s="5" t="n">
+      <c r="T4" s="5" t="n">
         <v>1.502478612110669</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -723,55 +737,56 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>688388</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>嘉元科技</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>21.41</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>25.46</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>18.91639420831388</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>25.69</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>22.902</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>23.614</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="P5" s="3" t="n">
         <v>-3.015160498009672</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>23.562</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>23.56</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>0.008488964346353711</v>
       </c>
-      <c r="R5" s="5" t="n">
+      <c r="T5" s="5" t="n">
         <v>3.023649462356026</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -791,55 +806,56 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>301338</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>凯格精机</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>65.19</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>18.00889707010278</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>78.22</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>70.116</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>71.02500000000001</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="P6" s="3" t="n">
         <v>-1.279831045406554</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="Q6" s="4" t="n">
         <v>71.69000000000001</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>71.53200000000001</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="S6" s="3" t="n">
         <v>0.2208801655203319</v>
       </c>
-      <c r="R6" s="5" t="n">
+      <c r="T6" s="5" t="n">
         <v>1.500711210926886</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -859,55 +875,56 @@
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>688628</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>优利德</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>65.3</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>77.08</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="L7" s="3" t="n">
         <v>18.03981623277182</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>78.36</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>71.622</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>71.79900000000001</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="P7" s="3" t="n">
         <v>-0.2465215392972175</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="Q7" s="4" t="n">
         <v>73.21600000000001</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>72.22999999999999</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="S7" s="3" t="n">
         <v>1.365083760210473</v>
       </c>
-      <c r="R7" s="5" t="n">
+      <c r="T7" s="5" t="n">
         <v>1.61160529950769</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -927,55 +944,56 @@
       <c r="C8" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="n"/>
       <c r="F8" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>300632</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>光莆股份</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>13.92</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <v>14.94252873563218</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>16.7</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>14.676</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>14.823</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="P8" s="3" t="n">
         <v>-0.991702084598256</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="Q8" s="4" t="n">
         <v>14.984</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>14.908</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="S8" s="3" t="n">
         <v>0.5097933995170445</v>
       </c>
-      <c r="R8" s="5" t="n">
+      <c r="T8" s="5" t="n">
         <v>1.501495484115301</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -995,55 +1013,56 @@
       <c r="C9" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>300672</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>国科微</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="J9" s="4" t="n">
         <v>128.51</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>150.65</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>17.22823126604936</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>154.21</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>137.146</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>138.103</v>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="P9" s="3" t="n">
         <v>-0.6929610508098927</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>140.342</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>139.218</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="S9" s="3" t="n">
         <v>0.8073668634802855</v>
       </c>
-      <c r="R9" s="5" t="n">
+      <c r="T9" s="5" t="n">
         <v>1.500327914290178</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1063,55 +1082,56 @@
       <c r="C10" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E10" s="3" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>688515</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>裕太微-U</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>100.5</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>118.36</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>17.77114427860695</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>120.6</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>107.958</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>108.01</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>-0.04814369039902733</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="Q10" s="4" t="n">
         <v>110.678</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>109.094</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>1.451958861165581</v>
       </c>
-      <c r="R10" s="5" t="n">
+      <c r="T10" s="5" t="n">
         <v>1.500102551564608</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1131,55 +1151,56 @@
       <c r="C11" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>300671</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>富满微</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>38.85</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>45.77</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>17.81209781209783</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>46.62</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>41.904</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>42.463</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="P11" s="3" t="n">
         <v>-1.316440194993285</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>42.79</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>42.684</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="S11" s="3" t="n">
         <v>0.2483366132508547</v>
       </c>
-      <c r="R11" s="5" t="n">
+      <c r="T11" s="5" t="n">
         <v>1.564776808244139</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1199,55 +1220,56 @@
       <c r="C12" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E12" s="3" t="n"/>
       <c r="F12" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>300042</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>朗科科技</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>27.55</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>32.7</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <v>18.69328493647913</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>33.06</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>29.592</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>29.773</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="P12" s="3" t="n">
         <v>-0.607933362442481</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>30.336</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>30.067</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="S12" s="3" t="n">
         <v>0.894668573519164</v>
       </c>
-      <c r="R12" s="5" t="n">
+      <c r="T12" s="5" t="n">
         <v>1.502601935961645</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1267,55 +1289,56 @@
       <c r="C13" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E13" s="3" t="n"/>
       <c r="F13" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>688416</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>恒烁股份</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>51.4</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>61.03</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="L13" s="3" t="n">
         <v>18.73540856031128</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>61.68</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>55.61</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>56.00699999999999</v>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="P13" s="3" t="n">
         <v>-0.7088399664327505</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="Q13" s="4" t="n">
         <v>56.98</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>56.532</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="S13" s="3" t="n">
         <v>0.7924715205547272</v>
       </c>
-      <c r="R13" s="5" t="n">
+      <c r="T13" s="5" t="n">
         <v>1.501311486987478</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1335,55 +1358,56 @@
       <c r="C14" s="3" t="n">
         <v>3.92</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E14" s="3" t="n"/>
       <c r="F14" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>688141</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>杰华特</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>67.45</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>80.7</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="L14" s="3" t="n">
         <v>19.64418087472202</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>80.94</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>73.34</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>74.45099999999999</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="P14" s="3" t="n">
         <v>-1.492256652026147</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="Q14" s="4" t="n">
         <v>75.048</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>74.98099999999999</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="S14" s="3" t="n">
         <v>0.08935597017911689</v>
       </c>
-      <c r="R14" s="5" t="n">
+      <c r="T14" s="5" t="n">
         <v>1.581612622205264</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1403,55 +1427,56 @@
       <c r="C15" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E15" s="3" t="n"/>
       <c r="F15" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>301717</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>超纯应材</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>263.63</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>299.5</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="L15" s="3" t="n">
         <v>13.60619049425331</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>316.35</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>278.08</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>282.667</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="P15" s="3" t="n">
         <v>-1.622757520333107</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="Q15" s="4" t="n">
         <v>283.302</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>282.917</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="S15" s="3" t="n">
         <v>0.1360823138941702</v>
       </c>
-      <c r="R15" s="5" t="n">
+      <c r="T15" s="5" t="n">
         <v>1.758839834227277</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1471,55 +1496,56 @@
       <c r="C16" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>688797</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>臻宝科技</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>220.88</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <v>19.39459459459458</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>199.554</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>200.066</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="P16" s="3" t="n">
         <v>-0.2559155478691899</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="Q16" s="4" t="n">
         <v>204.524</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>202.01</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="S16" s="3" t="n">
         <v>1.244492846888767</v>
       </c>
-      <c r="R16" s="5" t="n">
+      <c r="T16" s="5" t="n">
         <v>1.500408394757957</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1539,55 +1565,56 @@
       <c r="C17" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>301611</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>珂玛科技</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="J17" s="4" t="n">
         <v>62.45</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>74.62</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="L17" s="3" t="n">
         <v>19.48759007205765</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="M17" s="4" t="n">
         <v>74.94</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="N17" s="4" t="n">
         <v>67.664</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="O17" s="4" t="n">
         <v>68.711</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="P17" s="3" t="n">
         <v>-1.523773486050262</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="Q17" s="4" t="n">
         <v>69.11800000000001</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="R17" s="4" t="n">
         <v>69.11600000000001</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="S17" s="3" t="n">
         <v>0.002893685977189975</v>
       </c>
-      <c r="R17" s="5" t="n">
+      <c r="T17" s="5" t="n">
         <v>1.526667172027452</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1607,55 +1634,56 @@
       <c r="C18" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E18" s="3" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>688605</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>先锋精科</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="J18" s="4" t="n">
         <v>55.81</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="K18" s="4" t="n">
         <v>66.79000000000001</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="L18" s="3" t="n">
         <v>19.67389356746103</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <v>66.97</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>60.182</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="O18" s="4" t="n">
         <v>61.573</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="P18" s="3" t="n">
         <v>-2.25910707615351</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>61.818</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>61.816</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="S18" s="3" t="n">
         <v>0.003235408308555066</v>
       </c>
-      <c r="R18" s="5" t="n">
+      <c r="T18" s="5" t="n">
         <v>2.262342484462065</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1675,55 +1703,56 @@
       <c r="C19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E19" s="3" t="n"/>
       <c r="F19" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>003026</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>中晶科技</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="J19" s="4" t="n">
         <v>27.83</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>29.67</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>6.611570247933907</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>30.61</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>27.57</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="O19" s="4" t="n">
         <v>27.731</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="P19" s="3" t="n">
         <v>-0.5805776928347273</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="Q19" s="4" t="n">
         <v>28.148</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>27.891</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="S19" s="3" t="n">
         <v>0.9214441934674467</v>
       </c>
-      <c r="R19" s="5" t="n">
+      <c r="T19" s="5" t="n">
         <v>1.502021886302174</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1743,55 +1772,56 @@
       <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E20" s="3" t="n"/>
       <c r="F20" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>688268</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>华特气体</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="J20" s="4" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="K20" s="4" t="n">
         <v>112.39</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="L20" s="3" t="n">
         <v>13.41069626639759</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="M20" s="4" t="n">
         <v>118.92</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>103.382</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>105.176</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="P20" s="3" t="n">
         <v>-1.705712329809095</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>105.626</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>105.624</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="S20" s="3" t="n">
         <v>0.001893509050976405</v>
       </c>
-      <c r="R20" s="5" t="n">
+      <c r="T20" s="5" t="n">
         <v>1.707605838860071</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1811,55 +1841,56 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>300540</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>蜀道装备</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="J21" s="4" t="n">
         <v>20.65</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="K21" s="4" t="n">
         <v>23.96</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <v>16.02905569007265</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="M21" s="4" t="n">
         <v>24.78</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <v>21.898</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="O21" s="4" t="n">
         <v>22.063</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="P21" s="3" t="n">
         <v>-0.7478584054752102</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="Q21" s="4" t="n">
         <v>22.424</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="R21" s="4" t="n">
         <v>22.256</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="S21" s="3" t="n">
         <v>0.7548526240114928</v>
       </c>
-      <c r="R21" s="5" t="n">
+      <c r="T21" s="5" t="n">
         <v>1.502711029486703</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1879,55 +1910,56 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E22" s="3" t="n"/>
       <c r="F22" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>688138</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>清溢光电</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="J22" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>30.19</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>16.11538461538462</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="M22" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <v>27.528</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="O22" s="4" t="n">
         <v>27.97</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="P22" s="3" t="n">
         <v>-1.580264569181256</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="Q22" s="4" t="n">
         <v>28.154</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>28.153</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="S22" s="3" t="n">
         <v>0.003552019323005418</v>
       </c>
-      <c r="R22" s="5" t="n">
+      <c r="T22" s="5" t="n">
         <v>1.583816588504261</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -1947,55 +1979,56 @@
       <c r="C23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E23" s="3" t="n"/>
       <c r="F23" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>300821</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>东岳硅材</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="J23" s="4" t="n">
         <v>15.55</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="K23" s="4" t="n">
         <v>18.11</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="L23" s="3" t="n">
         <v>16.46302250803857</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <v>18.66</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>16.496</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="O23" s="4" t="n">
         <v>17.006</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="P23" s="3" t="n">
         <v>-2.998941550041145</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="Q23" s="4" t="n">
         <v>16.986</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="R23" s="4" t="n">
         <v>16.985</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="S23" s="3" t="n">
         <v>0.005887547836302964</v>
       </c>
-      <c r="R23" s="5" t="n">
+      <c r="T23" s="5" t="n">
         <v>3.004829097877448</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2015,55 +2048,56 @@
       <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E24" s="3" t="n"/>
       <c r="F24" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>688733</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>壹石通</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="J24" s="4" t="n">
         <v>21.41</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="K24" s="4" t="n">
         <v>25.07</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="L24" s="3" t="n">
         <v>17.09481550677254</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>25.69</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>22.986</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="O24" s="4" t="n">
         <v>23.195</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="P24" s="3" t="n">
         <v>-0.9010562621254548</v>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>23.484</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>23.344</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="S24" s="3" t="n">
         <v>0.5997258396161831</v>
       </c>
-      <c r="R24" s="5" t="n">
+      <c r="T24" s="5" t="n">
         <v>1.500782101741638</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2083,55 +2117,56 @@
       <c r="C25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>688106</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>金宏气体</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="J25" s="4" t="n">
         <v>19.28</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="K25" s="4" t="n">
         <v>22.64</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="L25" s="3" t="n">
         <v>17.42738589211619</v>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <v>23.13</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>20.436</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="O25" s="4" t="n">
         <v>20.839</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="P25" s="3" t="n">
         <v>-1.933873986275725</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="Q25" s="4" t="n">
         <v>20.96</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>20.919</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="S25" s="3" t="n">
         <v>0.1959940723744058</v>
       </c>
-      <c r="R25" s="5" t="n">
+      <c r="T25" s="5" t="n">
         <v>2.129868058650131</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2151,55 +2186,56 @@
       <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E26" s="3" t="n"/>
       <c r="F26" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>688233</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>神工股份</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="J26" s="4" t="n">
         <v>61.55</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="K26" s="4" t="n">
         <v>73.51000000000001</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <v>19.43135662063364</v>
       </c>
-      <c r="K26" s="4" t="n">
+      <c r="M26" s="4" t="n">
         <v>73.86</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>66.926</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>67.899</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="P26" s="3" t="n">
         <v>-1.433010795446177</v>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>68.548</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>68.34999999999999</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="S26" s="3" t="n">
         <v>0.289685442574994</v>
       </c>
-      <c r="R26" s="5" t="n">
+      <c r="T26" s="5" t="n">
         <v>1.722696238021171</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2219,55 +2255,56 @@
       <c r="C27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E27" s="3" t="n"/>
       <c r="F27" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>300806</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>斯迪克</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="J27" s="4" t="n">
         <v>36.6</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="K27" s="4" t="n">
         <v>42.2</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.30054644808743</v>
       </c>
-      <c r="K27" s="4" t="n">
+      <c r="M27" s="4" t="n">
         <v>43.92</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <v>38.312</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="O27" s="4" t="n">
         <v>38.398</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="P27" s="3" t="n">
         <v>-0.2239699984374344</v>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="Q27" s="4" t="n">
         <v>39.27800000000001</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="R27" s="4" t="n">
         <v>38.63399999999999</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="S27" s="3" t="n">
         <v>1.666925506030981</v>
       </c>
-      <c r="R27" s="5" t="n">
+      <c r="T27" s="5" t="n">
         <v>1.890895504468415</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2287,55 +2324,56 @@
       <c r="C28" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E28" s="3" t="n"/>
       <c r="F28" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>920493</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>并行科技</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="J28" s="4" t="n">
         <v>86.43000000000001</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="K28" s="4" t="n">
         <v>99.17</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="L28" s="3" t="n">
         <v>14.74025222723592</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <v>103.71</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>91.07600000000001</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>91.12800000000001</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="P28" s="3" t="n">
         <v>-0.0570625932754032</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>93.11000000000001</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>91.785</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="S28" s="3" t="n">
         <v>1.443591000708189</v>
       </c>
-      <c r="R28" s="5" t="n">
+      <c r="T28" s="5" t="n">
         <v>1.500653593983592</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2355,55 +2393,56 @@
       <c r="C29" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E29" s="3" t="n"/>
       <c r="F29" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>301169</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>零点有数</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="J29" s="4" t="n">
         <v>42.89</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="K29" s="4" t="n">
         <v>51.1</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="L29" s="3" t="n">
         <v>19.14199114012591</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>51.46</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>45.654</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="O29" s="4" t="n">
         <v>46.396</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="P29" s="3" t="n">
         <v>-1.599275799637889</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>47.072</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="R29" s="4" t="n">
         <v>47.072</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="S29" s="3" t="n">
         <v>2.220446049250313e-14</v>
       </c>
-      <c r="R29" s="5" t="n">
+      <c r="T29" s="5" t="n">
         <v>1.599275799637911</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2423,58 +2462,59 @@
       <c r="C30" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>301052</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>果麦文化</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="J30" s="4" t="n">
         <v>32.45</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="K30" s="4" t="n">
         <v>34.69</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="L30" s="3" t="n">
         <v>6.902927580893659</v>
       </c>
-      <c r="K30" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>38.94</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>32.11799999999999</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>33.262</v>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="P30" s="3" t="n">
         <v>-3.439360230894128</v>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>33.19600000000001</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>33.194</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="S30" s="3" t="n">
         <v>0.006025185274460831</v>
       </c>
-      <c r="R30" s="5" t="n">
+      <c r="T30" s="5" t="n">
         <v>3.445385416168589</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2494,58 +2534,59 @@
       <c r="C31" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>3</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>603258</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>电魂网络</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="K31" s="4" t="n">
         <v>16.16</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="L31" s="3" t="n">
         <v>7.733333333333325</v>
       </c>
-      <c r="K31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>14.786</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="O31" s="4" t="n">
         <v>14.95</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="P31" s="3" t="n">
         <v>-1.096989966555195</v>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>15.306</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>14.885</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="S31" s="3" t="n">
         <v>2.828350688612713</v>
       </c>
-      <c r="R31" s="5" t="n">
+      <c r="T31" s="5" t="n">
         <v>3.925340655167908</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2565,55 +2606,56 @@
       <c r="C32" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E32" s="3" t="n"/>
       <c r="F32" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>300251</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>光线传媒</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="J32" s="4" t="n">
         <v>11.59</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="K32" s="4" t="n">
         <v>12.01</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="L32" s="3" t="n">
         <v>3.623813632441752</v>
       </c>
-      <c r="K32" s="4" t="n">
+      <c r="M32" s="4" t="n">
         <v>13.9</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>11.622</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>11.649</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="P32" s="3" t="n">
         <v>-0.2317795518928856</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>11.816</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="R32" s="4" t="n">
         <v>11.668</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="S32" s="3" t="n">
         <v>1.26842646554679</v>
       </c>
-      <c r="R32" s="5" t="n">
+      <c r="T32" s="5" t="n">
         <v>1.500206017439676</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2633,55 +2675,56 @@
       <c r="C33" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E33" s="3" t="n"/>
       <c r="F33" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>300133</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>华策影视</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="J33" s="4" t="n">
         <v>8.92</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="K33" s="4" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="L33" s="3" t="n">
         <v>5.94170403587444</v>
       </c>
-      <c r="K33" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <v>10.7</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="O33" s="4" t="n">
         <v>9.052000000000001</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="P33" s="3" t="n">
         <v>-1.789659743703054</v>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>9.059999999999999</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>9.058000000000002</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="S33" s="3" t="n">
         <v>0.02207992934419867</v>
       </c>
-      <c r="R33" s="5" t="n">
+      <c r="T33" s="5" t="n">
         <v>1.811739673047252</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2701,55 +2744,56 @@
       <c r="C34" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E34" s="3" t="n"/>
       <c r="F34" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>002400</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>省广集团</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="J34" s="4" t="n">
         <v>6.45</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="K34" s="4" t="n">
         <v>6.85</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="L34" s="3" t="n">
         <v>6.201550387596888</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="M34" s="4" t="n">
         <v>7.09</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="N34" s="4" t="n">
         <v>6.525999999999999</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="O34" s="4" t="n">
         <v>6.565</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="P34" s="3" t="n">
         <v>-0.5940594059406057</v>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>6.641999999999999</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="R34" s="4" t="n">
         <v>6.581999999999999</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="S34" s="3" t="n">
         <v>0.9115770282588809</v>
       </c>
-      <c r="R34" s="5" t="n">
+      <c r="T34" s="5" t="n">
         <v>1.505636434199487</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2769,55 +2813,56 @@
       <c r="C35" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E35" s="3" t="n"/>
       <c r="F35" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>002555</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>三七互娱</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="J35" s="4" t="n">
         <v>16.1</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="K35" s="4" t="n">
         <v>17.29</v>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="L35" s="3" t="n">
         <v>7.391304347826066</v>
       </c>
-      <c r="K35" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <v>17.71</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>16.418</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="O35" s="4" t="n">
         <v>16.676</v>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="P35" s="3" t="n">
         <v>-1.547133605181095</v>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="Q35" s="4" t="n">
         <v>16.684</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="R35" s="4" t="n">
         <v>16.678</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="S35" s="3" t="n">
         <v>0.03597553663508002</v>
       </c>
-      <c r="R35" s="5" t="n">
+      <c r="T35" s="5" t="n">
         <v>1.583109141816175</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2837,55 +2882,56 @@
       <c r="C36" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E36" s="3" t="n"/>
       <c r="F36" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>300418</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>昆仑万维</t>
         </is>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="J36" s="4" t="n">
         <v>39.19</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="K36" s="4" t="n">
         <v>42.11</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <v>7.45088032661394</v>
       </c>
-      <c r="K36" s="4" t="n">
+      <c r="M36" s="4" t="n">
         <v>47.02</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <v>39.884</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="O36" s="4" t="n">
         <v>40.01</v>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="P36" s="3" t="n">
         <v>-0.3149212696825776</v>
       </c>
-      <c r="O36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>40.746</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="R36" s="4" t="n">
         <v>40.009</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="S36" s="3" t="n">
         <v>1.842085530755577</v>
       </c>
-      <c r="R36" s="5" t="n">
+      <c r="T36" s="5" t="n">
         <v>2.157006800438155</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2905,55 +2951,56 @@
       <c r="C37" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E37" s="3" t="n"/>
       <c r="F37" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>600986</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>浙文互联</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="J37" s="4" t="n">
         <v>6.79</v>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="K37" s="4" t="n">
         <v>7.34</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="L37" s="3" t="n">
         <v>8.100147275405</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>7.46</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>6.907999999999999</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="O37" s="4" t="n">
         <v>6.93</v>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="P37" s="3" t="n">
         <v>-0.3174603174603163</v>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>7.058</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="R37" s="4" t="n">
         <v>6.953999999999999</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="S37" s="3" t="n">
         <v>1.495542134023609</v>
       </c>
-      <c r="R37" s="5" t="n">
+      <c r="T37" s="5" t="n">
         <v>1.813002451483925</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -2973,55 +3020,56 @@
       <c r="C38" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E38" s="3" t="n"/>
       <c r="F38" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>600556</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>天下秀</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>4.68</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>5.06</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="L38" s="3" t="n">
         <v>8.119658119658112</v>
       </c>
-      <c r="K38" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>5.14</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>4.81</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="O38" s="4" t="n">
         <v>4.857</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="P38" s="3" t="n">
         <v>-0.9676755198682274</v>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>4.895999999999999</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="R38" s="4" t="n">
         <v>4.867</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="S38" s="3" t="n">
         <v>0.5958495993424906</v>
       </c>
-      <c r="R38" s="5" t="n">
+      <c r="T38" s="5" t="n">
         <v>1.563525119210718</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3041,55 +3089,56 @@
       <c r="C39" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E39" s="3" t="n"/>
       <c r="F39" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>603444</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>吉比特</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="J39" s="4" t="n">
         <v>328.69</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="K39" s="4" t="n">
         <v>358.12</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="L39" s="3" t="n">
         <v>8.953725394748858</v>
       </c>
-      <c r="K39" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>361.55</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>332.52</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="O39" s="4" t="n">
         <v>334.83</v>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="P39" s="3" t="n">
         <v>-0.6899023385001368</v>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="Q39" s="4" t="n">
         <v>339.542</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="R39" s="4" t="n">
         <v>336.813</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="S39" s="3" t="n">
         <v>0.8102418849628812</v>
       </c>
-      <c r="R39" s="5" t="n">
+      <c r="T39" s="5" t="n">
         <v>1.500144223463018</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3109,55 +3158,56 @@
       <c r="C40" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E40" s="3" t="n"/>
       <c r="F40" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>300182</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>捷成股份</t>
         </is>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="J40" s="4" t="n">
         <v>5.33</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="K40" s="4" t="n">
         <v>5.9</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <v>10.69418386491559</v>
       </c>
-      <c r="K40" s="4" t="n">
+      <c r="M40" s="4" t="n">
         <v>6.39</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>5.526000000000001</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="O40" s="4" t="n">
         <v>5.555000000000001</v>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="P40" s="3" t="n">
         <v>-0.5220522052205245</v>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>5.648</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="R40" s="4" t="n">
         <v>5.58</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="S40" s="3" t="n">
         <v>1.218637992831528</v>
       </c>
-      <c r="R40" s="5" t="n">
+      <c r="T40" s="5" t="n">
         <v>1.740690198052053</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3177,55 +3227,56 @@
       <c r="C41" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E41" s="3" t="n"/>
       <c r="F41" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>300364</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>中文在线</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="J41" s="4" t="n">
         <v>23.45</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="K41" s="4" t="n">
         <v>26.59</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="L41" s="3" t="n">
         <v>13.39019189765458</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <v>28.14</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>24.172</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="O41" s="4" t="n">
         <v>24.289</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="P41" s="3" t="n">
         <v>-0.4816995347688091</v>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="Q41" s="4" t="n">
         <v>24.904</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="R41" s="4" t="n">
         <v>24.422</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="S41" s="3" t="n">
         <v>1.973630333306042</v>
       </c>
-      <c r="R41" s="5" t="n">
+      <c r="T41" s="5" t="n">
         <v>2.455329868074851</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3245,55 +3296,56 @@
       <c r="C42" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E42" s="3" t="n"/>
       <c r="F42" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>300063</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>天龙集团</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>7.93</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="K42" s="4" t="n">
         <v>9.01</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <v>13.61916771752838</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <v>9.51</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>8.251999999999999</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="O42" s="4" t="n">
         <v>8.348000000000001</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="P42" s="3" t="n">
         <v>-1.149976042165812</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>8.484</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="R42" s="4" t="n">
         <v>8.375</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="S42" s="3" t="n">
         <v>1.301492537313442</v>
       </c>
-      <c r="R42" s="5" t="n">
+      <c r="T42" s="5" t="n">
         <v>2.451468579479255</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3313,55 +3365,56 @@
       <c r="C43" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E43" s="3" t="n"/>
       <c r="F43" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>301262</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>海看股份</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="J43" s="4" t="n">
         <v>20.35</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="K43" s="4" t="n">
         <v>23.36</v>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="L43" s="3" t="n">
         <v>14.79115479115478</v>
       </c>
-      <c r="K43" s="4" t="n">
+      <c r="M43" s="4" t="n">
         <v>24.42</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="N43" s="4" t="n">
         <v>20.914</v>
       </c>
-      <c r="M43" s="4" t="n">
+      <c r="O43" s="4" t="n">
         <v>21.21099999999993</v>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="P43" s="3" t="n">
         <v>-1.400216868605564</v>
       </c>
-      <c r="O43" s="4" t="n">
+      <c r="Q43" s="4" t="n">
         <v>21.638</v>
       </c>
-      <c r="P43" s="4" t="n">
+      <c r="R43" s="4" t="n">
         <v>21.336</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="S43" s="3" t="n">
         <v>1.415448068991365</v>
       </c>
-      <c r="R43" s="5" t="n">
+      <c r="T43" s="5" t="n">
         <v>2.815664937596929</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3381,55 +3434,56 @@
       <c r="C44" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E44" s="3" t="n"/>
       <c r="F44" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>300959</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>线上线下</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="J44" s="4" t="n">
         <v>68.5</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="K44" s="4" t="n">
         <v>79.03</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="L44" s="3" t="n">
         <v>15.37226277372263</v>
       </c>
-      <c r="K44" s="4" t="n">
+      <c r="M44" s="4" t="n">
         <v>82.2</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="N44" s="4" t="n">
         <v>72.27799999999999</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="O44" s="4" t="n">
         <v>73.40299999999999</v>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="P44" s="3" t="n">
         <v>-1.532634905930275</v>
       </c>
-      <c r="O44" s="4" t="n">
+      <c r="Q44" s="4" t="n">
         <v>74.042</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="R44" s="4" t="n">
         <v>73.756</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="S44" s="3" t="n">
         <v>0.3877650631813001</v>
       </c>
-      <c r="R44" s="5" t="n">
+      <c r="T44" s="5" t="n">
         <v>1.920399969111575</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3449,55 +3503,56 @@
       <c r="C45" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>300785</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>值得买</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="J45" s="4" t="n">
         <v>32.47</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="K45" s="4" t="n">
         <v>37.95</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="L45" s="3" t="n">
         <v>16.87711733908224</v>
       </c>
-      <c r="K45" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <v>38.96</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="N45" s="4" t="n">
         <v>34.376</v>
       </c>
-      <c r="M45" s="4" t="n">
+      <c r="O45" s="4" t="n">
         <v>34.82600000000001</v>
       </c>
-      <c r="N45" s="3" t="n">
+      <c r="P45" s="3" t="n">
         <v>-1.292138057772951</v>
       </c>
-      <c r="O45" s="4" t="n">
+      <c r="Q45" s="4" t="n">
         <v>35.33</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="R45" s="4" t="n">
         <v>35.05500000000001</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="S45" s="3" t="n">
         <v>0.7844815290257934</v>
       </c>
-      <c r="R45" s="5" t="n">
+      <c r="T45" s="5" t="n">
         <v>2.076619586798745</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3517,55 +3572,56 @@
       <c r="C46" s="3" t="n">
         <v>15.49</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>301171</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>易点天下</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="J46" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="K46" s="4" t="n">
         <v>33.87</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="L46" s="3" t="n">
         <v>17.19723183391002</v>
       </c>
-      <c r="K46" s="4" t="n">
+      <c r="M46" s="4" t="n">
         <v>34.68</v>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="N46" s="4" t="n">
         <v>30.872</v>
       </c>
-      <c r="M46" s="4" t="n">
+      <c r="O46" s="4" t="n">
         <v>30.89</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="P46" s="3" t="n">
         <v>-0.0582712852055467</v>
       </c>
-      <c r="O46" s="4" t="n">
+      <c r="Q46" s="4" t="n">
         <v>31.734</v>
       </c>
-      <c r="P46" s="4" t="n">
+      <c r="R46" s="4" t="n">
         <v>31.077</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="S46" s="3" t="n">
         <v>2.11410367796121</v>
       </c>
-      <c r="R46" s="5" t="n">
+      <c r="T46" s="5" t="n">
         <v>2.172374963166757</v>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3585,55 +3641,56 @@
       <c r="C47" s="3" t="n">
         <v>67.14</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E47" s="3" t="n"/>
       <c r="F47" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>301182</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>凯旺科技</t>
         </is>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="J47" s="4" t="n">
         <v>43.21</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="K47" s="4" t="n">
         <v>50.56</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="L47" s="3" t="n">
         <v>17.00995140013886</v>
       </c>
-      <c r="K47" s="4" t="n">
+      <c r="M47" s="4" t="n">
         <v>51.85</v>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="N47" s="4" t="n">
         <v>46.172</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="O47" s="4" t="n">
         <v>46.638</v>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="P47" s="3" t="n">
         <v>-0.9991852137741675</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="Q47" s="4" t="n">
         <v>47.264</v>
       </c>
-      <c r="P47" s="4" t="n">
+      <c r="R47" s="4" t="n">
         <v>46.95</v>
       </c>
-      <c r="Q47" s="3" t="n">
+      <c r="S47" s="3" t="n">
         <v>0.6687965921192696</v>
       </c>
-      <c r="R47" s="5" t="n">
+      <c r="T47" s="5" t="n">
         <v>1.667981805893437</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3653,55 +3710,56 @@
       <c r="C48" s="3" t="n">
         <v>67.14</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E48" s="3" t="n"/>
       <c r="F48" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>688697</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>纽威数控</t>
         </is>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="J48" s="4" t="n">
         <v>11.76</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="K48" s="4" t="n">
         <v>13.78</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="L48" s="3" t="n">
         <v>17.17687074829932</v>
       </c>
-      <c r="K48" s="4" t="n">
+      <c r="M48" s="4" t="n">
         <v>14.11</v>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="N48" s="4" t="n">
         <v>12.474</v>
       </c>
-      <c r="M48" s="4" t="n">
+      <c r="O48" s="4" t="n">
         <v>12.548</v>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="P48" s="3" t="n">
         <v>-0.5897354160025459</v>
       </c>
-      <c r="O48" s="4" t="n">
+      <c r="Q48" s="4" t="n">
         <v>12.832</v>
       </c>
-      <c r="P48" s="4" t="n">
+      <c r="R48" s="4" t="n">
         <v>12.656</v>
       </c>
-      <c r="Q48" s="3" t="n">
+      <c r="S48" s="3" t="n">
         <v>1.390644753476589</v>
       </c>
-      <c r="R48" s="5" t="n">
+      <c r="T48" s="5" t="n">
         <v>1.980380169479135</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3721,58 +3779,59 @@
       <c r="C49" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>3</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>300006</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>莱美药业</t>
         </is>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="J49" s="4" t="n">
         <v>8.27</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="K49" s="4" t="n">
         <v>9.58</v>
       </c>
-      <c r="J49" s="3" t="n">
+      <c r="L49" s="3" t="n">
         <v>15.8403869407497</v>
       </c>
-      <c r="K49" s="4" t="n">
+      <c r="M49" s="4" t="n">
         <v>9.92</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="N49" s="4" t="n">
         <v>8.528</v>
       </c>
-      <c r="M49" s="4" t="n">
+      <c r="O49" s="4" t="n">
         <v>8.674000000000001</v>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="P49" s="3" t="n">
         <v>-1.683191145953433</v>
       </c>
-      <c r="O49" s="4" t="n">
+      <c r="Q49" s="4" t="n">
         <v>8.82</v>
       </c>
-      <c r="P49" s="4" t="n">
+      <c r="R49" s="4" t="n">
         <v>8.818999999999999</v>
       </c>
-      <c r="Q49" s="3" t="n">
+      <c r="S49" s="3" t="n">
         <v>0.01133915409912145</v>
       </c>
-      <c r="R49" s="5" t="n">
+      <c r="T49" s="5" t="n">
         <v>1.694530300052555</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3792,55 +3851,56 @@
       <c r="C50" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E50" s="3" t="n"/>
       <c r="F50" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>002950</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>奥美医疗</t>
         </is>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="J50" s="4" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="K50" s="4" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="L50" s="3" t="n">
         <v>7.785888077858871</v>
       </c>
-      <c r="K50" s="4" t="n">
+      <c r="M50" s="4" t="n">
         <v>9.039999999999999</v>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="N50" s="4" t="n">
         <v>8.343999999999999</v>
       </c>
-      <c r="M50" s="4" t="n">
+      <c r="O50" s="4" t="n">
         <v>8.372</v>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="P50" s="3" t="n">
         <v>-0.3344481605351279</v>
       </c>
-      <c r="O50" s="4" t="n">
+      <c r="Q50" s="4" t="n">
         <v>8.504</v>
       </c>
-      <c r="P50" s="4" t="n">
+      <c r="R50" s="4" t="n">
         <v>8.406000000000001</v>
       </c>
-      <c r="Q50" s="3" t="n">
+      <c r="S50" s="3" t="n">
         <v>1.165833928146554</v>
       </c>
-      <c r="R50" s="5" t="n">
+      <c r="T50" s="5" t="n">
         <v>1.500282088681681</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3860,55 +3920,56 @@
       <c r="C51" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E51" s="3" t="n"/>
       <c r="F51" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>301408</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>华人健康</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="J51" s="4" t="n">
         <v>13.78</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="K51" s="4" t="n">
         <v>14.88</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="L51" s="3" t="n">
         <v>7.982583454281578</v>
       </c>
-      <c r="K51" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>16.53</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="N51" s="4" t="n">
         <v>13.936</v>
       </c>
-      <c r="M51" s="4" t="n">
+      <c r="O51" s="4" t="n">
         <v>13.95</v>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="P51" s="3" t="n">
         <v>-0.100358422939073</v>
       </c>
-      <c r="O51" s="4" t="n">
+      <c r="Q51" s="4" t="n">
         <v>14.236</v>
       </c>
-      <c r="P51" s="4" t="n">
+      <c r="R51" s="4" t="n">
         <v>14.039</v>
       </c>
-      <c r="Q51" s="3" t="n">
+      <c r="S51" s="3" t="n">
         <v>1.403233848564733</v>
       </c>
-      <c r="R51" s="5" t="n">
+      <c r="T51" s="5" t="n">
         <v>1.503592271503806</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3928,55 +3989,56 @@
       <c r="C52" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E52" s="3" t="n"/>
       <c r="F52" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>300702</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>天宇股份</t>
         </is>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="J52" s="4" t="n">
         <v>20.01</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="K52" s="4" t="n">
         <v>21.77</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="L52" s="3" t="n">
         <v>8.795602198900543</v>
       </c>
-      <c r="K52" s="4" t="n">
+      <c r="M52" s="4" t="n">
         <v>24.01</v>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="N52" s="4" t="n">
         <v>20.394</v>
       </c>
-      <c r="M52" s="4" t="n">
+      <c r="O52" s="4" t="n">
         <v>20.548</v>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="P52" s="3" t="n">
         <v>-0.749464668094213</v>
       </c>
-      <c r="O52" s="4" t="n">
+      <c r="Q52" s="4" t="n">
         <v>20.792</v>
       </c>
-      <c r="P52" s="4" t="n">
+      <c r="R52" s="4" t="n">
         <v>20.632</v>
       </c>
-      <c r="Q52" s="3" t="n">
+      <c r="S52" s="3" t="n">
         <v>0.7754943776657752</v>
       </c>
-      <c r="R52" s="5" t="n">
+      <c r="T52" s="5" t="n">
         <v>1.524959045759988</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -3996,55 +4058,56 @@
       <c r="C53" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E53" s="3" t="n"/>
       <c r="F53" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>603259</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>药明康德</t>
         </is>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="J53" s="4" t="n">
         <v>141.48</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="K53" s="4" t="n">
         <v>154.19</v>
       </c>
-      <c r="J53" s="3" t="n">
+      <c r="L53" s="3" t="n">
         <v>8.983601922533225</v>
       </c>
-      <c r="K53" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <v>155.62</v>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="N53" s="4" t="n">
         <v>145.54</v>
       </c>
-      <c r="M53" s="4" t="n">
+      <c r="O53" s="4" t="n">
         <v>146.801</v>
       </c>
-      <c r="N53" s="3" t="n">
+      <c r="P53" s="3" t="n">
         <v>-0.8589859742099804</v>
       </c>
-      <c r="O53" s="4" t="n">
+      <c r="Q53" s="4" t="n">
         <v>148.116</v>
       </c>
-      <c r="P53" s="4" t="n">
+      <c r="R53" s="4" t="n">
         <v>146.77</v>
       </c>
-      <c r="Q53" s="3" t="n">
+      <c r="S53" s="3" t="n">
         <v>0.9170811473734553</v>
       </c>
-      <c r="R53" s="5" t="n">
+      <c r="T53" s="5" t="n">
         <v>1.776067121583436</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4064,55 +4127,56 @@
       <c r="C54" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E54" s="3" t="n"/>
       <c r="F54" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>600479</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>千金药业</t>
         </is>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="J54" s="4" t="n">
         <v>10.46</v>
       </c>
-      <c r="I54" s="4" t="n">
+      <c r="K54" s="4" t="n">
         <v>11.43</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="L54" s="3" t="n">
         <v>9.273422562141477</v>
       </c>
-      <c r="K54" s="4" t="n">
+      <c r="M54" s="4" t="n">
         <v>11.5</v>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="N54" s="4" t="n">
         <v>10.75629889298905</v>
       </c>
-      <c r="M54" s="4" t="n">
+      <c r="O54" s="4" t="n">
         <v>10.87729335793374</v>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="P54" s="3" t="n">
         <v>-1.112358203122654</v>
       </c>
-      <c r="O54" s="4" t="n">
+      <c r="Q54" s="4" t="n">
         <v>10.93193357933587</v>
       </c>
-      <c r="P54" s="4" t="n">
+      <c r="R54" s="4" t="n">
         <v>10.88938929889313</v>
       </c>
-      <c r="Q54" s="3" t="n">
+      <c r="S54" s="3" t="n">
         <v>0.3906948247967001</v>
       </c>
-      <c r="R54" s="5" t="n">
+      <c r="T54" s="5" t="n">
         <v>1.503053027919354</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4132,55 +4196,56 @@
       <c r="C55" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E55" s="3" t="n"/>
       <c r="F55" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>688710</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>益诺思</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="J55" s="4" t="n">
         <v>83.36</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="K55" s="4" t="n">
         <v>91.54000000000001</v>
       </c>
-      <c r="J55" s="3" t="n">
+      <c r="L55" s="3" t="n">
         <v>9.812859884836866</v>
       </c>
-      <c r="K55" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>100.03</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="N55" s="4" t="n">
         <v>83.75</v>
       </c>
-      <c r="M55" s="4" t="n">
+      <c r="O55" s="4" t="n">
         <v>84.50099999999999</v>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="P55" s="3" t="n">
         <v>-0.8887468787351471</v>
       </c>
-      <c r="O55" s="4" t="n">
+      <c r="Q55" s="4" t="n">
         <v>85.82000000000001</v>
       </c>
-      <c r="P55" s="4" t="n">
+      <c r="R55" s="4" t="n">
         <v>84.71000000000001</v>
       </c>
-      <c r="Q55" s="3" t="n">
+      <c r="S55" s="3" t="n">
         <v>1.310352968952899</v>
       </c>
-      <c r="R55" s="5" t="n">
+      <c r="T55" s="5" t="n">
         <v>2.199099847688046</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4200,55 +4265,56 @@
       <c r="C56" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E56" s="3" t="n"/>
       <c r="F56" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>300363</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>博腾股份</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="J56" s="4" t="n">
         <v>20.93</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="K56" s="4" t="n">
         <v>23.15</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="L56" s="3" t="n">
         <v>10.60678451982799</v>
       </c>
-      <c r="K56" s="4" t="n">
+      <c r="M56" s="4" t="n">
         <v>25.11</v>
       </c>
-      <c r="L56" s="4" t="n">
+      <c r="N56" s="4" t="n">
         <v>21.43</v>
       </c>
-      <c r="M56" s="4" t="n">
+      <c r="O56" s="4" t="n">
         <v>21.526</v>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="P56" s="3" t="n">
         <v>-0.4459723125522785</v>
       </c>
-      <c r="O56" s="4" t="n">
+      <c r="Q56" s="4" t="n">
         <v>21.876</v>
       </c>
-      <c r="P56" s="4" t="n">
+      <c r="R56" s="4" t="n">
         <v>21.647</v>
       </c>
-      <c r="Q56" s="3" t="n">
+      <c r="S56" s="3" t="n">
         <v>1.057883309465502</v>
       </c>
-      <c r="R56" s="5" t="n">
+      <c r="T56" s="5" t="n">
         <v>1.50385562201778</v>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4268,55 +4334,56 @@
       <c r="C57" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E57" s="3" t="n"/>
       <c r="F57" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>300255</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>常山药业</t>
         </is>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="J57" s="4" t="n">
         <v>18.73</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="K57" s="4" t="n">
         <v>20.9</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="L57" s="3" t="n">
         <v>11.58569140416443</v>
       </c>
-      <c r="K57" s="4" t="n">
+      <c r="M57" s="4" t="n">
         <v>22.47</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <v>19.526</v>
       </c>
-      <c r="M57" s="4" t="n">
+      <c r="O57" s="4" t="n">
         <v>19.721</v>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="P57" s="3" t="n">
         <v>-0.9887936717204893</v>
       </c>
-      <c r="O57" s="4" t="n">
+      <c r="Q57" s="4" t="n">
         <v>19.884</v>
       </c>
-      <c r="P57" s="4" t="n">
+      <c r="R57" s="4" t="n">
         <v>19.782</v>
       </c>
-      <c r="Q57" s="3" t="n">
+      <c r="S57" s="3" t="n">
         <v>0.515620260843197</v>
       </c>
-      <c r="R57" s="5" t="n">
+      <c r="T57" s="5" t="n">
         <v>1.504413932563686</v>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4336,55 +4403,56 @@
       <c r="C58" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E58" s="3" t="n"/>
       <c r="F58" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>300705</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>九典制药</t>
         </is>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="J58" s="4" t="n">
         <v>10.33</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="K58" s="4" t="n">
         <v>11.54</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="L58" s="3" t="n">
         <v>11.71345595353339</v>
       </c>
-      <c r="K58" s="4" t="n">
+      <c r="M58" s="4" t="n">
         <v>12.39</v>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="N58" s="4" t="n">
         <v>10.682</v>
       </c>
-      <c r="M58" s="4" t="n">
+      <c r="O58" s="4" t="n">
         <v>10.718</v>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="P58" s="3" t="n">
         <v>-0.3358835603657573</v>
       </c>
-      <c r="O58" s="4" t="n">
+      <c r="Q58" s="4" t="n">
         <v>10.926</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="R58" s="4" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q58" s="3" t="n">
+      <c r="S58" s="3" t="n">
         <v>1.166666666666649</v>
       </c>
-      <c r="R58" s="5" t="n">
+      <c r="T58" s="5" t="n">
         <v>1.502550227032406</v>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4404,55 +4472,56 @@
       <c r="C59" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E59" s="3" t="n"/>
       <c r="F59" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>688607</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>康众科技</t>
         </is>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="J59" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="K59" s="4" t="n">
         <v>34.67</v>
       </c>
-      <c r="J59" s="3" t="n">
+      <c r="L59" s="3" t="n">
         <v>11.83870967741936</v>
       </c>
-      <c r="K59" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <v>37.2</v>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="N59" s="4" t="n">
         <v>32.822</v>
       </c>
-      <c r="M59" s="4" t="n">
+      <c r="O59" s="4" t="n">
         <v>33.042</v>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="P59" s="3" t="n">
         <v>-0.6658192603353319</v>
       </c>
-      <c r="O59" s="4" t="n">
+      <c r="Q59" s="4" t="n">
         <v>33.384</v>
       </c>
-      <c r="P59" s="4" t="n">
+      <c r="R59" s="4" t="n">
         <v>33.10700000000001</v>
       </c>
-      <c r="Q59" s="3" t="n">
+      <c r="S59" s="3" t="n">
         <v>0.8366810644274469</v>
       </c>
-      <c r="R59" s="5" t="n">
+      <c r="T59" s="5" t="n">
         <v>1.502500324762779</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4472,55 +4541,56 @@
       <c r="C60" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E60" s="3" t="n"/>
       <c r="F60" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>300434</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>金石亚药</t>
         </is>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="J60" s="4" t="n">
         <v>11.31</v>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="K60" s="4" t="n">
         <v>12.66</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="L60" s="3" t="n">
         <v>11.93633952254642</v>
       </c>
-      <c r="K60" s="4" t="n">
+      <c r="M60" s="4" t="n">
         <v>13.57</v>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>12.044</v>
       </c>
-      <c r="M60" s="4" t="n">
+      <c r="O60" s="4" t="n">
         <v>12.294</v>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="P60" s="3" t="n">
         <v>-2.033512282414185</v>
       </c>
-      <c r="O60" s="4" t="n">
+      <c r="Q60" s="4" t="n">
         <v>12.242</v>
       </c>
-      <c r="P60" s="4" t="n">
+      <c r="R60" s="4" t="n">
         <v>12.24</v>
       </c>
-      <c r="Q60" s="3" t="n">
+      <c r="S60" s="3" t="n">
         <v>0.01633986928104569</v>
       </c>
-      <c r="R60" s="5" t="n">
+      <c r="T60" s="5" t="n">
         <v>2.049852151695231</v>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4540,55 +4610,56 @@
       <c r="C61" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E61" s="3" t="n"/>
       <c r="F61" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>301277</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>新天地</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="J61" s="4" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="K61" s="4" t="n">
         <v>10.34</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="L61" s="3" t="n">
         <v>12.14750542299348</v>
       </c>
-      <c r="K61" s="4" t="n">
+      <c r="M61" s="4" t="n">
         <v>11.06</v>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="N61" s="4" t="n">
         <v>9.634</v>
       </c>
-      <c r="M61" s="4" t="n">
+      <c r="O61" s="4" t="n">
         <v>9.775000000000002</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="P61" s="3" t="n">
         <v>-1.442455242966767</v>
       </c>
-      <c r="O61" s="4" t="n">
+      <c r="Q61" s="4" t="n">
         <v>9.818000000000001</v>
       </c>
-      <c r="P61" s="4" t="n">
+      <c r="R61" s="4" t="n">
         <v>9.792000000000002</v>
       </c>
-      <c r="Q61" s="3" t="n">
+      <c r="S61" s="3" t="n">
         <v>0.2655228758169814</v>
       </c>
-      <c r="R61" s="5" t="n">
+      <c r="T61" s="5" t="n">
         <v>1.707978118783748</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4608,55 +4679,56 @@
       <c r="C62" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E62" s="3" t="n"/>
       <c r="F62" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>301333</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>诺思格</t>
         </is>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="J62" s="4" t="n">
         <v>51.85</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="K62" s="4" t="n">
         <v>58.46</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="L62" s="3" t="n">
         <v>12.74831243972998</v>
       </c>
-      <c r="K62" s="4" t="n">
+      <c r="M62" s="4" t="n">
         <v>62.22</v>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="N62" s="4" t="n">
         <v>53.51000000000001</v>
       </c>
-      <c r="M62" s="4" t="n">
+      <c r="O62" s="4" t="n">
         <v>54.26900000000001</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="P62" s="3" t="n">
         <v>-1.398588512778931</v>
       </c>
-      <c r="O62" s="4" t="n">
+      <c r="Q62" s="4" t="n">
         <v>54.876</v>
       </c>
-      <c r="P62" s="4" t="n">
+      <c r="R62" s="4" t="n">
         <v>54.463</v>
       </c>
-      <c r="Q62" s="3" t="n">
+      <c r="S62" s="3" t="n">
         <v>0.7583129831261637</v>
       </c>
-      <c r="R62" s="5" t="n">
+      <c r="T62" s="5" t="n">
         <v>2.156901495905095</v>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4676,55 +4748,56 @@
       <c r="C63" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E63" s="3" t="n"/>
       <c r="F63" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>300246</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>宝莱特</t>
         </is>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="J63" s="4" t="n">
         <v>12.22</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="K63" s="4" t="n">
         <v>13.85</v>
       </c>
-      <c r="J63" s="3" t="n">
+      <c r="L63" s="3" t="n">
         <v>13.33878887070377</v>
       </c>
-      <c r="K63" s="4" t="n">
+      <c r="M63" s="4" t="n">
         <v>14.66</v>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="N63" s="4" t="n">
         <v>12.864</v>
       </c>
-      <c r="M63" s="4" t="n">
+      <c r="O63" s="4" t="n">
         <v>12.941</v>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="P63" s="3" t="n">
         <v>-0.5950081137470087</v>
       </c>
-      <c r="O63" s="4" t="n">
+      <c r="Q63" s="4" t="n">
         <v>13.106</v>
       </c>
-      <c r="P63" s="4" t="n">
+      <c r="R63" s="4" t="n">
         <v>12.988</v>
       </c>
-      <c r="Q63" s="3" t="n">
+      <c r="S63" s="3" t="n">
         <v>0.9085309516476681</v>
       </c>
-      <c r="R63" s="5" t="n">
+      <c r="T63" s="5" t="n">
         <v>1.503539065394677</v>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4744,55 +4817,56 @@
       <c r="C64" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E64" s="3" t="n"/>
       <c r="F64" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>300109</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>新开源</t>
         </is>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="J64" s="4" t="n">
         <v>10.77</v>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="K64" s="4" t="n">
         <v>12.33</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="L64" s="3" t="n">
         <v>14.48467966573816</v>
       </c>
-      <c r="K64" s="4" t="n">
+      <c r="M64" s="4" t="n">
         <v>12.92</v>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="N64" s="4" t="n">
         <v>11.36</v>
       </c>
-      <c r="M64" s="4" t="n">
+      <c r="O64" s="4" t="n">
         <v>11.514</v>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="P64" s="3" t="n">
         <v>-1.337502171269755</v>
       </c>
-      <c r="O64" s="4" t="n">
+      <c r="Q64" s="4" t="n">
         <v>11.602</v>
       </c>
-      <c r="P64" s="4" t="n">
+      <c r="R64" s="4" t="n">
         <v>11.577</v>
       </c>
-      <c r="Q64" s="3" t="n">
+      <c r="S64" s="3" t="n">
         <v>0.2159454090005841</v>
       </c>
-      <c r="R64" s="5" t="n">
+      <c r="T64" s="5" t="n">
         <v>1.55344758027034</v>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4812,55 +4886,56 @@
       <c r="C65" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E65" s="3" t="n"/>
       <c r="F65" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>300347</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>泰格医药</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="J65" s="4" t="n">
         <v>47.82</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="K65" s="4" t="n">
         <v>54.89</v>
       </c>
-      <c r="J65" s="3" t="n">
+      <c r="L65" s="3" t="n">
         <v>14.78460895023004</v>
       </c>
-      <c r="K65" s="4" t="n">
+      <c r="M65" s="4" t="n">
         <v>57.38</v>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="N65" s="4" t="n">
         <v>50.25599999999999</v>
       </c>
-      <c r="M65" s="4" t="n">
+      <c r="O65" s="4" t="n">
         <v>50.69799999999999</v>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="P65" s="3" t="n">
         <v>-0.8718292634817937</v>
       </c>
-      <c r="O65" s="4" t="n">
+      <c r="Q65" s="4" t="n">
         <v>51.302</v>
       </c>
-      <c r="P65" s="4" t="n">
+      <c r="R65" s="4" t="n">
         <v>50.98099999999999</v>
       </c>
-      <c r="Q65" s="3" t="n">
+      <c r="S65" s="3" t="n">
         <v>0.6296463388321349</v>
       </c>
-      <c r="R65" s="5" t="n">
+      <c r="T65" s="5" t="n">
         <v>1.501475602313929</v>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4880,55 +4955,56 @@
       <c r="C66" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E66" s="3" t="n"/>
       <c r="F66" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
           <t>300723</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>一品红</t>
         </is>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="J66" s="4" t="n">
         <v>28.77</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="K66" s="4" t="n">
         <v>33.08</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="L66" s="3" t="n">
         <v>14.98088286409454</v>
       </c>
-      <c r="K66" s="4" t="n">
+      <c r="M66" s="4" t="n">
         <v>34.52</v>
       </c>
-      <c r="L66" s="4" t="n">
+      <c r="N66" s="4" t="n">
         <v>30.38</v>
       </c>
-      <c r="M66" s="4" t="n">
+      <c r="O66" s="4" t="n">
         <v>30.584</v>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="P66" s="3" t="n">
         <v>-0.6670154329060929</v>
       </c>
-      <c r="O66" s="4" t="n">
+      <c r="Q66" s="4" t="n">
         <v>31.088</v>
       </c>
-      <c r="P66" s="4" t="n">
+      <c r="R66" s="4" t="n">
         <v>30.831</v>
       </c>
-      <c r="Q66" s="3" t="n">
+      <c r="S66" s="3" t="n">
         <v>0.8335765949855745</v>
       </c>
-      <c r="R66" s="5" t="n">
+      <c r="T66" s="5" t="n">
         <v>1.500592027891667</v>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -4948,55 +5024,56 @@
       <c r="C67" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E67" s="3" t="n"/>
       <c r="F67" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
           <t>300683</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>海特生物</t>
         </is>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="J67" s="4" t="n">
         <v>21.76</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="K67" s="4" t="n">
         <v>25.03</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="L67" s="3" t="n">
         <v>15.02757352941175</v>
       </c>
-      <c r="K67" s="4" t="n">
+      <c r="M67" s="4" t="n">
         <v>26.11</v>
       </c>
-      <c r="L67" s="4" t="n">
+      <c r="N67" s="4" t="n">
         <v>23.268</v>
       </c>
-      <c r="M67" s="4" t="n">
+      <c r="O67" s="4" t="n">
         <v>23.612</v>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="P67" s="3" t="n">
         <v>-1.456886328985241</v>
       </c>
-      <c r="O67" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>23.674</v>
       </c>
-      <c r="P67" s="4" t="n">
+      <c r="R67" s="4" t="n">
         <v>23.663</v>
       </c>
-      <c r="Q67" s="3" t="n">
+      <c r="S67" s="3" t="n">
         <v>0.0464860753074392</v>
       </c>
-      <c r="R67" s="5" t="n">
+      <c r="T67" s="5" t="n">
         <v>1.50337240429268</v>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5016,55 +5093,56 @@
       <c r="C68" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E68" s="3" t="n"/>
       <c r="F68" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>300725</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>药石科技</t>
         </is>
       </c>
-      <c r="H68" s="4" t="n">
+      <c r="J68" s="4" t="n">
         <v>41.36</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="K68" s="4" t="n">
         <v>47.86</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="L68" s="3" t="n">
         <v>15.71566731141198</v>
       </c>
-      <c r="K68" s="4" t="n">
+      <c r="M68" s="4" t="n">
         <v>49.63</v>
       </c>
-      <c r="L68" s="4" t="n">
+      <c r="N68" s="4" t="n">
         <v>44.188</v>
       </c>
-      <c r="M68" s="4" t="n">
+      <c r="O68" s="4" t="n">
         <v>44.511</v>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="P68" s="3" t="n">
         <v>-0.7256633191795259</v>
       </c>
-      <c r="O68" s="4" t="n">
+      <c r="Q68" s="4" t="n">
         <v>45.09999999999999</v>
       </c>
-      <c r="P68" s="4" t="n">
+      <c r="R68" s="4" t="n">
         <v>44.753</v>
       </c>
-      <c r="Q68" s="3" t="n">
+      <c r="S68" s="3" t="n">
         <v>0.7753670145018043</v>
       </c>
-      <c r="R68" s="5" t="n">
+      <c r="T68" s="5" t="n">
         <v>1.50103033368133</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5084,55 +5162,56 @@
       <c r="C69" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E69" s="3" t="n"/>
       <c r="F69" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>301257</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>普蕊斯</t>
         </is>
       </c>
-      <c r="H69" s="4" t="n">
+      <c r="J69" s="4" t="n">
         <v>31.5</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="K69" s="4" t="n">
         <v>36.68</v>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="L69" s="3" t="n">
         <v>16.44444444444444</v>
       </c>
-      <c r="K69" s="4" t="n">
+      <c r="M69" s="4" t="n">
         <v>37.8</v>
       </c>
-      <c r="L69" s="4" t="n">
+      <c r="N69" s="4" t="n">
         <v>33.264</v>
       </c>
-      <c r="M69" s="4" t="n">
+      <c r="O69" s="4" t="n">
         <v>33.722</v>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="P69" s="3" t="n">
         <v>-1.358163809975699</v>
       </c>
-      <c r="O69" s="4" t="n">
+      <c r="Q69" s="4" t="n">
         <v>34.134</v>
       </c>
-      <c r="P69" s="4" t="n">
+      <c r="R69" s="4" t="n">
         <v>33.854</v>
       </c>
-      <c r="Q69" s="3" t="n">
+      <c r="S69" s="3" t="n">
         <v>0.8270809948602853</v>
       </c>
-      <c r="R69" s="5" t="n">
+      <c r="T69" s="5" t="n">
         <v>2.185244804835984</v>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5152,55 +5231,56 @@
       <c r="C70" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E70" s="3" t="n"/>
       <c r="F70" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>301093</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>华兰股份</t>
         </is>
       </c>
-      <c r="H70" s="4" t="n">
+      <c r="J70" s="4" t="n">
         <v>47.68</v>
       </c>
-      <c r="I70" s="4" t="n">
+      <c r="K70" s="4" t="n">
         <v>55.64</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="L70" s="3" t="n">
         <v>16.69463087248322</v>
       </c>
-      <c r="K70" s="4" t="n">
+      <c r="M70" s="4" t="n">
         <v>57.21</v>
       </c>
-      <c r="L70" s="4" t="n">
+      <c r="N70" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="M70" s="4" t="n">
+      <c r="O70" s="4" t="n">
         <v>51.384</v>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="P70" s="3" t="n">
         <v>-1.720379884789036</v>
       </c>
-      <c r="O70" s="4" t="n">
+      <c r="Q70" s="4" t="n">
         <v>51.824</v>
       </c>
-      <c r="P70" s="4" t="n">
+      <c r="R70" s="4" t="n">
         <v>51.822</v>
       </c>
-      <c r="Q70" s="3" t="n">
+      <c r="S70" s="3" t="n">
         <v>0.003859364748559635</v>
       </c>
-      <c r="R70" s="5" t="n">
+      <c r="T70" s="5" t="n">
         <v>1.724239249537596</v>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5220,55 +5300,56 @@
       <c r="C71" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E71" s="3" t="n"/>
       <c r="F71" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>301201</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>诚达药业</t>
         </is>
       </c>
-      <c r="H71" s="4" t="n">
+      <c r="J71" s="4" t="n">
         <v>24.01</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="K71" s="4" t="n">
         <v>28.02</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="L71" s="3" t="n">
         <v>16.70137442732194</v>
       </c>
-      <c r="K71" s="4" t="n">
+      <c r="M71" s="4" t="n">
         <v>28.81</v>
       </c>
-      <c r="L71" s="4" t="n">
+      <c r="N71" s="4" t="n">
         <v>25.546</v>
       </c>
-      <c r="M71" s="4" t="n">
+      <c r="O71" s="4" t="n">
         <v>25.963</v>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="P71" s="3" t="n">
         <v>-1.606131802950361</v>
       </c>
-      <c r="O71" s="4" t="n">
+      <c r="Q71" s="4" t="n">
         <v>26.066</v>
       </c>
-      <c r="P71" s="4" t="n">
+      <c r="R71" s="4" t="n">
         <v>26.065</v>
       </c>
-      <c r="Q71" s="3" t="n">
+      <c r="S71" s="3" t="n">
         <v>0.003836562440051594</v>
       </c>
-      <c r="R71" s="5" t="n">
+      <c r="T71" s="5" t="n">
         <v>1.609968365390413</v>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5288,55 +5369,56 @@
       <c r="C72" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E72" s="3" t="n"/>
       <c r="F72" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>920047</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>诺思兰德</t>
         </is>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="J72" s="4" t="n">
         <v>12.62</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="K72" s="4" t="n">
         <v>14.75</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="L72" s="3" t="n">
         <v>16.87797147385104</v>
       </c>
-      <c r="K72" s="4" t="n">
+      <c r="M72" s="4" t="n">
         <v>15.14</v>
       </c>
-      <c r="L72" s="4" t="n">
+      <c r="N72" s="4" t="n">
         <v>13.434</v>
       </c>
-      <c r="M72" s="4" t="n">
+      <c r="O72" s="4" t="n">
         <v>13.55</v>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="P72" s="3" t="n">
         <v>-0.8560885608856372</v>
       </c>
-      <c r="O72" s="4" t="n">
+      <c r="Q72" s="4" t="n">
         <v>13.722</v>
       </c>
-      <c r="P72" s="4" t="n">
+      <c r="R72" s="4" t="n">
         <v>13.634</v>
       </c>
-      <c r="Q72" s="3" t="n">
+      <c r="S72" s="3" t="n">
         <v>0.6454452105031372</v>
       </c>
-      <c r="R72" s="5" t="n">
+      <c r="T72" s="5" t="n">
         <v>1.501533771388774</v>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5356,55 +5438,56 @@
       <c r="C73" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E73" s="3" t="n"/>
       <c r="F73" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>300204</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>舒泰神</t>
         </is>
       </c>
-      <c r="H73" s="4" t="n">
+      <c r="J73" s="4" t="n">
         <v>16.91</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="K73" s="4" t="n">
         <v>19.8</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="L73" s="3" t="n">
         <v>17.09047900650502</v>
       </c>
-      <c r="K73" s="4" t="n">
+      <c r="M73" s="4" t="n">
         <v>20.29</v>
       </c>
-      <c r="L73" s="4" t="n">
+      <c r="N73" s="4" t="n">
         <v>17.97</v>
       </c>
-      <c r="M73" s="4" t="n">
+      <c r="O73" s="4" t="n">
         <v>18.211</v>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="P73" s="3" t="n">
         <v>-1.323375981549613</v>
       </c>
-      <c r="O73" s="4" t="n">
+      <c r="Q73" s="4" t="n">
         <v>18.47</v>
       </c>
-      <c r="P73" s="4" t="n">
+      <c r="R73" s="4" t="n">
         <v>18.264</v>
       </c>
-      <c r="Q73" s="3" t="n">
+      <c r="S73" s="3" t="n">
         <v>1.127901883486615</v>
       </c>
-      <c r="R73" s="5" t="n">
+      <c r="T73" s="5" t="n">
         <v>2.451277865036228</v>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5424,55 +5507,56 @@
       <c r="C74" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E74" s="3" t="n"/>
       <c r="F74" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>300534</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>陇神戎发</t>
         </is>
       </c>
-      <c r="H74" s="4" t="n">
+      <c r="J74" s="4" t="n">
         <v>9.68</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="K74" s="4" t="n">
         <v>11.41</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="L74" s="3" t="n">
         <v>17.8719008264463</v>
       </c>
-      <c r="K74" s="4" t="n">
+      <c r="M74" s="4" t="n">
         <v>11.61</v>
       </c>
-      <c r="L74" s="4" t="n">
+      <c r="N74" s="4" t="n">
         <v>10.302</v>
       </c>
-      <c r="M74" s="4" t="n">
+      <c r="O74" s="4" t="n">
         <v>10.524</v>
       </c>
-      <c r="N74" s="3" t="n">
+      <c r="P74" s="3" t="n">
         <v>-2.109464082098089</v>
       </c>
-      <c r="O74" s="4" t="n">
+      <c r="Q74" s="4" t="n">
         <v>10.564</v>
       </c>
-      <c r="P74" s="4" t="n">
+      <c r="R74" s="4" t="n">
         <v>10.562</v>
       </c>
-      <c r="Q74" s="3" t="n">
+      <c r="S74" s="3" t="n">
         <v>0.01893580761218594</v>
       </c>
-      <c r="R74" s="5" t="n">
+      <c r="T74" s="5" t="n">
         <v>2.128399889710275</v>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="U74" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5492,55 +5576,56 @@
       <c r="C75" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E75" s="3" t="n"/>
       <c r="F75" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>300436</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>广生堂</t>
         </is>
       </c>
-      <c r="H75" s="4" t="n">
+      <c r="J75" s="4" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="K75" s="4" t="n">
         <v>83.91</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="L75" s="3" t="n">
         <v>18.34978843441466</v>
       </c>
-      <c r="K75" s="4" t="n">
+      <c r="M75" s="4" t="n">
         <v>85.08</v>
       </c>
-      <c r="L75" s="4" t="n">
+      <c r="N75" s="4" t="n">
         <v>76.474</v>
       </c>
-      <c r="M75" s="4" t="n">
+      <c r="O75" s="4" t="n">
         <v>77.93899999999999</v>
       </c>
-      <c r="N75" s="3" t="n">
+      <c r="P75" s="3" t="n">
         <v>-1.879675130550806</v>
       </c>
-      <c r="O75" s="4" t="n">
+      <c r="Q75" s="4" t="n">
         <v>78.164</v>
       </c>
-      <c r="P75" s="4" t="n">
+      <c r="R75" s="4" t="n">
         <v>78.16199999999999</v>
       </c>
-      <c r="Q75" s="3" t="n">
+      <c r="S75" s="3" t="n">
         <v>0.002558788157935865</v>
       </c>
-      <c r="R75" s="5" t="n">
+      <c r="T75" s="5" t="n">
         <v>1.882233918708742</v>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5560,55 +5645,56 @@
       <c r="C76" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E76" s="3" t="n"/>
       <c r="F76" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
           <t>301234</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>五洲医疗</t>
         </is>
       </c>
-      <c r="H76" s="4" t="n">
+      <c r="J76" s="4" t="n">
         <v>125.7</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="K76" s="4" t="n">
         <v>149.04</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="L76" s="3" t="n">
         <v>18.56801909307875</v>
       </c>
-      <c r="K76" s="4" t="n">
+      <c r="M76" s="4" t="n">
         <v>150.84</v>
       </c>
-      <c r="L76" s="4" t="n">
+      <c r="N76" s="4" t="n">
         <v>130.836</v>
       </c>
-      <c r="M76" s="4" t="n">
+      <c r="O76" s="4" t="n">
         <v>131.754</v>
       </c>
-      <c r="N76" s="3" t="n">
+      <c r="P76" s="3" t="n">
         <v>-0.6967530397559152</v>
       </c>
-      <c r="O76" s="4" t="n">
+      <c r="Q76" s="4" t="n">
         <v>134.844</v>
       </c>
-      <c r="P76" s="4" t="n">
+      <c r="R76" s="4" t="n">
         <v>132.851</v>
       </c>
-      <c r="Q76" s="3" t="n">
+      <c r="S76" s="3" t="n">
         <v>1.50017688989923</v>
       </c>
-      <c r="R76" s="5" t="n">
+      <c r="T76" s="5" t="n">
         <v>2.196929929655145</v>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5628,55 +5714,56 @@
       <c r="C77" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E77" s="3" t="n"/>
       <c r="F77" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>920367</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>新赣江</t>
         </is>
       </c>
-      <c r="H77" s="4" t="n">
+      <c r="J77" s="4" t="n">
         <v>19.95</v>
       </c>
-      <c r="I77" s="4" t="n">
+      <c r="K77" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="L77" s="3" t="n">
         <v>19.2982456140351</v>
       </c>
-      <c r="K77" s="4" t="n">
+      <c r="M77" s="4" t="n">
         <v>23.94</v>
       </c>
-      <c r="L77" s="4" t="n">
+      <c r="N77" s="4" t="n">
         <v>21.502</v>
       </c>
-      <c r="M77" s="4" t="n">
+      <c r="O77" s="4" t="n">
         <v>21.968</v>
       </c>
-      <c r="N77" s="3" t="n">
+      <c r="P77" s="3" t="n">
         <v>-2.12126729788783</v>
       </c>
-      <c r="O77" s="4" t="n">
+      <c r="Q77" s="4" t="n">
         <v>22.098</v>
       </c>
-      <c r="P77" s="4" t="n">
+      <c r="R77" s="4" t="n">
         <v>21.968</v>
       </c>
-      <c r="Q77" s="3" t="n">
+      <c r="S77" s="3" t="n">
         <v>0.5917698470502719</v>
       </c>
-      <c r="R77" s="5" t="n">
+      <c r="T77" s="5" t="n">
         <v>2.713037144938102</v>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5696,55 +5783,56 @@
       <c r="C78" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E78" s="3" t="n"/>
       <c r="F78" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>688293</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>奥浦迈</t>
         </is>
       </c>
-      <c r="H78" s="4" t="n">
+      <c r="J78" s="4" t="n">
         <v>54.08</v>
       </c>
-      <c r="I78" s="4" t="n">
+      <c r="K78" s="4" t="n">
         <v>64.63</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="L78" s="3" t="n">
         <v>19.50813609467454</v>
       </c>
-      <c r="K78" s="4" t="n">
+      <c r="M78" s="4" t="n">
         <v>64.89</v>
       </c>
-      <c r="L78" s="4" t="n">
+      <c r="N78" s="4" t="n">
         <v>58.05423652173778</v>
       </c>
-      <c r="M78" s="4" t="n">
+      <c r="O78" s="4" t="n">
         <v>59.41505217391117</v>
       </c>
-      <c r="N78" s="3" t="n">
+      <c r="P78" s="3" t="n">
         <v>-2.29035505714984</v>
       </c>
-      <c r="O78" s="4" t="n">
+      <c r="Q78" s="4" t="n">
         <v>59.69761739130344</v>
       </c>
-      <c r="P78" s="4" t="n">
+      <c r="R78" s="4" t="n">
         <v>59.69563130434619</v>
       </c>
-      <c r="Q78" s="3" t="n">
+      <c r="S78" s="3" t="n">
         <v>0.00332702228595938</v>
       </c>
-      <c r="R78" s="5" t="n">
+      <c r="T78" s="5" t="n">
         <v>2.293682079435799</v>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5764,58 +5852,59 @@
       <c r="C79" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" t="inlineStr">
         <is>
           <t>空转多</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="G79" t="n">
         <v>3</v>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>600621</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>华鑫股份</t>
         </is>
       </c>
-      <c r="H79" s="4" t="n">
+      <c r="J79" s="4" t="n">
         <v>14.9</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="K79" s="4" t="n">
         <v>15.91</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="L79" s="3" t="n">
         <v>6.778523489932886</v>
       </c>
-      <c r="K79" s="4" t="n">
+      <c r="M79" s="4" t="n">
         <v>16.39</v>
       </c>
-      <c r="L79" s="4" t="n">
+      <c r="N79" s="4" t="n">
         <v>14.66</v>
       </c>
-      <c r="M79" s="4" t="n">
+      <c r="O79" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="N79" s="3" t="n">
+      <c r="P79" s="3" t="n">
         <v>-0.7447528774542911</v>
       </c>
-      <c r="O79" s="4" t="n">
+      <c r="Q79" s="4" t="n">
         <v>14.996</v>
       </c>
-      <c r="P79" s="4" t="n">
+      <c r="R79" s="4" t="n">
         <v>14.883</v>
       </c>
-      <c r="Q79" s="3" t="n">
+      <c r="S79" s="3" t="n">
         <v>0.7592555264395617</v>
       </c>
-      <c r="R79" s="5" t="n">
+      <c r="T79" s="5" t="n">
         <v>1.504008403893853</v>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="U79" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5835,55 +5924,56 @@
       <c r="C80" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E80" s="3" t="n"/>
       <c r="F80" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>601519</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>大智慧</t>
         </is>
       </c>
-      <c r="H80" s="4" t="n">
+      <c r="J80" s="4" t="n">
         <v>8.76</v>
       </c>
-      <c r="I80" s="4" t="n">
+      <c r="K80" s="4" t="n">
         <v>9.390000000000001</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="L80" s="3" t="n">
         <v>7.191780821917826</v>
       </c>
-      <c r="K80" s="4" t="n">
+      <c r="M80" s="4" t="n">
         <v>9.630000000000001</v>
       </c>
-      <c r="L80" s="4" t="n">
+      <c r="N80" s="4" t="n">
         <v>9.022</v>
       </c>
-      <c r="M80" s="4" t="n">
+      <c r="O80" s="4" t="n">
         <v>9.144000000000002</v>
       </c>
-      <c r="N80" s="3" t="n">
+      <c r="P80" s="3" t="n">
         <v>-1.334208223972022</v>
       </c>
-      <c r="O80" s="4" t="n">
+      <c r="Q80" s="4" t="n">
         <v>9.218</v>
       </c>
-      <c r="P80" s="4" t="n">
+      <c r="R80" s="4" t="n">
         <v>9.118</v>
       </c>
-      <c r="Q80" s="3" t="n">
+      <c r="S80" s="3" t="n">
         <v>1.096731739416534</v>
       </c>
-      <c r="R80" s="5" t="n">
+      <c r="T80" s="5" t="n">
         <v>2.430939963388556</v>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5903,55 +5993,56 @@
       <c r="C81" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E81" s="3" t="n"/>
       <c r="F81" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
           <t>600958</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>东方证券</t>
         </is>
       </c>
-      <c r="H81" s="4" t="n">
+      <c r="J81" s="4" t="n">
         <v>8.48</v>
       </c>
-      <c r="I81" s="4" t="n">
+      <c r="K81" s="4" t="n">
         <v>9.15</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="L81" s="3" t="n">
         <v>7.900943396226423</v>
       </c>
-      <c r="K81" s="4" t="n">
+      <c r="M81" s="4" t="n">
         <v>9.32</v>
       </c>
-      <c r="L81" s="4" t="n">
+      <c r="N81" s="4" t="n">
         <v>8.586</v>
       </c>
-      <c r="M81" s="4" t="n">
+      <c r="O81" s="4" t="n">
         <v>8.595000000000002</v>
       </c>
-      <c r="N81" s="3" t="n">
+      <c r="P81" s="3" t="n">
         <v>-0.1047120418848468</v>
       </c>
-      <c r="O81" s="4" t="n">
+      <c r="Q81" s="4" t="n">
         <v>8.75</v>
       </c>
-      <c r="P81" s="4" t="n">
+      <c r="R81" s="4" t="n">
         <v>8.629</v>
       </c>
-      <c r="Q81" s="3" t="n">
+      <c r="S81" s="3" t="n">
         <v>1.402248232703673</v>
       </c>
-      <c r="R81" s="5" t="n">
+      <c r="T81" s="5" t="n">
         <v>1.50696027458852</v>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -5971,55 +6062,56 @@
       <c r="C82" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E82" s="3" t="n"/>
       <c r="F82" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
           <t>601377</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>兴业证券</t>
         </is>
       </c>
-      <c r="H82" s="4" t="n">
+      <c r="J82" s="4" t="n">
         <v>5.52</v>
       </c>
-      <c r="I82" s="4" t="n">
+      <c r="K82" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="L82" s="3" t="n">
         <v>8.695652173913061</v>
       </c>
-      <c r="K82" s="4" t="n">
+      <c r="M82" s="4" t="n">
         <v>6.07</v>
       </c>
-      <c r="L82" s="4" t="n">
+      <c r="N82" s="4" t="n">
         <v>5.613999999999999</v>
       </c>
-      <c r="M82" s="4" t="n">
+      <c r="O82" s="4" t="n">
         <v>5.625999999999999</v>
       </c>
-      <c r="N82" s="3" t="n">
+      <c r="P82" s="3" t="n">
         <v>-0.2132954141486065</v>
       </c>
-      <c r="O82" s="4" t="n">
+      <c r="Q82" s="4" t="n">
         <v>5.726</v>
       </c>
-      <c r="P82" s="4" t="n">
+      <c r="R82" s="4" t="n">
         <v>5.653</v>
       </c>
-      <c r="Q82" s="3" t="n">
+      <c r="S82" s="3" t="n">
         <v>1.291349725809288</v>
       </c>
-      <c r="R82" s="5" t="n">
+      <c r="T82" s="5" t="n">
         <v>1.504645139957894</v>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6039,55 +6131,56 @@
       <c r="C83" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E83" s="3" t="n"/>
       <c r="F83" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>002736</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>国信证券</t>
         </is>
       </c>
-      <c r="H83" s="4" t="n">
+      <c r="J83" s="4" t="n">
         <v>9.66</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="K83" s="4" t="n">
         <v>10.52</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="L83" s="3" t="n">
         <v>8.902691511387161</v>
       </c>
-      <c r="K83" s="4" t="n">
+      <c r="M83" s="4" t="n">
         <v>10.62</v>
       </c>
-      <c r="L83" s="4" t="n">
+      <c r="N83" s="4" t="n">
         <v>9.806000000000001</v>
       </c>
-      <c r="M83" s="4" t="n">
+      <c r="O83" s="4" t="n">
         <v>9.812999999999999</v>
       </c>
-      <c r="N83" s="3" t="n">
+      <c r="P83" s="3" t="n">
         <v>-0.07133394476712684</v>
       </c>
-      <c r="O83" s="4" t="n">
+      <c r="Q83" s="4" t="n">
         <v>10.008</v>
       </c>
-      <c r="P83" s="4" t="n">
+      <c r="R83" s="4" t="n">
         <v>9.866999999999999</v>
       </c>
-      <c r="Q83" s="3" t="n">
+      <c r="S83" s="3" t="n">
         <v>1.429005776831871</v>
       </c>
-      <c r="R83" s="5" t="n">
+      <c r="T83" s="5" t="n">
         <v>1.500339721598998</v>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6107,55 +6200,56 @@
       <c r="C84" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E84" s="3" t="n"/>
       <c r="F84" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>601136</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>首创证券</t>
         </is>
       </c>
-      <c r="H84" s="4" t="n">
+      <c r="J84" s="4" t="n">
         <v>13.49</v>
       </c>
-      <c r="I84" s="4" t="n">
+      <c r="K84" s="4" t="n">
         <v>14.78</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="L84" s="3" t="n">
         <v>9.562638991845795</v>
       </c>
-      <c r="K84" s="4" t="n">
+      <c r="M84" s="4" t="n">
         <v>14.83</v>
       </c>
-      <c r="L84" s="4" t="n">
+      <c r="N84" s="4" t="n">
         <v>13.94</v>
       </c>
-      <c r="M84" s="4" t="n">
+      <c r="O84" s="4" t="n">
         <v>14.029</v>
       </c>
-      <c r="N84" s="3" t="n">
+      <c r="P84" s="3" t="n">
         <v>-0.6344001710741898</v>
       </c>
-      <c r="O84" s="4" t="n">
+      <c r="Q84" s="4" t="n">
         <v>14.184</v>
       </c>
-      <c r="P84" s="4" t="n">
+      <c r="R84" s="4" t="n">
         <v>14.062</v>
       </c>
-      <c r="Q84" s="3" t="n">
+      <c r="S84" s="3" t="n">
         <v>0.8675864030721181</v>
       </c>
-      <c r="R84" s="5" t="n">
+      <c r="T84" s="5" t="n">
         <v>1.501986574146308</v>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="U84" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6175,55 +6269,56 @@
       <c r="C85" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E85" s="3" t="n"/>
       <c r="F85" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>688318</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>财富趋势</t>
         </is>
       </c>
-      <c r="H85" s="4" t="n">
+      <c r="J85" s="4" t="n">
         <v>69.98999999999999</v>
       </c>
-      <c r="I85" s="4" t="n">
+      <c r="K85" s="4" t="n">
         <v>77.61</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="L85" s="3" t="n">
         <v>10.88726960994428</v>
       </c>
-      <c r="K85" s="4" t="n">
+      <c r="M85" s="4" t="n">
         <v>83.98</v>
       </c>
-      <c r="L85" s="4" t="n">
+      <c r="N85" s="4" t="n">
         <v>73.66400000000002</v>
       </c>
-      <c r="M85" s="4" t="n">
+      <c r="O85" s="4" t="n">
         <v>73.70700000000001</v>
       </c>
-      <c r="N85" s="3" t="n">
+      <c r="P85" s="3" t="n">
         <v>-0.05833909940710091</v>
       </c>
-      <c r="O85" s="4" t="n">
+      <c r="Q85" s="4" t="n">
         <v>75.06800000000001</v>
       </c>
-      <c r="P85" s="4" t="n">
+      <c r="R85" s="4" t="n">
         <v>74.001</v>
       </c>
-      <c r="Q85" s="3" t="n">
+      <c r="S85" s="3" t="n">
         <v>1.441872407129652</v>
       </c>
-      <c r="R85" s="5" t="n">
+      <c r="T85" s="5" t="n">
         <v>1.500211506536753</v>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6243,55 +6338,56 @@
       <c r="C86" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E86" s="3" t="n"/>
       <c r="F86" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>300803</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>指南针</t>
         </is>
       </c>
-      <c r="H86" s="4" t="n">
+      <c r="J86" s="4" t="n">
         <v>48.38</v>
       </c>
-      <c r="I86" s="4" t="n">
+      <c r="K86" s="4" t="n">
         <v>55.17</v>
       </c>
-      <c r="J86" s="3" t="n">
+      <c r="L86" s="3" t="n">
         <v>14.03472509301364</v>
       </c>
-      <c r="K86" s="4" t="n">
+      <c r="M86" s="4" t="n">
         <v>58.05</v>
       </c>
-      <c r="L86" s="4" t="n">
+      <c r="N86" s="4" t="n">
         <v>51.812</v>
       </c>
-      <c r="M86" s="4" t="n">
+      <c r="O86" s="4" t="n">
         <v>52.057</v>
       </c>
-      <c r="N86" s="3" t="n">
+      <c r="P86" s="3" t="n">
         <v>-0.4706379545498129</v>
       </c>
-      <c r="O86" s="4" t="n">
+      <c r="Q86" s="4" t="n">
         <v>52.79600000000001</v>
       </c>
-      <c r="P86" s="4" t="n">
+      <c r="R86" s="4" t="n">
         <v>52.258</v>
       </c>
-      <c r="Q86" s="3" t="n">
+      <c r="S86" s="3" t="n">
         <v>1.029507443836364</v>
       </c>
-      <c r="R86" s="5" t="n">
+      <c r="T86" s="5" t="n">
         <v>1.500145398386177</v>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="U86" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6311,55 +6407,56 @@
       <c r="C87" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E87" s="3" t="n"/>
       <c r="F87" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>300085</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>银之杰</t>
         </is>
       </c>
-      <c r="H87" s="4" t="n">
+      <c r="J87" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="I87" s="4" t="n">
+      <c r="K87" s="4" t="n">
         <v>28.83</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="L87" s="3" t="n">
         <v>15.82965046203293</v>
       </c>
-      <c r="K87" s="4" t="n">
+      <c r="M87" s="4" t="n">
         <v>29.86</v>
       </c>
-      <c r="L87" s="4" t="n">
+      <c r="N87" s="4" t="n">
         <v>26.71</v>
       </c>
-      <c r="M87" s="4" t="n">
+      <c r="O87" s="4" t="n">
         <v>26.998</v>
       </c>
-      <c r="N87" s="3" t="n">
+      <c r="P87" s="3" t="n">
         <v>-1.066745684865533</v>
       </c>
-      <c r="O87" s="4" t="n">
+      <c r="Q87" s="4" t="n">
         <v>27.322</v>
       </c>
-      <c r="P87" s="4" t="n">
+      <c r="R87" s="4" t="n">
         <v>27.123</v>
       </c>
-      <c r="Q87" s="3" t="n">
+      <c r="S87" s="3" t="n">
         <v>0.7336946502968011</v>
       </c>
-      <c r="R87" s="5" t="n">
+      <c r="T87" s="5" t="n">
         <v>1.800440335162334</v>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6379,55 +6476,56 @@
       <c r="C88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E88" s="3" t="n"/>
       <c r="F88" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>300945</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>曼卡龙</t>
         </is>
       </c>
-      <c r="H88" s="4" t="n">
+      <c r="J88" s="4" t="n">
         <v>10.02</v>
       </c>
-      <c r="I88" s="4" t="n">
+      <c r="K88" s="4" t="n">
         <v>11.52</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="L88" s="3" t="n">
         <v>14.97005988023952</v>
       </c>
-      <c r="K88" s="4" t="n">
+      <c r="M88" s="4" t="n">
         <v>12.02</v>
       </c>
-      <c r="L88" s="4" t="n">
+      <c r="N88" s="4" t="n">
         <v>10.506</v>
       </c>
-      <c r="M88" s="4" t="n">
+      <c r="O88" s="4" t="n">
         <v>10.536</v>
       </c>
-      <c r="N88" s="3" t="n">
+      <c r="P88" s="3" t="n">
         <v>-0.2847380410022526</v>
       </c>
-      <c r="O88" s="4" t="n">
+      <c r="Q88" s="4" t="n">
         <v>10.762</v>
       </c>
-      <c r="P88" s="4" t="n">
+      <c r="R88" s="4" t="n">
         <v>10.632</v>
       </c>
-      <c r="Q88" s="3" t="n">
+      <c r="S88" s="3" t="n">
         <v>1.222723852520691</v>
       </c>
-      <c r="R88" s="5" t="n">
+      <c r="T88" s="5" t="n">
         <v>1.507461893522943</v>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="U88" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6447,55 +6545,56 @@
       <c r="C89" s="3" t="n">
         <v>16.07</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E89" s="3" t="n"/>
       <c r="F89" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
           <t>300069</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>金利华电</t>
         </is>
       </c>
-      <c r="H89" s="4" t="n">
+      <c r="J89" s="4" t="n">
         <v>21.06</v>
       </c>
-      <c r="I89" s="4" t="n">
+      <c r="K89" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="L89" s="3" t="n">
         <v>13.91263057929724</v>
       </c>
-      <c r="K89" s="4" t="n">
+      <c r="M89" s="4" t="n">
         <v>25.27</v>
       </c>
-      <c r="L89" s="4" t="n">
+      <c r="N89" s="4" t="n">
         <v>21.766</v>
       </c>
-      <c r="M89" s="4" t="n">
+      <c r="O89" s="4" t="n">
         <v>22.147</v>
       </c>
-      <c r="N89" s="3" t="n">
+      <c r="P89" s="3" t="n">
         <v>-1.720323294351378</v>
       </c>
-      <c r="O89" s="4" t="n">
+      <c r="Q89" s="4" t="n">
         <v>22.318</v>
       </c>
-      <c r="P89" s="4" t="n">
+      <c r="R89" s="4" t="n">
         <v>22.316</v>
       </c>
-      <c r="Q89" s="3" t="n">
+      <c r="S89" s="3" t="n">
         <v>0.008962179602090004</v>
       </c>
-      <c r="R89" s="5" t="n">
+      <c r="T89" s="5" t="n">
         <v>1.729285473953468</v>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6515,55 +6614,56 @@
       <c r="C90" s="3" t="n">
         <v>16.07</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E90" s="3" t="n"/>
       <c r="F90" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
           <t>301082</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>久盛电气</t>
         </is>
       </c>
-      <c r="H90" s="4" t="n">
+      <c r="J90" s="4" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="I90" s="4" t="n">
+      <c r="K90" s="4" t="n">
         <v>10.23</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="L90" s="3" t="n">
         <v>16.51480637813214</v>
       </c>
-      <c r="K90" s="4" t="n">
+      <c r="M90" s="4" t="n">
         <v>10.53</v>
       </c>
-      <c r="L90" s="4" t="n">
+      <c r="N90" s="4" t="n">
         <v>9.296000000000001</v>
       </c>
-      <c r="M90" s="4" t="n">
+      <c r="O90" s="4" t="n">
         <v>9.324000000000002</v>
       </c>
-      <c r="N90" s="3" t="n">
+      <c r="P90" s="3" t="n">
         <v>-0.3003003003003046</v>
       </c>
-      <c r="O90" s="4" t="n">
+      <c r="Q90" s="4" t="n">
         <v>9.526</v>
       </c>
-      <c r="P90" s="4" t="n">
+      <c r="R90" s="4" t="n">
         <v>9.413</v>
       </c>
-      <c r="Q90" s="3" t="n">
+      <c r="S90" s="3" t="n">
         <v>1.200467438648678</v>
       </c>
-      <c r="R90" s="5" t="n">
+      <c r="T90" s="5" t="n">
         <v>1.500767738948983</v>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6583,55 +6683,56 @@
       <c r="C91" s="3" t="n">
         <v>16.07</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E91" s="3" t="n"/>
       <c r="F91" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>300427</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>红相股份</t>
         </is>
       </c>
-      <c r="H91" s="4" t="n">
+      <c r="J91" s="4" t="n">
         <v>5.21</v>
       </c>
-      <c r="I91" s="4" t="n">
+      <c r="K91" s="4" t="n">
         <v>6.14</v>
       </c>
-      <c r="J91" s="3" t="n">
+      <c r="L91" s="3" t="n">
         <v>17.85028790786946</v>
       </c>
-      <c r="K91" s="4" t="n">
+      <c r="M91" s="4" t="n">
         <v>6.25</v>
       </c>
-      <c r="L91" s="4" t="n">
+      <c r="N91" s="4" t="n">
         <v>5.538</v>
       </c>
-      <c r="M91" s="4" t="n">
+      <c r="O91" s="4" t="n">
         <v>5.588</v>
       </c>
-      <c r="N91" s="3" t="n">
+      <c r="P91" s="3" t="n">
         <v>-0.8947745168217613</v>
       </c>
-      <c r="O91" s="4" t="n">
+      <c r="Q91" s="4" t="n">
         <v>5.678</v>
       </c>
-      <c r="P91" s="4" t="n">
+      <c r="R91" s="4" t="n">
         <v>5.643000000000001</v>
       </c>
-      <c r="Q91" s="3" t="n">
+      <c r="S91" s="3" t="n">
         <v>0.6202374623427209</v>
       </c>
-      <c r="R91" s="5" t="n">
+      <c r="T91" s="5" t="n">
         <v>1.515011979164482</v>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="U91" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
@@ -6651,64 +6752,65 @@
       <c r="C92" s="3" t="n">
         <v>1.59</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
+      <c r="E92" s="3" t="n"/>
       <c r="F92" t="inlineStr">
         <is>
+          <t>空</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
           <t>688323</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>瑞华泰</t>
         </is>
       </c>
-      <c r="H92" s="4" t="n">
+      <c r="J92" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="I92" s="4" t="n">
+      <c r="K92" s="4" t="n">
         <v>21.78</v>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="L92" s="3" t="n">
         <v>19.01639344262296</v>
       </c>
-      <c r="K92" s="4" t="n">
+      <c r="M92" s="4" t="n">
         <v>21.96</v>
       </c>
-      <c r="L92" s="4" t="n">
+      <c r="N92" s="4" t="n">
         <v>19.84</v>
       </c>
-      <c r="M92" s="4" t="n">
+      <c r="O92" s="4" t="n">
         <v>19.986</v>
       </c>
-      <c r="N92" s="3" t="n">
+      <c r="P92" s="3" t="n">
         <v>-0.7305113579505473</v>
       </c>
-      <c r="O92" s="4" t="n">
+      <c r="Q92" s="4" t="n">
         <v>20.312</v>
       </c>
-      <c r="P92" s="4" t="n">
+      <c r="R92" s="4" t="n">
         <v>20.156</v>
       </c>
-      <c r="Q92" s="3" t="n">
+      <c r="S92" s="3" t="n">
         <v>0.7739630879142867</v>
       </c>
-      <c r="R92" s="5" t="n">
+      <c r="T92" s="5" t="n">
         <v>1.504474445864834</v>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="U92" t="inlineStr">
         <is>
           <t>涨停内可达</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S92"/>
+  <autoFilter ref="A2:U92"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$U$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$U$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U92"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5破10明日门槛完整名单｜信号日 2026-10-27｜90 只｜报告 多空阶段_2026-10-27.xlsx</t>
+          <t>5破10明日门槛完整名单｜信号日 2026-10-28｜80 只｜报告 多空阶段_2026-10-28.xlsx</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" t="inlineStr">
@@ -607,46 +607,46 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>688308</t>
+          <t>301630</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>欧科亿</t>
+          <t>同宇新材</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>59.41</v>
+        <v>171.1</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>68.95999999999999</v>
+        <v>196.43</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>16.07473489311564</v>
+        <v>14.80420806545881</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>71.29000000000001</v>
+        <v>205.32</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>64.092</v>
+        <v>170.124</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>64.788</v>
+        <v>170.376</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-1.074273013521021</v>
+        <v>-0.1479081560783468</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>65.364</v>
+        <v>175.41</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>65.086</v>
+        <v>173.069</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.4271271855698755</v>
+        <v>1.352639698617319</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>1.501400199090897</v>
+        <v>1.500547854695666</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" t="inlineStr">
@@ -676,46 +676,46 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>300776</t>
+          <t>301526</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>帝尔激光</t>
+          <t>国际复材</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>79.31999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>92.8</v>
+        <v>23.61</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>16.99445284921837</v>
+        <v>15.73529411764707</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>95.18000000000001</v>
+        <v>24.48</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>84.974</v>
+        <v>20.71</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>85.59400000000001</v>
+        <v>21.088</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-0.7243498376054425</v>
+        <v>-1.792488619119881</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>86.774</v>
+        <v>21.264</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>86.10400000000001</v>
+        <v>21.263</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7781287745052268</v>
+        <v>0.004703005220352274</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>1.502478612110669</v>
+        <v>1.797191624340233</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" t="inlineStr">
@@ -754,37 +754,37 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>21.41</v>
+        <v>22.16</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>25.46</v>
+        <v>26.01</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>18.91639420831388</v>
+        <v>17.37364620938628</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>25.69</v>
+        <v>26.59</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>22.902</v>
+        <v>23.012</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>23.614</v>
+        <v>23.285</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-3.015160498009672</v>
+        <v>-1.172428602104358</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>23.562</v>
+        <v>23.602</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>23.56</v>
+        <v>23.426</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.008488964346353711</v>
+        <v>0.7513019721676617</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>3.023649462356026</v>
+        <v>1.92373057427202</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" t="inlineStr">
@@ -814,46 +814,46 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>301338</t>
+          <t>300308</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>凯格精机</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>65.19</v>
+        <v>634.5599999999999</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>76.93000000000001</v>
+        <v>676.03</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>18.00889707010278</v>
+        <v>6.535237014624307</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>78.22</v>
+        <v>761.47</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>70.116</v>
+        <v>618.9440000000001</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>71.02500000000001</v>
+        <v>631.02</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.279831045406554</v>
+        <v>-1.913726981712138</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>71.69000000000001</v>
+        <v>631.624</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>71.53200000000001</v>
+        <v>631.6229999999999</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.2208801655203319</v>
+        <v>0.0001583222903667192</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>1.500711210926886</v>
+        <v>1.913885304002505</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" t="inlineStr">
@@ -883,46 +883,46 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>688628</t>
+          <t>300394</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>优利德</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>65.3</v>
+        <v>200.92</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>77.08</v>
+        <v>223.34</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>18.03981623277182</v>
+        <v>11.1586701174597</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>78.36</v>
+        <v>241.1</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>71.622</v>
+        <v>202.134</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>71.79900000000001</v>
+        <v>204.329</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-0.2465215392972175</v>
+        <v>-1.074247904115433</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>73.21600000000001</v>
+        <v>206.64</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>72.22999999999999</v>
+        <v>205.383</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.365083760210473</v>
+        <v>0.6120272856078746</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>1.61160529950769</v>
+        <v>1.686275189723307</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" t="inlineStr">
@@ -952,46 +952,46 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>300632</t>
+          <t>300548</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>光莆股份</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.92</v>
+        <v>162.79</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>16</v>
+        <v>189.37</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>14.94252873563218</v>
+        <v>16.32778426193255</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>16.7</v>
+        <v>195.34</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.676</v>
+        <v>166.846</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>14.823</v>
+        <v>169.518</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-0.991702084598256</v>
+        <v>-1.576233792281623</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>14.984</v>
+        <v>171.148</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>14.908</v>
+        <v>171.146</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5097933995170445</v>
+        <v>0.001168592897271559</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>1.501495484115301</v>
+        <v>1.577402385178894</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1002,16 +1002,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" t="inlineStr">
@@ -1021,46 +1021,46 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>300672</t>
+          <t>688167</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>国科微</t>
+          <t>炬光科技</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>128.51</v>
+        <v>193.6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>150.65</v>
+        <v>226.97</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>17.22823126604936</v>
+        <v>17.23657024793388</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>154.21</v>
+        <v>232.32</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>137.146</v>
+        <v>199.842</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>138.103</v>
+        <v>203.349</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>-0.6929610508098927</v>
+        <v>-1.724621217709432</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>140.342</v>
+        <v>205.168</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>139.218</v>
+        <v>205.166</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8073668634802855</v>
+        <v>0.0009748203893433782</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>1.500327914290178</v>
+        <v>1.725596038098776</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1071,16 +1071,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" t="inlineStr">
@@ -1090,46 +1090,46 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>688515</t>
+          <t>300131</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>裕太微-U</t>
+          <t>英唐智控</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>100.5</v>
+        <v>11.35</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>118.36</v>
+        <v>13.32</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>17.77114427860695</v>
+        <v>17.3568281938326</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>120.6</v>
+        <v>13.62</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>107.958</v>
+        <v>11.822</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>108.01</v>
+        <v>12.024</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-0.04814369039902733</v>
+        <v>-1.67997338656023</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>110.678</v>
+        <v>12.104</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>109.094</v>
+        <v>12.103</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.451958861165581</v>
+        <v>0.008262414277471208</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>1.500102551564608</v>
+        <v>1.688235800837701</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1140,16 +1140,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" t="inlineStr">
@@ -1159,46 +1159,46 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>300671</t>
+          <t>688312</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>富满微</t>
+          <t>燕麦科技</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>38.85</v>
+        <v>34.03</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>45.77</v>
+        <v>40.34</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>17.81209781209783</v>
+        <v>18.54246253305907</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>46.62</v>
+        <v>40.83</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>41.904</v>
+        <v>35.178</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>42.463</v>
+        <v>35.549</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.316440194993285</v>
+        <v>-1.043629919266353</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>42.79</v>
+        <v>36.148</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>42.684</v>
+        <v>35.983</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.2483366132508547</v>
+        <v>0.4585498707722957</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>1.564776808244139</v>
+        <v>1.502179790038649</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" t="inlineStr">
@@ -1228,46 +1228,46 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>300042</t>
+          <t>301486</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>致尚科技</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>27.55</v>
+        <v>180.89</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>32.7</v>
+        <v>216.18</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.69328493647913</v>
+        <v>19.5090939244845</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>33.06</v>
+        <v>217.06</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>29.592</v>
+        <v>186.316</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>29.773</v>
+        <v>188.545</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-0.607933362442481</v>
+        <v>-1.182211143228429</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>30.336</v>
+        <v>191.972</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>30.067</v>
+        <v>191.363</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.894668573519164</v>
+        <v>0.3182433385764183</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>1.502601935961645</v>
+        <v>1.500454481804847</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>光上游</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3.92</v>
+        <v>5.13</v>
       </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" t="inlineStr">
@@ -1297,46 +1297,46 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>688416</t>
+          <t>688079</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>恒烁股份</t>
+          <t>美迪凯</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>51.4</v>
+        <v>11.67</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>61.03</v>
+        <v>13.74</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>18.73540856031128</v>
+        <v>17.73778920308484</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>61.68</v>
+        <v>14</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>55.61</v>
+        <v>12.076</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>56.00699999999999</v>
+        <v>12.206</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0.7088399664327505</v>
+        <v>-1.065049975421917</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>56.98</v>
+        <v>12.39</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>56.532</v>
+        <v>12.336</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0.7924715205547272</v>
+        <v>0.437743190661477</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>1.501311486987478</v>
+        <v>1.502793166083394</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3.92</v>
+        <v>18</v>
       </c>
       <c r="E14" s="3" t="n"/>
       <c r="F14" t="inlineStr">
@@ -1366,46 +1366,46 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>688141</t>
+          <t>688392</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>杰华特</t>
+          <t>骄成超声</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>67.45</v>
+        <v>116.32</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>80.7</v>
+        <v>134.69</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>19.64418087472202</v>
+        <v>15.79264099037139</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>80.94</v>
+        <v>139.58</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>73.34</v>
+        <v>117.91</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>74.45099999999999</v>
+        <v>120.236</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-1.492256652026147</v>
+        <v>-1.934528760105125</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>75.048</v>
+        <v>121.068</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>74.98099999999999</v>
+        <v>121.067</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.08935597017911689</v>
+        <v>0.0008259889151984723</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>1.581612622205264</v>
+        <v>1.935354749020324</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1416,16 +1416,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>半导体芯片</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2.17</v>
+        <v>18</v>
       </c>
       <c r="E15" s="3" t="n"/>
       <c r="F15" t="inlineStr">
@@ -1435,46 +1435,46 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>301717</t>
+          <t>688807</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>超纯应材</t>
+          <t>优迅股份</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>263.63</v>
+        <v>219.11</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>299.5</v>
+        <v>254.97</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>13.60619049425331</v>
+        <v>16.36620875359407</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>316.35</v>
+        <v>262.93</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>278.08</v>
+        <v>226.7</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>282.667</v>
+        <v>230.231</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-1.622757520333107</v>
+        <v>-1.533677046097182</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>283.302</v>
+        <v>231.858</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>282.917</v>
+        <v>231.856</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0.1360823138941702</v>
+        <v>0.0008626043751291945</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>1.758839834227277</v>
+        <v>1.534539650472311</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1485,16 +1485,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>半导体芯片</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" t="inlineStr">
@@ -1504,46 +1504,46 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>688797</t>
+          <t>688508</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>臻宝科技</t>
+          <t>芯朋微</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>185</v>
+        <v>58.65</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>220.88</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>19.39459459459458</v>
+        <v>17.15260017050297</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>222</v>
+        <v>70.38</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>199.554</v>
+        <v>61.08199999999999</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>200.066</v>
+        <v>61.703</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.2559155478691899</v>
+        <v>-1.006434046966931</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>204.524</v>
+        <v>62.27999999999999</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>202.01</v>
+        <v>61.974</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1.244492846888767</v>
+        <v>0.4937554458321003</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>1.500408394757957</v>
+        <v>1.500189492799031</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1554,16 +1554,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>半导体芯片</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2.17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" t="inlineStr">
@@ -1573,46 +1573,46 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>688141</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>杰华特</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>62.45</v>
+        <v>72.05</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>74.62</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>19.48759007205765</v>
+        <v>19.50034698126302</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>74.94</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>67.664</v>
+        <v>74.398</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>68.711</v>
+        <v>74.65599999999999</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-1.523773486050262</v>
+        <v>-0.3455850835833663</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>69.11800000000001</v>
+        <v>76.53999999999999</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>69.11600000000001</v>
+        <v>75.66600000000001</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>0.002893685977189975</v>
+        <v>1.155076256178433</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>1.526667172027452</v>
+        <v>1.5006613397618</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1632,56 +1632,59 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2.17</v>
+        <v>4.26</v>
       </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>688605</t>
+          <t>688383</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>先锋精科</t>
+          <t>新益昌</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>55.81</v>
+        <v>89.38</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>66.79000000000001</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.67389356746103</v>
+        <v>2.696352651599931</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>66.97</v>
+        <v>107.25</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>60.182</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>61.573</v>
+        <v>86.79799999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-2.25910707615351</v>
+        <v>-0.6428719555750084</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>61.818</v>
+        <v>87.67999999999999</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>61.816</v>
+        <v>86.934</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.003235408308555066</v>
+        <v>0.8581222536636846</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>2.262342484462065</v>
+        <v>1.500994209238693</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -1692,16 +1695,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" t="inlineStr">
@@ -1711,46 +1714,46 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>003026</t>
+          <t>301717</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>中晶科技</t>
+          <t>超纯应材</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>27.83</v>
+        <v>279.16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>29.67</v>
+        <v>313.78</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>6.611570247933907</v>
+        <v>12.40149018484022</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>30.61</v>
+        <v>334.99</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>27.57</v>
+        <v>282.09</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>27.731</v>
+        <v>282.311</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>-0.5805776928347273</v>
+        <v>-0.07828246154062413</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>28.148</v>
+        <v>288.94</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>27.891</v>
+        <v>284.889</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>0.9214441934674467</v>
+        <v>1.421957323729583</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>1.502021886302174</v>
+        <v>1.500239785270208</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -1761,16 +1764,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" t="inlineStr">
@@ -1780,46 +1783,46 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>688268</t>
+          <t>688605</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>华特气体</t>
+          <t>先锋精科</t>
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>99.09999999999999</v>
+        <v>59.88</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>112.39</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>13.41069626639759</v>
+        <v>12.89245156980627</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>118.92</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>103.382</v>
+        <v>60.598</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>105.176</v>
+        <v>61.206</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-1.705712329809095</v>
+        <v>-0.9933666633990201</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>105.626</v>
+        <v>61.95399999999999</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>105.624</v>
+        <v>61.641</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.001893509050976405</v>
+        <v>0.5077789133855592</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>1.707605838860071</v>
+        <v>1.501145576784579</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -1830,16 +1833,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" t="inlineStr">
@@ -1849,46 +1852,46 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>301369</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>蜀道装备</t>
+          <t>联动科技</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>20.65</v>
+        <v>91.66</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>23.96</v>
+        <v>104.47</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>16.02905569007265</v>
+        <v>13.97556185904429</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>24.78</v>
+        <v>109.99</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>21.898</v>
+        <v>90.85799999999999</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>22.063</v>
+        <v>92.80300000000001</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-0.7478584054752102</v>
+        <v>-2.095837419048974</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>22.424</v>
+        <v>93.462</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>22.256</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.7548526240114928</v>
+        <v>0.002139952921043076</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>1.502711029486703</v>
+        <v>2.097977371970017</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -1899,16 +1902,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" t="inlineStr">
@@ -1918,46 +1921,46 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>688138</t>
+          <t>688785</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>清溢光电</t>
+          <t>恒运昌</t>
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>26</v>
+        <v>280.08</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>30.19</v>
+        <v>323.49</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>16.11538461538462</v>
+        <v>15.49914310197087</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>31.2</v>
+        <v>336.09</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>27.528</v>
+        <v>280.44</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>27.97</v>
+        <v>287.8299999999999</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-1.580264569181256</v>
+        <v>-2.567487753187625</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>28.154</v>
+        <v>288.252</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>28.153</v>
+        <v>288.251</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.003552019323005418</v>
+        <v>0.000346919871918594</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>1.583816588504261</v>
+        <v>2.567834673059544</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -1968,16 +1971,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" t="inlineStr">
@@ -1987,46 +1990,46 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>300821</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>珂玛科技</t>
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>15.55</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>18.11</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>16.46302250803857</v>
+        <v>15.81039755351681</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>18.66</v>
+        <v>78.48</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>16.496</v>
+        <v>67.498</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>17.006</v>
+        <v>68.30600000000001</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-2.998941550041145</v>
+        <v>-1.182912189265961</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>16.986</v>
+        <v>69.152</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>16.985</v>
+        <v>68.93300000000001</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.005887547836302964</v>
+        <v>0.3176997954535521</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>3.004829097877448</v>
+        <v>1.500611984719513</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2037,16 +2040,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" t="inlineStr">
@@ -2056,46 +2059,46 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>688733</t>
+          <t>300400</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>壹石通</t>
+          <t>劲拓股份</t>
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>21.41</v>
+        <v>25.32</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>25.07</v>
+        <v>30.16</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>17.09481550677254</v>
+        <v>19.11532385466035</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>25.69</v>
+        <v>30.38</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>22.986</v>
+        <v>26.428</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>23.195</v>
+        <v>26.993</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-0.9010562621254548</v>
+        <v>-2.093135257288947</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>23.484</v>
+        <v>27.18</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>23.344</v>
+        <v>27.178</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.5997258396161831</v>
+        <v>0.007358893222475515</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>1.500782101741638</v>
+        <v>2.100494150511423</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2106,16 +2109,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" t="inlineStr">
@@ -2125,46 +2128,46 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>688106</t>
+          <t>301629</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>金宏气体</t>
+          <t>矽电股份</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>19.28</v>
+        <v>195.64</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>22.64</v>
+        <v>233.25</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>17.42738589211619</v>
+        <v>19.22408505418116</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>23.13</v>
+        <v>234.76</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>20.436</v>
+        <v>203.364</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>20.839</v>
+        <v>206.945</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-1.933873986275725</v>
+        <v>-1.730411461982662</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>20.96</v>
+        <v>208.836</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>20.919</v>
+        <v>208.834</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.1959940723744058</v>
+        <v>0.0009576984590475845</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>2.129868058650131</v>
+        <v>1.731369160441709</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2175,7 +2178,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2194,46 +2197,46 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>688233</t>
+          <t>688106</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>神工股份</t>
+          <t>金宏气体</t>
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>61.55</v>
+        <v>19.82</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>21.95</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>19.43135662063364</v>
+        <v>10.74672048435923</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>73.86</v>
+        <v>23.78</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>66.926</v>
+        <v>20.258</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>67.899</v>
+        <v>20.568</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-1.433010795446177</v>
+        <v>-1.507195643718373</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>68.548</v>
+        <v>20.592</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>68.34999999999999</v>
+        <v>20.59</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.289685442574994</v>
+        <v>0.009713453132609295</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>1.722696238021171</v>
+        <v>1.516909096850982</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2244,12 +2247,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MLCC</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -2263,46 +2266,46 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>300806</t>
+          <t>688268</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>斯迪克</t>
+          <t>华特气体</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>36.6</v>
+        <v>102.56</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>42.2</v>
+        <v>114.39</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>15.30054644808743</v>
+        <v>11.53471138845554</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>43.92</v>
+        <v>123.07</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>38.312</v>
+        <v>104.06</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>38.398</v>
+        <v>104.841</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.2239699984374344</v>
+        <v>-0.7449375721330309</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>39.27800000000001</v>
+        <v>106.346</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>38.63399999999999</v>
+        <v>105.549</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.666925506030981</v>
+        <v>0.7550995272338046</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>1.890895504468415</v>
+        <v>1.500037099366835</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -2313,16 +2316,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" t="inlineStr">
@@ -2332,46 +2335,46 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>920493</t>
+          <t>300666</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>并行科技</t>
+          <t>江丰电子</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>86.43000000000001</v>
+        <v>164.79</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>99.17</v>
+        <v>186.36</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>14.74025222723592</v>
+        <v>13.08938649189879</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>103.71</v>
+        <v>197.74</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>91.07600000000001</v>
+        <v>166.268</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>91.12800000000001</v>
+        <v>169.07</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-0.0570625932754032</v>
+        <v>-1.657301709351167</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>93.11000000000001</v>
+        <v>170.068</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>91.785</v>
+        <v>170.066</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>1.443591000708189</v>
+        <v>0.001176014018100524</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>1.500653593983592</v>
+        <v>1.658477723369267</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -2382,16 +2385,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" t="inlineStr">
@@ -2401,46 +2404,46 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>301169</t>
+          <t>688138</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>零点有数</t>
+          <t>清溢光电</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>42.89</v>
+        <v>27.33</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>51.1</v>
+        <v>31.33</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>19.14199114012591</v>
+        <v>14.6359312111233</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>51.46</v>
+        <v>32.79</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>45.654</v>
+        <v>27.81</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>46.396</v>
+        <v>27.98099999999999</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.599275799637889</v>
+        <v>-0.6111289803795161</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>47.072</v>
+        <v>28.532</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>47.072</v>
+        <v>28.27999999999999</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2.220446049250313e-14</v>
+        <v>0.8910891089109141</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>1.599275799637911</v>
+        <v>1.50221808929043</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -2451,68 +2454,65 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.49</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>301052</t>
+          <t>300821</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>果麦文化</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>32.45</v>
+        <v>15.77</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>34.69</v>
+        <v>18.33</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>6.902927580893659</v>
+        <v>16.23335447051362</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>38.94</v>
+        <v>18.92</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>32.11799999999999</v>
+        <v>16.562</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>33.262</v>
+        <v>16.773</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-3.439360230894128</v>
+        <v>-1.257974125082006</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>33.19600000000001</v>
+        <v>16.984</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>33.194</v>
+        <v>16.84</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0.006025185274460831</v>
+        <v>0.8551068883610791</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>3.445385416168589</v>
+        <v>2.113081013443086</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -2523,68 +2523,65 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>15.49</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>603258</t>
+          <t>688720</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>电魂网络</t>
+          <t>艾森股份</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>15</v>
+        <v>46.5</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>16.16</v>
+        <v>54.33</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>7.733333333333325</v>
+        <v>16.83870967741936</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>16.5</v>
+        <v>55.8</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.786</v>
+        <v>47.872</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>14.95</v>
+        <v>48.544</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-1.096989966555195</v>
+        <v>-1.384311140408701</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>15.306</v>
+        <v>49.014</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>14.885</v>
+        <v>48.95699999999999</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2.828350688612713</v>
+        <v>0.1164287027391353</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>3.925340655167908</v>
+        <v>1.500739843147836</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -2595,16 +2592,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>15.49</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" t="inlineStr">
@@ -2614,46 +2611,46 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>300251</t>
+          <t>688146</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>光线传媒</t>
+          <t>中船特气</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.59</v>
+        <v>142.35</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>12.01</v>
+        <v>167.72</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>3.623813632441752</v>
+        <v>17.82226905514577</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.9</v>
+        <v>170.82</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11.622</v>
+        <v>147.968</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.649</v>
+        <v>150.401</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-0.2317795518928856</v>
+        <v>-1.617675414392183</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>11.816</v>
+        <v>151.682</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>11.668</v>
+        <v>151.681</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1.26842646554679</v>
+        <v>0.0006592783539316471</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>1.500206017439676</v>
+        <v>1.618334692746115</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -2664,16 +2661,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>15.49</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" t="inlineStr">
@@ -2683,46 +2680,46 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>300133</t>
+          <t>300540</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>华策影视</t>
+          <t>蜀道装备</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.92</v>
+        <v>20.48</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>24.2</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>5.94170403587444</v>
+        <v>18.1640625</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>10.7</v>
+        <v>24.57</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.890000000000001</v>
+        <v>21.776</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>9.052000000000001</v>
+        <v>21.932</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-1.789659743703054</v>
+        <v>-0.7112894400875369</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>9.059999999999999</v>
+        <v>22.286</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>9.058000000000002</v>
+        <v>22.111</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0.02207992934419867</v>
+        <v>0.79146126362446</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>1.811739673047252</v>
+        <v>1.502750703711997</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -2733,16 +2730,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>15.49</v>
+        <v>0</v>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" t="inlineStr">
@@ -2752,46 +2749,46 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>002400</t>
+          <t>688727</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>省广集团</t>
+          <t>恒坤新材</t>
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.45</v>
+        <v>34.32</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.85</v>
+        <v>40.83</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>6.201550387596888</v>
+        <v>18.96853146853146</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.09</v>
+        <v>41.18</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.525999999999999</v>
+        <v>35.766</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.565</v>
+        <v>36.261</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>-0.5940594059406057</v>
+        <v>-1.365103003226598</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.641999999999999</v>
+        <v>36.714</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>6.581999999999999</v>
+        <v>36.664</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0.9115770282588809</v>
+        <v>0.1363735544403166</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>1.505636434199487</v>
+        <v>1.501476557666914</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -2802,16 +2799,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>15.49</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" t="inlineStr">
@@ -2821,46 +2818,46 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>002555</t>
+          <t>688549</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>三七互娱</t>
+          <t>中巨芯-U</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>16.1</v>
+        <v>16.63</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.29</v>
+        <v>19.89</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>7.391304347826066</v>
+        <v>19.6031268791341</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>17.71</v>
+        <v>19.95</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>16.418</v>
+        <v>17.396</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>16.676</v>
+        <v>17.709</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-1.547133605181095</v>
+        <v>-1.767462871985992</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>16.684</v>
+        <v>17.886</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>16.678</v>
+        <v>17.885</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0.03597553663508002</v>
+        <v>0.005591277606931122</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>1.583109141816175</v>
+        <v>1.773054149592923</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -2871,16 +2868,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>15.49</v>
+        <v>10.67</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" t="inlineStr">
@@ -2890,46 +2887,46 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>300418</t>
+          <t>002348</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>高乐股份</t>
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>39.19</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>42.11</v>
+        <v>9.19</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>7.45088032661394</v>
+        <v>8.628841607564986</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>47.02</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>39.884</v>
+        <v>8.501999999999999</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>40.01</v>
+        <v>8.560999999999998</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.3149212696825776</v>
+        <v>-0.6891718257212909</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>40.746</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>40.009</v>
+        <v>8.587999999999999</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.842085530755577</v>
+        <v>0.8150908244061617</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>2.157006800438155</v>
+        <v>1.504262650127453</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -2940,16 +2937,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>15.49</v>
+        <v>10.67</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" t="inlineStr">
@@ -2959,46 +2956,46 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>600986</t>
+          <t>301169</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>浙文互联</t>
+          <t>零点有数</t>
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>6.79</v>
+        <v>44.63</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>7.34</v>
+        <v>50.26</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>8.100147275405</v>
+        <v>12.6148330719247</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>7.46</v>
+        <v>53.55</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>6.907999999999999</v>
+        <v>45.61</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>6.93</v>
+        <v>46.34099999999999</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>-0.3174603174603163</v>
+        <v>-1.577436826999834</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>7.058</v>
+        <v>46.75599999999999</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>6.953999999999999</v>
+        <v>46.755</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1.495542134023609</v>
+        <v>0.002138808683538329</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>1.813002451483925</v>
+        <v>1.579575635683372</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -3009,16 +3006,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15.49</v>
+        <v>10.67</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" t="inlineStr">
@@ -3028,46 +3025,46 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>920493</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>天下秀</t>
+          <t>并行科技</t>
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>4.68</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>5.06</v>
+        <v>99.17</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>8.119658119658112</v>
+        <v>14.74025222723592</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>5.14</v>
+        <v>103.71</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>4.81</v>
+        <v>91.07600000000001</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>4.857</v>
+        <v>91.12800000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>-0.9676755198682274</v>
+        <v>-0.0570625932754032</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>4.895999999999999</v>
+        <v>93.11000000000001</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>4.867</v>
+        <v>91.785</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>0.5958495993424906</v>
+        <v>1.443591000708189</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>1.563525119210718</v>
+        <v>1.500653593983592</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -3078,16 +3075,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>15.49</v>
+        <v>10.67</v>
       </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" t="inlineStr">
@@ -3097,46 +3094,46 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>603444</t>
+          <t>300067</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>吉比特</t>
+          <t>安诺其</t>
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>328.69</v>
+        <v>4.89</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>358.12</v>
+        <v>5.78</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>8.953725394748858</v>
+        <v>18.20040899795503</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>361.55</v>
+        <v>5.86</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>332.52</v>
+        <v>5.046</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>334.83</v>
+        <v>5.151000000000001</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>-0.6899023385001368</v>
+        <v>-2.038439138031456</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>339.542</v>
+        <v>5.2</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>336.813</v>
+        <v>5.198</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.8102418849628812</v>
+        <v>0.03847633705271747</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>1.500144223463018</v>
+        <v>2.076915475084173</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -3147,16 +3144,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>15.49</v>
+        <v>10.67</v>
       </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" t="inlineStr">
@@ -3166,46 +3163,46 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>300182</t>
+          <t>301396</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>捷成股份</t>
+          <t>宏景科技</t>
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>5.33</v>
+        <v>117.4</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>5.9</v>
+        <v>139.54</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>10.69418386491559</v>
+        <v>18.85860306643952</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>6.39</v>
+        <v>140.88</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>5.526000000000001</v>
+        <v>122.944</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>5.555000000000001</v>
+        <v>124.351</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-0.5220522052205245</v>
+        <v>-1.131474616207362</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>5.648</v>
+        <v>126.268</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>5.58</v>
+        <v>125.804</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>1.218637992831528</v>
+        <v>0.3688277002320994</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>1.740690198052053</v>
+        <v>1.500302316439461</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -3216,7 +3213,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3225,7 +3222,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>15.49</v>
+        <v>12.68</v>
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" t="inlineStr">
@@ -3235,46 +3232,46 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>300364</t>
+          <t>003032</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>中文在线</t>
+          <t>传智教育</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>23.45</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>26.59</v>
+        <v>8.69</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>13.39019189765458</v>
+        <v>5.717761557177603</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>28.14</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>24.172</v>
+        <v>8.106</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>24.289</v>
+        <v>8.142999999999999</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.4816995347688091</v>
+        <v>-0.4543779933685266</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>24.904</v>
+        <v>8.27</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>24.422</v>
+        <v>8.184000000000001</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>1.973630333306042</v>
+        <v>1.050830889540544</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>2.455329868074851</v>
+        <v>1.50520888290907</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -3285,7 +3282,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3294,7 +3291,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>15.49</v>
+        <v>12.68</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" t="inlineStr">
@@ -3304,46 +3301,46 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>300063</t>
+          <t>603533</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>天龙集团</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>7.93</v>
+        <v>28.03</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>9.01</v>
+        <v>29.73</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>13.61916771752838</v>
+        <v>6.064930431680349</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>9.51</v>
+        <v>30.83</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>8.251999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>8.348000000000001</v>
+        <v>27.53</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-1.149976042165812</v>
+        <v>-1.198692335633855</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>8.484</v>
+        <v>27.824</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>8.375</v>
+        <v>27.74</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>1.301492537313442</v>
+        <v>0.302811824080762</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>2.451468579479255</v>
+        <v>1.501504159714617</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -3354,7 +3351,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3363,7 +3360,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>15.49</v>
+        <v>12.68</v>
       </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" t="inlineStr">
@@ -3373,46 +3370,46 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>301262</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>海看股份</t>
+          <t>吉比特</t>
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>20.35</v>
+        <v>327.66</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>23.36</v>
+        <v>357.62</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>14.79115479115478</v>
+        <v>9.14362448879935</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>24.42</v>
+        <v>360.42</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>20.914</v>
+        <v>333.35</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>21.21099999999993</v>
+        <v>333.717</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>-1.400216868605564</v>
+        <v>-0.1099734205928904</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>21.638</v>
+        <v>340.698</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>21.336</v>
+        <v>336.027</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>1.415448068991365</v>
+        <v>1.390066869626527</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>2.815664937596929</v>
+        <v>1.500040290219418</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -3423,7 +3420,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3432,7 +3429,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>15.49</v>
+        <v>12.68</v>
       </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" t="inlineStr">
@@ -3442,46 +3439,46 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>301231</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>线上线下</t>
+          <t>荣信文化</t>
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>68.5</v>
+        <v>29.03</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>79.03</v>
+        <v>32.77</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>15.37226277372263</v>
+        <v>12.88322425077506</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>82.2</v>
+        <v>34.83</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>72.27799999999999</v>
+        <v>29.35</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>73.40299999999999</v>
+        <v>29.777</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>-1.532634905930275</v>
+        <v>-1.433992678913243</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>74.042</v>
+        <v>30.012</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>73.756</v>
+        <v>29.992</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>0.3877650631813001</v>
+        <v>0.06668444918644933</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>1.920399969111575</v>
+        <v>1.500677128099692</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -3492,7 +3489,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3501,7 +3498,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>15.49</v>
+        <v>12.68</v>
       </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" t="inlineStr">
@@ -3511,46 +3508,46 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>300785</t>
+          <t>300959</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>值得买</t>
+          <t>线上线下</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>32.47</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>37.95</v>
+        <v>80.77</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>16.87711733908224</v>
+        <v>14.00141143260409</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>38.96</v>
+        <v>85.02</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>34.376</v>
+        <v>72.75399999999999</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>34.82600000000001</v>
+        <v>73.11199999999999</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>-1.292138057772951</v>
+        <v>-0.4896597001860181</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>35.33</v>
+        <v>74.488</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>35.05500000000001</v>
+        <v>73.74199999999999</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0.7844815290257934</v>
+        <v>1.011635160424196</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>2.076619586798745</v>
+        <v>1.501294860610214</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -3561,7 +3558,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3570,7 +3567,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>15.49</v>
+        <v>12.68</v>
       </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" t="inlineStr">
@@ -3580,46 +3577,46 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>301171</t>
+          <t>300785</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>易点天下</t>
+          <t>值得买</t>
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>28.9</v>
+        <v>32.89</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>33.87</v>
+        <v>39.27</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>17.19723183391002</v>
+        <v>19.3979933110368</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>34.68</v>
+        <v>39.46</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>30.872</v>
+        <v>34.582</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>30.89</v>
+        <v>34.681</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.0582712852055467</v>
+        <v>-0.2854588968022709</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>31.734</v>
+        <v>35.634</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>31.077</v>
+        <v>35.206</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>2.11410367796121</v>
+        <v>1.215701868999597</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>2.172374963166757</v>
+        <v>1.501160765801868</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -3630,7 +3627,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3639,7 +3636,7 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>67.14</v>
+        <v>80</v>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" t="inlineStr">
@@ -3649,46 +3646,46 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>301182</t>
+          <t>688090</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>凯旺科技</t>
+          <t>瑞松科技</t>
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>43.21</v>
+        <v>56.98</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>50.56</v>
+        <v>59.17</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>17.00995140013886</v>
+        <v>3.843453843453859</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>51.85</v>
+        <v>68.37</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>46.172</v>
+        <v>55.638</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>46.638</v>
+        <v>56.24399999999999</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>-0.9991852137741675</v>
+        <v>-1.077448261147851</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>47.264</v>
+        <v>56.58199999999999</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>46.95</v>
+        <v>56.343</v>
       </c>
       <c r="S47" s="3" t="n">
-        <v>0.6687965921192696</v>
+        <v>0.4241875654473537</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>1.667981805893437</v>
+        <v>1.501635826595205</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -3699,7 +3696,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3708,7 +3705,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>67.14</v>
+        <v>80</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" t="inlineStr">
@@ -3718,46 +3715,46 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>688697</t>
+          <t>603790</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>纽威数控</t>
+          <t>雅运股份</t>
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>11.76</v>
+        <v>23.92</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>13.78</v>
+        <v>25.44</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>17.17687074829932</v>
+        <v>6.35451505016722</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>14.11</v>
+        <v>26.31</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>12.474</v>
+        <v>23.852</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>12.548</v>
+        <v>24.016</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>-0.5897354160025459</v>
+        <v>-0.682878081279148</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>12.832</v>
+        <v>24.35</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>12.656</v>
+        <v>24.152</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.390644753476589</v>
+        <v>0.8198078834051215</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>1.980380169479135</v>
+        <v>1.502685964684269</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -3768,7 +3765,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3777,7 +3774,7 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" t="inlineStr">
@@ -3799,37 +3796,37 @@
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>8.27</v>
+        <v>9.91</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>9.58</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>15.8403869407497</v>
+        <v>-17.86074672048435</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>9.92</v>
+        <v>11.89</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>8.528</v>
+        <v>8.598000000000001</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>8.674000000000001</v>
+        <v>8.708</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>-1.683191145953433</v>
+        <v>-1.263206247129067</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>8.82</v>
+        <v>8.662000000000001</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>8.818999999999999</v>
+        <v>8.547000000000001</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>0.01133915409912145</v>
+        <v>1.345501345501354</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>1.694530300052555</v>
+        <v>2.608707592630422</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -3840,7 +3837,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3849,56 +3846,59 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>002950</t>
+          <t>301080</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>奥美医疗</t>
+          <t>百普赛斯</t>
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>101.24</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>8.859999999999999</v>
+        <v>102.15</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>7.785888077858871</v>
+        <v>0.8988542078230077</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>9.039999999999999</v>
+        <v>121.48</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>8.343999999999999</v>
+        <v>92.77799999999999</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>8.372</v>
+        <v>94.16499999999999</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>-0.3344481605351279</v>
+        <v>-1.472946423830512</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>8.504</v>
+        <v>95.59200000000001</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>8.406000000000001</v>
+        <v>94.583</v>
       </c>
       <c r="S50" s="3" t="n">
-        <v>1.165833928146554</v>
+        <v>1.066787900574107</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>1.500282088681681</v>
+        <v>2.539734324404619</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3918,56 +3918,59 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>301408</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>华人健康</t>
+          <t>奥浦迈</t>
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>13.78</v>
+        <v>60.76</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>14.88</v>
+        <v>62.76</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>7.982583454281578</v>
+        <v>3.291639236339705</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>16.53</v>
+        <v>72.91</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>13.936</v>
+        <v>58.55</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>13.95</v>
+        <v>59.126</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-0.100358422939073</v>
+        <v>-0.9741907113621773</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>14.236</v>
+        <v>59.532</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>14.039</v>
+        <v>59.22000000000001</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>1.403233848564733</v>
+        <v>0.5268490374873203</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>1.503592271503806</v>
+        <v>1.501039748849498</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -3978,7 +3981,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3987,7 +3990,7 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" t="inlineStr">
@@ -3997,46 +4000,46 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>300702</t>
+          <t>688185</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>天宇股份</t>
+          <t>康希诺</t>
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>20.01</v>
+        <v>78.36</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>21.77</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>8.795602198900543</v>
+        <v>5.551301684532928</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>24.01</v>
+        <v>94.03</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>20.394</v>
+        <v>76.95399999999999</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>20.548</v>
+        <v>78.086</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>-0.749464668094213</v>
+        <v>-1.449683682094105</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>20.792</v>
+        <v>78.49600000000001</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>20.632</v>
+        <v>78.066</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>0.7754943776657752</v>
+        <v>0.5508159762252607</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>1.524959045759988</v>
+        <v>2.000499658319366</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -4047,7 +4050,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4056,7 +4059,7 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" t="inlineStr">
@@ -4066,46 +4069,46 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>603259</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>华兰股份</t>
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>141.48</v>
+        <v>51.32</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>154.19</v>
+        <v>54.32</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>8.983601922533225</v>
+        <v>5.845674201091189</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>155.62</v>
+        <v>61.58</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>145.54</v>
+        <v>50.696</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>146.801</v>
+        <v>51.258</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>-0.8589859742099804</v>
+        <v>-1.096414218268382</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>148.116</v>
+        <v>51.52</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>146.77</v>
+        <v>51.312</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>0.9170811473734553</v>
+        <v>0.4053632678515884</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>1.776067121583436</v>
+        <v>1.501777486119971</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -4116,7 +4119,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4125,7 +4128,7 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" t="inlineStr">
@@ -4135,46 +4138,46 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>600479</t>
+          <t>603127</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>千金药业</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>10.46</v>
+        <v>46.7</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>11.43</v>
+        <v>50.66</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>9.273422562141477</v>
+        <v>8.479657387580275</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>11.5</v>
+        <v>51.37</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>10.75629889298905</v>
+        <v>46.418</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>10.87729335793374</v>
+        <v>47.04600000000001</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>-1.112358203122654</v>
+        <v>-1.334863750371995</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>10.93193357933587</v>
+        <v>47.48</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>10.88938929889313</v>
+        <v>47.241</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>0.3906948247967001</v>
+        <v>0.5059164708621777</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>1.503053027919354</v>
+        <v>1.840780221234173</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -4185,7 +4188,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4194,7 +4197,7 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" t="inlineStr">
@@ -4204,46 +4207,46 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>688710</t>
+          <t>300109</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>益诺思</t>
+          <t>新开源</t>
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>83.36</v>
+        <v>11.24</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>91.54000000000001</v>
+        <v>12.67</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>9.812859884836866</v>
+        <v>12.72241992882561</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>100.03</v>
+        <v>13.48</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>83.75</v>
+        <v>11.452</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>84.50099999999999</v>
+        <v>11.502</v>
       </c>
       <c r="P55" s="3" t="n">
-        <v>-0.8887468787351471</v>
+        <v>-0.4347070074769532</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>85.82000000000001</v>
+        <v>11.72</v>
       </c>
       <c r="R55" s="4" t="n">
-        <v>84.71000000000001</v>
+        <v>11.596</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>1.310352968952899</v>
+        <v>1.069334253190735</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>2.199099847688046</v>
+        <v>1.504041260667688</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -4254,7 +4257,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4263,7 +4266,7 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" t="inlineStr">
@@ -4273,46 +4276,46 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>300363</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>博腾股份</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>20.93</v>
+        <v>9.33</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>23.15</v>
+        <v>10.53</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>10.60678451982799</v>
+        <v>12.86173633440513</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>25.11</v>
+        <v>11.19</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>21.43</v>
+        <v>9.654</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>21.526</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.4459723125522785</v>
+        <v>-0.5767250257466605</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>21.876</v>
+        <v>9.85</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>21.647</v>
+        <v>9.759</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>1.057883309465502</v>
+        <v>0.9324725894046537</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>1.50385562201778</v>
+        <v>1.509197615151314</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -4323,7 +4326,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4332,7 +4335,7 @@
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" t="inlineStr">
@@ -4342,46 +4345,46 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>300255</t>
+          <t>688202</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>常山药业</t>
+          <t>美迪西</t>
         </is>
       </c>
       <c r="J57" s="4" t="n">
-        <v>18.73</v>
+        <v>79.13</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>20.9</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>11.58569140416443</v>
+        <v>13.37040313408315</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>22.47</v>
+        <v>94.95</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>19.526</v>
+        <v>80.19799999999999</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>19.721</v>
+        <v>80.96000000000001</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>-0.9887936717204893</v>
+        <v>-0.9412055335968561</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>19.884</v>
+        <v>82.13799999999999</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>19.782</v>
+        <v>81.681</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>0.515620260843197</v>
+        <v>0.5594936398917616</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>1.504413932563686</v>
+        <v>1.500699173488618</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -4392,7 +4395,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4401,7 +4404,7 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" t="inlineStr">
@@ -4411,46 +4414,46 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>300705</t>
+          <t>300347</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>九典制药</t>
+          <t>泰格医药</t>
         </is>
       </c>
       <c r="J58" s="4" t="n">
-        <v>10.33</v>
+        <v>48.21</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>11.54</v>
+        <v>55.13</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>11.71345595353339</v>
+        <v>14.3538684920141</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>12.39</v>
+        <v>57.85</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>10.682</v>
+        <v>50.014</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>10.718</v>
+        <v>50.337</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>-0.3358835603657573</v>
+        <v>-0.6416751097602202</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>10.926</v>
+        <v>51.28000000000001</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>10.8</v>
+        <v>50.843</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>1.166666666666649</v>
+        <v>0.859508683594612</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>1.502550227032406</v>
+        <v>1.501183793354832</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -4461,7 +4464,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4470,7 +4473,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" t="inlineStr">
@@ -4480,46 +4483,46 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>688607</t>
+          <t>300404</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>康众科技</t>
+          <t>博济医药</t>
         </is>
       </c>
       <c r="J59" s="4" t="n">
-        <v>31</v>
+        <v>11.19</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>34.67</v>
+        <v>12.86</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>11.83870967741936</v>
+        <v>14.92403932082216</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>37.2</v>
+        <v>13.42</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>32.822</v>
+        <v>11.39</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>33.042</v>
+        <v>11.637</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>-0.6658192603353319</v>
+        <v>-2.122540173584253</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>33.384</v>
+        <v>11.698</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>33.10700000000001</v>
+        <v>11.696</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>0.8366810644274469</v>
+        <v>0.01709986320108658</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>1.502500324762779</v>
+        <v>2.13964003678534</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -4530,7 +4533,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4539,7 +4542,7 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" t="inlineStr">
@@ -4549,46 +4552,46 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>300434</t>
+          <t>300204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>金石亚药</t>
+          <t>舒泰神</t>
         </is>
       </c>
       <c r="J60" s="4" t="n">
-        <v>11.31</v>
+        <v>17.29</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>12.66</v>
+        <v>19.92</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>11.93633952254642</v>
+        <v>15.2111046847889</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>13.57</v>
+        <v>20.74</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>12.044</v>
+        <v>17.992</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>12.294</v>
+        <v>18.025</v>
       </c>
       <c r="P60" s="3" t="n">
-        <v>-2.033512282414185</v>
+        <v>-0.1830790568654761</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>12.242</v>
+        <v>18.362</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>12.24</v>
+        <v>18.123</v>
       </c>
       <c r="S60" s="3" t="n">
-        <v>0.01633986928104569</v>
+        <v>1.318766208685118</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>2.049852151695231</v>
+        <v>1.501845265550594</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -4599,7 +4602,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4608,7 +4611,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" t="inlineStr">
@@ -4618,46 +4621,46 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>300534</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>10.34</v>
+        <v>11.33</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>12.14750542299348</v>
+        <v>15.49439347604484</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>11.06</v>
+        <v>11.77</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>9.634</v>
+        <v>10.228</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>9.775000000000002</v>
+        <v>10.394</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>-1.442455242966767</v>
+        <v>-1.597075235712919</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>9.818000000000001</v>
+        <v>10.448</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>9.792000000000002</v>
+        <v>10.447</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.2655228758169814</v>
+        <v>0.009572125969170564</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>1.707978118783748</v>
+        <v>1.60664736168209</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -4668,7 +4671,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4677,7 +4680,7 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" t="inlineStr">
@@ -4687,46 +4690,46 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>301333</t>
+          <t>301111</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>诺思格</t>
+          <t>粤万年青</t>
         </is>
       </c>
       <c r="J62" s="4" t="n">
-        <v>51.85</v>
+        <v>17.81</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>58.46</v>
+        <v>20.77</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>12.74831243972998</v>
+        <v>16.61987647389107</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>62.22</v>
+        <v>21.37</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>53.51000000000001</v>
+        <v>18.556</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>54.26900000000001</v>
+        <v>18.884</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>-1.398588512778931</v>
+        <v>-1.736920144037279</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>54.876</v>
+        <v>19.018</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>54.463</v>
+        <v>19.016</v>
       </c>
       <c r="S62" s="3" t="n">
-        <v>0.7583129831261637</v>
+        <v>0.01051745898192902</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>2.156901495905095</v>
+        <v>1.747437603019208</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -4737,7 +4740,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4746,7 +4749,7 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" t="inlineStr">
@@ -4756,46 +4759,46 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>300246</t>
+          <t>300436</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>宝莱特</t>
+          <t>广生堂</t>
         </is>
       </c>
       <c r="J63" s="4" t="n">
-        <v>12.22</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>13.85</v>
+        <v>86.41</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>13.33878887070377</v>
+        <v>16.75449263613025</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>14.66</v>
+        <v>88.81</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>12.864</v>
+        <v>76.684</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>12.941</v>
+        <v>77.422</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>-0.5950081137470087</v>
+        <v>-0.9532174317377518</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>13.106</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>12.988</v>
+        <v>78.06299999999999</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>0.9085309516476681</v>
+        <v>0.54699409451342</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>1.503539065394677</v>
+        <v>1.500211526251172</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -4806,7 +4809,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4815,7 +4818,7 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" t="inlineStr">
@@ -4825,46 +4828,46 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>300109</t>
+          <t>920047</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>新开源</t>
+          <t>诺思兰德</t>
         </is>
       </c>
       <c r="J64" s="4" t="n">
-        <v>10.77</v>
+        <v>12.62</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>12.33</v>
+        <v>14.75</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>14.48467966573816</v>
+        <v>16.87797147385104</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>12.92</v>
+        <v>15.14</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>11.36</v>
+        <v>13.434</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>11.514</v>
+        <v>13.55</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>-1.337502171269755</v>
+        <v>-0.8560885608856372</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>11.602</v>
+        <v>13.722</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>11.577</v>
+        <v>13.634</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0.2159454090005841</v>
+        <v>0.6454452105031372</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>1.55344758027034</v>
+        <v>1.501533771388774</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -4875,7 +4878,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4884,7 +4887,7 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" t="inlineStr">
@@ -4894,46 +4897,46 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>300347</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>泰格医药</t>
+          <t>一品红</t>
         </is>
       </c>
       <c r="J65" s="4" t="n">
-        <v>47.82</v>
+        <v>29.14</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>54.89</v>
+        <v>34.32</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>14.78460895023004</v>
+        <v>17.77625257378175</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>57.38</v>
+        <v>34.96</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>50.25599999999999</v>
+        <v>30.548</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>50.69799999999999</v>
+        <v>30.561</v>
       </c>
       <c r="P65" s="3" t="n">
-        <v>-0.8718292634817937</v>
+        <v>-0.0425378750695149</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>51.302</v>
+        <v>31.358</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>50.98099999999999</v>
+        <v>30.907</v>
       </c>
       <c r="S65" s="3" t="n">
-        <v>0.6296463388321349</v>
+        <v>1.459216358753701</v>
       </c>
       <c r="T65" s="5" t="n">
-        <v>1.501475602313929</v>
+        <v>1.501754233823216</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -4944,7 +4947,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4953,7 +4956,7 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" t="inlineStr">
@@ -4963,46 +4966,46 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>300723</t>
+          <t>688137</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>一品红</t>
+          <t>近岸蛋白</t>
         </is>
       </c>
       <c r="J66" s="4" t="n">
-        <v>28.77</v>
+        <v>127.2</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>33.08</v>
+        <v>151.19</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>14.98088286409454</v>
+        <v>18.86006289308175</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>34.52</v>
+        <v>152.64</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>30.38</v>
+        <v>122.478</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>30.584</v>
+        <v>125.475</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>-0.6670154329060929</v>
+        <v>-2.388523610280935</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>31.088</v>
+        <v>131.316</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>30.831</v>
+        <v>126.653</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.8335765949855745</v>
+        <v>3.681713026931832</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>1.500592027891667</v>
+        <v>6.070236637212767</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -5013,7 +5016,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5022,7 +5025,7 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" t="inlineStr">
@@ -5032,46 +5035,46 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>300683</t>
+          <t>301201</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>海特生物</t>
+          <t>诚达药业</t>
         </is>
       </c>
       <c r="J67" s="4" t="n">
-        <v>21.76</v>
+        <v>23.95</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>25.03</v>
+        <v>28.49</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>15.02757352941175</v>
+        <v>18.95615866388309</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>26.11</v>
+        <v>28.74</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>23.268</v>
+        <v>25.346</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>23.612</v>
+        <v>25.705</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>-1.456886328985241</v>
+        <v>-1.396615444466065</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>23.674</v>
+        <v>25.96</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>23.663</v>
+        <v>25.933</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0.0464860753074392</v>
+        <v>0.1041144487718304</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>1.50337240429268</v>
+        <v>1.500729893237895</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -5082,7 +5085,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5091,7 +5094,7 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>9.02</v>
+        <v>10.95</v>
       </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" t="inlineStr">
@@ -5101,46 +5104,46 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>300725</t>
+          <t>920367</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>药石科技</t>
+          <t>新赣江</t>
         </is>
       </c>
       <c r="J68" s="4" t="n">
-        <v>41.36</v>
+        <v>19.95</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>47.86</v>
+        <v>23.8</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>15.71566731141198</v>
+        <v>19.2982456140351</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>49.63</v>
+        <v>23.94</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>44.188</v>
+        <v>21.502</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>44.511</v>
+        <v>21.968</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>-0.7256633191795259</v>
+        <v>-2.12126729788783</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>45.09999999999999</v>
+        <v>22.098</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>44.753</v>
+        <v>21.968</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.7753670145018043</v>
+        <v>0.5917698470502719</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>1.50103033368133</v>
+        <v>2.713037144938102</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -5151,65 +5154,68 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>301257</t>
+          <t>600621</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>普蕊斯</t>
+          <t>华鑫股份</t>
         </is>
       </c>
       <c r="J69" s="4" t="n">
-        <v>31.5</v>
+        <v>14.9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>36.68</v>
+        <v>15.91</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>16.44444444444444</v>
+        <v>6.778523489932886</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>37.8</v>
+        <v>16.39</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>33.264</v>
+        <v>14.66</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>33.722</v>
+        <v>14.77</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>-1.358163809975699</v>
+        <v>-0.7447528774542911</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>34.134</v>
+        <v>14.996</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>33.854</v>
+        <v>14.883</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>0.8270809948602853</v>
+        <v>0.7592555264395617</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>2.185244804835984</v>
+        <v>1.504008403893853</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -5220,16 +5226,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" t="inlineStr">
@@ -5239,46 +5245,46 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>601519</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>华兰股份</t>
+          <t>大智慧</t>
         </is>
       </c>
       <c r="J70" s="4" t="n">
-        <v>47.68</v>
+        <v>8.76</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>55.64</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>16.69463087248322</v>
+        <v>7.191780821917826</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>57.21</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>50.5</v>
+        <v>9.022</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>51.384</v>
+        <v>9.144000000000002</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>-1.720379884789036</v>
+        <v>-1.334208223972022</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>51.824</v>
+        <v>9.218</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>51.822</v>
+        <v>9.118</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0.003859364748559635</v>
+        <v>1.096731739416534</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>1.724239249537596</v>
+        <v>2.430939963388556</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -5289,16 +5295,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" t="inlineStr">
@@ -5308,46 +5314,46 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>600958</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>诚达药业</t>
+          <t>东方证券</t>
         </is>
       </c>
       <c r="J71" s="4" t="n">
-        <v>24.01</v>
+        <v>8.48</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>28.02</v>
+        <v>9.15</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>16.70137442732194</v>
+        <v>7.900943396226423</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>28.81</v>
+        <v>9.32</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>25.546</v>
+        <v>8.586</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>25.963</v>
+        <v>8.595000000000002</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>-1.606131802950361</v>
+        <v>-0.1047120418848468</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>26.066</v>
+        <v>8.75</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>26.065</v>
+        <v>8.629</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0.003836562440051594</v>
+        <v>1.402248232703673</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>1.609968365390413</v>
+        <v>1.50696027458852</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -5358,16 +5364,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" t="inlineStr">
@@ -5377,46 +5383,46 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>920047</t>
+          <t>601377</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>诺思兰德</t>
+          <t>兴业证券</t>
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>12.62</v>
+        <v>5.52</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>14.75</v>
+        <v>6</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>16.87797147385104</v>
+        <v>8.695652173913061</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>15.14</v>
+        <v>6.07</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>13.434</v>
+        <v>5.613999999999999</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>13.55</v>
+        <v>5.625999999999999</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>-0.8560885608856372</v>
+        <v>-0.2132954141486065</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>13.722</v>
+        <v>5.726</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>13.634</v>
+        <v>5.653</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>0.6454452105031372</v>
+        <v>1.291349725809288</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>1.501533771388774</v>
+        <v>1.504645139957894</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -5427,16 +5433,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" t="inlineStr">
@@ -5446,46 +5452,46 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>300204</t>
+          <t>002736</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>舒泰神</t>
+          <t>国信证券</t>
         </is>
       </c>
       <c r="J73" s="4" t="n">
-        <v>16.91</v>
+        <v>9.66</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>19.8</v>
+        <v>10.52</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>17.09047900650502</v>
+        <v>8.902691511387161</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>20.29</v>
+        <v>10.62</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>17.97</v>
+        <v>9.806000000000001</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>18.211</v>
+        <v>9.812999999999999</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>-1.323375981549613</v>
+        <v>-0.07133394476712684</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>18.47</v>
+        <v>10.008</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>18.264</v>
+        <v>9.866999999999999</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>1.127901883486615</v>
+        <v>1.429005776831871</v>
       </c>
       <c r="T73" s="5" t="n">
-        <v>2.451277865036228</v>
+        <v>1.500339721598998</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -5496,16 +5502,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" t="inlineStr">
@@ -5515,46 +5521,46 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>300534</t>
+          <t>601136</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>首创证券</t>
         </is>
       </c>
       <c r="J74" s="4" t="n">
-        <v>9.68</v>
+        <v>13.49</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>11.41</v>
+        <v>14.78</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>17.8719008264463</v>
+        <v>9.562638991845795</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>11.61</v>
+        <v>14.83</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>10.302</v>
+        <v>13.94</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>10.524</v>
+        <v>14.029</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>-2.109464082098089</v>
+        <v>-0.6344001710741898</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>10.564</v>
+        <v>14.184</v>
       </c>
       <c r="R74" s="4" t="n">
-        <v>10.562</v>
+        <v>14.062</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>0.01893580761218594</v>
+        <v>0.8675864030721181</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>2.128399889710275</v>
+        <v>1.501986574146308</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -5565,16 +5571,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" t="inlineStr">
@@ -5584,46 +5590,46 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>300436</t>
+          <t>688318</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>广生堂</t>
+          <t>财富趋势</t>
         </is>
       </c>
       <c r="J75" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>83.91</v>
+        <v>77.61</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>18.34978843441466</v>
+        <v>10.88726960994428</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>85.08</v>
+        <v>83.98</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>76.474</v>
+        <v>73.66400000000002</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>77.93899999999999</v>
+        <v>73.70700000000001</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>-1.879675130550806</v>
+        <v>-0.05833909940710091</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>78.164</v>
+        <v>75.06800000000001</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>78.16199999999999</v>
+        <v>74.001</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.002558788157935865</v>
+        <v>1.441872407129652</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>1.882233918708742</v>
+        <v>1.500211506536753</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -5634,16 +5640,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" t="inlineStr">
@@ -5653,46 +5659,46 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>301234</t>
+          <t>300803</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>五洲医疗</t>
+          <t>指南针</t>
         </is>
       </c>
       <c r="J76" s="4" t="n">
-        <v>125.7</v>
+        <v>48.38</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>149.04</v>
+        <v>55.17</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>18.56801909307875</v>
+        <v>14.03472509301364</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>150.84</v>
+        <v>58.05</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>130.836</v>
+        <v>51.812</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>131.754</v>
+        <v>52.057</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.6967530397559152</v>
+        <v>-0.4706379545498129</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>134.844</v>
+        <v>52.79600000000001</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>132.851</v>
+        <v>52.258</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.50017688989923</v>
+        <v>1.029507443836364</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>2.196929929655145</v>
+        <v>1.500145398386177</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -5703,16 +5709,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>互金证券</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>9.02</v>
+        <v>1.64</v>
       </c>
       <c r="E77" s="3" t="n"/>
       <c r="F77" t="inlineStr">
@@ -5722,46 +5728,46 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>920367</t>
+          <t>300085</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>新赣江</t>
+          <t>银之杰</t>
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>19.95</v>
+        <v>24.89</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>23.8</v>
+        <v>28.83</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>19.2982456140351</v>
+        <v>15.82965046203293</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>23.94</v>
+        <v>29.86</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>21.502</v>
+        <v>26.71</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>21.968</v>
+        <v>26.998</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>-2.12126729788783</v>
+        <v>-1.066745684865533</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>22.098</v>
+        <v>27.322</v>
       </c>
       <c r="R77" s="4" t="n">
-        <v>21.968</v>
+        <v>27.123</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>0.5917698470502719</v>
+        <v>0.7336946502968011</v>
       </c>
       <c r="T77" s="5" t="n">
-        <v>2.713037144938102</v>
+        <v>1.800440335162334</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -5772,16 +5778,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>黄金白银</t>
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>9.02</v>
+        <v>0</v>
       </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" t="inlineStr">
@@ -5791,46 +5797,46 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>300945</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>奥浦迈</t>
+          <t>曼卡龙</t>
         </is>
       </c>
       <c r="J78" s="4" t="n">
-        <v>54.08</v>
+        <v>10.02</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>64.63</v>
+        <v>11.52</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>19.50813609467454</v>
+        <v>14.97005988023952</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>64.89</v>
+        <v>12.02</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>58.05423652173778</v>
+        <v>10.506</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>59.41505217391117</v>
+        <v>10.536</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>-2.29035505714984</v>
+        <v>-0.2847380410022526</v>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>59.69761739130344</v>
+        <v>10.762</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>59.69563130434619</v>
+        <v>10.632</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0.00332702228595938</v>
+        <v>1.222723852520691</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>2.293682079435799</v>
+        <v>1.507461893522943</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -5841,68 +5847,65 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>1.64</v>
+        <v>16.07</v>
       </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>600621</t>
+          <t>300069</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>华鑫股份</t>
+          <t>金利华电</t>
         </is>
       </c>
       <c r="J79" s="4" t="n">
-        <v>14.9</v>
+        <v>21.06</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>15.91</v>
+        <v>23.99</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>6.778523489932886</v>
+        <v>13.91263057929724</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>16.39</v>
+        <v>25.27</v>
       </c>
       <c r="N79" s="4" t="n">
-        <v>14.66</v>
+        <v>21.766</v>
       </c>
       <c r="O79" s="4" t="n">
-        <v>14.77</v>
+        <v>22.147</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>-0.7447528774542911</v>
+        <v>-1.720323294351378</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>14.996</v>
+        <v>22.318</v>
       </c>
       <c r="R79" s="4" t="n">
-        <v>14.883</v>
+        <v>22.316</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>0.7592555264395617</v>
+        <v>0.008962179602090004</v>
       </c>
       <c r="T79" s="5" t="n">
-        <v>1.504008403893853</v>
+        <v>1.729285473953468</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -5913,16 +5916,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>1.64</v>
+        <v>16.07</v>
       </c>
       <c r="E80" s="3" t="n"/>
       <c r="F80" t="inlineStr">
@@ -5932,46 +5935,46 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>601519</t>
+          <t>301082</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>大智慧</t>
+          <t>久盛电气</t>
         </is>
       </c>
       <c r="J80" s="4" t="n">
-        <v>8.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>7.191780821917826</v>
+        <v>16.51480637813214</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>9.630000000000001</v>
+        <v>10.53</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>9.022</v>
+        <v>9.296000000000001</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>9.144000000000002</v>
+        <v>9.324000000000002</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>-1.334208223972022</v>
+        <v>-0.3003003003003046</v>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>9.218</v>
+        <v>9.526</v>
       </c>
       <c r="R80" s="4" t="n">
-        <v>9.118</v>
+        <v>9.413</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>1.096731739416534</v>
+        <v>1.200467438648678</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>2.430939963388556</v>
+        <v>1.500767738948983</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
@@ -5982,16 +5985,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>1.64</v>
+        <v>16.07</v>
       </c>
       <c r="E81" s="3" t="n"/>
       <c r="F81" t="inlineStr">
@@ -6001,46 +6004,46 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>600958</t>
+          <t>300427</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>东方证券</t>
+          <t>红相股份</t>
         </is>
       </c>
       <c r="J81" s="4" t="n">
-        <v>8.48</v>
+        <v>5.21</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>9.15</v>
+        <v>6.14</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>7.900943396226423</v>
+        <v>17.85028790786946</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>9.32</v>
+        <v>6.25</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>8.586</v>
+        <v>5.538</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>8.595000000000002</v>
+        <v>5.588</v>
       </c>
       <c r="P81" s="3" t="n">
-        <v>-0.1047120418848468</v>
+        <v>-0.8947745168217613</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>8.75</v>
+        <v>5.678</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>8.629</v>
+        <v>5.643000000000001</v>
       </c>
       <c r="S81" s="3" t="n">
-        <v>1.402248232703673</v>
+        <v>0.6202374623427209</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>1.50696027458852</v>
+        <v>1.515011979164482</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -6051,16 +6054,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="E82" s="3" t="n"/>
       <c r="F82" t="inlineStr">
@@ -6070,46 +6073,46 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>601377</t>
+          <t>688323</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>兴业证券</t>
+          <t>瑞华泰</t>
         </is>
       </c>
       <c r="J82" s="4" t="n">
-        <v>5.52</v>
+        <v>18.3</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>6</v>
+        <v>21.78</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>8.695652173913061</v>
+        <v>19.01639344262296</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>6.07</v>
+        <v>21.96</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>5.613999999999999</v>
+        <v>19.84</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>5.625999999999999</v>
+        <v>19.986</v>
       </c>
       <c r="P82" s="3" t="n">
-        <v>-0.2132954141486065</v>
+        <v>-0.7305113579505473</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>5.726</v>
+        <v>20.312</v>
       </c>
       <c r="R82" s="4" t="n">
-        <v>5.653</v>
+        <v>20.156</v>
       </c>
       <c r="S82" s="3" t="n">
-        <v>1.291349725809288</v>
+        <v>0.7739630879142867</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>1.504645139957894</v>
+        <v>1.504474445864834</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
@@ -6117,698 +6120,8 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>互金证券</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>002736</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>国信证券</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>9.66</v>
-      </c>
-      <c r="K83" s="4" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>8.902691511387161</v>
-      </c>
-      <c r="M83" s="4" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v>9.806000000000001</v>
-      </c>
-      <c r="O83" s="4" t="n">
-        <v>9.812999999999999</v>
-      </c>
-      <c r="P83" s="3" t="n">
-        <v>-0.07133394476712684</v>
-      </c>
-      <c r="Q83" s="4" t="n">
-        <v>10.008</v>
-      </c>
-      <c r="R83" s="4" t="n">
-        <v>9.866999999999999</v>
-      </c>
-      <c r="S83" s="3" t="n">
-        <v>1.429005776831871</v>
-      </c>
-      <c r="T83" s="5" t="n">
-        <v>1.500339721598998</v>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>互金证券</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>601136</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>首创证券</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>9.562638991845795</v>
-      </c>
-      <c r="M84" s="4" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="O84" s="4" t="n">
-        <v>14.029</v>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>-0.6344001710741898</v>
-      </c>
-      <c r="Q84" s="4" t="n">
-        <v>14.184</v>
-      </c>
-      <c r="R84" s="4" t="n">
-        <v>14.062</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>0.8675864030721181</v>
-      </c>
-      <c r="T84" s="5" t="n">
-        <v>1.501986574146308</v>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>互金证券</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>688318</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>财富趋势</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="n">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="K85" s="4" t="n">
-        <v>77.61</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>10.88726960994428</v>
-      </c>
-      <c r="M85" s="4" t="n">
-        <v>83.98</v>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v>73.66400000000002</v>
-      </c>
-      <c r="O85" s="4" t="n">
-        <v>73.70700000000001</v>
-      </c>
-      <c r="P85" s="3" t="n">
-        <v>-0.05833909940710091</v>
-      </c>
-      <c r="Q85" s="4" t="n">
-        <v>75.06800000000001</v>
-      </c>
-      <c r="R85" s="4" t="n">
-        <v>74.001</v>
-      </c>
-      <c r="S85" s="3" t="n">
-        <v>1.441872407129652</v>
-      </c>
-      <c r="T85" s="5" t="n">
-        <v>1.500211506536753</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>互金证券</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>300803</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>指南针</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>55.17</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>14.03472509301364</v>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v>58.05</v>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v>51.812</v>
-      </c>
-      <c r="O86" s="4" t="n">
-        <v>52.057</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>-0.4706379545498129</v>
-      </c>
-      <c r="Q86" s="4" t="n">
-        <v>52.79600000000001</v>
-      </c>
-      <c r="R86" s="4" t="n">
-        <v>52.258</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>1.029507443836364</v>
-      </c>
-      <c r="T86" s="5" t="n">
-        <v>1.500145398386177</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>互金证券</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>300085</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>银之杰</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>24.89</v>
-      </c>
-      <c r="K87" s="4" t="n">
-        <v>28.83</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>15.82965046203293</v>
-      </c>
-      <c r="M87" s="4" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v>26.71</v>
-      </c>
-      <c r="O87" s="4" t="n">
-        <v>26.998</v>
-      </c>
-      <c r="P87" s="3" t="n">
-        <v>-1.066745684865533</v>
-      </c>
-      <c r="Q87" s="4" t="n">
-        <v>27.322</v>
-      </c>
-      <c r="R87" s="4" t="n">
-        <v>27.123</v>
-      </c>
-      <c r="S87" s="3" t="n">
-        <v>0.7336946502968011</v>
-      </c>
-      <c r="T87" s="5" t="n">
-        <v>1.800440335162334</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>黄金白银</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>300945</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>曼卡龙</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="K88" s="4" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>14.97005988023952</v>
-      </c>
-      <c r="M88" s="4" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v>10.506</v>
-      </c>
-      <c r="O88" s="4" t="n">
-        <v>10.536</v>
-      </c>
-      <c r="P88" s="3" t="n">
-        <v>-0.2847380410022526</v>
-      </c>
-      <c r="Q88" s="4" t="n">
-        <v>10.762</v>
-      </c>
-      <c r="R88" s="4" t="n">
-        <v>10.632</v>
-      </c>
-      <c r="S88" s="3" t="n">
-        <v>1.222723852520691</v>
-      </c>
-      <c r="T88" s="5" t="n">
-        <v>1.507461893522943</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>300069</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>金利华电</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>21.06</v>
-      </c>
-      <c r="K89" s="4" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>13.91263057929724</v>
-      </c>
-      <c r="M89" s="4" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v>21.766</v>
-      </c>
-      <c r="O89" s="4" t="n">
-        <v>22.147</v>
-      </c>
-      <c r="P89" s="3" t="n">
-        <v>-1.720323294351378</v>
-      </c>
-      <c r="Q89" s="4" t="n">
-        <v>22.318</v>
-      </c>
-      <c r="R89" s="4" t="n">
-        <v>22.316</v>
-      </c>
-      <c r="S89" s="3" t="n">
-        <v>0.008962179602090004</v>
-      </c>
-      <c r="T89" s="5" t="n">
-        <v>1.729285473953468</v>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>301082</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>久盛电气</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>16.51480637813214</v>
-      </c>
-      <c r="M90" s="4" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v>9.296000000000001</v>
-      </c>
-      <c r="O90" s="4" t="n">
-        <v>9.324000000000002</v>
-      </c>
-      <c r="P90" s="3" t="n">
-        <v>-0.3003003003003046</v>
-      </c>
-      <c r="Q90" s="4" t="n">
-        <v>9.526</v>
-      </c>
-      <c r="R90" s="4" t="n">
-        <v>9.413</v>
-      </c>
-      <c r="S90" s="3" t="n">
-        <v>1.200467438648678</v>
-      </c>
-      <c r="T90" s="5" t="n">
-        <v>1.500767738948983</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>300427</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>红相股份</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="K91" s="4" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>17.85028790786946</v>
-      </c>
-      <c r="M91" s="4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v>5.538</v>
-      </c>
-      <c r="O91" s="4" t="n">
-        <v>5.588</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>-0.8947745168217613</v>
-      </c>
-      <c r="Q91" s="4" t="n">
-        <v>5.678</v>
-      </c>
-      <c r="R91" s="4" t="n">
-        <v>5.643000000000001</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>0.6202374623427209</v>
-      </c>
-      <c r="T91" s="5" t="n">
-        <v>1.515011979164482</v>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>688323</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>瑞华泰</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="K92" s="4" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>19.01639344262296</v>
-      </c>
-      <c r="M92" s="4" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="N92" s="4" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="O92" s="4" t="n">
-        <v>19.986</v>
-      </c>
-      <c r="P92" s="3" t="n">
-        <v>-0.7305113579505473</v>
-      </c>
-      <c r="Q92" s="4" t="n">
-        <v>20.312</v>
-      </c>
-      <c r="R92" s="4" t="n">
-        <v>20.156</v>
-      </c>
-      <c r="S92" s="3" t="n">
-        <v>0.7739630879142867</v>
-      </c>
-      <c r="T92" s="5" t="n">
-        <v>1.504474445864834</v>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:U92"/>
+  <autoFilter ref="A2:U82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>

--- a/data/five_break_10_targets.xlsx
+++ b/data/five_break_10_targets.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控结果" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$U$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'监控结果'!$A$2:$U$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5破10明日门槛完整名单｜信号日 2026-10-28｜80 只｜报告 多空阶段_2026-10-28.xlsx</t>
+          <t>5破10明日门槛完整名单｜信号日 2026-10-28｜75 只｜报告 多空阶段_2026-10-28.xlsx</t>
         </is>
       </c>
     </row>
@@ -616,37 +616,37 @@
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>171.1</v>
+        <v>171.39</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>196.43</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>14.80420806545881</v>
+        <v>14.6099539062956</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>205.32</v>
+        <v>205.66</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>170.124</v>
+        <v>170.182</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>170.376</v>
+        <v>170.405</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-0.1479081560783468</v>
+        <v>-0.1308647046741496</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>175.41</v>
+        <v>175.468</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>173.069</v>
+        <v>173.098</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.352639698617319</v>
+        <v>1.369166599267468</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>1.500547854695666</v>
+        <v>1.500031303941618</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -754,37 +754,37 @@
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>22.16</v>
+        <v>22.14</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>26.01</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>17.37364620938628</v>
+        <v>17.47967479674797</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>26.59</v>
+        <v>26.56</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>23.012</v>
+        <v>23.008</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>23.285</v>
+        <v>23.283</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-1.172428602104358</v>
+        <v>-1.181119271571507</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>23.602</v>
+        <v>23.598</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>23.426</v>
+        <v>23.424</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7513019721676617</v>
+        <v>0.7428278688524692</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>1.92373057427202</v>
+        <v>1.923947140423976</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" t="inlineStr">
@@ -823,25 +823,25 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>634.5599999999999</v>
+        <v>636.3</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>676.03</v>
+        <v>675.16</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>6.535237014624307</v>
+        <v>6.107182146786116</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>761.47</v>
+        <v>763.5599999999999</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>618.9440000000001</v>
+        <v>619.1180000000001</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>631.02</v>
+        <v>631.107</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.913726981712138</v>
+        <v>-1.899677867619898</v>
       </c>
       <c r="Q6" s="4" t="n">
         <v>631.624</v>
@@ -853,7 +853,7 @@
         <v>0.0001583222903667192</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>1.913885304002505</v>
+        <v>1.899836189910264</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" t="inlineStr">
@@ -892,37 +892,37 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>200.92</v>
+        <v>201.43</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>223.34</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>11.1586701174597</v>
+        <v>10.87722782107927</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>241.1</v>
+        <v>241.71</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>202.134</v>
+        <v>202.236</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>204.329</v>
+        <v>204.38</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-1.074247904115433</v>
+        <v>-1.049026323515034</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>206.64</v>
+        <v>206.742</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>205.383</v>
+        <v>205.434</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6120272856078746</v>
+        <v>0.6367008382254458</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>1.686275189723307</v>
+        <v>1.68572716174048</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" t="inlineStr">
@@ -961,37 +961,37 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>162.79</v>
+        <v>163</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>189.37</v>
+        <v>189.26</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>16.32778426193255</v>
+        <v>16.11042944785275</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>195.34</v>
+        <v>195.6</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>166.846</v>
+        <v>166.866</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>169.518</v>
+        <v>169.528</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-1.576233792281623</v>
+        <v>-1.57024208390355</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>171.148</v>
+        <v>171.146</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>171.146</v>
+        <v>171.145</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.001168592897271559</v>
+        <v>0.0005842998627159091</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>1.577402385178894</v>
+        <v>1.570826383766266</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" t="inlineStr">
@@ -1030,25 +1030,25 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>193.6</v>
+        <v>194.26</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>226.97</v>
+        <v>226.64</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>17.23657024793388</v>
+        <v>16.66838258004735</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>232.32</v>
+        <v>233.11</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>199.842</v>
+        <v>199.908</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>203.349</v>
+        <v>203.382</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>-1.724621217709432</v>
+        <v>-1.708115762456852</v>
       </c>
       <c r="Q9" s="4" t="n">
         <v>205.168</v>
@@ -1060,7 +1060,7 @@
         <v>0.0009748203893433782</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>1.725596038098776</v>
+        <v>1.709090582846196</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" t="inlineStr">
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.35</v>
+        <v>11.37</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13.32</v>
+        <v>13.31</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>17.3568281938326</v>
+        <v>17.06244503078278</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>13.62</v>
+        <v>13.64</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>11.822</v>
+        <v>11.824</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>12.024</v>
+        <v>12.025</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-1.67997338656023</v>
+        <v>-1.671517671517686</v>
       </c>
       <c r="Q10" s="4" t="n">
         <v>12.104</v>
@@ -1126,10 +1126,10 @@
         <v>12.103</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.008262414277471208</v>
+        <v>0.008262414277449004</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>1.688235800837701</v>
+        <v>1.679780085795135</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" t="inlineStr">
@@ -1159,46 +1159,46 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>688312</t>
+          <t>920045</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>燕麦科技</t>
+          <t>蘅东光</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>34.03</v>
+        <v>419.8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>40.34</v>
+        <v>496.28</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>18.54246253305907</v>
+        <v>18.21819914244877</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>40.83</v>
+        <v>503.76</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>35.178</v>
+        <v>414.566</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>35.549</v>
+        <v>421.4520000000001</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.043629919266353</v>
+        <v>-1.633875269307083</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>36.148</v>
+        <v>428.3819999999999</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>35.983</v>
+        <v>428.381</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.4585498707722957</v>
+        <v>0.0002334370571954736</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>1.502179790038649</v>
+        <v>1.634108706364279</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" t="inlineStr">
@@ -1228,46 +1228,46 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>301486</t>
+          <t>688312</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>致尚科技</t>
+          <t>燕麦科技</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>180.89</v>
+        <v>34.12</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>216.18</v>
+        <v>40.34</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>19.5090939244845</v>
+        <v>18.22977725674093</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>217.06</v>
+        <v>40.94</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>186.316</v>
+        <v>35.19600000000001</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>188.545</v>
+        <v>35.55800000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-1.182211143228429</v>
+        <v>-1.018055008718155</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>191.972</v>
+        <v>36.166</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>191.363</v>
+        <v>35.992</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.3182433385764183</v>
+        <v>0.4834407646143513</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>1.500454481804847</v>
+        <v>1.501495773332506</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1283,11 +1283,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>光上游</t>
+          <t>CPO</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5.13</v>
+        <v>2.04</v>
       </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" t="inlineStr">
@@ -1297,46 +1297,46 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>688079</t>
+          <t>301312</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>美迪凯</t>
+          <t>智立方</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11.67</v>
+        <v>55.52</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>13.74</v>
+        <v>66.38</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>17.73778920308484</v>
+        <v>19.56051873198845</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>14</v>
+        <v>66.62</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>12.076</v>
+        <v>57.51800000000001</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>12.206</v>
+        <v>58.565</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-1.065049975421917</v>
+        <v>-1.787757192862616</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>12.39</v>
+        <v>59.182</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>12.336</v>
+        <v>59.181</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0.437743190661477</v>
+        <v>0.001689731501652858</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>1.502793166083394</v>
+        <v>1.789446924364269</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1352,11 +1352,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>半导体芯片</t>
+          <t>光上游</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>18</v>
+        <v>5.13</v>
       </c>
       <c r="E14" s="3" t="n"/>
       <c r="F14" t="inlineStr">
@@ -1366,46 +1366,46 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>688392</t>
+          <t>688079</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>骄成超声</t>
+          <t>美迪凯</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>116.32</v>
+        <v>11.69</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>134.69</v>
+        <v>13.74</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15.79264099037139</v>
+        <v>17.53635585970916</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>139.58</v>
+        <v>14.02</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>117.91</v>
+        <v>12.08</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>120.236</v>
+        <v>12.208</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-1.934528760105125</v>
+        <v>-1.048492791612055</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>121.068</v>
+        <v>12.394</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>121.067</v>
+        <v>12.338</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0.0008259889151984723</v>
+        <v>0.4538823147998139</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>1.935354749020324</v>
+        <v>1.502375106411868</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1435,46 +1435,46 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>688807</t>
+          <t>688392</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>优迅股份</t>
+          <t>骄成超声</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>219.11</v>
+        <v>116.22</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>254.97</v>
+        <v>134.74</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>16.36620875359407</v>
+        <v>15.93529512992602</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>262.93</v>
+        <v>139.46</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>226.7</v>
+        <v>117.9</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>230.231</v>
+        <v>120.231</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-1.533677046097182</v>
+        <v>-1.938767871846681</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>231.858</v>
+        <v>121.068</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>231.856</v>
+        <v>121.067</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0.0008626043751291945</v>
+        <v>0.0008259889152428812</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>1.534539650472311</v>
+        <v>1.939593860761923</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1504,46 +1504,46 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>688508</t>
+          <t>688807</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>芯朋微</t>
+          <t>优迅股份</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>58.65</v>
+        <v>219.31</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>254.87</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>17.15260017050297</v>
+        <v>16.21449090328759</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>70.38</v>
+        <v>263.17</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>61.08199999999999</v>
+        <v>226.72</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>61.703</v>
+        <v>230.241</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-1.006434046966931</v>
+        <v>-1.52926715919407</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>62.27999999999999</v>
+        <v>231.858</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>61.974</v>
+        <v>231.856</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.4937554458321003</v>
+        <v>0.0008626043751291945</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>1.500189492799031</v>
+        <v>1.530129763569199</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1573,46 +1573,46 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>688141</t>
+          <t>688508</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>杰华特</t>
+          <t>芯朋微</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>72.05</v>
+        <v>58.7</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>86.09999999999999</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>19.50034698126302</v>
+        <v>17.05281090289608</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>86.45999999999999</v>
+        <v>70.44</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>74.398</v>
+        <v>61.092</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>74.65599999999999</v>
+        <v>61.70800000000001</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0.3455850835833663</v>
+        <v>-0.9982498217411151</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>76.53999999999999</v>
+        <v>62.29</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>75.66600000000001</v>
+        <v>61.979</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>1.155076256178433</v>
+        <v>0.5017828619371167</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>1.5006613397618</v>
+        <v>1.500032683678232</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -1628,63 +1628,60 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>半导体设备</t>
+          <t>半导体芯片</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.26</v>
+        <v>18</v>
       </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>688383</t>
+          <t>688141</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>新益昌</t>
+          <t>杰华特</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>89.38</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>91.79000000000001</v>
+        <v>86.11</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>2.696352651599931</v>
+        <v>19.16689731525047</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>107.25</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>86.23999999999999</v>
+        <v>74.44199999999999</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>86.79799999999999</v>
+        <v>74.678</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>-0.6428719555750084</v>
+        <v>-0.3160234607247125</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>87.67999999999999</v>
+        <v>76.58599999999998</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>86.934</v>
+        <v>75.68900000000001</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.8581222536636846</v>
+        <v>1.185112764074003</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1.500994209238693</v>
+        <v>1.501136224798716</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -1709,51 +1706,54 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>301717</t>
+          <t>920125</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>超纯应材</t>
+          <t>鸿仕达</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>279.16</v>
+        <v>124.66</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>313.78</v>
+        <v>126.17</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>12.40149018484022</v>
+        <v>1.211294721642875</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>334.99</v>
+        <v>149.59</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>282.09</v>
+        <v>118.398</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>282.311</v>
+        <v>119.796</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>-0.07828246154062413</v>
+        <v>-1.166983872583416</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>288.94</v>
+        <v>121.07</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>284.889</v>
+        <v>119.913</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>1.421957323729583</v>
+        <v>0.9648661946577874</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>1.500239785270208</v>
+        <v>2.131850067241203</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -1778,51 +1778,54 @@
       <c r="E20" s="3" t="n"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>688605</t>
+          <t>688383</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>先锋精科</t>
+          <t>新益昌</t>
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>59.88</v>
+        <v>89.2</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>91.78</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>12.89245156980627</v>
+        <v>2.89237668161435</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>71.84999999999999</v>
+        <v>107.04</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>60.598</v>
+        <v>86.202</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>61.206</v>
+        <v>86.779</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-0.9933666633990201</v>
+        <v>-0.6649074084744022</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>61.95399999999999</v>
+        <v>87.64</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>61.641</v>
+        <v>86.91400000000002</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.5077789133855592</v>
+        <v>0.835308465839768</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>1.501145576784579</v>
+        <v>1.50021587431417</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -1852,46 +1855,46 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>301369</t>
+          <t>301717</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>联动科技</t>
+          <t>超纯应材</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>91.66</v>
+        <v>279.82</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>104.47</v>
+        <v>313.79</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>13.97556185904429</v>
+        <v>12.13994710885571</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>109.99</v>
+        <v>335.78</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>90.85799999999999</v>
+        <v>282.224</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>92.80300000000001</v>
+        <v>282.378</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-2.095837419048974</v>
+        <v>-0.05453682652333258</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>93.462</v>
+        <v>289.076</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>93.45999999999999</v>
+        <v>284.957</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>0.002139952921043076</v>
+        <v>1.445481248047953</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>2.097977371970017</v>
+        <v>1.500018074571285</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -1921,46 +1924,46 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>688785</t>
+          <t>688605</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>恒运昌</t>
+          <t>先锋精科</t>
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>280.08</v>
+        <v>59.81</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>323.49</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>15.49914310197087</v>
+        <v>13.02457782979434</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>336.09</v>
+        <v>71.77</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>280.44</v>
+        <v>60.58399999999999</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>287.8299999999999</v>
+        <v>61.199</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-2.567487753187625</v>
+        <v>-1.004918381019315</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>288.252</v>
+        <v>61.94</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>288.251</v>
+        <v>61.63399999999999</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0.000346919871918594</v>
+        <v>0.4964792160171427</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>2.567834673059544</v>
+        <v>1.501397597036458</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -1990,46 +1993,46 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>301611</t>
+          <t>301369</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>联动科技</t>
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>65.40000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>75.73999999999999</v>
+        <v>104.66</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>15.81039755351681</v>
+        <v>14.6707570943355</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>78.48</v>
+        <v>109.52</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>67.498</v>
+        <v>90.81799999999998</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>68.30600000000001</v>
+        <v>92.783</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>-1.182912189265961</v>
+        <v>-2.11784486382206</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>69.152</v>
+        <v>93.46000000000001</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>68.93300000000001</v>
+        <v>93.45899999999999</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.3176997954535521</v>
+        <v>0.001069987909163572</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>1.500611984719513</v>
+        <v>2.118914851731224</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2059,46 +2062,46 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>300400</t>
+          <t>688785</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>劲拓股份</t>
+          <t>恒运昌</t>
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>25.32</v>
+        <v>279.95</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>30.16</v>
+        <v>323.55</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>19.11532385466035</v>
+        <v>15.57420968030005</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>30.38</v>
+        <v>335.94</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>26.428</v>
+        <v>280.426</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>26.993</v>
+        <v>287.823</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>-2.093135257288947</v>
+        <v>-2.569982246033153</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>27.18</v>
+        <v>288.25</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>27.178</v>
+        <v>288.2499999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>0.007358893222475515</v>
+        <v>2.220446049250313e-14</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>2.100494150511423</v>
+        <v>2.569982246033176</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2128,46 +2131,46 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>301629</t>
+          <t>301611</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>矽电股份</t>
+          <t>珂玛科技</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>195.64</v>
+        <v>65.45</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>233.25</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.22408505418116</v>
+        <v>15.72192513368982</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>234.76</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>203.364</v>
+        <v>67.50800000000001</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>206.945</v>
+        <v>68.31100000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-1.730411461982662</v>
+        <v>-1.175506141031457</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>208.836</v>
+        <v>69.16199999999999</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>208.834</v>
+        <v>68.93800000000002</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.0009576984590475845</v>
+        <v>0.3249296469290952</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>1.731369160441709</v>
+        <v>1.500435787960552</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2183,11 +2186,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" t="inlineStr">
@@ -2197,46 +2200,46 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>688106</t>
+          <t>300400</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>金宏气体</t>
+          <t>劲拓股份</t>
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>19.82</v>
+        <v>25.35</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>21.95</v>
+        <v>30.14</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>10.74672048435923</v>
+        <v>18.89546351084812</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>23.78</v>
+        <v>30.42</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>20.258</v>
+        <v>26.43</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>20.568</v>
+        <v>26.994</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-1.507195643718373</v>
+        <v>-2.089353189597698</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>20.592</v>
+        <v>27.178</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>20.59</v>
+        <v>27.177</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.009713453132609295</v>
+        <v>0.003679581999471715</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>1.516909096850982</v>
+        <v>2.09303277159717</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2252,11 +2255,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>半导体上游</t>
+          <t>半导体设备</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" t="inlineStr">
@@ -2266,46 +2269,46 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>688268</t>
+          <t>301629</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>华特气体</t>
+          <t>矽电股份</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>102.56</v>
+        <v>195.62</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>114.39</v>
+        <v>233.26</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>11.53471138845554</v>
+        <v>19.24138636131274</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>123.07</v>
+        <v>234.74</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>104.06</v>
+        <v>203.362</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>104.841</v>
+        <v>206.944</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.7449375721330309</v>
+        <v>-1.730903046234711</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>106.346</v>
+        <v>208.836</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>105.549</v>
+        <v>208.834</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.7550995272338046</v>
+        <v>0.0009576984590475845</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>1.500037099366835</v>
+        <v>1.731860744693758</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -2344,25 +2347,25 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>164.79</v>
+        <v>168.47</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>186.36</v>
+        <v>184.52</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.08938649189879</v>
+        <v>9.526918739241408</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>197.74</v>
+        <v>202.16</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>166.268</v>
+        <v>166.636</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>169.07</v>
+        <v>169.254</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>-1.657301709351167</v>
+        <v>-1.54678766823827</v>
       </c>
       <c r="Q28" s="4" t="n">
         <v>170.068</v>
@@ -2374,7 +2377,7 @@
         <v>0.001176014018100524</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>1.658477723369267</v>
+        <v>1.54796368225637</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -2404,46 +2407,46 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>688138</t>
+          <t>688106</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>清溢光电</t>
+          <t>金宏气体</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>27.33</v>
+        <v>19.87</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>31.33</v>
+        <v>21.92</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>14.6359312111233</v>
+        <v>10.31706089582285</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>32.79</v>
+        <v>23.84</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>27.81</v>
+        <v>20.262</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>27.98099999999999</v>
+        <v>20.57</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.6111289803795161</v>
+        <v>-1.49732620320856</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>28.532</v>
+        <v>20.59</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>28.27999999999999</v>
+        <v>20.589</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.8910891089109141</v>
+        <v>0.004856962455668246</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>1.50221808929043</v>
+        <v>1.502183165664228</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -2473,46 +2476,46 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>300821</t>
+          <t>688268</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>东岳硅材</t>
+          <t>华特气体</t>
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>15.77</v>
+        <v>102.48</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>18.33</v>
+        <v>114.39</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>16.23335447051362</v>
+        <v>11.62177985948478</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>18.92</v>
+        <v>122.97</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>16.562</v>
+        <v>104.044</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>16.773</v>
+        <v>104.833</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-1.257974125082006</v>
+        <v>-0.7526256045329305</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>16.984</v>
+        <v>106.33</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>16.84</v>
+        <v>105.541</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0.8551068883610791</v>
+        <v>0.7475767711126569</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>2.113081013443086</v>
+        <v>1.500202375645587</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -2542,46 +2545,46 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>688720</t>
+          <t>688138</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>艾森股份</t>
+          <t>清溢光电</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>46.5</v>
+        <v>27.32</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>54.33</v>
+        <v>31.33</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>16.83870967741936</v>
+        <v>14.67789165446558</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>55.8</v>
+        <v>32.78</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>47.872</v>
+        <v>27.808</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>48.544</v>
+        <v>27.98</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-1.384311140408701</v>
+        <v>-0.6147248034309993</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>49.014</v>
+        <v>28.53</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>48.95699999999999</v>
+        <v>28.279</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.1164287027391353</v>
+        <v>0.8875844266063249</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>1.500739843147836</v>
+        <v>1.502309230037324</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -2611,46 +2614,46 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>688146</t>
+          <t>300821</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>中船特气</t>
+          <t>东岳硅材</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>142.35</v>
+        <v>15.76</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>167.72</v>
+        <v>18.33</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>17.82226905514577</v>
+        <v>16.30710659898476</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>170.82</v>
+        <v>18.91</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>147.968</v>
+        <v>16.56</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>150.401</v>
+        <v>16.772</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-1.617675414392183</v>
+        <v>-1.264011447650848</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>151.682</v>
+        <v>16.982</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>151.681</v>
+        <v>16.839</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0.0006592783539316471</v>
+        <v>0.8492190747669159</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>1.618334692746115</v>
+        <v>2.113230522417764</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -2680,46 +2683,46 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>300540</t>
+          <t>688720</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>蜀道装备</t>
+          <t>艾森股份</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>20.48</v>
+        <v>46.6</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>24.2</v>
+        <v>54.33</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>18.1640625</v>
+        <v>16.58798283261802</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>24.57</v>
+        <v>55.92</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>21.776</v>
+        <v>47.892</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>21.932</v>
+        <v>48.554</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-0.7112894400875369</v>
+        <v>-1.363430407381483</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>22.286</v>
+        <v>49.034</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>22.111</v>
+        <v>48.967</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0.79146126362446</v>
+        <v>0.136826842567439</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>1.502750703711997</v>
+        <v>1.500257249948922</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -2749,46 +2752,46 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>688727</t>
+          <t>688146</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>恒坤新材</t>
+          <t>中船特气</t>
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>34.32</v>
+        <v>142.6</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>40.83</v>
+        <v>167.6</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>18.96853146853146</v>
+        <v>17.53155680224403</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>41.18</v>
+        <v>171.12</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>35.766</v>
+        <v>147.994</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>36.261</v>
+        <v>150.414</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>-1.365103003226598</v>
+        <v>-1.608892789235039</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>36.714</v>
+        <v>151.684</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>36.664</v>
+        <v>151.682</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0.1363735544403166</v>
+        <v>0.001318548014950238</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>1.501476557666914</v>
+        <v>1.610211337249989</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -2818,46 +2821,46 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>688549</t>
+          <t>300540</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>中巨芯-U</t>
+          <t>蜀道装备</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>16.63</v>
+        <v>20.46</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>19.89</v>
+        <v>24.2</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19.6031268791341</v>
+        <v>18.2795698924731</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>19.95</v>
+        <v>24.55</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>17.396</v>
+        <v>21.772</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>17.709</v>
+        <v>21.93</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-1.767462871985992</v>
+        <v>-0.7204742362061145</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>17.886</v>
+        <v>22.282</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>17.885</v>
+        <v>22.109</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0.005591277606931122</v>
+        <v>0.7824867700936267</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>1.773054149592923</v>
+        <v>1.502961006299741</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -2873,11 +2876,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>10.67</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" t="inlineStr">
@@ -2887,46 +2890,46 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>002348</t>
+          <t>688727</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>高乐股份</t>
+          <t>恒坤新材</t>
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>8.460000000000001</v>
+        <v>34.26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>9.19</v>
+        <v>40.83</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>8.628841607564986</v>
+        <v>19.17688266199651</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>41.11</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>8.501999999999999</v>
+        <v>35.754</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>8.560999999999998</v>
+        <v>36.255</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.6891718257212909</v>
+        <v>-1.381878361605293</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>8.657999999999999</v>
+        <v>36.702</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>8.587999999999999</v>
+        <v>36.658</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.8150908244061617</v>
+        <v>0.1200283703420624</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>1.504262650127453</v>
+        <v>1.501906731947356</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -2942,11 +2945,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>10.67</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" t="inlineStr">
@@ -2956,46 +2959,46 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>301169</t>
+          <t>688549</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>零点有数</t>
+          <t>中巨芯-U</t>
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>44.63</v>
+        <v>16.63</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>50.26</v>
+        <v>19.89</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>12.6148330719247</v>
+        <v>19.6031268791341</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>53.55</v>
+        <v>19.95</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>45.61</v>
+        <v>17.396</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>46.34099999999999</v>
+        <v>17.709</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>-1.577436826999834</v>
+        <v>-1.767462871985992</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>46.75599999999999</v>
+        <v>17.886</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>46.755</v>
+        <v>17.885</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.002138808683538329</v>
+        <v>0.005591277606931122</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>1.579575635683372</v>
+        <v>1.773054149592923</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -3011,11 +3014,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>算力</t>
+          <t>半导体上游</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>10.67</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" t="inlineStr">
@@ -3025,46 +3028,46 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>920493</t>
+          <t>688535</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>并行科技</t>
+          <t>华海诚科</t>
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>86.43000000000001</v>
+        <v>72.48</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>99.17</v>
+        <v>86.83</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>14.74025222723592</v>
+        <v>19.7985651214128</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>103.71</v>
+        <v>86.97</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>91.07600000000001</v>
+        <v>74.69199999999999</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>91.12800000000001</v>
+        <v>75.91800000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>-0.0570625932754032</v>
+        <v>-1.614900287151944</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>93.11000000000001</v>
+        <v>76.86800000000001</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>91.785</v>
+        <v>76.866</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>1.443591000708189</v>
+        <v>0.002601930632550875</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>1.500653593983592</v>
+        <v>1.617502217784494</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -3094,46 +3097,46 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>300067</t>
+          <t>002348</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>安诺其</t>
+          <t>高乐股份</t>
         </is>
       </c>
       <c r="J39" s="4" t="n">
-        <v>4.89</v>
+        <v>8.44</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>5.78</v>
+        <v>9.19</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>18.20040899795503</v>
+        <v>8.886255924170626</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>5.86</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>5.046</v>
+        <v>8.497999999999999</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>5.151000000000001</v>
+        <v>8.558999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>-2.038439138031456</v>
+        <v>-0.7127000817852558</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>5.2</v>
+        <v>8.654</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>5.198</v>
+        <v>8.585999999999999</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.03847633705271747</v>
+        <v>0.7919869555089942</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>2.076915475084173</v>
+        <v>1.50468703729425</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -3163,46 +3166,46 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>301396</t>
+          <t>301169</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>宏景科技</t>
+          <t>零点有数</t>
         </is>
       </c>
       <c r="J40" s="4" t="n">
-        <v>117.4</v>
+        <v>44.55</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>139.54</v>
+        <v>50.3</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>18.85860306643952</v>
+        <v>12.90684624017957</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>140.88</v>
+        <v>53.46</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>122.944</v>
+        <v>45.60200000000001</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>124.351</v>
+        <v>46.337</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-1.131474616207362</v>
+        <v>-1.586205408205088</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>126.268</v>
+        <v>46.756</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>125.804</v>
+        <v>46.75500000000001</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0.3688277002320994</v>
+        <v>0.002138808683538329</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>1.500302316439461</v>
+        <v>1.588344216888626</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -3218,11 +3221,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>12.68</v>
+        <v>10.67</v>
       </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" t="inlineStr">
@@ -3232,46 +3235,46 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>003032</t>
+          <t>300067</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>传智教育</t>
+          <t>安诺其</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>4.89</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>8.69</v>
+        <v>5.78</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>5.717761557177603</v>
+        <v>18.20040899795503</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>9.039999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>8.106</v>
+        <v>5.046</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>8.142999999999999</v>
+        <v>5.151000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.4543779933685266</v>
+        <v>-2.038439138031456</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>8.27</v>
+        <v>5.2</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>8.184000000000001</v>
+        <v>5.198</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>1.050830889540544</v>
+        <v>0.03847633705271747</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>1.50520888290907</v>
+        <v>2.076915475084173</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -3287,11 +3290,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AI应用</t>
+          <t>算力</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>12.68</v>
+        <v>10.67</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" t="inlineStr">
@@ -3301,46 +3304,46 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>603533</t>
+          <t>301396</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>掌阅科技</t>
+          <t>宏景科技</t>
         </is>
       </c>
       <c r="J42" s="4" t="n">
-        <v>28.03</v>
+        <v>117.6</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>29.73</v>
+        <v>139.55</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>6.064930431680349</v>
+        <v>18.66496598639458</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>30.83</v>
+        <v>141.12</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>27.2</v>
+        <v>122.986</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>27.53</v>
+        <v>124.372</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>-1.198692335633855</v>
+        <v>-1.114398739266054</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>27.824</v>
+        <v>126.312</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>27.74</v>
+        <v>125.826</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>0.302811824080762</v>
+        <v>0.3862476753612176</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>1.501504159714617</v>
+        <v>1.500646414627271</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -3370,46 +3373,46 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>603444</t>
+          <t>003032</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>吉比特</t>
+          <t>传智教育</t>
         </is>
       </c>
       <c r="J43" s="4" t="n">
-        <v>327.66</v>
+        <v>8.23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>357.62</v>
+        <v>8.69</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>9.14362448879935</v>
+        <v>5.58930741190764</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>360.42</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>333.35</v>
+        <v>8.108000000000001</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>333.717</v>
+        <v>8.144</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>-0.1099734205928904</v>
+        <v>-0.4420432220039294</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>340.698</v>
+        <v>8.272</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>336.027</v>
+        <v>8.184999999999999</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>1.390066869626527</v>
+        <v>1.062919975565069</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>1.500040290219418</v>
+        <v>1.504963197568998</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -3439,46 +3442,46 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>301231</t>
+          <t>603533</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>荣信文化</t>
+          <t>掌阅科技</t>
         </is>
       </c>
       <c r="J44" s="4" t="n">
-        <v>29.03</v>
+        <v>28.03</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>32.77</v>
+        <v>29.73</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>12.88322425077506</v>
+        <v>6.064930431680349</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>34.83</v>
+        <v>30.83</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>29.35</v>
+        <v>27.2</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>29.777</v>
+        <v>27.53</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>-1.433992678913243</v>
+        <v>-1.198692335633855</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>30.012</v>
+        <v>27.824</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>29.992</v>
+        <v>27.74</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>0.06668444918644933</v>
+        <v>0.302811824080762</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>1.500677128099692</v>
+        <v>1.501504159714617</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -3508,46 +3511,46 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>线上线下</t>
+          <t>吉比特</t>
         </is>
       </c>
       <c r="J45" s="4" t="n">
-        <v>70.84999999999999</v>
+        <v>327.7</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>80.77</v>
+        <v>357.62</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>14.00141143260409</v>
+        <v>9.130302105584388</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>85.02</v>
+        <v>360.47</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>72.75399999999999</v>
+        <v>333.358</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>73.11199999999999</v>
+        <v>333.7209999999999</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>-0.4896597001860181</v>
+        <v>-0.108773496423642</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>74.488</v>
+        <v>340.706</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>73.74199999999999</v>
+        <v>336.0310000000001</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1.011635160424196</v>
+        <v>1.391240689103079</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>1.501294860610214</v>
+        <v>1.500014185526721</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -3577,46 +3580,46 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>300785</t>
+          <t>301231</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>值得买</t>
+          <t>荣信文化</t>
         </is>
       </c>
       <c r="J46" s="4" t="n">
-        <v>32.89</v>
+        <v>29.12</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>39.27</v>
+        <v>32.77</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>19.3979933110368</v>
+        <v>12.53434065934067</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>39.46</v>
+        <v>34.94</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>34.582</v>
+        <v>29.368</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>34.681</v>
+        <v>29.78599999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.2854588968022709</v>
+        <v>-1.40334385281673</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>35.634</v>
+        <v>30.03</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>35.206</v>
+        <v>30.001</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.215701868999597</v>
+        <v>0.09666344455183662</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>1.501160765801868</v>
+        <v>1.500007297368566</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -3632,11 +3635,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>80</v>
+        <v>12.68</v>
       </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" t="inlineStr">
@@ -3646,46 +3649,46 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>688090</t>
+          <t>300959</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>瑞松科技</t>
+          <t>线上线下</t>
         </is>
       </c>
       <c r="J47" s="4" t="n">
-        <v>56.98</v>
+        <v>70.89</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>59.17</v>
+        <v>80.77</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>3.843453843453859</v>
+        <v>13.93708562561715</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>68.37</v>
+        <v>85.06</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>55.638</v>
+        <v>72.76199999999999</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>56.24399999999999</v>
+        <v>73.116</v>
       </c>
       <c r="P47" s="3" t="n">
-        <v>-1.077448261147851</v>
+        <v>-0.4841621532906792</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>56.58199999999999</v>
+        <v>74.49600000000001</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>56.343</v>
+        <v>73.746</v>
       </c>
       <c r="S47" s="3" t="n">
-        <v>0.4241875654473537</v>
+        <v>1.017004312098302</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>1.501635826595205</v>
+        <v>1.501166465388981</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -3701,11 +3704,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>机器人</t>
+          <t>AI应用</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>80</v>
+        <v>12.68</v>
       </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" t="inlineStr">
@@ -3715,46 +3718,46 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>603790</t>
+          <t>300785</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>雅运股份</t>
+          <t>值得买</t>
         </is>
       </c>
       <c r="J48" s="4" t="n">
-        <v>23.92</v>
+        <v>32.9</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>25.44</v>
+        <v>39.27</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.35451505016722</v>
+        <v>19.3617021276596</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>26.31</v>
+        <v>39.48</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>23.852</v>
+        <v>34.584</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>24.016</v>
+        <v>34.682</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>-0.682878081279148</v>
+        <v>-0.2825673259904238</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>24.35</v>
+        <v>35.636</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>24.152</v>
+        <v>35.207</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.8198078834051215</v>
+        <v>1.218507683131209</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>1.502685964684269</v>
+        <v>1.501075009121633</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -3770,63 +3773,60 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>10.95</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>300006</t>
+          <t>688090</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>莱美药业</t>
+          <t>瑞松科技</t>
         </is>
       </c>
       <c r="J49" s="4" t="n">
-        <v>9.91</v>
+        <v>56.95</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>8.140000000000001</v>
+        <v>59.17</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>-17.86074672048435</v>
+        <v>3.898156277436349</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>11.89</v>
+        <v>68.34</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>8.598000000000001</v>
+        <v>55.63200000000001</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>8.708</v>
+        <v>56.241</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>-1.263206247129067</v>
+        <v>-1.082839921054024</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>8.662000000000001</v>
+        <v>56.576</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>8.547000000000001</v>
+        <v>56.34</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>1.345501345501354</v>
+        <v>0.4188853390131531</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>2.608707592630422</v>
+        <v>1.501725260067177</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -3842,63 +3842,60 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>药</t>
+          <t>机器人</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>10.95</v>
+        <v>80</v>
       </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>301080</t>
+          <t>603790</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>百普赛斯</t>
+          <t>雅运股份</t>
         </is>
       </c>
       <c r="J50" s="4" t="n">
-        <v>101.24</v>
+        <v>24.06</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>102.15</v>
+        <v>25.44</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.8988542078230077</v>
+        <v>5.735660847880308</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>121.48</v>
+        <v>26.46</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>92.77799999999999</v>
+        <v>23.88</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>94.16499999999999</v>
+        <v>24.03</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>-1.472946423830512</v>
+        <v>-0.6242197253433113</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>95.59200000000001</v>
+        <v>24.378</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>94.583</v>
+        <v>24.166</v>
       </c>
       <c r="S50" s="3" t="n">
-        <v>1.066787900574107</v>
+        <v>0.8772655797401496</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>2.539734324404619</v>
+        <v>1.501485305083461</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -3927,50 +3924,50 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>300006</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>奥浦迈</t>
+          <t>莱美药业</t>
         </is>
       </c>
       <c r="J51" s="4" t="n">
-        <v>60.76</v>
+        <v>9.92</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>62.76</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>3.291639236339705</v>
+        <v>-17.94354838709677</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>72.91</v>
+        <v>11.9</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>58.55</v>
+        <v>8.6</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>59.126</v>
+        <v>8.709</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>-0.9741907113621773</v>
+        <v>-1.251578826501321</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>59.532</v>
+        <v>8.664</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>59.22000000000001</v>
+        <v>8.548</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>0.5268490374873203</v>
+        <v>1.357042583060353</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>1.501039748849498</v>
+        <v>2.608621409561673</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -3995,51 +3992,54 @@
       <c r="E52" s="3" t="n"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>688185</t>
+          <t>301080</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>康希诺</t>
+          <t>百普赛斯</t>
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>78.36</v>
+        <v>101.24</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>82.70999999999999</v>
+        <v>102.15</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>5.551301684532928</v>
+        <v>0.8988542078230077</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>94.03</v>
+        <v>121.48</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>76.95399999999999</v>
+        <v>92.77799999999999</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>78.086</v>
+        <v>94.16499999999999</v>
       </c>
       <c r="P52" s="3" t="n">
-        <v>-1.449683682094105</v>
+        <v>-1.472946423830512</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>78.49600000000001</v>
+        <v>95.59200000000001</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>78.066</v>
+        <v>94.583</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>0.5508159762252607</v>
+        <v>1.066787900574107</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>2.000499658319366</v>
+        <v>2.539734324404619</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -4064,51 +4064,54 @@
       <c r="E53" s="3" t="n"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>空</t>
-        </is>
+          <t>空转多</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>301093</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>华兰股份</t>
+          <t>奥浦迈</t>
         </is>
       </c>
       <c r="J53" s="4" t="n">
-        <v>51.32</v>
+        <v>60.6</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>54.32</v>
+        <v>62.76</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>5.845674201091189</v>
+        <v>3.564356435643568</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>61.58</v>
+        <v>72.72</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>50.696</v>
+        <v>58.51800000000001</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>51.258</v>
+        <v>59.11</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>-1.096414218268382</v>
+        <v>-1.001522585010983</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>51.52</v>
+        <v>59.5</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>51.312</v>
+        <v>59.20399999999999</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>0.4053632678515884</v>
+        <v>0.4999662184987708</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>1.501777486119971</v>
+        <v>1.501488803509754</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -4138,46 +4141,46 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>603127</t>
+          <t>688185</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>昭衍新药</t>
+          <t>康希诺</t>
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>46.7</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>50.66</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>8.479657387580275</v>
+        <v>5.645676331587679</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>51.37</v>
+        <v>93.94</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>46.418</v>
+        <v>76.94</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>47.04600000000001</v>
+        <v>78.07899999999999</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>-1.334863750371995</v>
+        <v>-1.458778929033411</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>47.48</v>
+        <v>78.482</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>47.241</v>
+        <v>78.059</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>0.5059164708621777</v>
+        <v>0.54189779525744</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>1.840780221234173</v>
+        <v>2.000676724290851</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -4207,46 +4210,46 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>300109</t>
+          <t>301093</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>新开源</t>
+          <t>华兰股份</t>
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>11.24</v>
+        <v>51.35</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>12.67</v>
+        <v>54.32</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>12.72241992882561</v>
+        <v>5.783836416747801</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>13.48</v>
+        <v>61.62</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>11.452</v>
+        <v>50.702</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>11.502</v>
+        <v>51.26100000000001</v>
       </c>
       <c r="P55" s="3" t="n">
-        <v>-0.4347070074769532</v>
+        <v>-1.090497649285049</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>11.72</v>
+        <v>51.526</v>
       </c>
       <c r="R55" s="4" t="n">
-        <v>11.596</v>
+        <v>51.315</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>1.069334253190735</v>
+        <v>0.4111858131150781</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>1.504041260667688</v>
+        <v>1.501683462400127</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -4276,46 +4279,46 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>603127</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>昭衍新药</t>
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>9.33</v>
+        <v>46.85</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>10.53</v>
+        <v>50.66</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>12.86173633440513</v>
+        <v>8.132337246531463</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>11.19</v>
+        <v>51.53</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>9.654</v>
+        <v>46.448</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>47.061</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.5767250257466605</v>
+        <v>-1.30256475638002</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>9.85</v>
+        <v>47.51</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>9.759</v>
+        <v>47.256</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>0.9324725894046537</v>
+        <v>0.5374978838665889</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>1.509197615151314</v>
+        <v>1.840062640246609</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -4345,46 +4348,46 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>688202</t>
+          <t>300109</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>美迪西</t>
+          <t>新开源</t>
         </is>
       </c>
       <c r="J57" s="4" t="n">
-        <v>79.13</v>
+        <v>11.24</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>89.70999999999999</v>
+        <v>12.67</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>13.37040313408315</v>
+        <v>12.72241992882561</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>94.95</v>
+        <v>13.48</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>80.19799999999999</v>
+        <v>11.452</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>80.96000000000001</v>
+        <v>11.502</v>
       </c>
       <c r="P57" s="3" t="n">
-        <v>-0.9412055335968561</v>
+        <v>-0.4347070074769532</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>82.13799999999999</v>
+        <v>11.72</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>81.681</v>
+        <v>11.596</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>0.5594936398917616</v>
+        <v>1.069334253190735</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>1.500699173488618</v>
+        <v>1.504041260667688</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -4414,46 +4417,46 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>300347</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>泰格医药</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="J58" s="4" t="n">
-        <v>48.21</v>
+        <v>9.32</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>55.13</v>
+        <v>10.53</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>14.3538684920141</v>
+        <v>12.98283261802573</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>57.85</v>
+        <v>11.18</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>50.014</v>
+        <v>9.652000000000001</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>50.337</v>
+        <v>9.709</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>-0.6416751097602202</v>
+        <v>-0.5870841487279677</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>51.28000000000001</v>
+        <v>9.847999999999999</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>50.843</v>
+        <v>9.758000000000001</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>0.859508683594612</v>
+        <v>0.9223201475712095</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>1.501183793354832</v>
+        <v>1.509404296299177</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -4483,46 +4486,46 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>300404</t>
+          <t>688202</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>博济医药</t>
+          <t>美迪西</t>
         </is>
       </c>
       <c r="J59" s="4" t="n">
-        <v>11.19</v>
+        <v>79.05</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>12.86</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>14.92403932082216</v>
+        <v>13.48513598987982</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>13.42</v>
+        <v>94.86</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>11.39</v>
+        <v>80.18199999999999</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>11.637</v>
+        <v>80.952</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>-2.122540173584253</v>
+        <v>-0.9511809467338761</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>11.698</v>
+        <v>82.122</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>11.696</v>
+        <v>81.67299999999999</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>0.01709986320108658</v>
+        <v>0.5497532844391806</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>2.13964003678534</v>
+        <v>1.500934231173057</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -4552,46 +4555,46 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>300204</t>
+          <t>920047</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>舒泰神</t>
+          <t>诺思兰德</t>
         </is>
       </c>
       <c r="J60" s="4" t="n">
-        <v>17.29</v>
+        <v>12.88</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>19.92</v>
+        <v>14.69</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>15.2111046847889</v>
+        <v>14.0527950310559</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>20.74</v>
+        <v>15.45</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>17.992</v>
+        <v>13.336</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>18.025</v>
+        <v>13.441</v>
       </c>
       <c r="P60" s="3" t="n">
-        <v>-0.1830790568654761</v>
+        <v>-0.78119187560447</v>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>18.362</v>
+        <v>13.618</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>18.123</v>
+        <v>13.52</v>
       </c>
       <c r="S60" s="3" t="n">
-        <v>1.318766208685118</v>
+        <v>0.7248520710058992</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>1.501845265550594</v>
+        <v>1.506043946610369</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -4621,46 +4624,46 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>300534</t>
+          <t>300347</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>陇神戎发</t>
+          <t>泰格医药</t>
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>9.81</v>
+        <v>48.26</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>11.33</v>
+        <v>55.13</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>15.49439347604484</v>
+        <v>14.23539162867799</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>11.77</v>
+        <v>57.91</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>10.228</v>
+        <v>50.02399999999999</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>10.394</v>
+        <v>50.342</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>-1.597075235712919</v>
+        <v>-0.6316793134957033</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>10.448</v>
+        <v>51.29</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>10.447</v>
+        <v>50.848</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.009572125969170564</v>
+        <v>0.8692573945877857</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>1.60664736168209</v>
+        <v>1.500936708083489</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -4690,46 +4693,46 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>301111</t>
+          <t>300534</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>粤万年青</t>
+          <t>陇神戎发</t>
         </is>
       </c>
       <c r="J62" s="4" t="n">
-        <v>17.81</v>
+        <v>9.85</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>20.77</v>
+        <v>11.31</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>16.61987647389107</v>
+        <v>14.82233502538073</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>21.37</v>
+        <v>11.82</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>18.556</v>
+        <v>10.232</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>18.884</v>
+        <v>10.396</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>-1.736920144037279</v>
+        <v>-1.577529819161194</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>19.018</v>
+        <v>10.448</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>19.016</v>
+        <v>10.447</v>
       </c>
       <c r="S62" s="3" t="n">
-        <v>0.01051745898192902</v>
+        <v>0.009572125969170564</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>1.747437603019208</v>
+        <v>1.587101945130365</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -4759,46 +4762,46 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>300436</t>
+          <t>300404</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>广生堂</t>
+          <t>博济医药</t>
         </is>
       </c>
       <c r="J63" s="4" t="n">
-        <v>74.01000000000001</v>
+        <v>11.19</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>86.41</v>
+        <v>12.86</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>16.75449263613025</v>
+        <v>14.92403932082216</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>88.81</v>
+        <v>13.42</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>76.684</v>
+        <v>11.39</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>77.422</v>
+        <v>11.637</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>-0.9532174317377518</v>
+        <v>-2.122540173584253</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>78.48999999999999</v>
+        <v>11.698</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>78.06299999999999</v>
+        <v>11.696</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>0.54699409451342</v>
+        <v>0.01709986320108658</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>1.500211526251172</v>
+        <v>2.13964003678534</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -4828,46 +4831,46 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>920047</t>
+          <t>300204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>诺思兰德</t>
+          <t>舒泰神</t>
         </is>
       </c>
       <c r="J64" s="4" t="n">
-        <v>12.62</v>
+        <v>17.27</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>14.75</v>
+        <v>19.92</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>16.87797147385104</v>
+        <v>15.3445280833816</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>15.14</v>
+        <v>20.72</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>13.434</v>
+        <v>17.988</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>13.55</v>
+        <v>18.023</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>-0.8560885608856372</v>
+        <v>-0.194196304721761</v>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>13.722</v>
+        <v>18.358</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>13.634</v>
+        <v>18.121</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0.6454452105031372</v>
+        <v>1.307874841344292</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>1.501533771388774</v>
+        <v>1.502071146066053</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -4897,46 +4900,46 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>300723</t>
+          <t>920367</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>一品红</t>
+          <t>新赣江</t>
         </is>
       </c>
       <c r="J65" s="4" t="n">
-        <v>29.14</v>
+        <v>20.56</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>34.32</v>
+        <v>23.8</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>17.77625257378175</v>
+        <v>15.75875486381324</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>34.96</v>
+        <v>24.67</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>30.548</v>
+        <v>21.45</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>30.561</v>
+        <v>21.644</v>
       </c>
       <c r="P65" s="3" t="n">
-        <v>-0.0425378750695149</v>
+        <v>-0.8963223064128778</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>31.358</v>
+        <v>21.962</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>30.907</v>
+        <v>21.707</v>
       </c>
       <c r="S65" s="3" t="n">
-        <v>1.459216358753701</v>
+        <v>1.174736260192555</v>
       </c>
       <c r="T65" s="5" t="n">
-        <v>1.501754233823216</v>
+        <v>2.071058566605433</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -4966,46 +4969,46 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>688137</t>
+          <t>300436</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>近岸蛋白</t>
+          <t>广生堂</t>
         </is>
       </c>
       <c r="J66" s="4" t="n">
-        <v>127.2</v>
+        <v>74</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>151.19</v>
+        <v>86.41</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18.86006289308175</v>
+        <v>16.77027027027027</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>152.64</v>
+        <v>88.8</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>122.478</v>
+        <v>76.68199999999999</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>125.475</v>
+        <v>77.42099999999999</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>-2.388523610280935</v>
+        <v>-0.9545213830872812</v>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>131.316</v>
+        <v>78.488</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>126.653</v>
+        <v>78.06199999999998</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>3.681713026931832</v>
+        <v>0.5457200686633801</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>6.070236637212767</v>
+        <v>1.500241451750661</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
@@ -5035,46 +5038,46 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>301201</t>
+          <t>301111</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>诚达药业</t>
+          <t>粤万年青</t>
         </is>
       </c>
       <c r="J67" s="4" t="n">
-        <v>23.95</v>
+        <v>17.78</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>28.49</v>
+        <v>20.78</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>18.95615866388309</v>
+        <v>16.87289088863892</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>28.74</v>
+        <v>21.33</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>25.346</v>
+        <v>18.552</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>25.705</v>
+        <v>18.882</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>-1.396615444466065</v>
+        <v>-1.747696218620898</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>25.96</v>
+        <v>19.016</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>25.933</v>
+        <v>19.015</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0.1041144487718304</v>
+        <v>0.005259006047864112</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>1.500729893237895</v>
+        <v>1.752955224668762</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -5104,46 +5107,46 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>920367</t>
+          <t>300723</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>新赣江</t>
+          <t>一品红</t>
         </is>
       </c>
       <c r="J68" s="4" t="n">
-        <v>19.95</v>
+        <v>29.12</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>23.8</v>
+        <v>34.32</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>19.2982456140351</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>23.94</v>
+        <v>34.94</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>21.502</v>
+        <v>30.544</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>21.968</v>
+        <v>30.559</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>-2.12126729788783</v>
+        <v>-0.04908537583034889</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>22.098</v>
+        <v>31.354</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>21.968</v>
+        <v>30.905</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.5917698470502719</v>
+        <v>1.452839346384072</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>2.713037144938102</v>
+        <v>1.501924722214421</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
@@ -5159,63 +5162,60 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1.64</v>
+        <v>10.95</v>
       </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>空转多</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>3</v>
+          <t>空</t>
+        </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>600621</t>
+          <t>301201</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>华鑫股份</t>
+          <t>诚达药业</t>
         </is>
       </c>
       <c r="J69" s="4" t="n">
-        <v>14.9</v>
+        <v>24</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>15.91</v>
+        <v>28.49</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>6.778523489932886</v>
+        <v>18.70833333333333</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>16.39</v>
+        <v>28.8</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>14.66</v>
+        <v>25.356</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>14.77</v>
+        <v>25.71</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>-0.7447528774542911</v>
+        <v>-1.37689614935822</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>14.996</v>
+        <v>25.97</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>14.883</v>
+        <v>25.938</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>0.7592555264395617</v>
+        <v>0.123371115737525</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>1.504008403893853</v>
+        <v>1.500267265095745</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -5231,11 +5231,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>药</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1.64</v>
+        <v>10.95</v>
       </c>
       <c r="E70" s="3" t="n"/>
       <c r="F70" t="inlineStr">
@@ -5245,46 +5245,46 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>601519</t>
+          <t>688137</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>大智慧</t>
+          <t>近岸蛋白</t>
         </is>
       </c>
       <c r="J70" s="4" t="n">
-        <v>8.76</v>
+        <v>127.2</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>151.19</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>7.191780821917826</v>
+        <v>18.86006289308175</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>9.630000000000001</v>
+        <v>152.64</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>9.022</v>
+        <v>122.478</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>9.144000000000002</v>
+        <v>125.475</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>-1.334208223972022</v>
+        <v>-2.388523610280935</v>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>9.218</v>
+        <v>131.316</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>9.118</v>
+        <v>126.653</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>1.096731739416534</v>
+        <v>3.681713026931832</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>2.430939963388556</v>
+        <v>6.070236637212767</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
@@ -5300,11 +5300,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1.64</v>
+        <v>6.25</v>
       </c>
       <c r="E71" s="3" t="n"/>
       <c r="F71" t="inlineStr">
@@ -5314,46 +5314,46 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>600958</t>
+          <t>600011</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>东方证券</t>
+          <t>华能国际</t>
         </is>
       </c>
       <c r="J71" s="4" t="n">
-        <v>8.48</v>
+        <v>7.4</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>9.15</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>7.900943396226423</v>
+        <v>9.729729729729719</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>9.32</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>8.586</v>
+        <v>7.455999999999999</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>8.595000000000002</v>
+        <v>7.489</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>-0.1047120418848468</v>
+        <v>-0.4406462812124645</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>8.75</v>
+        <v>7.63</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>8.629</v>
+        <v>7.55</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.402248232703673</v>
+        <v>1.059602649006619</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>1.50696027458852</v>
+        <v>1.500248930219084</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>1.64</v>
+        <v>16.07</v>
       </c>
       <c r="E72" s="3" t="n"/>
       <c r="F72" t="inlineStr">
@@ -5383,46 +5383,46 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>601377</t>
+          <t>300069</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>兴业证券</t>
+          <t>金利华电</t>
         </is>
       </c>
       <c r="J72" s="4" t="n">
-        <v>5.52</v>
+        <v>22.39</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>6</v>
+        <v>23.47</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>8.695652173913061</v>
+        <v>4.823581956230449</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>6.07</v>
+        <v>26.86</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>5.613999999999999</v>
+        <v>21.894</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>5.625999999999999</v>
+        <v>22.104</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>-0.2132954141486065</v>
+        <v>-0.9500542888165042</v>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>5.726</v>
+        <v>22.29</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>5.653</v>
+        <v>22.168</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>1.291349725809288</v>
+        <v>0.5503428365211116</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>1.504645139957894</v>
+        <v>1.500397125337616</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
@@ -5438,11 +5438,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>1.64</v>
+        <v>16.07</v>
       </c>
       <c r="E73" s="3" t="n"/>
       <c r="F73" t="inlineStr">
@@ -5452,46 +5452,46 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>002736</t>
+          <t>603016</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>国信证券</t>
+          <t>新宏泰</t>
         </is>
       </c>
       <c r="J73" s="4" t="n">
-        <v>9.66</v>
+        <v>26.85</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>10.52</v>
+        <v>29.3</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>8.902691511387161</v>
+        <v>9.124767225325892</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>10.62</v>
+        <v>29.53</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>9.806000000000001</v>
+        <v>27.45</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>9.812999999999999</v>
+        <v>27.708</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>-0.07133394476712684</v>
+        <v>-0.9311390212213055</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>10.008</v>
+        <v>27.89</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>9.866999999999999</v>
+        <v>27.73200000000001</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>1.429005776831871</v>
+        <v>0.5697389297562028</v>
       </c>
       <c r="T73" s="5" t="n">
-        <v>1.500339721598998</v>
+        <v>1.500877950977508</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -5507,11 +5507,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1.64</v>
+        <v>16.07</v>
       </c>
       <c r="E74" s="3" t="n"/>
       <c r="F74" t="inlineStr">
@@ -5521,46 +5521,46 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>601136</t>
+          <t>300427</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>首创证券</t>
+          <t>红相股份</t>
         </is>
       </c>
       <c r="J74" s="4" t="n">
-        <v>13.49</v>
+        <v>5.24</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>14.78</v>
+        <v>6.2</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>9.562638991845795</v>
+        <v>18.32061068702291</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>14.83</v>
+        <v>6.28</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>13.94</v>
+        <v>5.51</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>14.029</v>
+        <v>5.559000000000001</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>-0.6344001710741898</v>
+        <v>-0.8814534988307421</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>14.184</v>
+        <v>5.644</v>
       </c>
       <c r="R74" s="4" t="n">
-        <v>14.062</v>
+        <v>5.609</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>0.8675864030721181</v>
+        <v>0.6239971474416128</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>1.501986574146308</v>
+        <v>1.505450646272355</v>
       </c>
       <c r="U74" t="inlineStr">
         <is>
@@ -5576,11 +5576,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.64</v>
+        <v>9.52</v>
       </c>
       <c r="E75" s="3" t="n"/>
       <c r="F75" t="inlineStr">
@@ -5590,46 +5590,46 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>688318</t>
+          <t>002149</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>财富趋势</t>
+          <t>西部材料</t>
         </is>
       </c>
       <c r="J75" s="4" t="n">
-        <v>69.98999999999999</v>
+        <v>29.37</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>77.61</v>
+        <v>31.79</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>10.88726960994428</v>
+        <v>8.239700374531832</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>83.98</v>
+        <v>32.3</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>73.66400000000002</v>
+        <v>29.022</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>73.70700000000001</v>
+        <v>29.404</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>-0.05833909940710091</v>
+        <v>-1.299142973745071</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>75.06800000000001</v>
+        <v>29.642</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>74.001</v>
+        <v>29.582</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>1.441872407129652</v>
+        <v>0.2028260428638795</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>1.500211506536753</v>
+        <v>1.501969016608951</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -5645,11 +5645,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1.64</v>
+        <v>9.52</v>
       </c>
       <c r="E76" s="3" t="n"/>
       <c r="F76" t="inlineStr">
@@ -5659,46 +5659,46 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>300803</t>
+          <t>301232</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>指南针</t>
+          <t>飞沃科技</t>
         </is>
       </c>
       <c r="J76" s="4" t="n">
-        <v>48.38</v>
+        <v>68.58</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>55.17</v>
+        <v>75.17</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>14.03472509301364</v>
+        <v>9.609215514727332</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>58.05</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>51.812</v>
+        <v>67.336</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>52.057</v>
+        <v>67.667</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.4706379545498129</v>
+        <v>-0.4891601519204425</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>52.79600000000001</v>
+        <v>68.94000000000001</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>52.258</v>
+        <v>68.25</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.029507443836364</v>
+        <v>1.010989010989038</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>1.500145398386177</v>
+        <v>1.500149162909481</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -5714,11 +5714,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>互金证券</t>
+          <t>商业航天</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>1.64</v>
+        <v>9.52</v>
       </c>
       <c r="E77" s="3" t="n"/>
       <c r="F77" t="inlineStr">
@@ -5728,46 +5728,46 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>300085</t>
+          <t>300342</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>银之杰</t>
+          <t>天银机电</t>
         </is>
       </c>
       <c r="J77" s="4" t="n">
-        <v>24.89</v>
+        <v>26.66</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>28.83</v>
+        <v>29.23</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>15.82965046203293</v>
+        <v>9.639909977494376</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>29.86</v>
+        <v>31.99</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>26.71</v>
+        <v>26.254</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>26.998</v>
+        <v>26.782</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>-1.066745684865533</v>
+        <v>-1.971473377641708</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>27.322</v>
+        <v>26.952</v>
       </c>
       <c r="R77" s="4" t="n">
-        <v>27.123</v>
+        <v>26.95</v>
       </c>
       <c r="S77" s="3" t="n">
-        <v>0.7336946502968011</v>
+        <v>0.007421150278297262</v>
       </c>
       <c r="T77" s="5" t="n">
-        <v>1.800440335162334</v>
+        <v>1.978894527920005</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -5775,353 +5775,8 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>黄金白银</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>300945</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>曼卡龙</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="K78" s="4" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>14.97005988023952</v>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v>12.02</v>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>10.506</v>
-      </c>
-      <c r="O78" s="4" t="n">
-        <v>10.536</v>
-      </c>
-      <c r="P78" s="3" t="n">
-        <v>-0.2847380410022526</v>
-      </c>
-      <c r="Q78" s="4" t="n">
-        <v>10.762</v>
-      </c>
-      <c r="R78" s="4" t="n">
-        <v>10.632</v>
-      </c>
-      <c r="S78" s="3" t="n">
-        <v>1.222723852520691</v>
-      </c>
-      <c r="T78" s="5" t="n">
-        <v>1.507461893522943</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>300069</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>金利华电</t>
-        </is>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>21.06</v>
-      </c>
-      <c r="K79" s="4" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>13.91263057929724</v>
-      </c>
-      <c r="M79" s="4" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>21.766</v>
-      </c>
-      <c r="O79" s="4" t="n">
-        <v>22.147</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>-1.720323294351378</v>
-      </c>
-      <c r="Q79" s="4" t="n">
-        <v>22.318</v>
-      </c>
-      <c r="R79" s="4" t="n">
-        <v>22.316</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>0.008962179602090004</v>
-      </c>
-      <c r="T79" s="5" t="n">
-        <v>1.729285473953468</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>301082</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>久盛电气</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>10.23</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>16.51480637813214</v>
-      </c>
-      <c r="M80" s="4" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>9.296000000000001</v>
-      </c>
-      <c r="O80" s="4" t="n">
-        <v>9.324000000000002</v>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>-0.3003003003003046</v>
-      </c>
-      <c r="Q80" s="4" t="n">
-        <v>9.526</v>
-      </c>
-      <c r="R80" s="4" t="n">
-        <v>9.413</v>
-      </c>
-      <c r="S80" s="3" t="n">
-        <v>1.200467438648678</v>
-      </c>
-      <c r="T80" s="5" t="n">
-        <v>1.500767738948983</v>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>300427</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>红相股份</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="K81" s="4" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>17.85028790786946</v>
-      </c>
-      <c r="M81" s="4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>5.538</v>
-      </c>
-      <c r="O81" s="4" t="n">
-        <v>5.588</v>
-      </c>
-      <c r="P81" s="3" t="n">
-        <v>-0.8947745168217613</v>
-      </c>
-      <c r="Q81" s="4" t="n">
-        <v>5.678</v>
-      </c>
-      <c r="R81" s="4" t="n">
-        <v>5.643000000000001</v>
-      </c>
-      <c r="S81" s="3" t="n">
-        <v>0.6202374623427209</v>
-      </c>
-      <c r="T81" s="5" t="n">
-        <v>1.515011979164482</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>商业航天</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>688323</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>瑞华泰</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="K82" s="4" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>19.01639344262296</v>
-      </c>
-      <c r="M82" s="4" t="n">
-        <v>21.96</v>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="O82" s="4" t="n">
-        <v>19.986</v>
-      </c>
-      <c r="P82" s="3" t="n">
-        <v>-0.7305113579505473</v>
-      </c>
-      <c r="Q82" s="4" t="n">
-        <v>20.312</v>
-      </c>
-      <c r="R82" s="4" t="n">
-        <v>20.156</v>
-      </c>
-      <c r="S82" s="3" t="n">
-        <v>0.7739630879142867</v>
-      </c>
-      <c r="T82" s="5" t="n">
-        <v>1.504474445864834</v>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>涨停内可达</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:U82"/>
+  <autoFilter ref="A2:U77"/>
   <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
   </mergeCells>
